--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -2205,13 +2205,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46167.38994775463</v>
+        <v>46167.55661442129</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.71147724537</v>
+        <v>46175.878143912036</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.71148831019</v>
+        <v>46175.87815497685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2258,13 +2258,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46167.3900909375</v>
+        <v>46167.556757604165</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.7114078125</v>
+        <v>46175.878074479166</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.71142508102</v>
+        <v>46175.87809174768</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2321,13 +2321,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46167.39009450232</v>
+        <v>46167.55676116898</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.7114558912</v>
+        <v>46175.87812255787</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71147844907</v>
+        <v>46175.87814511574</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2384,13 +2384,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46167.390099490745</v>
+        <v>46167.5567661574</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71145641204</v>
+        <v>46175.8781230787</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71147767361</v>
+        <v>46175.87814434028</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2447,13 +2447,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46167.39010253472</v>
+        <v>46167.55676920139</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71145681713</v>
+        <v>46175.878123483795</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71147898148</v>
+        <v>46175.87814564815</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2510,13 +2510,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46167.39010650463</v>
+        <v>46167.556773171294</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.711457384255</v>
+        <v>46175.87812405093</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.71147805556</v>
+        <v>46175.87814472222</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2573,11 +2573,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46167.38995350694</v>
+        <v>46167.55662017361</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.565103807865</v>
+        <v>46167.73177047454</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2620,11 +2620,11 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46167.390111099536</v>
+        <v>46167.55677776621</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46175.71148474537</v>
+        <v>46175.878151412035</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2683,11 +2683,11 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46167.39011652778</v>
+        <v>46167.55678319444</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46167.57079327546</v>
+        <v>46167.73745994213</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2746,11 +2746,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="9">
-        <v>46167.46745108796</v>
+        <v>46167.63411775463</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46167.57087763889</v>
+        <v>46167.73754430556</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -2799,11 +2799,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="5">
-        <v>46167.46776753472</v>
+        <v>46167.63443420139</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46167.57087484954</v>
+        <v>46167.7375415162</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2852,11 +2852,11 @@
         <v>66</v>
       </c>
       <c r="B15" s="9">
-        <v>46167.46778902778</v>
+        <v>46167.634455694446</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46167.57087202546</v>
+        <v>46167.737538692134</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2905,11 +2905,11 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46167.4677987037</v>
+        <v>46167.63446537037</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46167.57086895833</v>
+        <v>46167.737535625</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>63</v>
@@ -2958,11 +2958,11 @@
         <v>68</v>
       </c>
       <c r="B17" s="9">
-        <v>46167.46780734954</v>
+        <v>46167.6344740162</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46167.570866215276</v>
+        <v>46167.73753288195</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>63</v>
@@ -3011,11 +3011,11 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46167.46781417824</v>
+        <v>46167.63448084491</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46167.57086368055</v>
+        <v>46167.73753034722</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>63</v>
@@ -3064,11 +3064,11 @@
         <v>70</v>
       </c>
       <c r="B19" s="9">
-        <v>46167.46786875</v>
+        <v>46167.63453541667</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46167.57085797454</v>
+        <v>46167.737524641205</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>71</v>
@@ -3117,11 +3117,11 @@
         <v>72</v>
       </c>
       <c r="B20" s="5">
-        <v>46167.46807726852</v>
+        <v>46167.63474393518</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46171.34429259259</v>
+        <v>46171.51095925926</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>71</v>
@@ -3170,11 +3170,11 @@
         <v>73</v>
       </c>
       <c r="B21" s="9">
-        <v>46167.38995982639</v>
+        <v>46167.55662649305</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46183.70452347222</v>
+        <v>46183.87119013889</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>74</v>
@@ -3217,13 +3217,13 @@
         <v>76</v>
       </c>
       <c r="B22" s="5">
-        <v>46167.39012296296</v>
+        <v>46167.55678962963</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.704502175926</v>
+        <v>46183.8711688426</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.70452240741</v>
+        <v>46183.871189074074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>77</v>
@@ -3282,13 +3282,13 @@
         <v>82</v>
       </c>
       <c r="B23" s="9">
-        <v>46167.390128252315</v>
+        <v>46167.556794918986</v>
       </c>
       <c r="C23" s="9">
-        <v>46183.704511284726</v>
+        <v>46183.87117795139</v>
       </c>
       <c r="D23" s="9">
-        <v>46183.704527650465</v>
+        <v>46183.87119431713</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>83</v>
@@ -3347,13 +3347,13 @@
         <v>86</v>
       </c>
       <c r="B24" s="5">
-        <v>46167.39013399306</v>
+        <v>46167.55680065972</v>
       </c>
       <c r="C24" s="5">
-        <v>46183.704518136576</v>
+        <v>46183.87118480324</v>
       </c>
       <c r="D24" s="5">
-        <v>46183.704533854165</v>
+        <v>46183.871200520836</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>87</v>
@@ -3412,11 +3412,11 @@
         <v>89</v>
       </c>
       <c r="B25" s="9">
-        <v>46167.390139826384</v>
+        <v>46167.556806493056</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46183.70453556713</v>
+        <v>46183.8712022338</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>90</v>
@@ -3475,11 +3475,11 @@
         <v>93</v>
       </c>
       <c r="B26" s="5">
-        <v>46167.38996634259</v>
+        <v>46167.556633009255</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46167.45723863426</v>
+        <v>46167.62390530093</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>94</v>
@@ -3522,11 +3522,11 @@
         <v>96</v>
       </c>
       <c r="B27" s="9">
-        <v>46167.39014790509</v>
+        <v>46167.556814571755</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46183.70452424769</v>
+        <v>46183.87119091435</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>97</v>
@@ -3585,11 +3585,11 @@
         <v>99</v>
       </c>
       <c r="B28" s="5">
-        <v>46167.390153506945</v>
+        <v>46167.55682017361</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46183.70453320602</v>
+        <v>46183.87119987269</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>100</v>
@@ -3648,11 +3648,11 @@
         <v>102</v>
       </c>
       <c r="B29" s="9">
-        <v>46167.390159201386</v>
+        <v>46167.55682586806</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46183.704532812495</v>
+        <v>46183.87119947917</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>103</v>
@@ -3711,11 +3711,11 @@
         <v>106</v>
       </c>
       <c r="B30" s="5">
-        <v>46167.390164756944</v>
+        <v>46167.556831423615</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46184.00819033565</v>
+        <v>46184.17485700232</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>107</v>
@@ -3774,11 +3774,11 @@
         <v>113</v>
       </c>
       <c r="B31" s="9">
-        <v>46167.39016981481</v>
+        <v>46167.55683648148</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46184.00819033565</v>
+        <v>46184.17485700232</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>114</v>
@@ -3837,11 +3837,11 @@
         <v>116</v>
       </c>
       <c r="B32" s="5">
-        <v>46167.39017408565</v>
+        <v>46167.55684075231</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46184.00819043981</v>
+        <v>46184.17485710648</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>117</v>
@@ -3900,11 +3900,11 @@
         <v>119</v>
       </c>
       <c r="B33" s="9">
-        <v>46167.39017840278</v>
+        <v>46167.55684506944</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46184.008190312496</v>
+        <v>46184.17485697917</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>120</v>
@@ -3963,11 +3963,11 @@
         <v>122</v>
       </c>
       <c r="B34" s="5">
-        <v>46167.39018246528</v>
+        <v>46167.55684913194</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.71219472222</v>
+        <v>46169.87886138889</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>123</v>
@@ -4026,11 +4026,11 @@
         <v>125</v>
       </c>
       <c r="B35" s="9">
-        <v>46167.38997502315</v>
+        <v>46167.556641689815</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46167.460278530096</v>
+        <v>46167.62694519676</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>126</v>
@@ -4073,11 +4073,11 @@
         <v>128</v>
       </c>
       <c r="B36" s="5">
-        <v>46167.39018787037</v>
+        <v>46167.55685453703</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.71122353009</v>
+        <v>46169.87789019676</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>129</v>
@@ -4136,11 +4136,11 @@
         <v>133</v>
       </c>
       <c r="B37" s="9">
-        <v>46167.39019276621</v>
+        <v>46167.556859432865</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.711356921296</v>
+        <v>46169.87802358797</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>134</v>
@@ -4195,11 +4195,11 @@
         <v>136</v>
       </c>
       <c r="B38" s="5">
-        <v>46167.39019759259</v>
+        <v>46167.556864259255</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.71137733797</v>
+        <v>46169.878044004625</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>137</v>
@@ -4254,11 +4254,11 @@
         <v>139</v>
       </c>
       <c r="B39" s="9">
-        <v>46167.39020285879</v>
+        <v>46167.55686952546</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46184.030893206014</v>
+        <v>46184.197559872686</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>140</v>
@@ -4317,11 +4317,11 @@
         <v>143</v>
       </c>
       <c r="B40" s="5">
-        <v>46167.39020760417</v>
+        <v>46167.556874270835</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.71141525463</v>
+        <v>46169.8780819213</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>144</v>
@@ -4376,11 +4376,11 @@
         <v>146</v>
       </c>
       <c r="B41" s="9">
-        <v>46167.39021280092</v>
+        <v>46167.55687946759</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46183.00375375</v>
+        <v>46183.17042041667</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>147</v>
@@ -4435,11 +4435,11 @@
         <v>149</v>
       </c>
       <c r="B42" s="5">
-        <v>46167.390217974535</v>
+        <v>46167.556884641206</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.71125807871</v>
+        <v>46169.87792474537</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>150</v>
@@ -4498,11 +4498,11 @@
         <v>152</v>
       </c>
       <c r="B43" s="9">
-        <v>46167.390222835646</v>
+        <v>46167.55688950232</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.71148430556</v>
+        <v>46169.87815097222</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>153</v>
@@ -4557,11 +4557,11 @@
         <v>155</v>
       </c>
       <c r="B44" s="5">
-        <v>46167.390227916665</v>
+        <v>46167.55689458334</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.711522881946</v>
+        <v>46169.87818954861</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>156</v>
@@ -4616,11 +4616,11 @@
         <v>158</v>
       </c>
       <c r="B45" s="9">
-        <v>46167.39028723379</v>
+        <v>46167.556953900465</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46185.352352754635</v>
+        <v>46185.51901942129</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>159</v>
@@ -4675,11 +4675,11 @@
         <v>161</v>
       </c>
       <c r="B46" s="5">
-        <v>46167.39029436343</v>
+        <v>46167.55696103009</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.712276018516</v>
+        <v>46169.87894268519</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>162</v>
@@ -4738,11 +4738,11 @@
         <v>164</v>
       </c>
       <c r="B47" s="9">
-        <v>46167.39029858796</v>
+        <v>46167.556965254626</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46170.00517337963</v>
+        <v>46170.1718400463</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>124</v>
@@ -4791,11 +4791,11 @@
         <v>166</v>
       </c>
       <c r="B48" s="5">
-        <v>46167.39030298611</v>
+        <v>46167.55696965278</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.71236159722</v>
+        <v>46169.87902826389</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>167</v>
@@ -4844,11 +4844,11 @@
         <v>169</v>
       </c>
       <c r="B49" s="9">
-        <v>46167.390307118054</v>
+        <v>46167.556973784725</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46169.71128416667</v>
+        <v>46169.87795083333</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>170</v>
@@ -4907,11 +4907,11 @@
         <v>174</v>
       </c>
       <c r="B50" s="5">
-        <v>46167.390311944444</v>
+        <v>46167.556978611115</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46169.711649178236</v>
+        <v>46169.87831584491</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>175</v>
@@ -4966,11 +4966,11 @@
         <v>177</v>
       </c>
       <c r="B51" s="9">
-        <v>46167.39031701389</v>
+        <v>46167.55698368055</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46169.71166302083</v>
+        <v>46169.878329687504</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>178</v>
@@ -5025,11 +5025,11 @@
         <v>180</v>
       </c>
       <c r="B52" s="5">
-        <v>46167.390322175925</v>
+        <v>46167.556988842596</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.711293761575</v>
+        <v>46169.87796042824</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>181</v>
@@ -5088,11 +5088,11 @@
         <v>183</v>
       </c>
       <c r="B53" s="9">
-        <v>46167.39032604167</v>
+        <v>46167.556992708334</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46169.71169729167</v>
+        <v>46169.878363958334</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>115</v>
@@ -5141,11 +5141,11 @@
         <v>185</v>
       </c>
       <c r="B54" s="5">
-        <v>46167.39033052084</v>
+        <v>46167.5569971875</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.711711261574</v>
+        <v>46169.87837792824</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>186</v>
@@ -5194,11 +5194,11 @@
         <v>188</v>
       </c>
       <c r="B55" s="9">
-        <v>46167.39033473379</v>
+        <v>46167.55700140046</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46169.711310810184</v>
+        <v>46169.87797747685</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>189</v>
@@ -5257,11 +5257,11 @@
         <v>193</v>
       </c>
       <c r="B56" s="5">
-        <v>46167.390338530095</v>
+        <v>46167.55700519676</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46169.71174711805</v>
+        <v>46169.878413784725</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>121</v>
@@ -5310,11 +5310,11 @@
         <v>195</v>
       </c>
       <c r="B57" s="9">
-        <v>46167.39034336805</v>
+        <v>46167.557010034725</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46169.71176355324</v>
+        <v>46169.878430219906</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>196</v>
@@ -5363,11 +5363,11 @@
         <v>198</v>
       </c>
       <c r="B58" s="5">
-        <v>46167.39034810185</v>
+        <v>46167.55701476852</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46169.711782812505</v>
+        <v>46169.87844947916</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>199</v>
@@ -5416,11 +5416,11 @@
         <v>202</v>
       </c>
       <c r="B59" s="9">
-        <v>46167.39035103009</v>
+        <v>46167.55701769676</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46169.711324178235</v>
+        <v>46169.87799084491</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>203</v>
@@ -5479,11 +5479,11 @@
         <v>205</v>
       </c>
       <c r="B60" s="5">
-        <v>46167.39035501158</v>
+        <v>46167.557021678236</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46169.711814317125</v>
+        <v>46169.878480983796</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>118</v>
@@ -5532,11 +5532,11 @@
         <v>207</v>
       </c>
       <c r="B61" s="9">
-        <v>46167.39035967593</v>
+        <v>46167.55702634259</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46169.71183905093</v>
+        <v>46169.87850571759</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>208</v>
@@ -5585,11 +5585,11 @@
         <v>210</v>
       </c>
       <c r="B62" s="5">
-        <v>46167.3903700463</v>
+        <v>46167.55703671296</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46184.350501469904</v>
+        <v>46184.517168136575</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>211</v>
@@ -5632,13 +5632,13 @@
         <v>213</v>
       </c>
       <c r="B63" s="9">
-        <v>46167.39037385417</v>
+        <v>46167.557040520835</v>
       </c>
       <c r="C63" s="9">
-        <v>46184.35049503473</v>
+        <v>46184.517161701384</v>
       </c>
       <c r="D63" s="9">
-        <v>46184.350511550925</v>
+        <v>46184.51717821759</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>214</v>
@@ -5697,11 +5697,11 @@
         <v>218</v>
       </c>
       <c r="B64" s="5">
-        <v>46167.39037918982</v>
+        <v>46167.557045856476</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.5413390625</v>
+        <v>46184.70800572917</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>219</v>
@@ -5760,11 +5760,11 @@
         <v>222</v>
       </c>
       <c r="B65" s="9">
-        <v>46167.390385300925</v>
+        <v>46167.5570519676</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46184.54174880787</v>
+        <v>46184.70841547454</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>110</v>
@@ -5823,11 +5823,11 @@
         <v>224</v>
       </c>
       <c r="B66" s="5">
-        <v>46167.39039785879</v>
+        <v>46167.55706452546</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46167.574203321754</v>
+        <v>46167.740869988425</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>225</v>
@@ -5886,11 +5886,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46167.390401770834</v>
+        <v>46167.5570684375</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46167.57419234954</v>
+        <v>46167.74085901621</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5939,11 +5939,11 @@
         <v>232</v>
       </c>
       <c r="B68" s="5">
-        <v>46167.39040607639</v>
+        <v>46167.55707274306</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46167.574189074076</v>
+        <v>46167.74085574074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>
@@ -5992,11 +5992,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46167.49309082176</v>
+        <v>46167.65975748842</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46167.57418625</v>
+        <v>46167.74085291667</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>230</v>
@@ -6045,11 +6045,11 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46167.49310259259</v>
+        <v>46167.65976925926</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46167.57418384259</v>
+        <v>46167.74085050926</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>230</v>
@@ -6098,11 +6098,11 @@
         <v>235</v>
       </c>
       <c r="B71" s="9">
-        <v>46167.493115324076</v>
+        <v>46167.65978199074</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46167.574178993054</v>
+        <v>46167.74084565972</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>230</v>
@@ -6151,11 +6151,11 @@
         <v>236</v>
       </c>
       <c r="B72" s="5">
-        <v>46167.493131157404</v>
+        <v>46167.659797824075</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46167.574173472225</v>
+        <v>46167.74084013889</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>230</v>
@@ -6204,11 +6204,11 @@
         <v>238</v>
       </c>
       <c r="B73" s="9">
-        <v>46167.49320972222</v>
+        <v>46167.65987638889</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46167.5741724074</v>
+        <v>46167.740839074075</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>239</v>
@@ -6257,11 +6257,11 @@
         <v>240</v>
       </c>
       <c r="B74" s="5">
-        <v>46167.49322012732</v>
+        <v>46167.65988679398</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46167.57417168982</v>
+        <v>46167.740838356476</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>239</v>
@@ -6310,11 +6310,11 @@
         <v>241</v>
       </c>
       <c r="B75" s="9">
-        <v>46167.39041047454</v>
+        <v>46167.5570771412</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46167.46252136574</v>
+        <v>46167.629188032406</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>242</v>
@@ -6357,11 +6357,11 @@
         <v>244</v>
       </c>
       <c r="B76" s="5">
-        <v>46167.39041413194</v>
+        <v>46167.55708079861</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46167.57427354167</v>
+        <v>46167.74094020833</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>245</v>
@@ -6420,11 +6420,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46167.39041931713</v>
+        <v>46167.5570859838</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46167.57435462963</v>
+        <v>46167.7410212963</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>250</v>
@@ -6483,11 +6483,11 @@
         <v>253</v>
       </c>
       <c r="B78" s="5">
-        <v>46167.390425150465</v>
+        <v>46167.55709181713</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46167.57427079861</v>
+        <v>46167.74093746528</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>254</v>
@@ -6546,11 +6546,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46167.390430162035</v>
+        <v>46167.55709682871</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46167.57435202546</v>
+        <v>46167.74101869213</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>257</v>
@@ -6609,11 +6609,11 @@
         <v>259</v>
       </c>
       <c r="B80" s="5">
-        <v>46167.390486122684</v>
+        <v>46167.55715278935</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46167.574268067125</v>
+        <v>46167.740934733796</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>260</v>
@@ -6672,11 +6672,11 @@
         <v>262</v>
       </c>
       <c r="B81" s="9">
-        <v>46167.390497500004</v>
+        <v>46167.55716416667</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46167.57434896991</v>
+        <v>46167.74101563657</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6735,11 +6735,11 @@
         <v>263</v>
       </c>
       <c r="B82" s="5">
-        <v>46167.39050201389</v>
+        <v>46167.557168680556</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46167.54759836805</v>
+        <v>46167.71426503472</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>264</v>
@@ -6782,11 +6782,11 @@
         <v>266</v>
       </c>
       <c r="B83" s="9">
-        <v>46167.39050553241</v>
+        <v>46167.55717219907</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46167.5745837963</v>
+        <v>46167.74125046296</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>267</v>
@@ -6845,11 +6845,11 @@
         <v>271</v>
       </c>
       <c r="B84" s="5">
-        <v>46167.390511562495</v>
+        <v>46167.557178229166</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46167.57457285879</v>
+        <v>46167.741239525465</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>230</v>
@@ -6898,11 +6898,11 @@
         <v>274</v>
       </c>
       <c r="B85" s="9">
-        <v>46167.3905183912</v>
+        <v>46167.55718505787</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46167.57456997685</v>
+        <v>46167.74123664352</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>230</v>
@@ -6951,11 +6951,11 @@
         <v>276</v>
       </c>
       <c r="B86" s="5">
-        <v>46167.46329738426</v>
+        <v>46167.629964050924</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46167.57456707176</v>
+        <v>46167.74123373843</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>230</v>
@@ -7004,11 +7004,11 @@
         <v>278</v>
       </c>
       <c r="B87" s="9">
-        <v>46167.46330802083</v>
+        <v>46167.6299746875</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46167.57456405093</v>
+        <v>46167.74123071759</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>230</v>
@@ -7057,11 +7057,11 @@
         <v>279</v>
       </c>
       <c r="B88" s="5">
-        <v>46167.46344912037</v>
+        <v>46167.63011578703</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46167.57456138889</v>
+        <v>46167.74122805556</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>230</v>
@@ -7110,11 +7110,11 @@
         <v>280</v>
       </c>
       <c r="B89" s="9">
-        <v>46167.46345984953</v>
+        <v>46167.630126516204</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46167.574558796296</v>
+        <v>46167.74122546296</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>230</v>
@@ -7163,11 +7163,11 @@
         <v>281</v>
       </c>
       <c r="B90" s="5">
-        <v>46167.46478888889</v>
+        <v>46167.63145555556</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46167.57455276621</v>
+        <v>46167.74121943287</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>239</v>
@@ -7216,11 +7216,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46167.46510601851</v>
+        <v>46167.631772685185</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46167.574552129634</v>
+        <v>46167.74121879629</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>239</v>
@@ -7269,11 +7269,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46167.39052417824</v>
+        <v>46167.557190844906</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46167.574720439814</v>
+        <v>46167.74138710648</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>284</v>
@@ -7332,11 +7332,11 @@
         <v>285</v>
       </c>
       <c r="B93" s="9">
-        <v>46167.39052842592</v>
+        <v>46167.557195092595</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46167.57470545139</v>
+        <v>46167.74137211806</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>230</v>
@@ -7385,11 +7385,11 @@
         <v>288</v>
       </c>
       <c r="B94" s="5">
-        <v>46167.390534328704</v>
+        <v>46167.557200995376</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46167.574702708334</v>
+        <v>46167.741369375</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>230</v>
@@ -7438,11 +7438,11 @@
         <v>289</v>
       </c>
       <c r="B95" s="9">
-        <v>46167.4654825</v>
+        <v>46167.63214916667</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46167.57469976852</v>
+        <v>46167.741366435184</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>230</v>
@@ -7491,11 +7491,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46167.46552440972</v>
+        <v>46167.63219107639</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46167.57469695601</v>
+        <v>46167.741363622685</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>230</v>
@@ -7544,11 +7544,11 @@
         <v>291</v>
       </c>
       <c r="B97" s="9">
-        <v>46167.4655343287</v>
+        <v>46167.63220099537</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46167.57469454861</v>
+        <v>46167.741361215274</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>230</v>
@@ -7597,11 +7597,11 @@
         <v>292</v>
       </c>
       <c r="B98" s="5">
-        <v>46167.46554172454</v>
+        <v>46167.63220839121</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46167.57469188658</v>
+        <v>46167.74135855324</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>230</v>
@@ -7650,11 +7650,11 @@
         <v>293</v>
       </c>
       <c r="B99" s="9">
-        <v>46167.46558924769</v>
+        <v>46167.63225591435</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46167.57468628472</v>
+        <v>46167.74135295139</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>239</v>
@@ -7703,11 +7703,11 @@
         <v>294</v>
       </c>
       <c r="B100" s="5">
-        <v>46167.46559707176</v>
+        <v>46167.63226373843</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46167.574685590276</v>
+        <v>46167.74135225694</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>239</v>
@@ -7756,11 +7756,11 @@
         <v>295</v>
       </c>
       <c r="B101" s="9">
-        <v>46167.39053989583</v>
+        <v>46167.5572065625</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46167.57486626157</v>
+        <v>46167.74153292824</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>296</v>
@@ -7819,11 +7819,11 @@
         <v>297</v>
       </c>
       <c r="B102" s="5">
-        <v>46167.39054424768</v>
+        <v>46167.557210914354</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46167.574856273146</v>
+        <v>46167.74152293982</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>230</v>
@@ -7872,11 +7872,11 @@
         <v>299</v>
       </c>
       <c r="B103" s="9">
-        <v>46167.3905503125</v>
+        <v>46167.55721697917</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46167.574853495375</v>
+        <v>46167.74152016204</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>230</v>
@@ -7925,11 +7925,11 @@
         <v>300</v>
       </c>
       <c r="B104" s="5">
-        <v>46167.46567538194</v>
+        <v>46167.632342048615</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46167.57485089121</v>
+        <v>46167.74151755787</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>230</v>
@@ -7978,11 +7978,11 @@
         <v>301</v>
       </c>
       <c r="B105" s="9">
-        <v>46167.46569201389</v>
+        <v>46167.63235868055</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46167.57484836805</v>
+        <v>46167.74151503472</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>230</v>
@@ -8031,11 +8031,11 @@
         <v>302</v>
       </c>
       <c r="B106" s="5">
-        <v>46167.46569923611</v>
+        <v>46167.63236590278</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46167.57484596065</v>
+        <v>46167.74151262731</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>230</v>
@@ -8084,11 +8084,11 @@
         <v>303</v>
       </c>
       <c r="B107" s="9">
-        <v>46167.46570746528</v>
+        <v>46167.63237413194</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46167.57484369213</v>
+        <v>46167.7415103588</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>230</v>
@@ -8137,11 +8137,11 @@
         <v>304</v>
       </c>
       <c r="B108" s="5">
-        <v>46167.46577653935</v>
+        <v>46167.63244320602</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46167.57483846065</v>
+        <v>46167.74150512731</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>239</v>
@@ -8190,11 +8190,11 @@
         <v>305</v>
       </c>
       <c r="B109" s="9">
-        <v>46167.46578601852</v>
+        <v>46167.63245268518</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46167.5748378125</v>
+        <v>46167.74150447917</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>239</v>
@@ -8243,11 +8243,11 @@
         <v>306</v>
       </c>
       <c r="B110" s="5">
-        <v>46167.39055582176</v>
+        <v>46167.55722248842</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46167.55296565972</v>
+        <v>46167.71963232639</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>242</v>
@@ -8290,11 +8290,11 @@
         <v>308</v>
       </c>
       <c r="B111" s="9">
-        <v>46167.3905590162</v>
+        <v>46167.557225682875</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46185.016327731486</v>
+        <v>46185.18299439814</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>309</v>
@@ -8353,11 +8353,11 @@
         <v>311</v>
       </c>
       <c r="B112" s="5">
-        <v>46167.39056482639</v>
+        <v>46167.557231493054</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46168.02544952546</v>
+        <v>46168.192116192135</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>312</v>
@@ -8416,11 +8416,11 @@
         <v>313</v>
       </c>
       <c r="B113" s="9">
-        <v>46167.39057079861</v>
+        <v>46167.55723746528</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46167.57497528935</v>
+        <v>46167.74164195602</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>314</v>
@@ -8479,11 +8479,11 @@
         <v>316</v>
       </c>
       <c r="B114" s="5">
-        <v>46167.39058180556</v>
+        <v>46167.55724847222</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46167.57497258102</v>
+        <v>46167.74163924769</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>317</v>
@@ -8542,11 +8542,11 @@
         <v>319</v>
       </c>
       <c r="B115" s="9">
-        <v>46167.390586863425</v>
+        <v>46167.55725353009</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46167.57496805556</v>
+        <v>46167.74163472222</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>59</v>
@@ -8605,11 +8605,11 @@
         <v>321</v>
       </c>
       <c r="B116" s="5">
-        <v>46167.39059244213</v>
+        <v>46167.5572591088</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46167.56463365741</v>
+        <v>46167.73130032407</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>322</v>
@@ -8652,11 +8652,11 @@
         <v>324</v>
       </c>
       <c r="B117" s="9">
-        <v>46167.39059601852</v>
+        <v>46167.557262685186</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46167.57525833334</v>
+        <v>46167.741924999995</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>325</v>
@@ -8715,11 +8715,11 @@
         <v>327</v>
       </c>
       <c r="B118" s="5">
-        <v>46167.390604189815</v>
+        <v>46167.55727085649</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46167.575242245366</v>
+        <v>46167.74190891204</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>230</v>
@@ -8768,11 +8768,11 @@
         <v>329</v>
       </c>
       <c r="B119" s="9">
-        <v>46167.390608657406</v>
+        <v>46167.55727532407</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46167.575239756945</v>
+        <v>46167.74190642362</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>230</v>
@@ -8821,11 +8821,11 @@
         <v>330</v>
       </c>
       <c r="B120" s="5">
-        <v>46167.46593938657</v>
+        <v>46167.632606053245</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46167.57523703703</v>
+        <v>46167.7419037037</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>230</v>
@@ -8874,11 +8874,11 @@
         <v>331</v>
       </c>
       <c r="B121" s="9">
-        <v>46167.465947766206</v>
+        <v>46167.63261443287</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46167.57523454861</v>
+        <v>46167.74190121528</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>230</v>
@@ -8927,11 +8927,11 @@
         <v>332</v>
       </c>
       <c r="B122" s="5">
-        <v>46167.46595575231</v>
+        <v>46167.63262241898</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46167.575232256946</v>
+        <v>46167.74189892361</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>230</v>
@@ -8980,11 +8980,11 @@
         <v>333</v>
       </c>
       <c r="B123" s="9">
-        <v>46167.46596372685</v>
+        <v>46167.63263039352</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46167.575229884256</v>
+        <v>46167.74189655093</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>230</v>
@@ -9033,11 +9033,11 @@
         <v>334</v>
       </c>
       <c r="B124" s="5">
-        <v>46167.46602341435</v>
+        <v>46167.63269008102</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46167.57522479167</v>
+        <v>46167.74189145833</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>239</v>
@@ -9086,11 +9086,11 @@
         <v>335</v>
       </c>
       <c r="B125" s="9">
-        <v>46167.46603207176</v>
+        <v>46167.632698738424</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46167.57522412037</v>
+        <v>46167.74189078704</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>239</v>
@@ -9139,11 +9139,11 @@
         <v>336</v>
       </c>
       <c r="B126" s="5">
-        <v>46167.39061293982</v>
+        <v>46167.55727960648</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46167.575408449076</v>
+        <v>46167.74207511574</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>337</v>
@@ -9202,11 +9202,11 @@
         <v>338</v>
       </c>
       <c r="B127" s="9">
-        <v>46167.39061770833</v>
+        <v>46167.557284375</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46167.575396099535</v>
+        <v>46167.74206276621</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>230</v>
@@ -9255,11 +9255,11 @@
         <v>341</v>
       </c>
       <c r="B128" s="5">
-        <v>46167.39062342593</v>
+        <v>46167.55729009259</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46167.575393136576</v>
+        <v>46167.74205980324</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>230</v>
@@ -9308,11 +9308,11 @@
         <v>342</v>
       </c>
       <c r="B129" s="9">
-        <v>46167.466146412036</v>
+        <v>46167.6328130787</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46167.57539021991</v>
+        <v>46167.74205688658</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>230</v>
@@ -9361,11 +9361,11 @@
         <v>344</v>
       </c>
       <c r="B130" s="5">
-        <v>46167.466169189815</v>
+        <v>46167.63283585648</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46167.57538729167</v>
+        <v>46167.74205395833</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>230</v>
@@ -9414,11 +9414,11 @@
         <v>346</v>
       </c>
       <c r="B131" s="9">
-        <v>46167.46617670139</v>
+        <v>46167.63284336806</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46167.575384571755</v>
+        <v>46167.74205123843</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>230</v>
@@ -9467,11 +9467,11 @@
         <v>347</v>
       </c>
       <c r="B132" s="5">
-        <v>46167.46618496528</v>
+        <v>46167.63285163195</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46167.575381504634</v>
+        <v>46167.7420481713</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>230</v>
@@ -9520,11 +9520,11 @@
         <v>348</v>
       </c>
       <c r="B133" s="9">
-        <v>46167.46622511574</v>
+        <v>46167.63289178241</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46167.57537494213</v>
+        <v>46167.7420416088</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>239</v>
@@ -9573,11 +9573,11 @@
         <v>350</v>
       </c>
       <c r="B134" s="5">
-        <v>46167.4662325463</v>
+        <v>46167.632899212964</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46167.57537417824</v>
+        <v>46167.74204084491</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>239</v>
@@ -9626,11 +9626,11 @@
         <v>351</v>
       </c>
       <c r="B135" s="9">
-        <v>46167.39067069444</v>
+        <v>46167.55733736111</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46167.57555109954</v>
+        <v>46167.74221776621</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>352</v>
@@ -9689,11 +9689,11 @@
         <v>353</v>
       </c>
       <c r="B136" s="5">
-        <v>46167.390676979165</v>
+        <v>46167.557343645836</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46167.5755378125</v>
+        <v>46167.74220447917</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>230</v>
@@ -9740,11 +9740,11 @@
         <v>356</v>
       </c>
       <c r="B137" s="9">
-        <v>46167.39068413194</v>
+        <v>46167.55735079861</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46167.57553487268</v>
+        <v>46167.74220153935</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>230</v>
@@ -9791,11 +9791,11 @@
         <v>357</v>
       </c>
       <c r="B138" s="5">
-        <v>46167.46635693287</v>
+        <v>46167.63302359954</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46167.57553195602</v>
+        <v>46167.742198622684</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>230</v>
@@ -9842,11 +9842,11 @@
         <v>358</v>
       </c>
       <c r="B139" s="9">
-        <v>46167.466368194444</v>
+        <v>46167.63303486111</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46167.57552888889</v>
+        <v>46167.742195555555</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>230</v>
@@ -9893,11 +9893,11 @@
         <v>359</v>
       </c>
       <c r="B140" s="5">
-        <v>46167.46638398148</v>
+        <v>46167.633050648146</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46167.57552626157</v>
+        <v>46167.74219292824</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>230</v>
@@ -9944,11 +9944,11 @@
         <v>360</v>
       </c>
       <c r="B141" s="9">
-        <v>46167.46639400463</v>
+        <v>46167.633060671295</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46167.575523796295</v>
+        <v>46167.74219046296</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>230</v>
@@ -9995,11 +9995,11 @@
         <v>361</v>
       </c>
       <c r="B142" s="5">
-        <v>46167.46644851852</v>
+        <v>46167.633115185185</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46167.575518125</v>
+        <v>46167.74218479167</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>239</v>
@@ -10046,11 +10046,11 @@
         <v>363</v>
       </c>
       <c r="B143" s="9">
-        <v>46167.466456145834</v>
+        <v>46167.6331228125</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46167.57551737269</v>
+        <v>46167.74218403935</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>239</v>
@@ -10097,11 +10097,11 @@
         <v>365</v>
       </c>
       <c r="B144" s="5">
-        <v>46167.39069082176</v>
+        <v>46167.557357488426</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46167.575698472225</v>
+        <v>46167.74236513889</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>366</v>
@@ -10160,11 +10160,11 @@
         <v>367</v>
       </c>
       <c r="B145" s="9">
-        <v>46167.39069545139</v>
+        <v>46167.55736211805</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46167.57568439815</v>
+        <v>46167.742351064815</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>230</v>
@@ -10213,11 +10213,11 @@
         <v>370</v>
       </c>
       <c r="B146" s="5">
-        <v>46167.39070600695</v>
+        <v>46167.55737267361</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46167.57568181713</v>
+        <v>46167.74234848379</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>230</v>
@@ -10266,11 +10266,11 @@
         <v>371</v>
       </c>
       <c r="B147" s="9">
-        <v>46167.46658493056</v>
+        <v>46167.63325159722</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46167.57567884259</v>
+        <v>46167.74234550926</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>230</v>
@@ -10319,11 +10319,11 @@
         <v>373</v>
       </c>
       <c r="B148" s="5">
-        <v>46167.466592627316</v>
+        <v>46167.63325929398</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46167.57567547454</v>
+        <v>46167.7423421412</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>230</v>
@@ -10372,11 +10372,11 @@
         <v>375</v>
       </c>
       <c r="B149" s="9">
-        <v>46167.46660762731</v>
+        <v>46167.633274293985</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46167.57567302084</v>
+        <v>46167.742339687495</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>230</v>
@@ -10425,11 +10425,11 @@
         <v>376</v>
       </c>
       <c r="B150" s="5">
-        <v>46167.46661520834</v>
+        <v>46167.633281875</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46167.57567049768</v>
+        <v>46167.74233716435</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>230</v>
@@ -10478,11 +10478,11 @@
         <v>378</v>
       </c>
       <c r="B151" s="9">
-        <v>46167.466655937504</v>
+        <v>46167.63332260417</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46167.57566503472</v>
+        <v>46167.74233170139</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>239</v>
@@ -10531,11 +10531,11 @@
         <v>380</v>
       </c>
       <c r="B152" s="5">
-        <v>46167.46666502315</v>
+        <v>46167.633331689816</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46167.57566434028</v>
+        <v>46167.74233100694</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>239</v>
@@ -10584,11 +10584,11 @@
         <v>381</v>
       </c>
       <c r="B153" s="9">
-        <v>46167.39071162037</v>
+        <v>46167.557378287034</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46167.57583180556</v>
+        <v>46167.742498472224</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>382</v>
@@ -10647,11 +10647,11 @@
         <v>383</v>
       </c>
       <c r="B154" s="5">
-        <v>46167.39071626157</v>
+        <v>46167.55738292824</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46167.57582646991</v>
+        <v>46167.742493136575</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>230</v>
@@ -10700,11 +10700,11 @@
         <v>385</v>
       </c>
       <c r="B155" s="9">
-        <v>46167.390721724536</v>
+        <v>46167.5573883912</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46167.57582333333</v>
+        <v>46167.742490000004</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>230</v>
@@ -10753,11 +10753,11 @@
         <v>386</v>
       </c>
       <c r="B156" s="5">
-        <v>46167.466749942134</v>
+        <v>46167.63341660879</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46167.57582049769</v>
+        <v>46167.74248716435</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>230</v>
@@ -10806,11 +10806,11 @@
         <v>387</v>
       </c>
       <c r="B157" s="9">
-        <v>46167.46676704861</v>
+        <v>46167.63343371528</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46167.57581730324</v>
+        <v>46167.74248396991</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>230</v>
@@ -10859,11 +10859,11 @@
         <v>388</v>
       </c>
       <c r="B158" s="5">
-        <v>46167.46677699074</v>
+        <v>46167.63344365741</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46167.57581446759</v>
+        <v>46167.742481134264</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>230</v>
@@ -10912,11 +10912,11 @@
         <v>389</v>
       </c>
       <c r="B159" s="9">
-        <v>46167.466785219905</v>
+        <v>46167.63345188658</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46167.575811689814</v>
+        <v>46167.74247835648</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>230</v>
@@ -10965,11 +10965,11 @@
         <v>390</v>
       </c>
       <c r="B160" s="5">
-        <v>46167.46683974537</v>
+        <v>46167.633506412036</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46167.57580475694</v>
+        <v>46167.74247142361</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>239</v>
@@ -11018,11 +11018,11 @@
         <v>391</v>
       </c>
       <c r="B161" s="9">
-        <v>46167.46684732639</v>
+        <v>46167.63351399306</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46167.57580399305</v>
+        <v>46167.74247065972</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>239</v>
@@ -11071,11 +11071,11 @@
         <v>392</v>
       </c>
       <c r="B162" s="5">
-        <v>46167.39072740741</v>
+        <v>46167.55739407407</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46167.57598174769</v>
+        <v>46167.74264841435</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>393</v>
@@ -11134,11 +11134,11 @@
         <v>395</v>
       </c>
       <c r="B163" s="9">
-        <v>46167.390732534725</v>
+        <v>46167.55739920139</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46167.575971631944</v>
+        <v>46167.742638298616</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>230</v>
@@ -11187,11 +11187,11 @@
         <v>397</v>
       </c>
       <c r="B164" s="5">
-        <v>46167.39073734954</v>
+        <v>46167.5574040162</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46167.575968749996</v>
+        <v>46167.74263541667</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>230</v>
@@ -11240,11 +11240,11 @@
         <v>398</v>
       </c>
       <c r="B165" s="9">
-        <v>46167.46717653935</v>
+        <v>46167.633843206015</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46167.57596537037</v>
+        <v>46167.742632037036</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>230</v>
@@ -11293,11 +11293,11 @@
         <v>399</v>
       </c>
       <c r="B166" s="5">
-        <v>46167.467183229164</v>
+        <v>46167.633849895836</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46167.575962268515</v>
+        <v>46167.742628935186</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>230</v>
@@ -11346,11 +11346,11 @@
         <v>400</v>
       </c>
       <c r="B167" s="9">
-        <v>46167.467191250005</v>
+        <v>46167.63385791666</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46167.5759596875</v>
+        <v>46167.74262635417</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>230</v>
@@ -11399,11 +11399,11 @@
         <v>401</v>
       </c>
       <c r="B168" s="5">
-        <v>46167.467200416664</v>
+        <v>46167.633867083336</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46167.575956886576</v>
+        <v>46167.74262355324</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>237</v>
@@ -11452,11 +11452,11 @@
         <v>402</v>
       </c>
       <c r="B169" s="9">
-        <v>46167.46724568287</v>
+        <v>46167.63391234954</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46167.57595074074</v>
+        <v>46167.742617407406</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>239</v>
@@ -11505,11 +11505,11 @@
         <v>403</v>
       </c>
       <c r="B170" s="5">
-        <v>46167.46725350694</v>
+        <v>46167.63392017361</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46167.57595010417</v>
+        <v>46167.74261677083</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>239</v>
@@ -11558,11 +11558,11 @@
         <v>404</v>
       </c>
       <c r="B171" s="9">
-        <v>46167.39074253472</v>
+        <v>46167.557409201385</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46167.5680759838</v>
+        <v>46167.734742650464</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>405</v>
@@ -11605,11 +11605,11 @@
         <v>407</v>
       </c>
       <c r="B172" s="5">
-        <v>46167.390746550926</v>
+        <v>46167.5574132176</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46167.57617571759</v>
+        <v>46167.74284238426</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>408</v>
@@ -11668,11 +11668,11 @@
         <v>412</v>
       </c>
       <c r="B173" s="9">
-        <v>46167.39075387732</v>
+        <v>46167.55742054398</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46167.57619577546</v>
+        <v>46167.74286244213</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>230</v>
@@ -11721,11 +11721,11 @@
         <v>414</v>
       </c>
       <c r="B174" s="5">
-        <v>46167.39075885416</v>
+        <v>46167.557425520834</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46167.576192939814</v>
+        <v>46167.742859606486</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>230</v>
@@ -11774,11 +11774,11 @@
         <v>415</v>
       </c>
       <c r="B175" s="9">
-        <v>46167.39076354167</v>
+        <v>46167.55743020833</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46167.5761903588</v>
+        <v>46167.74285702546</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>230</v>
@@ -11827,11 +11827,11 @@
         <v>416</v>
       </c>
       <c r="B176" s="5">
-        <v>46167.39076825231</v>
+        <v>46167.557434918985</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46167.576187708335</v>
+        <v>46167.742854375</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>230</v>
@@ -11880,11 +11880,11 @@
         <v>417</v>
       </c>
       <c r="B177" s="9">
-        <v>46167.46973636574</v>
+        <v>46167.636403032404</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46167.576185</v>
+        <v>46167.74285166667</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>230</v>
@@ -11933,11 +11933,11 @@
         <v>418</v>
       </c>
       <c r="B178" s="5">
-        <v>46167.469745069444</v>
+        <v>46167.63641173611</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46167.57618225695</v>
+        <v>46167.74284892361</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>230</v>
@@ -11986,11 +11986,11 @@
         <v>419</v>
       </c>
       <c r="B179" s="9">
-        <v>46167.46976197917</v>
+        <v>46167.636428645834</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46167.57617980324</v>
+        <v>46167.742846469904</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>239</v>
@@ -12039,11 +12039,11 @@
         <v>420</v>
       </c>
       <c r="B180" s="5">
-        <v>46167.46977318287</v>
+        <v>46167.636439849535</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46167.57617702546</v>
+        <v>46167.74284369213</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>239</v>
@@ -12092,11 +12092,11 @@
         <v>421</v>
       </c>
       <c r="B181" s="9">
-        <v>46167.4700108449</v>
+        <v>46167.636677511575</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46167.57617417824</v>
+        <v>46167.742840844905</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>64</v>
@@ -12145,11 +12145,11 @@
         <v>422</v>
       </c>
       <c r="B182" s="5">
-        <v>46167.470026400464</v>
+        <v>46167.63669306713</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46167.576171469904</v>
+        <v>46167.742838136575</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>63</v>
@@ -12198,11 +12198,11 @@
         <v>423</v>
       </c>
       <c r="B183" s="9">
-        <v>46167.47003484954</v>
+        <v>46167.6367015162</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46167.57616909722</v>
+        <v>46167.742835763886</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>63</v>
@@ -12251,11 +12251,11 @@
         <v>424</v>
       </c>
       <c r="B184" s="5">
-        <v>46167.470044629634</v>
+        <v>46167.6367112963</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46167.57615849537</v>
+        <v>46167.74282516204</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>63</v>
@@ -12304,11 +12304,11 @@
         <v>425</v>
       </c>
       <c r="B185" s="9">
-        <v>46167.47005341435</v>
+        <v>46167.63672008102</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46167.57615778936</v>
+        <v>46167.742824456014</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>63</v>
@@ -12357,11 +12357,11 @@
         <v>426</v>
       </c>
       <c r="B186" s="5">
-        <v>46167.47006258102</v>
+        <v>46167.636729247686</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46167.576157083335</v>
+        <v>46167.74282375</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>63</v>
@@ -12410,11 +12410,11 @@
         <v>427</v>
       </c>
       <c r="B187" s="9">
-        <v>46167.47016936343</v>
+        <v>46167.63683603009</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46167.576156400464</v>
+        <v>46167.74282306713</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>71</v>
@@ -12463,11 +12463,11 @@
         <v>428</v>
       </c>
       <c r="B188" s="5">
-        <v>46167.47017965278</v>
+        <v>46167.636846319445</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46167.57615570602</v>
+        <v>46167.74282237269</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>71</v>
@@ -12516,11 +12516,11 @@
         <v>429</v>
       </c>
       <c r="B189" s="9">
-        <v>46167.39077278935</v>
+        <v>46167.55743945602</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46167.57637837963</v>
+        <v>46167.7430450463</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>430</v>
@@ -12579,11 +12579,11 @@
         <v>432</v>
       </c>
       <c r="B190" s="5">
-        <v>46167.390777569446</v>
+        <v>46167.55744423611</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46167.576399537036</v>
+        <v>46167.74306620371</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>230</v>
@@ -12630,11 +12630,11 @@
         <v>434</v>
       </c>
       <c r="B191" s="9">
-        <v>46167.39078217593</v>
+        <v>46167.55744884259</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46167.576396689816</v>
+        <v>46167.74306335648</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>230</v>
@@ -12681,11 +12681,11 @@
         <v>436</v>
       </c>
       <c r="B192" s="5">
-        <v>46167.390786828706</v>
+        <v>46167.55745349537</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46167.57639341435</v>
+        <v>46167.74306008102</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>230</v>
@@ -12732,11 +12732,11 @@
         <v>437</v>
       </c>
       <c r="B193" s="9">
-        <v>46167.39079111112</v>
+        <v>46167.55745777777</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46167.57639071759</v>
+        <v>46167.74305738426</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>230</v>
@@ -12783,11 +12783,11 @@
         <v>438</v>
       </c>
       <c r="B194" s="5">
-        <v>46167.47100416667</v>
+        <v>46167.637670833334</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46167.57638799769</v>
+        <v>46167.74305466435</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>230</v>
@@ -12834,11 +12834,11 @@
         <v>439</v>
       </c>
       <c r="B195" s="9">
-        <v>46167.471014097224</v>
+        <v>46167.63768076389</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46167.57638532408</v>
+        <v>46167.743051990736</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>230</v>
@@ -12885,11 +12885,11 @@
         <v>440</v>
       </c>
       <c r="B196" s="5">
-        <v>46167.47105734954</v>
+        <v>46167.637724016204</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46167.576382534724</v>
+        <v>46167.74304920139</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>239</v>
@@ -12936,11 +12936,11 @@
         <v>441</v>
       </c>
       <c r="B197" s="9">
-        <v>46167.47106564815</v>
+        <v>46167.63773231482</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46167.576379907405</v>
+        <v>46167.743046574076</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>239</v>
@@ -12987,11 +12987,11 @@
         <v>442</v>
       </c>
       <c r="B198" s="5">
-        <v>46167.47121344907</v>
+        <v>46167.63788011574</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46167.57637700232</v>
+        <v>46167.74304366898</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>63</v>
@@ -13040,11 +13040,11 @@
         <v>443</v>
       </c>
       <c r="B199" s="9">
-        <v>46167.47122186342</v>
+        <v>46167.637888530095</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46167.57637400463</v>
+        <v>46167.743040671296</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>63</v>
@@ -13093,11 +13093,11 @@
         <v>444</v>
       </c>
       <c r="B200" s="5">
-        <v>46167.47123055556</v>
+        <v>46167.63789722222</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46167.57637123842</v>
+        <v>46167.74303790509</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>63</v>
@@ -13146,11 +13146,11 @@
         <v>445</v>
       </c>
       <c r="B201" s="9">
-        <v>46167.47124101852</v>
+        <v>46167.63790768519</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46167.57636856481</v>
+        <v>46167.743035231484</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>63</v>
@@ -13199,11 +13199,11 @@
         <v>446</v>
       </c>
       <c r="B202" s="5">
-        <v>46167.471249953705</v>
+        <v>46167.63791662037</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46167.5763584838</v>
+        <v>46167.74302515046</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>63</v>
@@ -13252,11 +13252,11 @@
         <v>447</v>
       </c>
       <c r="B203" s="9">
-        <v>46167.47128002315</v>
+        <v>46167.637946689814</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46167.57635780092</v>
+        <v>46167.74302446759</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>63</v>
@@ -13305,11 +13305,11 @@
         <v>448</v>
       </c>
       <c r="B204" s="5">
-        <v>46167.4713290625</v>
+        <v>46167.637995729165</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46167.5763571412</v>
+        <v>46167.74302380787</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>71</v>
@@ -13358,11 +13358,11 @@
         <v>449</v>
       </c>
       <c r="B205" s="9">
-        <v>46167.47133753472</v>
+        <v>46167.63800420139</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46167.57635646991</v>
+        <v>46167.74302313657</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>71</v>
@@ -13411,11 +13411,11 @@
         <v>450</v>
       </c>
       <c r="B206" s="5">
-        <v>46167.3907955787</v>
+        <v>46167.55746224537</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46167.57697865741</v>
+        <v>46167.74364532407</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>451</v>
@@ -13474,11 +13474,11 @@
         <v>452</v>
       </c>
       <c r="B207" s="9">
-        <v>46167.390800231486</v>
+        <v>46167.55746689815</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46167.57701059028</v>
+        <v>46167.74367725695</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>230</v>
@@ -13527,11 +13527,11 @@
         <v>454</v>
       </c>
       <c r="B208" s="5">
-        <v>46167.39080877315</v>
+        <v>46167.55747543981</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46167.57700769676</v>
+        <v>46167.743674363424</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>230</v>
@@ -13580,11 +13580,11 @@
         <v>456</v>
       </c>
       <c r="B209" s="9">
-        <v>46167.39085260416</v>
+        <v>46167.557519270835</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46167.57700517361</v>
+        <v>46167.743671840275</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>230</v>
@@ -13633,11 +13633,11 @@
         <v>458</v>
       </c>
       <c r="B210" s="5">
-        <v>46167.390858645835</v>
+        <v>46167.5575253125</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46167.577002743055</v>
+        <v>46167.74366940973</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>230</v>
@@ -13686,11 +13686,11 @@
         <v>459</v>
       </c>
       <c r="B211" s="9">
-        <v>46167.47190484953</v>
+        <v>46167.6385715162</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46167.57700017361</v>
+        <v>46167.74366684028</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>230</v>
@@ -13739,11 +13739,11 @@
         <v>460</v>
       </c>
       <c r="B212" s="5">
-        <v>46167.47191232639</v>
+        <v>46167.63857899306</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46167.5769975</v>
+        <v>46167.74366416667</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>230</v>
@@ -13792,11 +13792,11 @@
         <v>461</v>
       </c>
       <c r="B213" s="9">
-        <v>46167.47199326388</v>
+        <v>46167.638659930555</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46167.57699435185</v>
+        <v>46167.74366101852</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>239</v>
@@ -13845,11 +13845,11 @@
         <v>463</v>
       </c>
       <c r="B214" s="5">
-        <v>46167.47200028935</v>
+        <v>46167.638666956016</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46167.57699173611</v>
+        <v>46167.743658402775</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>239</v>
@@ -13898,11 +13898,11 @@
         <v>464</v>
       </c>
       <c r="B215" s="9">
-        <v>46167.47204234954</v>
+        <v>46167.6387090162</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46167.57698893519</v>
+        <v>46167.74365560185</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>63</v>
@@ -13951,11 +13951,11 @@
         <v>465</v>
       </c>
       <c r="B216" s="5">
-        <v>46167.47204974537</v>
+        <v>46167.63871641204</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46167.576986493055</v>
+        <v>46167.74365315972</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>63</v>
@@ -14004,11 +14004,11 @@
         <v>466</v>
       </c>
       <c r="B217" s="9">
-        <v>46167.47205693287</v>
+        <v>46167.638723599535</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46167.5769841088</v>
+        <v>46167.74365077546</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>63</v>
@@ -14057,11 +14057,11 @@
         <v>467</v>
       </c>
       <c r="B218" s="5">
-        <v>46167.47206478009</v>
+        <v>46167.63873144676</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46167.576981412036</v>
+        <v>46167.7436480787</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>63</v>
@@ -14110,11 +14110,11 @@
         <v>468</v>
       </c>
       <c r="B219" s="9">
-        <v>46167.47207391204</v>
+        <v>46167.6387405787</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46167.57697206018</v>
+        <v>46167.74363872685</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>63</v>
@@ -14163,11 +14163,11 @@
         <v>469</v>
       </c>
       <c r="B220" s="5">
-        <v>46167.47208178241</v>
+        <v>46167.63874844907</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46167.57697135417</v>
+        <v>46167.74363802084</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>63</v>
@@ -14216,11 +14216,11 @@
         <v>470</v>
       </c>
       <c r="B221" s="9">
-        <v>46167.47208989583</v>
+        <v>46167.638756562505</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46167.576970671296</v>
+        <v>46167.74363733796</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>71</v>
@@ -14269,11 +14269,11 @@
         <v>472</v>
       </c>
       <c r="B222" s="5">
-        <v>46167.47216761574</v>
+        <v>46167.63883428241</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46167.576969999995</v>
+        <v>46167.743636666666</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>71</v>
@@ -14322,11 +14322,11 @@
         <v>473</v>
       </c>
       <c r="B223" s="9">
-        <v>46167.39086332176</v>
+        <v>46167.55752998842</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46167.57715442129</v>
+        <v>46167.74382108796</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>474</v>
@@ -14385,11 +14385,11 @@
         <v>476</v>
       </c>
       <c r="B224" s="5">
-        <v>46167.39086947917</v>
+        <v>46167.55753614583</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46167.57718232639</v>
+        <v>46167.74384899306</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>230</v>
@@ -14438,11 +14438,11 @@
         <v>477</v>
       </c>
       <c r="B225" s="9">
-        <v>46167.39087371528</v>
+        <v>46167.557540381946</v>
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46167.57717930556</v>
+        <v>46167.74384597222</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>230</v>
@@ -14491,11 +14491,11 @@
         <v>478</v>
       </c>
       <c r="B226" s="5">
-        <v>46167.39087840277</v>
+        <v>46167.557545069445</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46167.57717674768</v>
+        <v>46167.743843414355</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>230</v>
@@ -14544,11 +14544,11 @@
         <v>479</v>
       </c>
       <c r="B227" s="9">
-        <v>46167.39088229167</v>
+        <v>46167.55754895833</v>
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46167.57717400463</v>
+        <v>46167.7438406713</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>230</v>
@@ -14597,11 +14597,11 @@
         <v>480</v>
       </c>
       <c r="B228" s="5">
-        <v>46167.472371041666</v>
+        <v>46167.63903770833</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46167.57717127315</v>
+        <v>46167.743837939815</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>230</v>
@@ -14650,11 +14650,11 @@
         <v>481</v>
       </c>
       <c r="B229" s="9">
-        <v>46167.47238265046</v>
+        <v>46167.639049317135</v>
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46167.57716853009</v>
+        <v>46167.74383519676</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>230</v>
@@ -14703,11 +14703,11 @@
         <v>482</v>
       </c>
       <c r="B230" s="5">
-        <v>46167.472505451384</v>
+        <v>46167.639172118055</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46167.57716576389</v>
+        <v>46167.743832430555</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>462</v>
@@ -14756,11 +14756,11 @@
         <v>483</v>
       </c>
       <c r="B231" s="9">
-        <v>46167.472514803245</v>
+        <v>46167.63918146991</v>
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46167.577162905094</v>
+        <v>46167.74382957176</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>462</v>
@@ -14809,11 +14809,11 @@
         <v>484</v>
       </c>
       <c r="B232" s="5">
-        <v>46167.472554583335</v>
+        <v>46167.63922125</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46167.57715972222</v>
+        <v>46167.74382638889</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>63</v>
@@ -14862,11 +14862,11 @@
         <v>485</v>
       </c>
       <c r="B233" s="9">
-        <v>46167.47256563658</v>
+        <v>46167.63923230324</v>
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46167.57715695602</v>
+        <v>46167.74382362269</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>63</v>
@@ -14915,11 +14915,11 @@
         <v>486</v>
       </c>
       <c r="B234" s="5">
-        <v>46167.47257383102</v>
+        <v>46167.63924049769</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46167.5771475463</v>
+        <v>46167.74381421296</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>63</v>
@@ -14968,11 +14968,11 @@
         <v>487</v>
       </c>
       <c r="B235" s="9">
-        <v>46167.47258282408</v>
+        <v>46167.63924949074</v>
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46167.577146400465</v>
+        <v>46167.74381306713</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>63</v>
@@ -15021,11 +15021,11 @@
         <v>488</v>
       </c>
       <c r="B236" s="5">
-        <v>46167.472592708335</v>
+        <v>46167.639259375</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46167.57714168981</v>
+        <v>46167.74380835648</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>63</v>
@@ -15074,11 +15074,11 @@
         <v>489</v>
       </c>
       <c r="B237" s="9">
-        <v>46167.47260137732</v>
+        <v>46167.63926804398</v>
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46167.57714060185</v>
+        <v>46167.74380726852</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>63</v>
@@ -15127,11 +15127,11 @@
         <v>490</v>
       </c>
       <c r="B238" s="5">
-        <v>46167.472688657406</v>
+        <v>46167.63935532408</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46167.57713988426</v>
+        <v>46167.74380655093</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>471</v>
@@ -15180,11 +15180,11 @@
         <v>491</v>
       </c>
       <c r="B239" s="9">
-        <v>46167.47270023148</v>
+        <v>46167.63936689815</v>
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46167.57713924769</v>
+        <v>46167.74380591435</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>471</v>
@@ -15233,11 +15233,11 @@
         <v>492</v>
       </c>
       <c r="B240" s="5">
-        <v>46167.390885995366</v>
+        <v>46167.55755266204</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46167.568322962965</v>
+        <v>46167.73498962963</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>493</v>
@@ -15280,11 +15280,11 @@
         <v>495</v>
       </c>
       <c r="B241" s="9">
-        <v>46167.39088918982</v>
+        <v>46167.55755585648</v>
       </c>
       <c r="C241" s="10"/>
       <c r="D241" s="9">
-        <v>46167.57719876157</v>
+        <v>46167.743865428245</v>
       </c>
       <c r="E241" s="10" t="s">
         <v>496</v>
@@ -15343,11 +15343,11 @@
         <v>499</v>
       </c>
       <c r="B242" s="5">
-        <v>46167.39089385417</v>
+        <v>46167.55756052083</v>
       </c>
       <c r="C242" s="6"/>
       <c r="D242" s="5">
-        <v>46167.577231689815</v>
+        <v>46167.74389835648</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>500</v>
@@ -15406,11 +15406,11 @@
         <v>502</v>
       </c>
       <c r="B243" s="9">
-        <v>46167.39089962963</v>
+        <v>46167.557566296295</v>
       </c>
       <c r="C243" s="10"/>
       <c r="D243" s="9">
-        <v>46167.56879575232</v>
+        <v>46167.73546241898</v>
       </c>
       <c r="E243" s="10" t="s">
         <v>503</v>
@@ -15459,11 +15459,11 @@
         <v>505</v>
       </c>
       <c r="B244" s="5">
-        <v>46167.390903217594</v>
+        <v>46167.55756988426</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="5">
-        <v>46167.57729284722</v>
+        <v>46167.743959513886</v>
       </c>
       <c r="E244" s="6" t="s">
         <v>506</v>
@@ -15522,11 +15522,11 @@
         <v>508</v>
       </c>
       <c r="B245" s="9">
-        <v>46167.390908229165</v>
+        <v>46167.557574895836</v>
       </c>
       <c r="C245" s="10"/>
       <c r="D245" s="9">
-        <v>46167.57728997685</v>
+        <v>46167.74395664352</v>
       </c>
       <c r="E245" s="10" t="s">
         <v>509</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.70800572917</v>
+        <v>46188.171251168984</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>219</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.171251168984</v>
+        <v>46189.204083819444</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>219</v>
@@ -5745,8 +5745,8 @@
       <c r="R64" s="5">
         <v>46188</v>
       </c>
-      <c r="S64" s="11" t="s">
-        <v>112</v>
+      <c r="S64" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46184.70841547454</v>
+        <v>46189.169622650465</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>110</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="488">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46189.87503737268</v>
+        <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>193</v>
@@ -5252,9 +5252,7 @@
       <c r="R57" s="10"/>
       <c r="S57" s="10"/>
       <c r="T57" s="10"/>
-      <c r="U57" s="11" t="s">
-        <v>54</v>
-      </c>
+      <c r="U57" s="10"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -7990,7 +7988,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46189.879227303245</v>
+        <v>46189.891457164355</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>128</v>
@@ -8040,8 +8038,8 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="11" t="s">
-        <v>54</v>
+      <c r="U107" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -5395,7 +5395,7 @@
         <v>46189.87508320602</v>
       </c>
       <c r="D60" s="5">
-        <v>46189.87509991898</v>
+        <v>46190.1997147338</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>105</v>
@@ -5439,8 +5439,8 @@
       <c r="R60" s="5">
         <v>46189</v>
       </c>
-      <c r="S60" s="11" t="s">
-        <v>107</v>
+      <c r="S60" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="488">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.872632557875</v>
+        <v>46190.641156666665</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>90</v>
@@ -3525,9 +3525,11 @@
       <c r="B28" s="5">
         <v>46167.55682586806</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46190.64114762731</v>
+      </c>
       <c r="D28" s="5">
-        <v>46183.87119947917</v>
+        <v>46190.641165381945</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>98</v>
@@ -3575,10 +3577,10 @@
         <v>33</v>
       </c>
       <c r="T28" s="6">
-        <v>0</v>
-      </c>
-      <c r="U28" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U28" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3903,9 +3905,11 @@
       <c r="B34" s="5">
         <v>46189.87339945602</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46190.64358769676</v>
+      </c>
       <c r="D34" s="5">
-        <v>46189.876154247686</v>
+        <v>46190.643601261574</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>121</v>
@@ -3940,8 +3944,12 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
+      <c r="T34" s="6">
+        <v>1</v>
+      </c>
+      <c r="U34" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
@@ -3950,9 +3958,11 @@
       <c r="B35" s="9">
         <v>46189.874116527775</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46190.643571747685</v>
+      </c>
       <c r="D35" s="9">
-        <v>46189.87818366898</v>
+        <v>46190.64358837963</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>123</v>
@@ -4000,10 +4010,10 @@
         <v>125</v>
       </c>
       <c r="T35" s="10">
-        <v>0</v>
-      </c>
-      <c r="U35" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4013,9 +4023,11 @@
       <c r="B36" s="5">
         <v>46189.87428425926</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46190.643442395834</v>
+      </c>
       <c r="D36" s="5">
-        <v>46189.87922747685</v>
+        <v>46190.643529444445</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>127</v>
@@ -4063,10 +4075,10 @@
         <v>125</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4188,7 +4200,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.8780819213</v>
+        <v>46190.64115600694</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>138</v>
@@ -7988,7 +8000,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46189.891457164355</v>
+        <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>128</v>
@@ -8038,8 +8050,8 @@
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="12" t="s">
-        <v>61</v>
+      <c r="U107" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -3592,7 +3592,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46189.87512261574</v>
+        <v>46191.169550266204</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>102</v>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46189.87512283565</v>
+        <v>46191.169552928244</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>109</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46189.87512273148</v>
+        <v>46191.169554444445</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>112</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46189.87512292824</v>
+        <v>46191.169555925924</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="487">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -372,7 +372,7 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser  ot 4328 - 4330</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>1215103776642061</t>
@@ -424,9 +424,6 @@
   </si>
   <si>
     <t>Recepcion motor ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>Alta</t>
   </si>
   <si>
     <t>1215768600270741</t>
@@ -3592,7 +3589,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46191.169550266204</v>
+        <v>46192.18633622685</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>102</v>
@@ -3636,7 +3633,7 @@
       <c r="R29" s="9">
         <v>46191</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="S29" s="12" t="s">
         <v>107</v>
       </c>
       <c r="T29" s="10">
@@ -3655,7 +3652,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46191.169552928244</v>
+        <v>46192.186336643514</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>109</v>
@@ -3699,7 +3696,7 @@
       <c r="R30" s="5">
         <v>46191</v>
       </c>
-      <c r="S30" s="11" t="s">
+      <c r="S30" s="12" t="s">
         <v>107</v>
       </c>
       <c r="T30" s="6">
@@ -3718,7 +3715,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46191.169554444445</v>
+        <v>46192.18633769676</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>112</v>
@@ -3762,7 +3759,7 @@
       <c r="R31" s="9">
         <v>46191</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="S31" s="12" t="s">
         <v>107</v>
       </c>
       <c r="T31" s="10">
@@ -3781,7 +3778,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46191.169555925924</v>
+        <v>46192.18633627315</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>
@@ -3825,7 +3822,7 @@
       <c r="R32" s="5">
         <v>46191</v>
       </c>
-      <c r="S32" s="11" t="s">
+      <c r="S32" s="12" t="s">
         <v>107</v>
       </c>
       <c r="T32" s="6">
@@ -4007,7 +4004,7 @@
         <v>46167</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -4018,7 +4015,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B36" s="5">
         <v>46189.87428425926</v>
@@ -4030,7 +4027,7 @@
         <v>46190.643529444445</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -4063,7 +4060,7 @@
         <v>95</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q36" s="5">
         <v>46160</v>
@@ -4072,7 +4069,7 @@
         <v>46167</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4083,7 +4080,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B37" s="9">
         <v>46167.556641689815</v>
@@ -4093,7 +4090,7 @@
         <v>46189.87936171296</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>25</v>
@@ -4117,7 +4114,7 @@
         <v>26</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4130,7 +4127,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B38" s="5">
         <v>46167.55686952546</v>
@@ -4140,16 +4137,16 @@
         <v>46184.197559872686</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46160</v>
@@ -4167,13 +4164,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q38" s="5">
         <v>46160</v>
@@ -4182,7 +4179,7 @@
         <v>46183</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -4193,7 +4190,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B39" s="9">
         <v>46167.556874270835</v>
@@ -4203,16 +4200,16 @@
         <v>46190.64115600694</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I39" s="9">
         <v>46160</v>
@@ -4230,13 +4227,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>98</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4252,7 +4249,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B40" s="5">
         <v>46167.55687946759</v>
@@ -4262,16 +4259,16 @@
         <v>46183.17042041667</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I40" s="5">
         <v>46162</v>
@@ -4289,13 +4286,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4311,7 +4308,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B41" s="9">
         <v>46167.55696103009</v>
@@ -4321,16 +4318,16 @@
         <v>46169.87894268519</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I41" s="9">
         <v>46160</v>
@@ -4348,10 +4345,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4374,7 +4371,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="5">
         <v>46167.556965254626</v>
@@ -4390,10 +4387,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I42" s="5">
         <v>46161</v>
@@ -4411,13 +4408,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4427,7 +4424,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B43" s="9">
         <v>46167.55696965278</v>
@@ -4437,16 +4434,16 @@
         <v>46169.87902826389</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I43" s="9">
         <v>46171</v>
@@ -4464,13 +4461,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>119</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4480,7 +4477,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B44" s="5">
         <v>46167.556973784725</v>
@@ -4490,16 +4487,16 @@
         <v>46169.87795083333</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46192</v>
@@ -4517,13 +4514,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q44" s="5">
         <v>46192</v>
@@ -4543,7 +4540,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B45" s="9">
         <v>46167.556978611115</v>
@@ -4553,16 +4550,16 @@
         <v>46169.87831584491</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I45" s="9">
         <v>46192</v>
@@ -4580,13 +4577,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4602,7 +4599,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B46" s="5">
         <v>46167.55698368055</v>
@@ -4612,16 +4609,16 @@
         <v>46169.878329687504</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46196</v>
@@ -4639,13 +4636,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4661,7 +4658,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B47" s="9">
         <v>46167.556988842596</v>
@@ -4671,16 +4668,16 @@
         <v>46169.87796042824</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I47" s="9">
         <v>46192</v>
@@ -4698,10 +4695,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4724,7 +4721,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
         <v>46167.556992708334</v>
@@ -4740,10 +4737,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I48" s="5">
         <v>46192</v>
@@ -4761,13 +4758,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4777,7 +4774,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B49" s="9">
         <v>46167.5569971875</v>
@@ -4787,16 +4784,16 @@
         <v>46169.87837792824</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I49" s="9">
         <v>46196</v>
@@ -4814,13 +4811,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>110</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4830,7 +4827,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5">
         <v>46167.55700140046</v>
@@ -4840,16 +4837,16 @@
         <v>46169.87797747685</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4867,10 +4864,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4893,7 +4890,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B51" s="9">
         <v>46167.55700519676</v>
@@ -4909,10 +4906,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -4930,13 +4927,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4946,7 +4943,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B52" s="5">
         <v>46167.557010034725</v>
@@ -4956,16 +4953,16 @@
         <v>46169.878430219906</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -4983,13 +4980,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>116</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4999,7 +4996,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
         <v>46167.55701476852</v>
@@ -5009,16 +5006,16 @@
         <v>46169.87844947916</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5036,10 +5033,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5052,7 +5049,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" s="5">
         <v>46167.55701769676</v>
@@ -5062,16 +5059,16 @@
         <v>46169.87799084491</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I54" s="5">
         <v>46192</v>
@@ -5089,10 +5086,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5115,7 +5112,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46167.557021678236</v>
@@ -5131,10 +5128,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I55" s="9">
         <v>46192</v>
@@ -5152,13 +5149,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5168,7 +5165,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B56" s="5">
         <v>46167.55702634259</v>
@@ -5178,16 +5175,16 @@
         <v>46169.87850571759</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I56" s="5">
         <v>46196</v>
@@ -5205,13 +5202,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5221,7 +5218,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B57" s="9">
         <v>46167.55703671296</v>
@@ -5231,7 +5228,7 @@
         <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5255,7 +5252,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5268,7 +5265,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46167.557040520835</v>
@@ -5280,16 +5277,16 @@
         <v>46184.51717821759</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="H58" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5307,13 +5304,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5322,7 +5319,7 @@
         <v>46168</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5333,7 +5330,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46167.557045856476</v>
@@ -5345,16 +5342,16 @@
         <v>46189.875034826386</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5372,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5387,7 +5384,7 @@
         <v>46188</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5398,7 +5395,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46167.5570519676</v>
@@ -5416,10 +5413,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5437,13 +5434,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5452,7 +5449,7 @@
         <v>46189</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5463,7 +5460,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
@@ -5473,16 +5470,16 @@
         <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5500,10 +5497,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5526,7 +5523,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5536,16 +5533,16 @@
         <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5563,13 +5560,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5579,7 +5576,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5589,16 +5586,16 @@
         <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5616,13 +5613,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5632,7 +5629,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5642,16 +5639,16 @@
         <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5669,13 +5666,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5685,7 +5682,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5695,16 +5692,16 @@
         <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5722,13 +5719,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5738,7 +5735,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5748,16 +5745,16 @@
         <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5775,13 +5772,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5791,7 +5788,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5801,16 +5798,16 @@
         <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5828,13 +5825,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5844,7 +5841,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5854,16 +5851,16 @@
         <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5881,13 +5878,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5897,7 +5894,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5907,16 +5904,16 @@
         <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -5934,13 +5931,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5950,7 +5947,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -5960,7 +5957,7 @@
         <v>46167.629188032406</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5984,7 +5981,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5997,7 +5994,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6007,16 +6004,16 @@
         <v>46167.74094020833</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="H71" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6034,13 +6031,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6060,7 +6057,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6070,16 +6067,16 @@
         <v>46167.7410212963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6097,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6123,7 +6120,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6133,16 +6130,16 @@
         <v>46167.74093746528</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6160,13 +6157,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6186,7 +6183,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6196,16 +6193,16 @@
         <v>46167.74101869213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6223,13 +6220,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6249,7 +6246,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6259,16 +6256,16 @@
         <v>46167.740934733796</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6286,13 +6283,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6312,7 +6309,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6322,16 +6319,16 @@
         <v>46167.74101563657</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6349,13 +6346,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6375,7 +6372,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6385,7 +6382,7 @@
         <v>46167.71426503472</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6409,7 +6406,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6422,7 +6419,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6432,16 +6429,16 @@
         <v>46167.74125046296</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6459,13 +6456,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6485,7 +6482,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46167.557178229166</v>
@@ -6495,16 +6492,16 @@
         <v>46167.741239525465</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6522,13 +6519,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>253</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>254</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6538,7 +6535,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46167.55718505787</v>
@@ -6548,16 +6545,16 @@
         <v>46167.74123664352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6575,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6591,7 +6588,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B81" s="9">
         <v>46167.629964050924</v>
@@ -6601,16 +6598,16 @@
         <v>46167.74123373843</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6628,13 +6625,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6644,7 +6641,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46167.6299746875</v>
@@ -6654,16 +6651,16 @@
         <v>46167.74123071759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6681,13 +6678,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6697,7 +6694,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B83" s="9">
         <v>46167.63011578703</v>
@@ -6707,16 +6704,16 @@
         <v>46167.74122805556</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6734,13 +6731,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6750,7 +6747,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46167.630126516204</v>
@@ -6760,16 +6757,16 @@
         <v>46167.74122546296</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6787,13 +6784,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6803,7 +6800,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
         <v>46167.63145555556</v>
@@ -6813,16 +6810,16 @@
         <v>46167.74121943287</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6840,13 +6837,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6856,7 +6853,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
         <v>46167.631772685185</v>
@@ -6866,16 +6863,16 @@
         <v>46167.74121879629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -6893,13 +6890,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6909,7 +6906,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B87" s="9">
         <v>46167.557190844906</v>
@@ -6919,16 +6916,16 @@
         <v>46167.74138710648</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -6946,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -6972,7 +6969,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B88" s="5">
         <v>46167.557195092595</v>
@@ -6982,16 +6979,16 @@
         <v>46189.87510653935</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7009,13 +7006,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7025,7 +7022,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B89" s="9">
         <v>46167.557200995376</v>
@@ -7035,16 +7032,16 @@
         <v>46189.87510706019</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7062,13 +7059,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>268</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7078,7 +7075,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B90" s="5">
         <v>46167.63214916667</v>
@@ -7088,16 +7085,16 @@
         <v>46167.741366435184</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7115,13 +7112,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7131,7 +7128,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B91" s="9">
         <v>46167.63219107639</v>
@@ -7141,16 +7138,16 @@
         <v>46167.741363622685</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7168,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7184,7 +7181,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B92" s="5">
         <v>46167.63220099537</v>
@@ -7194,16 +7191,16 @@
         <v>46167.741361215274</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7221,13 +7218,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7237,7 +7234,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B93" s="9">
         <v>46167.63220839121</v>
@@ -7247,16 +7244,16 @@
         <v>46167.74135855324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7274,13 +7271,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7290,7 +7287,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B94" s="5">
         <v>46167.63225591435</v>
@@ -7300,16 +7297,16 @@
         <v>46167.74135295139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7327,13 +7324,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7343,7 +7340,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B95" s="9">
         <v>46167.63226373843</v>
@@ -7353,16 +7350,16 @@
         <v>46167.74135225694</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7380,13 +7377,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7396,7 +7393,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B96" s="5">
         <v>46167.5572065625</v>
@@ -7406,16 +7403,16 @@
         <v>46167.74153292824</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7433,13 +7430,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7459,7 +7456,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B97" s="9">
         <v>46167.557210914354</v>
@@ -7469,16 +7466,16 @@
         <v>46189.87509809028</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7496,13 +7493,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7512,7 +7509,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B98" s="5">
         <v>46167.55721697917</v>
@@ -7522,16 +7519,16 @@
         <v>46189.87509940972</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7549,13 +7546,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7565,7 +7562,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B99" s="9">
         <v>46167.632342048615</v>
@@ -7575,16 +7572,16 @@
         <v>46167.74151755787</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7602,10 +7599,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7618,7 +7615,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B100" s="5">
         <v>46167.63235868055</v>
@@ -7628,16 +7625,16 @@
         <v>46167.74151503472</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7655,13 +7652,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7671,7 +7668,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B101" s="9">
         <v>46167.63236590278</v>
@@ -7681,16 +7678,16 @@
         <v>46167.74151262731</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7708,13 +7705,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7724,7 +7721,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B102" s="5">
         <v>46167.63237413194</v>
@@ -7734,16 +7731,16 @@
         <v>46167.7415103588</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7761,13 +7758,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7777,7 +7774,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B103" s="9">
         <v>46167.63244320602</v>
@@ -7787,16 +7784,16 @@
         <v>46167.74150512731</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7814,13 +7811,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7830,7 +7827,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B104" s="5">
         <v>46167.63245268518</v>
@@ -7840,16 +7837,16 @@
         <v>46167.74150447917</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -7867,13 +7864,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7883,7 +7880,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46167.55722248842</v>
@@ -7893,7 +7890,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -7917,7 +7914,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -7930,7 +7927,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B106" s="5">
         <v>46167.557225682875</v>
@@ -7940,16 +7937,16 @@
         <v>46185.18299439814</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -7967,13 +7964,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q106" s="5">
         <v>46184</v>
@@ -7982,7 +7979,7 @@
         <v>46184</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -7993,7 +7990,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B107" s="9">
         <v>46167.557231493054</v>
@@ -8003,16 +8000,16 @@
         <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8030,13 +8027,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8045,7 +8042,7 @@
         <v>46167</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
@@ -8056,7 +8053,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B108" s="5">
         <v>46167.55723746528</v>
@@ -8072,10 +8069,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8093,13 +8090,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q108" s="5">
         <v>46168</v>
@@ -8119,7 +8116,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B109" s="9">
         <v>46167.55724847222</v>
@@ -8129,16 +8126,16 @@
         <v>46167.74163924769</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8156,13 +8153,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q109" s="9">
         <v>46265</v>
@@ -8182,7 +8179,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B110" s="5">
         <v>46167.55725353009</v>
@@ -8198,10 +8195,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8219,13 +8216,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q110" s="5">
         <v>46220</v>
@@ -8245,7 +8242,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B111" s="9">
         <v>46167.5572591088</v>
@@ -8255,7 +8252,7 @@
         <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8279,7 +8276,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8292,7 +8289,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B112" s="5">
         <v>46167.557262685186</v>
@@ -8302,7 +8299,7 @@
         <v>46167.741924999995</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8329,13 +8326,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q112" s="5">
         <v>46224</v>
@@ -8355,7 +8352,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B113" s="9">
         <v>46167.55727085649</v>
@@ -8365,7 +8362,7 @@
         <v>46167.74190891204</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8392,10 +8389,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8408,7 +8405,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B114" s="5">
         <v>46167.55727532407</v>
@@ -8418,7 +8415,7 @@
         <v>46167.74190642362</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8445,10 +8442,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8461,7 +8458,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B115" s="9">
         <v>46167.632606053245</v>
@@ -8471,7 +8468,7 @@
         <v>46167.7419037037</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8498,13 +8495,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8514,7 +8511,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B116" s="5">
         <v>46167.63261443287</v>
@@ -8524,7 +8521,7 @@
         <v>46167.74190121528</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8551,13 +8548,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8567,7 +8564,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B117" s="9">
         <v>46167.63262241898</v>
@@ -8577,7 +8574,7 @@
         <v>46167.74189892361</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8604,13 +8601,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8620,7 +8617,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B118" s="5">
         <v>46167.63263039352</v>
@@ -8630,7 +8627,7 @@
         <v>46167.74189655093</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8657,13 +8654,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8673,7 +8670,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B119" s="9">
         <v>46167.63269008102</v>
@@ -8683,7 +8680,7 @@
         <v>46167.74189145833</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8710,13 +8707,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8726,7 +8723,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B120" s="5">
         <v>46167.632698738424</v>
@@ -8736,7 +8733,7 @@
         <v>46167.74189078704</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8763,13 +8760,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8779,7 +8776,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B121" s="9">
         <v>46167.55727960648</v>
@@ -8789,7 +8786,7 @@
         <v>46167.74207511574</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8816,13 +8813,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q121" s="9">
         <v>46231</v>
@@ -8842,7 +8839,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B122" s="5">
         <v>46167.557284375</v>
@@ -8852,7 +8849,7 @@
         <v>46189.87510767361</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8879,13 +8876,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O122" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="P122" s="6" t="s">
         <v>318</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>319</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8895,7 +8892,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B123" s="9">
         <v>46167.55729009259</v>
@@ -8905,7 +8902,7 @@
         <v>46189.87510009259</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8932,13 +8929,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O123" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="P123" s="10" t="s">
         <v>318</v>
-      </c>
-      <c r="P123" s="10" t="s">
-        <v>319</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8948,7 +8945,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B124" s="5">
         <v>46167.6328130787</v>
@@ -8958,7 +8955,7 @@
         <v>46189.87508946759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8985,13 +8982,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9001,7 +8998,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B125" s="9">
         <v>46167.63283585648</v>
@@ -9011,7 +9008,7 @@
         <v>46189.87509015047</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9038,13 +9035,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9054,7 +9051,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B126" s="5">
         <v>46167.63284336806</v>
@@ -9064,7 +9061,7 @@
         <v>46189.87509105324</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9091,13 +9088,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9107,7 +9104,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B127" s="9">
         <v>46167.63285163195</v>
@@ -9117,7 +9114,7 @@
         <v>46189.87509177084</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9144,13 +9141,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9160,7 +9157,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B128" s="5">
         <v>46167.63289178241</v>
@@ -9170,7 +9167,7 @@
         <v>46189.87509244213</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9197,13 +9194,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9213,7 +9210,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B129" s="9">
         <v>46167.632899212964</v>
@@ -9223,7 +9220,7 @@
         <v>46189.8750930324</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9250,13 +9247,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9266,7 +9263,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B130" s="5">
         <v>46167.55733736111</v>
@@ -9276,7 +9273,7 @@
         <v>46167.74221776621</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9303,13 +9300,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q130" s="5">
         <v>46232</v>
@@ -9329,7 +9326,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B131" s="9">
         <v>46167.557343645836</v>
@@ -9339,7 +9336,7 @@
         <v>46189.87510797454</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9364,13 +9361,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O131" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="P131" s="10" t="s">
         <v>333</v>
-      </c>
-      <c r="P131" s="10" t="s">
-        <v>334</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9380,7 +9377,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B132" s="5">
         <v>46167.55735079861</v>
@@ -9390,7 +9387,7 @@
         <v>46189.87510071759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9415,13 +9412,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>334</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9431,7 +9428,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B133" s="9">
         <v>46167.63302359954</v>
@@ -9441,7 +9438,7 @@
         <v>46189.875093634255</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9466,13 +9463,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9482,7 +9479,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B134" s="5">
         <v>46167.63303486111</v>
@@ -9492,7 +9489,7 @@
         <v>46189.8750941551</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9517,13 +9514,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9533,7 +9530,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B135" s="9">
         <v>46167.633050648146</v>
@@ -9543,7 +9540,7 @@
         <v>46189.87509472222</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9568,13 +9565,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9584,7 +9581,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B136" s="5">
         <v>46167.633060671295</v>
@@ -9594,7 +9591,7 @@
         <v>46189.87509519676</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9619,13 +9616,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9635,7 +9632,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B137" s="9">
         <v>46167.633115185185</v>
@@ -9645,7 +9642,7 @@
         <v>46189.87509570602</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9670,13 +9667,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9686,7 +9683,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B138" s="5">
         <v>46167.6331228125</v>
@@ -9696,7 +9693,7 @@
         <v>46189.87509615741</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9721,13 +9718,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9737,7 +9734,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B139" s="9">
         <v>46167.557357488426</v>
@@ -9747,7 +9744,7 @@
         <v>46167.74236513889</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9774,13 +9771,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q139" s="9">
         <v>46233</v>
@@ -9800,7 +9797,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B140" s="5">
         <v>46167.55736211805</v>
@@ -9810,7 +9807,7 @@
         <v>46189.877459745374</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9837,13 +9834,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O140" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="P140" s="6" t="s">
         <v>347</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>348</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9853,7 +9850,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B141" s="9">
         <v>46167.55737267361</v>
@@ -9863,7 +9860,7 @@
         <v>46189.87746077546</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9890,13 +9887,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O141" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="P141" s="10" t="s">
         <v>347</v>
-      </c>
-      <c r="P141" s="10" t="s">
-        <v>348</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9906,7 +9903,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B142" s="5">
         <v>46167.63325159722</v>
@@ -9916,7 +9913,7 @@
         <v>46189.877455671296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9943,13 +9940,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9959,7 +9956,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B143" s="9">
         <v>46167.63325929398</v>
@@ -9969,7 +9966,7 @@
         <v>46189.87745677083</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9996,13 +9993,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10012,7 +10009,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B144" s="5">
         <v>46167.633274293985</v>
@@ -10022,7 +10019,7 @@
         <v>46189.87745732639</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10049,13 +10046,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10065,7 +10062,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B145" s="9">
         <v>46167.633281875</v>
@@ -10075,7 +10072,7 @@
         <v>46189.877457916664</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10102,13 +10099,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10118,7 +10115,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B146" s="5">
         <v>46167.63332260417</v>
@@ -10128,7 +10125,7 @@
         <v>46189.87745863426</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10155,13 +10152,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10171,7 +10168,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B147" s="9">
         <v>46167.633331689816</v>
@@ -10181,7 +10178,7 @@
         <v>46189.87745917824</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10208,13 +10205,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10224,7 +10221,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B148" s="5">
         <v>46167.557378287034</v>
@@ -10234,7 +10231,7 @@
         <v>46167.742498472224</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10261,13 +10258,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q148" s="5">
         <v>46234</v>
@@ -10287,7 +10284,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B149" s="9">
         <v>46167.55738292824</v>
@@ -10297,7 +10294,7 @@
         <v>46167.742493136575</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10324,13 +10321,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10340,7 +10337,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B150" s="5">
         <v>46167.5573883912</v>
@@ -10350,7 +10347,7 @@
         <v>46167.742490000004</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10377,13 +10374,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10393,7 +10390,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B151" s="9">
         <v>46167.63341660879</v>
@@ -10403,7 +10400,7 @@
         <v>46167.74248716435</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10430,13 +10427,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10446,7 +10443,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B152" s="5">
         <v>46167.63343371528</v>
@@ -10456,7 +10453,7 @@
         <v>46167.74248396991</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10483,13 +10480,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10499,7 +10496,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B153" s="9">
         <v>46167.63344365741</v>
@@ -10509,7 +10506,7 @@
         <v>46167.742481134264</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10536,13 +10533,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10552,7 +10549,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B154" s="5">
         <v>46167.63345188658</v>
@@ -10562,7 +10559,7 @@
         <v>46167.74247835648</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10589,13 +10586,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10605,7 +10602,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B155" s="9">
         <v>46167.633506412036</v>
@@ -10615,7 +10612,7 @@
         <v>46167.74247142361</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10642,13 +10639,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10658,7 +10655,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B156" s="5">
         <v>46167.63351399306</v>
@@ -10668,7 +10665,7 @@
         <v>46167.74247065972</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10695,13 +10692,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10711,7 +10708,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B157" s="9">
         <v>46167.55739407407</v>
@@ -10721,7 +10718,7 @@
         <v>46167.74264841435</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10748,13 +10745,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q157" s="9">
         <v>46238</v>
@@ -10774,7 +10771,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B158" s="5">
         <v>46167.55739920139</v>
@@ -10784,7 +10781,7 @@
         <v>46167.742638298616</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10811,13 +10808,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10827,7 +10824,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B159" s="9">
         <v>46167.5574040162</v>
@@ -10837,7 +10834,7 @@
         <v>46167.74263541667</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10864,13 +10861,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10880,7 +10877,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B160" s="5">
         <v>46167.633843206015</v>
@@ -10890,7 +10887,7 @@
         <v>46167.742632037036</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10917,13 +10914,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10933,7 +10930,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B161" s="9">
         <v>46167.633849895836</v>
@@ -10943,7 +10940,7 @@
         <v>46167.742628935186</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10970,13 +10967,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10986,7 +10983,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B162" s="5">
         <v>46167.63385791666</v>
@@ -10996,7 +10993,7 @@
         <v>46167.74262635417</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11023,13 +11020,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11039,7 +11036,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B163" s="9">
         <v>46167.633867083336</v>
@@ -11049,7 +11046,7 @@
         <v>46167.74262355324</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11076,13 +11073,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11092,7 +11089,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B164" s="5">
         <v>46167.63391234954</v>
@@ -11102,7 +11099,7 @@
         <v>46167.742617407406</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11129,13 +11126,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11145,7 +11142,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B165" s="9">
         <v>46167.63392017361</v>
@@ -11155,7 +11152,7 @@
         <v>46167.74261677083</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11182,13 +11179,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11198,7 +11195,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B166" s="5">
         <v>46167.557409201385</v>
@@ -11208,7 +11205,7 @@
         <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -11232,7 +11229,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11245,7 +11242,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B167" s="9">
         <v>46167.5574132176</v>
@@ -11255,16 +11252,16 @@
         <v>46167.74284238426</v>
       </c>
       <c r="E167" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G167" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="F167" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G167" s="10" t="s">
+      <c r="H167" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I167" s="9">
         <v>46230</v>
@@ -11282,13 +11279,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q167" s="9">
         <v>46230</v>
@@ -11308,7 +11305,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B168" s="5">
         <v>46167.55742054398</v>
@@ -11318,16 +11315,16 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H168" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I168" s="5">
         <v>46239</v>
@@ -11345,13 +11342,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11361,7 +11358,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B169" s="9">
         <v>46167.557425520834</v>
@@ -11371,16 +11368,16 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H169" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I169" s="9">
         <v>46239</v>
@@ -11398,13 +11395,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11414,7 +11411,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B170" s="5">
         <v>46167.55743020833</v>
@@ -11424,16 +11421,16 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H170" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I170" s="5">
         <v>46239</v>
@@ -11451,13 +11448,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11467,7 +11464,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B171" s="9">
         <v>46167.557434918985</v>
@@ -11477,16 +11474,16 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H171" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I171" s="9">
         <v>46239</v>
@@ -11504,13 +11501,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11520,7 +11517,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B172" s="5">
         <v>46167.636403032404</v>
@@ -11530,16 +11527,16 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H172" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H172" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I172" s="5">
         <v>46239</v>
@@ -11557,13 +11554,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11573,7 +11570,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B173" s="9">
         <v>46167.63641173611</v>
@@ -11583,16 +11580,16 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H173" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I173" s="9">
         <v>46239</v>
@@ -11610,13 +11607,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11626,7 +11623,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B174" s="5">
         <v>46167.636428645834</v>
@@ -11636,16 +11633,16 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H174" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H174" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I174" s="5">
         <v>46239</v>
@@ -11663,13 +11660,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11679,7 +11676,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B175" s="9">
         <v>46167.636439849535</v>
@@ -11689,16 +11686,16 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H175" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I175" s="9">
         <v>46239</v>
@@ -11716,13 +11713,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11732,7 +11729,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B176" s="5">
         <v>46167.636677511575</v>
@@ -11748,10 +11745,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H176" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H176" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I176" s="5">
         <v>46230</v>
@@ -11769,7 +11766,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>63</v>
@@ -11785,7 +11782,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B177" s="9">
         <v>46167.63669306713</v>
@@ -11801,10 +11798,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H177" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H177" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I177" s="9">
         <v>46230</v>
@@ -11822,7 +11819,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>63</v>
@@ -11838,7 +11835,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B178" s="5">
         <v>46167.6367015162</v>
@@ -11854,10 +11851,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I178" s="5">
         <v>46230</v>
@@ -11875,7 +11872,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>63</v>
@@ -11891,7 +11888,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B179" s="9">
         <v>46167.6367112963</v>
@@ -11907,10 +11904,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H179" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H179" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I179" s="9">
         <v>46230</v>
@@ -11928,7 +11925,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>63</v>
@@ -11944,7 +11941,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B180" s="5">
         <v>46167.63672008102</v>
@@ -11960,10 +11957,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I180" s="5">
         <v>46230</v>
@@ -11981,7 +11978,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>63</v>
@@ -11997,7 +11994,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B181" s="9">
         <v>46167.636729247686</v>
@@ -12013,10 +12010,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H181" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H181" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I181" s="9">
         <v>46230</v>
@@ -12034,7 +12031,7 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O181" s="10" t="s">
         <v>63</v>
@@ -12050,7 +12047,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B182" s="5">
         <v>46167.63683603009</v>
@@ -12066,10 +12063,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H182" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="I182" s="5">
         <v>46230</v>
@@ -12087,7 +12084,7 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>71</v>
@@ -12103,7 +12100,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B183" s="9">
         <v>46167.636846319445</v>
@@ -12119,10 +12116,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="H183" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="H183" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="I183" s="9">
         <v>46230</v>
@@ -12140,7 +12137,7 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>71</v>
@@ -12156,7 +12153,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B184" s="5">
         <v>46167.55743945602</v>
@@ -12166,7 +12163,7 @@
         <v>46167.7430450463</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12193,13 +12190,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q184" s="5">
         <v>46231</v>
@@ -12219,7 +12216,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B185" s="9">
         <v>46167.55744423611</v>
@@ -12229,7 +12226,7 @@
         <v>46167.74306620371</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12254,13 +12251,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12270,7 +12267,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B186" s="5">
         <v>46167.55744884259</v>
@@ -12280,7 +12277,7 @@
         <v>46167.74306335648</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12305,13 +12302,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12321,7 +12318,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B187" s="9">
         <v>46167.55745349537</v>
@@ -12331,7 +12328,7 @@
         <v>46167.74306008102</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12356,13 +12353,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12372,7 +12369,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B188" s="5">
         <v>46167.55745777777</v>
@@ -12382,7 +12379,7 @@
         <v>46167.74305738426</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12407,13 +12404,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12423,7 +12420,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B189" s="9">
         <v>46167.637670833334</v>
@@ -12433,7 +12430,7 @@
         <v>46167.74305466435</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12458,13 +12455,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12474,7 +12471,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B190" s="5">
         <v>46167.63768076389</v>
@@ -12484,7 +12481,7 @@
         <v>46167.743051990736</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12509,13 +12506,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12525,7 +12522,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B191" s="9">
         <v>46167.637724016204</v>
@@ -12535,7 +12532,7 @@
         <v>46167.74304920139</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12560,13 +12557,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12576,7 +12573,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B192" s="5">
         <v>46167.63773231482</v>
@@ -12586,7 +12583,7 @@
         <v>46167.743046574076</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12611,13 +12608,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12627,7 +12624,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B193" s="9">
         <v>46167.63788011574</v>
@@ -12664,7 +12661,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>64</v>
@@ -12680,7 +12677,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B194" s="5">
         <v>46167.637888530095</v>
@@ -12717,7 +12714,7 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O194" s="6" t="s">
         <v>63</v>
@@ -12733,7 +12730,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B195" s="9">
         <v>46167.63789722222</v>
@@ -12770,7 +12767,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O195" s="10" t="s">
         <v>63</v>
@@ -12786,7 +12783,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B196" s="5">
         <v>46167.63790768519</v>
@@ -12823,7 +12820,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
@@ -12839,7 +12836,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B197" s="9">
         <v>46167.63791662037</v>
@@ -12876,7 +12873,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>63</v>
@@ -12892,7 +12889,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B198" s="5">
         <v>46167.637946689814</v>
@@ -12929,7 +12926,7 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
@@ -12945,7 +12942,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B199" s="9">
         <v>46167.637995729165</v>
@@ -12982,7 +12979,7 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>71</v>
@@ -12998,7 +12995,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B200" s="5">
         <v>46167.63800420139</v>
@@ -13035,7 +13032,7 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>71</v>
@@ -13051,7 +13048,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B201" s="9">
         <v>46167.55746224537</v>
@@ -13061,16 +13058,16 @@
         <v>46167.74364532407</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13088,13 +13085,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q201" s="9">
         <v>46241</v>
@@ -13114,7 +13111,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B202" s="5">
         <v>46167.55746689815</v>
@@ -13124,16 +13121,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13151,13 +13148,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13167,7 +13164,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B203" s="9">
         <v>46167.55747543981</v>
@@ -13177,16 +13174,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13204,13 +13201,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13220,7 +13217,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B204" s="5">
         <v>46167.557519270835</v>
@@ -13230,16 +13227,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13257,13 +13254,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13273,7 +13270,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B205" s="9">
         <v>46167.5575253125</v>
@@ -13283,16 +13280,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H205" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13310,13 +13307,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13326,7 +13323,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B206" s="5">
         <v>46167.6385715162</v>
@@ -13336,16 +13333,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13363,13 +13360,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13379,7 +13376,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B207" s="9">
         <v>46167.63857899306</v>
@@ -13389,16 +13386,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13416,13 +13413,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13432,7 +13429,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B208" s="5">
         <v>46167.638659930555</v>
@@ -13442,16 +13439,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13469,13 +13466,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13485,7 +13482,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B209" s="9">
         <v>46167.638666956016</v>
@@ -13495,16 +13492,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13522,13 +13519,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13538,7 +13535,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B210" s="5">
         <v>46167.6387090162</v>
@@ -13554,10 +13551,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13575,7 +13572,7 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>63</v>
@@ -13591,7 +13588,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B211" s="9">
         <v>46167.63871641204</v>
@@ -13607,10 +13604,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H211" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13628,7 +13625,7 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>63</v>
@@ -13644,7 +13641,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B212" s="5">
         <v>46167.638723599535</v>
@@ -13660,10 +13657,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13681,7 +13678,7 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>63</v>
@@ -13697,7 +13694,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B213" s="9">
         <v>46167.63873144676</v>
@@ -13713,10 +13710,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H213" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13734,7 +13731,7 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>63</v>
@@ -13750,7 +13747,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B214" s="5">
         <v>46167.6387405787</v>
@@ -13766,10 +13763,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13787,7 +13784,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>63</v>
@@ -13803,7 +13800,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B215" s="9">
         <v>46167.63874844907</v>
@@ -13819,10 +13816,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H215" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -13840,7 +13837,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>63</v>
@@ -13856,7 +13853,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B216" s="5">
         <v>46167.638756562505</v>
@@ -13872,10 +13869,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -13893,13 +13890,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13909,7 +13906,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B217" s="9">
         <v>46167.63883428241</v>
@@ -13925,10 +13922,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -13946,13 +13943,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13962,7 +13959,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B218" s="5">
         <v>46167.55752998842</v>
@@ -13972,16 +13969,16 @@
         <v>46167.74382108796</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -13999,13 +13996,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q218" s="5">
         <v>46244</v>
@@ -14025,7 +14022,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B219" s="9">
         <v>46167.55753614583</v>
@@ -14035,16 +14032,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H219" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H219" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14062,13 +14059,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14078,7 +14075,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B220" s="5">
         <v>46167.557540381946</v>
@@ -14088,16 +14085,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14115,13 +14112,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14131,7 +14128,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B221" s="9">
         <v>46167.557545069445</v>
@@ -14141,16 +14138,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14168,13 +14165,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14184,7 +14181,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B222" s="5">
         <v>46167.55754895833</v>
@@ -14194,16 +14191,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14221,13 +14218,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14237,7 +14234,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B223" s="9">
         <v>46167.63903770833</v>
@@ -14247,16 +14244,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14274,10 +14271,10 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14290,7 +14287,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B224" s="5">
         <v>46167.639049317135</v>
@@ -14300,16 +14297,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14327,10 +14324,10 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14343,7 +14340,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B225" s="9">
         <v>46167.639172118055</v>
@@ -14353,16 +14350,16 @@
         <v>46167.743832430555</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14380,10 +14377,10 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14396,7 +14393,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B226" s="5">
         <v>46167.63918146991</v>
@@ -14406,16 +14403,16 @@
         <v>46167.74382957176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14433,10 +14430,10 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14449,7 +14446,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B227" s="9">
         <v>46167.63922125</v>
@@ -14465,10 +14462,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14486,7 +14483,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>63</v>
@@ -14502,7 +14499,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B228" s="5">
         <v>46167.63923230324</v>
@@ -14518,10 +14515,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14539,7 +14536,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>63</v>
@@ -14555,7 +14552,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B229" s="9">
         <v>46167.63924049769</v>
@@ -14571,10 +14568,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14592,7 +14589,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>63</v>
@@ -14608,7 +14605,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B230" s="5">
         <v>46167.63924949074</v>
@@ -14624,10 +14621,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14645,7 +14642,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>63</v>
@@ -14661,7 +14658,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B231" s="9">
         <v>46167.639259375</v>
@@ -14677,10 +14674,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H231" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H231" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14698,7 +14695,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>63</v>
@@ -14714,7 +14711,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B232" s="5">
         <v>46167.63926804398</v>
@@ -14730,10 +14727,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H232" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14751,7 +14748,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>63</v>
@@ -14767,7 +14764,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B233" s="9">
         <v>46167.63935532408</v>
@@ -14777,16 +14774,16 @@
         <v>46167.74380655093</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14804,7 +14801,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>71</v>
@@ -14820,7 +14817,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B234" s="5">
         <v>46167.63936689815</v>
@@ -14830,16 +14827,16 @@
         <v>46167.74380591435</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>
@@ -14857,7 +14854,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>71</v>
@@ -14873,7 +14870,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B235" s="9">
         <v>46167.55755266204</v>
@@ -14883,7 +14880,7 @@
         <v>46167.73498962963</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>25</v>
@@ -14907,7 +14904,7 @@
         <v>26</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>26</v>
@@ -14920,7 +14917,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B236" s="5">
         <v>46167.55755585648</v>
@@ -14930,16 +14927,16 @@
         <v>46167.743865428245</v>
       </c>
       <c r="E236" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="F236" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G236" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="F236" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G236" s="6" t="s">
+      <c r="H236" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="H236" s="6" t="s">
-        <v>477</v>
       </c>
       <c r="I236" s="5">
         <v>46245</v>
@@ -14957,13 +14954,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q236" s="5">
         <v>46245</v>
@@ -14983,7 +14980,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B237" s="9">
         <v>46167.55756052083</v>
@@ -14993,7 +14990,7 @@
         <v>46189.872060740745</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15020,13 +15017,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q237" s="9">
         <v>46245</v>
@@ -15046,7 +15043,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B238" s="5">
         <v>46167.557566296295</v>
@@ -15056,7 +15053,7 @@
         <v>46167.73546241898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>25</v>
@@ -15080,7 +15077,7 @@
         <v>26</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>26</v>
@@ -15099,7 +15096,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B239" s="9">
         <v>46167.55756988426</v>
@@ -15109,7 +15106,7 @@
         <v>46167.743959513886</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15136,13 +15133,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q239" s="9">
         <v>46245</v>
@@ -15162,7 +15159,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B240" s="5">
         <v>46167.557574895836</v>
@@ -15172,7 +15169,7 @@
         <v>46167.74395664352</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15199,13 +15196,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q240" s="5">
         <v>46254</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.87831584491</v>
+        <v>46195.1701303125</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>156</v>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.878363958334</v>
+        <v>46195.17012525463</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46169.878480983796</v>
+        <v>46195.17012681713</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>113</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -4087,7 +4087,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46189.87936171296</v>
+        <v>46195.93002318287</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>129</v>
@@ -4132,9 +4132,11 @@
       <c r="B38" s="5">
         <v>46167.55686952546</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46195.93001813657</v>
+      </c>
       <c r="D38" s="5">
-        <v>46184.197559872686</v>
+        <v>46195.930020127314</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>132</v>
@@ -4182,10 +4184,10 @@
         <v>107</v>
       </c>
       <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -4195,9 +4197,11 @@
       <c r="B39" s="9">
         <v>46167.556874270835</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46195.928063217594</v>
+      </c>
       <c r="D39" s="9">
-        <v>46190.64115600694</v>
+        <v>46195.92806517361</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>137</v>
@@ -4254,9 +4258,11 @@
       <c r="B40" s="5">
         <v>46167.55687946759</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46195.929883310186</v>
+      </c>
       <c r="D40" s="5">
-        <v>46183.17042041667</v>
+        <v>46195.92988494213</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>140</v>
@@ -7934,7 +7940,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46185.18299439814</v>
+        <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>289</v>
@@ -7984,8 +7990,8 @@
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="12" t="s">
-        <v>61</v>
+      <c r="U106" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46190.641156666665</v>
+        <v>46196.64908548611</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>90</v>
@@ -3587,9 +3587,11 @@
       <c r="B29" s="9">
         <v>46167.556831423615</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46196.649080138886</v>
+      </c>
       <c r="D29" s="9">
-        <v>46192.18633622685</v>
+        <v>46196.64909515047</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>102</v>
@@ -3637,10 +3639,10 @@
         <v>107</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3650,9 +3652,11 @@
       <c r="B30" s="5">
         <v>46167.55683648148</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46196.6496064699</v>
+      </c>
       <c r="D30" s="5">
-        <v>46192.186336643514</v>
+        <v>46196.64962321759</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>109</v>
@@ -3700,10 +3704,10 @@
         <v>107</v>
       </c>
       <c r="T30" s="6">
-        <v>0</v>
-      </c>
-      <c r="U30" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U30" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3713,9 +3717,11 @@
       <c r="B31" s="9">
         <v>46167.55684075231</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46196.651088935185</v>
+      </c>
       <c r="D31" s="9">
-        <v>46192.18633769676</v>
+        <v>46196.651105439814</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>112</v>
@@ -3763,10 +3769,10 @@
         <v>107</v>
       </c>
       <c r="T31" s="10">
-        <v>0</v>
-      </c>
-      <c r="U31" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U31" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3776,9 +3782,11 @@
       <c r="B32" s="5">
         <v>46167.55684506944</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46196.65187996528</v>
+      </c>
       <c r="D32" s="5">
-        <v>46192.18633627315</v>
+        <v>46196.65189541667</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>
@@ -3826,10 +3834,10 @@
         <v>107</v>
       </c>
       <c r="T32" s="6">
-        <v>0</v>
-      </c>
-      <c r="U32" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U32" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -4553,7 +4561,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46195.1701303125</v>
+        <v>46196.64908697917</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>156</v>
@@ -4734,7 +4742,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46195.17012525463</v>
+        <v>46196.64961313657</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4903,7 +4911,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46169.878413784725</v>
+        <v>46196.6518865625</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>116</v>
@@ -5125,7 +5133,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46195.17012681713</v>
+        <v>46196.651095995374</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>113</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -801,7 +801,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1215103926667039</t>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="488">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -514,6 +514,9 @@
   </si>
   <si>
     <t>Fabricacion Corte Laser   ot 4328 - 4330,Generación OC materiales corte Laser  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215104027582344</t>
@@ -4498,7 +4501,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.87795083333</v>
+        <v>46197.202346921295</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>151</v>
@@ -4542,8 +4545,8 @@
       <c r="R44" s="5">
         <v>46204</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>33</v>
+      <c r="S44" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4554,7 +4557,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" s="9">
         <v>46167.556978611115</v>
@@ -4564,7 +4567,7 @@
         <v>46196.64908697917</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4597,7 +4600,7 @@
         <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B46" s="5">
         <v>46167.55698368055</v>
@@ -4623,7 +4626,7 @@
         <v>46169.878329687504</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4653,10 +4656,10 @@
         <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4672,17 +4675,17 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B47" s="9">
         <v>46167.556988842596</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46169.87796042824</v>
+        <v>46197.20234700231</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4712,7 +4715,7 @@
         <v>129</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4723,8 +4726,8 @@
       <c r="R47" s="9">
         <v>46204</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>33</v>
+      <c r="S47" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4735,7 +4738,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B48" s="5">
         <v>46167.556992708334</v>
@@ -4772,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4788,7 +4791,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B49" s="9">
         <v>46167.5569971875</v>
@@ -4798,7 +4801,7 @@
         <v>46169.87837792824</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4825,13 +4828,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>110</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4841,7 +4844,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46167.55700140046</v>
@@ -4851,16 +4854,16 @@
         <v>46169.87797747685</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4881,7 +4884,7 @@
         <v>129</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4904,7 +4907,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" s="9">
         <v>46167.55700519676</v>
@@ -4920,10 +4923,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -4941,13 +4944,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4957,7 +4960,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46167.557010034725</v>
@@ -4967,16 +4970,16 @@
         <v>46169.878430219906</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -4994,13 +4997,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>116</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5010,7 +5013,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B53" s="9">
         <v>46167.55701476852</v>
@@ -5020,16 +5023,16 @@
         <v>46169.87844947916</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5047,10 +5050,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5063,17 +5066,17 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="5">
         <v>46167.55701769676</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.87799084491</v>
+        <v>46197.202346817125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5103,7 +5106,7 @@
         <v>129</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5114,8 +5117,8 @@
       <c r="R54" s="5">
         <v>46204</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>33</v>
+      <c r="S54" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" s="9">
         <v>46167.557021678236</v>
@@ -5163,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5179,7 +5182,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B56" s="5">
         <v>46167.55702634259</v>
@@ -5189,7 +5192,7 @@
         <v>46169.87850571759</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5216,13 +5219,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5232,7 +5235,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B57" s="9">
         <v>46167.55703671296</v>
@@ -5242,7 +5245,7 @@
         <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5266,7 +5269,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5279,7 +5282,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46167.557040520835</v>
@@ -5291,16 +5294,16 @@
         <v>46184.51717821759</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5318,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5344,7 +5347,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46167.557045856476</v>
@@ -5356,16 +5359,16 @@
         <v>46189.875034826386</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5383,13 +5386,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5409,7 +5412,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46167.5570519676</v>
@@ -5427,10 +5430,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5448,13 +5451,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5474,7 +5477,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
@@ -5484,16 +5487,16 @@
         <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5511,10 +5514,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5537,7 +5540,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5547,16 +5550,16 @@
         <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5574,13 +5577,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5590,7 +5593,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5600,16 +5603,16 @@
         <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5627,13 +5630,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5643,7 +5646,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5653,16 +5656,16 @@
         <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5680,13 +5683,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5696,7 +5699,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5706,16 +5709,16 @@
         <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5733,13 +5736,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5749,7 +5752,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5759,16 +5762,16 @@
         <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5786,13 +5789,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5802,7 +5805,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5812,16 +5815,16 @@
         <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5839,13 +5842,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5855,7 +5858,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5865,16 +5868,16 @@
         <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5892,13 +5895,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5908,7 +5911,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5918,16 +5921,16 @@
         <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -5945,13 +5948,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5961,7 +5964,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -5971,7 +5974,7 @@
         <v>46167.629188032406</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5995,7 +5998,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6008,7 +6011,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6018,16 +6021,16 @@
         <v>46167.74094020833</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6045,13 +6048,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6071,7 +6074,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6081,16 +6084,16 @@
         <v>46167.7410212963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6108,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6134,7 +6137,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6144,16 +6147,16 @@
         <v>46167.74093746528</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6171,13 +6174,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6197,7 +6200,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6207,16 +6210,16 @@
         <v>46167.74101869213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6234,13 +6237,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6260,7 +6263,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6270,16 +6273,16 @@
         <v>46167.740934733796</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6297,13 +6300,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6323,7 +6326,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6333,16 +6336,16 @@
         <v>46167.74101563657</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6360,13 +6363,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6386,7 +6389,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6396,7 +6399,7 @@
         <v>46167.71426503472</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6420,7 +6423,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6433,7 +6436,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6443,16 +6446,16 @@
         <v>46167.74125046296</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6470,13 +6473,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6496,7 +6499,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46167.557178229166</v>
@@ -6506,16 +6509,16 @@
         <v>46167.741239525465</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6533,13 +6536,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6549,7 +6552,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46167.55718505787</v>
@@ -6559,16 +6562,16 @@
         <v>46167.74123664352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6586,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6602,7 +6605,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46167.629964050924</v>
@@ -6612,16 +6615,16 @@
         <v>46167.74123373843</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6639,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6655,7 +6658,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46167.6299746875</v>
@@ -6665,16 +6668,16 @@
         <v>46167.74123071759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6692,13 +6695,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6708,7 +6711,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B83" s="9">
         <v>46167.63011578703</v>
@@ -6718,16 +6721,16 @@
         <v>46167.74122805556</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6745,13 +6748,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6761,7 +6764,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46167.630126516204</v>
@@ -6771,16 +6774,16 @@
         <v>46167.74122546296</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6798,13 +6801,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6814,7 +6817,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B85" s="9">
         <v>46167.63145555556</v>
@@ -6824,16 +6827,16 @@
         <v>46167.74121943287</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6851,13 +6854,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6867,7 +6870,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
         <v>46167.631772685185</v>
@@ -6877,16 +6880,16 @@
         <v>46167.74121879629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -6904,13 +6907,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6920,7 +6923,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B87" s="9">
         <v>46167.557190844906</v>
@@ -6930,16 +6933,16 @@
         <v>46167.74138710648</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -6957,13 +6960,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -6983,7 +6986,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5">
         <v>46167.557195092595</v>
@@ -6993,16 +6996,16 @@
         <v>46189.87510653935</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7020,13 +7023,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7036,7 +7039,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" s="9">
         <v>46167.557200995376</v>
@@ -7046,16 +7049,16 @@
         <v>46189.87510706019</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7073,13 +7076,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7089,7 +7092,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B90" s="5">
         <v>46167.63214916667</v>
@@ -7099,16 +7102,16 @@
         <v>46167.741366435184</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7126,13 +7129,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7142,7 +7145,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B91" s="9">
         <v>46167.63219107639</v>
@@ -7152,16 +7155,16 @@
         <v>46167.741363622685</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7179,13 +7182,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7195,7 +7198,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B92" s="5">
         <v>46167.63220099537</v>
@@ -7205,16 +7208,16 @@
         <v>46167.741361215274</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7232,13 +7235,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7248,7 +7251,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B93" s="9">
         <v>46167.63220839121</v>
@@ -7258,16 +7261,16 @@
         <v>46167.74135855324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7285,13 +7288,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7301,7 +7304,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B94" s="5">
         <v>46167.63225591435</v>
@@ -7311,16 +7314,16 @@
         <v>46167.74135295139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7338,13 +7341,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7354,7 +7357,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B95" s="9">
         <v>46167.63226373843</v>
@@ -7364,16 +7367,16 @@
         <v>46167.74135225694</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7391,13 +7394,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7407,7 +7410,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B96" s="5">
         <v>46167.5572065625</v>
@@ -7417,16 +7420,16 @@
         <v>46167.74153292824</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7444,13 +7447,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7470,7 +7473,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B97" s="9">
         <v>46167.557210914354</v>
@@ -7480,16 +7483,16 @@
         <v>46189.87509809028</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7507,13 +7510,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7523,7 +7526,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B98" s="5">
         <v>46167.55721697917</v>
@@ -7533,16 +7536,16 @@
         <v>46189.87509940972</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7560,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7576,7 +7579,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B99" s="9">
         <v>46167.632342048615</v>
@@ -7586,16 +7589,16 @@
         <v>46167.74151755787</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7613,10 +7616,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7629,7 +7632,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B100" s="5">
         <v>46167.63235868055</v>
@@ -7639,16 +7642,16 @@
         <v>46167.74151503472</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7666,13 +7669,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7682,7 +7685,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B101" s="9">
         <v>46167.63236590278</v>
@@ -7692,16 +7695,16 @@
         <v>46167.74151262731</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7719,13 +7722,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7735,7 +7738,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B102" s="5">
         <v>46167.63237413194</v>
@@ -7745,16 +7748,16 @@
         <v>46167.7415103588</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7772,13 +7775,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7788,7 +7791,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B103" s="9">
         <v>46167.63244320602</v>
@@ -7798,16 +7801,16 @@
         <v>46167.74150512731</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7825,13 +7828,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7841,7 +7844,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B104" s="5">
         <v>46167.63245268518</v>
@@ -7851,16 +7854,16 @@
         <v>46167.74150447917</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -7878,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7894,7 +7897,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B105" s="9">
         <v>46167.55722248842</v>
@@ -7904,7 +7907,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -7928,7 +7931,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -7941,7 +7944,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46167.557225682875</v>
@@ -7951,16 +7954,16 @@
         <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -7978,13 +7981,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="5">
         <v>46184</v>
@@ -8004,7 +8007,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46167.557231493054</v>
@@ -8020,10 +8023,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8041,13 +8044,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>126</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8067,7 +8070,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B108" s="5">
         <v>46167.55723746528</v>
@@ -8083,10 +8086,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8104,13 +8107,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q108" s="5">
         <v>46168</v>
@@ -8130,7 +8133,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B109" s="9">
         <v>46167.55724847222</v>
@@ -8140,16 +8143,16 @@
         <v>46167.74163924769</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8167,13 +8170,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q109" s="9">
         <v>46265</v>
@@ -8193,7 +8196,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B110" s="5">
         <v>46167.55725353009</v>
@@ -8209,10 +8212,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8230,13 +8233,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q110" s="5">
         <v>46220</v>
@@ -8256,7 +8259,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B111" s="9">
         <v>46167.5572591088</v>
@@ -8266,7 +8269,7 @@
         <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8290,7 +8293,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8303,7 +8306,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B112" s="5">
         <v>46167.557262685186</v>
@@ -8313,7 +8316,7 @@
         <v>46167.741924999995</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8340,13 +8343,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q112" s="5">
         <v>46224</v>
@@ -8366,7 +8369,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B113" s="9">
         <v>46167.55727085649</v>
@@ -8376,7 +8379,7 @@
         <v>46167.74190891204</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8403,10 +8406,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8419,7 +8422,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B114" s="5">
         <v>46167.55727532407</v>
@@ -8429,7 +8432,7 @@
         <v>46167.74190642362</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8456,10 +8459,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8472,7 +8475,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B115" s="9">
         <v>46167.632606053245</v>
@@ -8482,7 +8485,7 @@
         <v>46167.7419037037</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8509,13 +8512,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8525,7 +8528,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B116" s="5">
         <v>46167.63261443287</v>
@@ -8535,7 +8538,7 @@
         <v>46167.74190121528</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8562,13 +8565,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8578,7 +8581,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B117" s="9">
         <v>46167.63262241898</v>
@@ -8588,7 +8591,7 @@
         <v>46167.74189892361</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8615,13 +8618,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8631,7 +8634,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B118" s="5">
         <v>46167.63263039352</v>
@@ -8641,7 +8644,7 @@
         <v>46167.74189655093</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8668,13 +8671,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8684,7 +8687,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B119" s="9">
         <v>46167.63269008102</v>
@@ -8694,7 +8697,7 @@
         <v>46167.74189145833</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8721,13 +8724,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8737,7 +8740,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B120" s="5">
         <v>46167.632698738424</v>
@@ -8747,7 +8750,7 @@
         <v>46167.74189078704</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8774,13 +8777,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8790,7 +8793,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B121" s="9">
         <v>46167.55727960648</v>
@@ -8800,7 +8803,7 @@
         <v>46167.74207511574</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8827,13 +8830,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q121" s="9">
         <v>46231</v>
@@ -8853,7 +8856,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B122" s="5">
         <v>46167.557284375</v>
@@ -8863,7 +8866,7 @@
         <v>46189.87510767361</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8890,13 +8893,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8906,7 +8909,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B123" s="9">
         <v>46167.55729009259</v>
@@ -8916,7 +8919,7 @@
         <v>46189.87510009259</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8943,13 +8946,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8959,7 +8962,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B124" s="5">
         <v>46167.6328130787</v>
@@ -8969,7 +8972,7 @@
         <v>46189.87508946759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8996,13 +8999,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9012,7 +9015,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B125" s="9">
         <v>46167.63283585648</v>
@@ -9022,7 +9025,7 @@
         <v>46189.87509015047</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9049,13 +9052,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9065,7 +9068,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B126" s="5">
         <v>46167.63284336806</v>
@@ -9075,7 +9078,7 @@
         <v>46189.87509105324</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9102,13 +9105,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9118,7 +9121,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B127" s="9">
         <v>46167.63285163195</v>
@@ -9128,7 +9131,7 @@
         <v>46189.87509177084</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9155,13 +9158,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9171,7 +9174,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B128" s="5">
         <v>46167.63289178241</v>
@@ -9181,7 +9184,7 @@
         <v>46189.87509244213</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9208,13 +9211,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9224,7 +9227,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B129" s="9">
         <v>46167.632899212964</v>
@@ -9234,7 +9237,7 @@
         <v>46189.8750930324</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9261,13 +9264,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9277,7 +9280,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B130" s="5">
         <v>46167.55733736111</v>
@@ -9287,7 +9290,7 @@
         <v>46167.74221776621</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9314,13 +9317,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q130" s="5">
         <v>46232</v>
@@ -9340,7 +9343,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B131" s="9">
         <v>46167.557343645836</v>
@@ -9350,7 +9353,7 @@
         <v>46189.87510797454</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9375,13 +9378,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9391,7 +9394,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B132" s="5">
         <v>46167.55735079861</v>
@@ -9401,7 +9404,7 @@
         <v>46189.87510071759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9426,13 +9429,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9442,7 +9445,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B133" s="9">
         <v>46167.63302359954</v>
@@ -9452,7 +9455,7 @@
         <v>46189.875093634255</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9477,13 +9480,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9493,7 +9496,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B134" s="5">
         <v>46167.63303486111</v>
@@ -9503,7 +9506,7 @@
         <v>46189.8750941551</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9528,13 +9531,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9544,7 +9547,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B135" s="9">
         <v>46167.633050648146</v>
@@ -9554,7 +9557,7 @@
         <v>46189.87509472222</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9579,13 +9582,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9595,7 +9598,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B136" s="5">
         <v>46167.633060671295</v>
@@ -9605,7 +9608,7 @@
         <v>46189.87509519676</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9630,13 +9633,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9646,7 +9649,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B137" s="9">
         <v>46167.633115185185</v>
@@ -9656,7 +9659,7 @@
         <v>46189.87509570602</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9681,13 +9684,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9697,7 +9700,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B138" s="5">
         <v>46167.6331228125</v>
@@ -9707,7 +9710,7 @@
         <v>46189.87509615741</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9732,13 +9735,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9748,7 +9751,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B139" s="9">
         <v>46167.557357488426</v>
@@ -9758,7 +9761,7 @@
         <v>46167.74236513889</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9785,13 +9788,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q139" s="9">
         <v>46233</v>
@@ -9811,7 +9814,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B140" s="5">
         <v>46167.55736211805</v>
@@ -9821,7 +9824,7 @@
         <v>46189.877459745374</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9848,13 +9851,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9864,7 +9867,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B141" s="9">
         <v>46167.55737267361</v>
@@ -9874,7 +9877,7 @@
         <v>46189.87746077546</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9901,13 +9904,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9917,7 +9920,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B142" s="5">
         <v>46167.63325159722</v>
@@ -9927,7 +9930,7 @@
         <v>46189.877455671296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9954,13 +9957,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9970,7 +9973,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B143" s="9">
         <v>46167.63325929398</v>
@@ -9980,7 +9983,7 @@
         <v>46189.87745677083</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10007,13 +10010,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10023,7 +10026,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B144" s="5">
         <v>46167.633274293985</v>
@@ -10033,7 +10036,7 @@
         <v>46189.87745732639</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10060,13 +10063,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10076,7 +10079,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B145" s="9">
         <v>46167.633281875</v>
@@ -10086,7 +10089,7 @@
         <v>46189.877457916664</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10113,13 +10116,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10129,7 +10132,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B146" s="5">
         <v>46167.63332260417</v>
@@ -10139,7 +10142,7 @@
         <v>46189.87745863426</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10166,13 +10169,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10182,7 +10185,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B147" s="9">
         <v>46167.633331689816</v>
@@ -10192,7 +10195,7 @@
         <v>46189.87745917824</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10219,13 +10222,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10235,7 +10238,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B148" s="5">
         <v>46167.557378287034</v>
@@ -10245,7 +10248,7 @@
         <v>46167.742498472224</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10272,13 +10275,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q148" s="5">
         <v>46234</v>
@@ -10298,7 +10301,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B149" s="9">
         <v>46167.55738292824</v>
@@ -10308,7 +10311,7 @@
         <v>46167.742493136575</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10335,13 +10338,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10351,7 +10354,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B150" s="5">
         <v>46167.5573883912</v>
@@ -10361,7 +10364,7 @@
         <v>46167.742490000004</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10388,13 +10391,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10404,7 +10407,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B151" s="9">
         <v>46167.63341660879</v>
@@ -10414,7 +10417,7 @@
         <v>46167.74248716435</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10441,13 +10444,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10457,7 +10460,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B152" s="5">
         <v>46167.63343371528</v>
@@ -10467,7 +10470,7 @@
         <v>46167.74248396991</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10494,13 +10497,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10510,7 +10513,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B153" s="9">
         <v>46167.63344365741</v>
@@ -10520,7 +10523,7 @@
         <v>46167.742481134264</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10547,13 +10550,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10563,7 +10566,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B154" s="5">
         <v>46167.63345188658</v>
@@ -10573,7 +10576,7 @@
         <v>46167.74247835648</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10600,13 +10603,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10616,7 +10619,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B155" s="9">
         <v>46167.633506412036</v>
@@ -10626,7 +10629,7 @@
         <v>46167.74247142361</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10653,13 +10656,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10669,7 +10672,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B156" s="5">
         <v>46167.63351399306</v>
@@ -10679,7 +10682,7 @@
         <v>46167.74247065972</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10706,13 +10709,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10722,7 +10725,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B157" s="9">
         <v>46167.55739407407</v>
@@ -10732,7 +10735,7 @@
         <v>46167.74264841435</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10759,13 +10762,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q157" s="9">
         <v>46238</v>
@@ -10785,7 +10788,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B158" s="5">
         <v>46167.55739920139</v>
@@ -10795,7 +10798,7 @@
         <v>46167.742638298616</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10822,13 +10825,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10838,7 +10841,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B159" s="9">
         <v>46167.5574040162</v>
@@ -10848,7 +10851,7 @@
         <v>46167.74263541667</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10875,13 +10878,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10891,7 +10894,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B160" s="5">
         <v>46167.633843206015</v>
@@ -10901,7 +10904,7 @@
         <v>46167.742632037036</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10928,13 +10931,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10944,7 +10947,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B161" s="9">
         <v>46167.633849895836</v>
@@ -10954,7 +10957,7 @@
         <v>46167.742628935186</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10981,13 +10984,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10997,7 +11000,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B162" s="5">
         <v>46167.63385791666</v>
@@ -11007,7 +11010,7 @@
         <v>46167.74262635417</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11034,13 +11037,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11050,7 +11053,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B163" s="9">
         <v>46167.633867083336</v>
@@ -11060,7 +11063,7 @@
         <v>46167.74262355324</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11087,13 +11090,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11103,7 +11106,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B164" s="5">
         <v>46167.63391234954</v>
@@ -11113,7 +11116,7 @@
         <v>46167.742617407406</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11140,13 +11143,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11156,7 +11159,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B165" s="9">
         <v>46167.63392017361</v>
@@ -11166,7 +11169,7 @@
         <v>46167.74261677083</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11193,13 +11196,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11209,7 +11212,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B166" s="5">
         <v>46167.557409201385</v>
@@ -11219,7 +11222,7 @@
         <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -11243,7 +11246,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11256,7 +11259,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B167" s="9">
         <v>46167.5574132176</v>
@@ -11266,16 +11269,16 @@
         <v>46167.74284238426</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I167" s="9">
         <v>46230</v>
@@ -11293,13 +11296,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q167" s="9">
         <v>46230</v>
@@ -11319,7 +11322,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B168" s="5">
         <v>46167.55742054398</v>
@@ -11329,16 +11332,16 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I168" s="5">
         <v>46239</v>
@@ -11356,13 +11359,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11372,7 +11375,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B169" s="9">
         <v>46167.557425520834</v>
@@ -11382,16 +11385,16 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I169" s="9">
         <v>46239</v>
@@ -11409,13 +11412,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11425,7 +11428,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B170" s="5">
         <v>46167.55743020833</v>
@@ -11435,16 +11438,16 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I170" s="5">
         <v>46239</v>
@@ -11462,13 +11465,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11478,7 +11481,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B171" s="9">
         <v>46167.557434918985</v>
@@ -11488,16 +11491,16 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I171" s="9">
         <v>46239</v>
@@ -11515,13 +11518,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11531,7 +11534,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B172" s="5">
         <v>46167.636403032404</v>
@@ -11541,16 +11544,16 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I172" s="5">
         <v>46239</v>
@@ -11568,13 +11571,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11584,7 +11587,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B173" s="9">
         <v>46167.63641173611</v>
@@ -11594,16 +11597,16 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I173" s="9">
         <v>46239</v>
@@ -11621,13 +11624,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11637,7 +11640,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B174" s="5">
         <v>46167.636428645834</v>
@@ -11647,16 +11650,16 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I174" s="5">
         <v>46239</v>
@@ -11674,13 +11677,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11690,7 +11693,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B175" s="9">
         <v>46167.636439849535</v>
@@ -11700,16 +11703,16 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I175" s="9">
         <v>46239</v>
@@ -11727,13 +11730,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11743,7 +11746,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B176" s="5">
         <v>46167.636677511575</v>
@@ -11759,10 +11762,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I176" s="5">
         <v>46230</v>
@@ -11780,7 +11783,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>63</v>
@@ -11796,7 +11799,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B177" s="9">
         <v>46167.63669306713</v>
@@ -11812,10 +11815,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I177" s="9">
         <v>46230</v>
@@ -11833,7 +11836,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>63</v>
@@ -11849,7 +11852,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B178" s="5">
         <v>46167.6367015162</v>
@@ -11865,10 +11868,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I178" s="5">
         <v>46230</v>
@@ -11886,7 +11889,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>63</v>
@@ -11902,7 +11905,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B179" s="9">
         <v>46167.6367112963</v>
@@ -11918,10 +11921,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I179" s="9">
         <v>46230</v>
@@ -11939,7 +11942,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>63</v>
@@ -11955,7 +11958,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B180" s="5">
         <v>46167.63672008102</v>
@@ -11971,10 +11974,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I180" s="5">
         <v>46230</v>
@@ -11992,7 +11995,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>63</v>
@@ -12008,7 +12011,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B181" s="9">
         <v>46167.636729247686</v>
@@ -12024,10 +12027,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I181" s="9">
         <v>46230</v>
@@ -12045,7 +12048,7 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O181" s="10" t="s">
         <v>63</v>
@@ -12061,7 +12064,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B182" s="5">
         <v>46167.63683603009</v>
@@ -12077,10 +12080,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I182" s="5">
         <v>46230</v>
@@ -12098,7 +12101,7 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>71</v>
@@ -12114,7 +12117,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B183" s="9">
         <v>46167.636846319445</v>
@@ -12130,10 +12133,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I183" s="9">
         <v>46230</v>
@@ -12151,7 +12154,7 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>71</v>
@@ -12167,7 +12170,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B184" s="5">
         <v>46167.55743945602</v>
@@ -12177,7 +12180,7 @@
         <v>46167.7430450463</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12204,13 +12207,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q184" s="5">
         <v>46231</v>
@@ -12230,7 +12233,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B185" s="9">
         <v>46167.55744423611</v>
@@ -12240,7 +12243,7 @@
         <v>46167.74306620371</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12265,13 +12268,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12281,7 +12284,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B186" s="5">
         <v>46167.55744884259</v>
@@ -12291,7 +12294,7 @@
         <v>46167.74306335648</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12316,13 +12319,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12332,7 +12335,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B187" s="9">
         <v>46167.55745349537</v>
@@ -12342,7 +12345,7 @@
         <v>46167.74306008102</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12367,13 +12370,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12383,7 +12386,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B188" s="5">
         <v>46167.55745777777</v>
@@ -12393,7 +12396,7 @@
         <v>46167.74305738426</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12418,13 +12421,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12434,7 +12437,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B189" s="9">
         <v>46167.637670833334</v>
@@ -12444,7 +12447,7 @@
         <v>46167.74305466435</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12469,13 +12472,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12485,7 +12488,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B190" s="5">
         <v>46167.63768076389</v>
@@ -12495,7 +12498,7 @@
         <v>46167.743051990736</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12520,13 +12523,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12536,7 +12539,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B191" s="9">
         <v>46167.637724016204</v>
@@ -12546,7 +12549,7 @@
         <v>46167.74304920139</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12571,13 +12574,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12587,7 +12590,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B192" s="5">
         <v>46167.63773231482</v>
@@ -12597,7 +12600,7 @@
         <v>46167.743046574076</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12622,13 +12625,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12638,7 +12641,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B193" s="9">
         <v>46167.63788011574</v>
@@ -12675,7 +12678,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>64</v>
@@ -12691,7 +12694,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B194" s="5">
         <v>46167.637888530095</v>
@@ -12728,7 +12731,7 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O194" s="6" t="s">
         <v>63</v>
@@ -12744,7 +12747,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B195" s="9">
         <v>46167.63789722222</v>
@@ -12781,7 +12784,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O195" s="10" t="s">
         <v>63</v>
@@ -12797,7 +12800,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B196" s="5">
         <v>46167.63790768519</v>
@@ -12834,7 +12837,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
@@ -12850,7 +12853,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B197" s="9">
         <v>46167.63791662037</v>
@@ -12887,7 +12890,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>63</v>
@@ -12903,7 +12906,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B198" s="5">
         <v>46167.637946689814</v>
@@ -12940,7 +12943,7 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
@@ -12956,7 +12959,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B199" s="9">
         <v>46167.637995729165</v>
@@ -12993,7 +12996,7 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>71</v>
@@ -13009,7 +13012,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B200" s="5">
         <v>46167.63800420139</v>
@@ -13046,7 +13049,7 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>71</v>
@@ -13062,7 +13065,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B201" s="9">
         <v>46167.55746224537</v>
@@ -13072,16 +13075,16 @@
         <v>46167.74364532407</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13099,13 +13102,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q201" s="9">
         <v>46241</v>
@@ -13125,7 +13128,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B202" s="5">
         <v>46167.55746689815</v>
@@ -13135,16 +13138,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13162,13 +13165,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13178,7 +13181,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B203" s="9">
         <v>46167.55747543981</v>
@@ -13188,16 +13191,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13215,13 +13218,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13231,7 +13234,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B204" s="5">
         <v>46167.557519270835</v>
@@ -13241,16 +13244,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13268,13 +13271,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13284,7 +13287,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B205" s="9">
         <v>46167.5575253125</v>
@@ -13294,16 +13297,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13321,13 +13324,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13337,7 +13340,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B206" s="5">
         <v>46167.6385715162</v>
@@ -13347,16 +13350,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13374,13 +13377,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13390,7 +13393,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B207" s="9">
         <v>46167.63857899306</v>
@@ -13400,16 +13403,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13427,13 +13430,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13443,7 +13446,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B208" s="5">
         <v>46167.638659930555</v>
@@ -13453,16 +13456,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13480,13 +13483,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13496,7 +13499,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B209" s="9">
         <v>46167.638666956016</v>
@@ -13506,16 +13509,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13533,13 +13536,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13549,7 +13552,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B210" s="5">
         <v>46167.6387090162</v>
@@ -13565,10 +13568,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13586,7 +13589,7 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>63</v>
@@ -13602,7 +13605,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B211" s="9">
         <v>46167.63871641204</v>
@@ -13618,10 +13621,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13639,7 +13642,7 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>63</v>
@@ -13655,7 +13658,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B212" s="5">
         <v>46167.638723599535</v>
@@ -13671,10 +13674,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13692,7 +13695,7 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>63</v>
@@ -13708,7 +13711,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B213" s="9">
         <v>46167.63873144676</v>
@@ -13724,10 +13727,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13745,7 +13748,7 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>63</v>
@@ -13761,7 +13764,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B214" s="5">
         <v>46167.6387405787</v>
@@ -13777,10 +13780,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13798,7 +13801,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>63</v>
@@ -13814,7 +13817,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B215" s="9">
         <v>46167.63874844907</v>
@@ -13830,10 +13833,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -13851,7 +13854,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>63</v>
@@ -13867,7 +13870,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B216" s="5">
         <v>46167.638756562505</v>
@@ -13883,10 +13886,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -13904,13 +13907,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13920,7 +13923,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B217" s="9">
         <v>46167.63883428241</v>
@@ -13936,10 +13939,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -13957,13 +13960,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13973,7 +13976,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B218" s="5">
         <v>46167.55752998842</v>
@@ -13983,16 +13986,16 @@
         <v>46167.74382108796</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -14010,13 +14013,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q218" s="5">
         <v>46244</v>
@@ -14036,7 +14039,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B219" s="9">
         <v>46167.55753614583</v>
@@ -14046,16 +14049,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14073,13 +14076,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14089,7 +14092,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B220" s="5">
         <v>46167.557540381946</v>
@@ -14099,16 +14102,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14126,13 +14129,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14142,7 +14145,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B221" s="9">
         <v>46167.557545069445</v>
@@ -14152,16 +14155,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14179,13 +14182,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14195,7 +14198,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B222" s="5">
         <v>46167.55754895833</v>
@@ -14205,16 +14208,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14232,13 +14235,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14248,7 +14251,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B223" s="9">
         <v>46167.63903770833</v>
@@ -14258,16 +14261,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14285,10 +14288,10 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14301,7 +14304,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B224" s="5">
         <v>46167.639049317135</v>
@@ -14311,16 +14314,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14338,10 +14341,10 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14354,7 +14357,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B225" s="9">
         <v>46167.639172118055</v>
@@ -14364,16 +14367,16 @@
         <v>46167.743832430555</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14391,10 +14394,10 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14407,7 +14410,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B226" s="5">
         <v>46167.63918146991</v>
@@ -14417,16 +14420,16 @@
         <v>46167.74382957176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14444,10 +14447,10 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14460,7 +14463,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B227" s="9">
         <v>46167.63922125</v>
@@ -14476,10 +14479,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14497,7 +14500,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>63</v>
@@ -14513,7 +14516,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B228" s="5">
         <v>46167.63923230324</v>
@@ -14529,10 +14532,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14550,7 +14553,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>63</v>
@@ -14566,7 +14569,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B229" s="9">
         <v>46167.63924049769</v>
@@ -14582,10 +14585,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14603,7 +14606,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>63</v>
@@ -14619,7 +14622,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B230" s="5">
         <v>46167.63924949074</v>
@@ -14635,10 +14638,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14656,7 +14659,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>63</v>
@@ -14672,7 +14675,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B231" s="9">
         <v>46167.639259375</v>
@@ -14688,10 +14691,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14709,7 +14712,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>63</v>
@@ -14725,7 +14728,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B232" s="5">
         <v>46167.63926804398</v>
@@ -14741,10 +14744,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14762,7 +14765,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>63</v>
@@ -14778,7 +14781,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B233" s="9">
         <v>46167.63935532408</v>
@@ -14788,16 +14791,16 @@
         <v>46167.74380655093</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14815,7 +14818,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>71</v>
@@ -14831,7 +14834,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B234" s="5">
         <v>46167.63936689815</v>
@@ -14841,16 +14844,16 @@
         <v>46167.74380591435</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>
@@ -14868,7 +14871,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>71</v>
@@ -14884,7 +14887,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B235" s="9">
         <v>46167.55755266204</v>
@@ -14894,7 +14897,7 @@
         <v>46167.73498962963</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>25</v>
@@ -14918,7 +14921,7 @@
         <v>26</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>26</v>
@@ -14931,7 +14934,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B236" s="5">
         <v>46167.55755585648</v>
@@ -14941,16 +14944,16 @@
         <v>46167.743865428245</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I236" s="5">
         <v>46245</v>
@@ -14968,13 +14971,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q236" s="5">
         <v>46245</v>
@@ -14994,7 +14997,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B237" s="9">
         <v>46167.55756052083</v>
@@ -15004,7 +15007,7 @@
         <v>46189.872060740745</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15031,13 +15034,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q237" s="9">
         <v>46245</v>
@@ -15057,7 +15060,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B238" s="5">
         <v>46167.557566296295</v>
@@ -15067,7 +15070,7 @@
         <v>46167.73546241898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>25</v>
@@ -15091,7 +15094,7 @@
         <v>26</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>26</v>
@@ -15110,7 +15113,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B239" s="9">
         <v>46167.55756988426</v>
@@ -15120,7 +15123,7 @@
         <v>46167.743959513886</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15147,13 +15150,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q239" s="9">
         <v>46245</v>
@@ -15173,7 +15176,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B240" s="5">
         <v>46167.557574895836</v>
@@ -15183,7 +15186,7 @@
         <v>46167.74395664352</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15210,13 +15213,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Q240" s="5">
         <v>46254</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="490">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -642,25 +642,31 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215103776739451</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215103975168124</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215103776739451</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215103975168124</t>
   </si>
   <si>
     <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Propuesta Mecanizado  ot 4328 - 4330,Propuesta Fabricación externa  ot 4328 - 4330 ,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,propuesta Corte Laser  ot 4328 - 4330,Propuesta Corte plasma   ot 4328 - 4330,OT 4328 - ZVN 1-9-86/2</t>
@@ -5291,7 +5297,7 @@
         <v>46184.517161701384</v>
       </c>
       <c r="D58" s="5">
-        <v>46184.51717821759</v>
+        <v>46197.715067453704</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>196</v>
@@ -5356,7 +5362,7 @@
         <v>46189.875018101855</v>
       </c>
       <c r="D59" s="9">
-        <v>46189.875034826386</v>
+        <v>46197.71510291667</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>201</v>
@@ -5430,10 +5436,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5457,7 +5463,7 @@
         <v>201</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5477,7 +5483,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
@@ -5487,16 +5493,16 @@
         <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5517,7 +5523,7 @@
         <v>193</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5540,7 +5546,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5550,16 +5556,16 @@
         <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5577,13 +5583,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5593,7 +5599,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5603,16 +5609,16 @@
         <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5630,13 +5636,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5646,7 +5652,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5656,16 +5662,16 @@
         <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5683,13 +5689,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5699,7 +5705,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5709,16 +5715,16 @@
         <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5736,13 +5742,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5752,7 +5758,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5762,16 +5768,16 @@
         <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5789,13 +5795,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5805,7 +5811,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5815,16 +5821,16 @@
         <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5842,13 +5848,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5858,7 +5864,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5868,16 +5874,16 @@
         <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5895,13 +5901,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5911,7 +5917,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5921,16 +5927,16 @@
         <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -5948,13 +5954,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5964,7 +5970,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -5974,7 +5980,7 @@
         <v>46167.629188032406</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5998,7 +6004,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6011,7 +6017,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6021,16 +6027,16 @@
         <v>46167.74094020833</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6048,13 +6054,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>160</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6074,7 +6080,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6084,7 +6090,7 @@
         <v>46167.7410212963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -6111,13 +6117,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6137,7 +6143,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6147,16 +6153,16 @@
         <v>46167.74093746528</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6174,13 +6180,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>168</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6200,7 +6206,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6210,7 +6216,7 @@
         <v>46167.74101869213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6237,13 +6243,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6263,7 +6269,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6273,16 +6279,16 @@
         <v>46167.740934733796</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6300,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6326,7 +6332,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6336,7 +6342,7 @@
         <v>46167.74101563657</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6363,13 +6369,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6389,7 +6395,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6399,7 +6405,7 @@
         <v>46167.71426503472</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6423,7 +6429,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6436,7 +6442,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6446,16 +6452,16 @@
         <v>46167.74125046296</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6473,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6499,7 +6505,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
         <v>46167.557178229166</v>
@@ -6509,16 +6515,16 @@
         <v>46167.741239525465</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6536,13 +6542,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6552,7 +6558,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46167.55718505787</v>
@@ -6562,16 +6568,16 @@
         <v>46167.74123664352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6589,13 +6595,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6605,7 +6611,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46167.629964050924</v>
@@ -6615,16 +6621,16 @@
         <v>46167.74123373843</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6642,13 +6648,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6658,7 +6664,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46167.6299746875</v>
@@ -6668,16 +6674,16 @@
         <v>46167.74123071759</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6695,13 +6701,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6711,7 +6717,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46167.63011578703</v>
@@ -6721,16 +6727,16 @@
         <v>46167.74122805556</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6748,13 +6754,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6764,7 +6770,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46167.630126516204</v>
@@ -6774,16 +6780,16 @@
         <v>46167.74122546296</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6801,13 +6807,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6817,7 +6823,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B85" s="9">
         <v>46167.63145555556</v>
@@ -6827,16 +6833,16 @@
         <v>46167.74121943287</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6854,13 +6860,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6870,7 +6876,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46167.631772685185</v>
@@ -6880,16 +6886,16 @@
         <v>46167.74121879629</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -6907,13 +6913,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6923,7 +6929,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B87" s="9">
         <v>46167.557190844906</v>
@@ -6933,16 +6939,16 @@
         <v>46167.74138710648</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -6960,13 +6966,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -6986,7 +6992,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B88" s="5">
         <v>46167.557195092595</v>
@@ -6996,16 +7002,16 @@
         <v>46189.87510653935</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7023,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7039,7 +7045,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B89" s="9">
         <v>46167.557200995376</v>
@@ -7049,16 +7055,16 @@
         <v>46189.87510706019</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7076,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7092,7 +7098,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B90" s="5">
         <v>46167.63214916667</v>
@@ -7102,16 +7108,16 @@
         <v>46167.741366435184</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7129,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7145,7 +7151,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B91" s="9">
         <v>46167.63219107639</v>
@@ -7155,16 +7161,16 @@
         <v>46167.741363622685</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7182,13 +7188,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7198,7 +7204,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B92" s="5">
         <v>46167.63220099537</v>
@@ -7208,16 +7214,16 @@
         <v>46167.741361215274</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7235,13 +7241,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7251,7 +7257,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B93" s="9">
         <v>46167.63220839121</v>
@@ -7261,16 +7267,16 @@
         <v>46167.74135855324</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7288,13 +7294,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7304,7 +7310,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B94" s="5">
         <v>46167.63225591435</v>
@@ -7314,16 +7320,16 @@
         <v>46167.74135295139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7341,13 +7347,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7357,7 +7363,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B95" s="9">
         <v>46167.63226373843</v>
@@ -7367,16 +7373,16 @@
         <v>46167.74135225694</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7394,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7410,7 +7416,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B96" s="5">
         <v>46167.5572065625</v>
@@ -7420,7 +7426,7 @@
         <v>46167.74153292824</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7447,13 +7453,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7473,7 +7479,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B97" s="9">
         <v>46167.557210914354</v>
@@ -7483,7 +7489,7 @@
         <v>46189.87509809028</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7510,13 +7516,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7526,7 +7532,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B98" s="5">
         <v>46167.55721697917</v>
@@ -7536,7 +7542,7 @@
         <v>46189.87509940972</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7563,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7579,7 +7585,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B99" s="9">
         <v>46167.632342048615</v>
@@ -7589,7 +7595,7 @@
         <v>46167.74151755787</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7616,10 +7622,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7632,7 +7638,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B100" s="5">
         <v>46167.63235868055</v>
@@ -7642,7 +7648,7 @@
         <v>46167.74151503472</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7669,13 +7675,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7685,7 +7691,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B101" s="9">
         <v>46167.63236590278</v>
@@ -7695,7 +7701,7 @@
         <v>46167.74151262731</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7722,13 +7728,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7738,7 +7744,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B102" s="5">
         <v>46167.63237413194</v>
@@ -7748,7 +7754,7 @@
         <v>46167.7415103588</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7775,13 +7781,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7791,7 +7797,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B103" s="9">
         <v>46167.63244320602</v>
@@ -7801,7 +7807,7 @@
         <v>46167.74150512731</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7828,13 +7834,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7844,7 +7850,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B104" s="5">
         <v>46167.63245268518</v>
@@ -7854,7 +7860,7 @@
         <v>46167.74150447917</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7881,13 +7887,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7897,7 +7903,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B105" s="9">
         <v>46167.55722248842</v>
@@ -7907,7 +7913,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -7931,7 +7937,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -7944,7 +7950,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B106" s="5">
         <v>46167.557225682875</v>
@@ -7954,16 +7960,16 @@
         <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -7981,13 +7987,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q106" s="5">
         <v>46184</v>
@@ -8007,7 +8013,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B107" s="9">
         <v>46167.557231493054</v>
@@ -8023,10 +8029,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8044,13 +8050,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>126</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8070,7 +8076,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46167.55723746528</v>
@@ -8086,10 +8092,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8107,13 +8113,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q108" s="5">
         <v>46168</v>
@@ -8133,7 +8139,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B109" s="9">
         <v>46167.55724847222</v>
@@ -8143,16 +8149,16 @@
         <v>46167.74163924769</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8170,13 +8176,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>178</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q109" s="9">
         <v>46265</v>
@@ -8196,7 +8202,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46167.55725353009</v>
@@ -8212,10 +8218,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8233,13 +8239,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q110" s="5">
         <v>46220</v>
@@ -8259,7 +8265,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B111" s="9">
         <v>46167.5572591088</v>
@@ -8269,7 +8275,7 @@
         <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8293,7 +8299,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8306,7 +8312,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B112" s="5">
         <v>46167.557262685186</v>
@@ -8316,7 +8322,7 @@
         <v>46167.741924999995</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8343,13 +8349,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q112" s="5">
         <v>46224</v>
@@ -8369,7 +8375,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B113" s="9">
         <v>46167.55727085649</v>
@@ -8379,7 +8385,7 @@
         <v>46167.74190891204</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8406,10 +8412,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8422,7 +8428,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B114" s="5">
         <v>46167.55727532407</v>
@@ -8432,7 +8438,7 @@
         <v>46167.74190642362</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8459,10 +8465,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8475,7 +8481,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B115" s="9">
         <v>46167.632606053245</v>
@@ -8485,7 +8491,7 @@
         <v>46167.7419037037</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8512,13 +8518,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8528,7 +8534,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46167.63261443287</v>
@@ -8538,7 +8544,7 @@
         <v>46167.74190121528</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8565,13 +8571,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8581,7 +8587,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B117" s="9">
         <v>46167.63262241898</v>
@@ -8591,7 +8597,7 @@
         <v>46167.74189892361</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8618,13 +8624,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8634,7 +8640,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B118" s="5">
         <v>46167.63263039352</v>
@@ -8644,7 +8650,7 @@
         <v>46167.74189655093</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8671,13 +8677,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8687,7 +8693,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B119" s="9">
         <v>46167.63269008102</v>
@@ -8697,7 +8703,7 @@
         <v>46167.74189145833</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8724,13 +8730,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8740,7 +8746,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B120" s="5">
         <v>46167.632698738424</v>
@@ -8750,7 +8756,7 @@
         <v>46167.74189078704</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8777,13 +8783,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8793,7 +8799,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B121" s="9">
         <v>46167.55727960648</v>
@@ -8803,7 +8809,7 @@
         <v>46167.74207511574</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8830,13 +8836,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q121" s="9">
         <v>46231</v>
@@ -8856,7 +8862,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B122" s="5">
         <v>46167.557284375</v>
@@ -8866,7 +8872,7 @@
         <v>46189.87510767361</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8893,13 +8899,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8909,7 +8915,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B123" s="9">
         <v>46167.55729009259</v>
@@ -8919,7 +8925,7 @@
         <v>46189.87510009259</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8946,13 +8952,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8962,7 +8968,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B124" s="5">
         <v>46167.6328130787</v>
@@ -8972,7 +8978,7 @@
         <v>46189.87508946759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8999,13 +9005,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9015,7 +9021,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B125" s="9">
         <v>46167.63283585648</v>
@@ -9025,7 +9031,7 @@
         <v>46189.87509015047</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9052,13 +9058,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9068,7 +9074,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B126" s="5">
         <v>46167.63284336806</v>
@@ -9078,7 +9084,7 @@
         <v>46189.87509105324</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9105,13 +9111,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9121,7 +9127,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B127" s="9">
         <v>46167.63285163195</v>
@@ -9131,7 +9137,7 @@
         <v>46189.87509177084</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9158,13 +9164,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9174,7 +9180,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B128" s="5">
         <v>46167.63289178241</v>
@@ -9184,7 +9190,7 @@
         <v>46189.87509244213</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9211,13 +9217,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9227,7 +9233,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B129" s="9">
         <v>46167.632899212964</v>
@@ -9237,7 +9243,7 @@
         <v>46189.8750930324</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9264,13 +9270,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9280,7 +9286,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B130" s="5">
         <v>46167.55733736111</v>
@@ -9290,7 +9296,7 @@
         <v>46167.74221776621</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9317,13 +9323,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q130" s="5">
         <v>46232</v>
@@ -9343,7 +9349,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B131" s="9">
         <v>46167.557343645836</v>
@@ -9353,7 +9359,7 @@
         <v>46189.87510797454</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9378,13 +9384,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9394,7 +9400,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B132" s="5">
         <v>46167.55735079861</v>
@@ -9404,7 +9410,7 @@
         <v>46189.87510071759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9429,13 +9435,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9445,7 +9451,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B133" s="9">
         <v>46167.63302359954</v>
@@ -9455,7 +9461,7 @@
         <v>46189.875093634255</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9480,13 +9486,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9496,7 +9502,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B134" s="5">
         <v>46167.63303486111</v>
@@ -9506,7 +9512,7 @@
         <v>46189.8750941551</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9531,13 +9537,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9547,7 +9553,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B135" s="9">
         <v>46167.633050648146</v>
@@ -9557,7 +9563,7 @@
         <v>46189.87509472222</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9582,13 +9588,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9598,7 +9604,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B136" s="5">
         <v>46167.633060671295</v>
@@ -9608,7 +9614,7 @@
         <v>46189.87509519676</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9633,13 +9639,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9649,7 +9655,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B137" s="9">
         <v>46167.633115185185</v>
@@ -9659,7 +9665,7 @@
         <v>46189.87509570602</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9684,13 +9690,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9700,7 +9706,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B138" s="5">
         <v>46167.6331228125</v>
@@ -9710,7 +9716,7 @@
         <v>46189.87509615741</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9735,13 +9741,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9751,7 +9757,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B139" s="9">
         <v>46167.557357488426</v>
@@ -9761,7 +9767,7 @@
         <v>46167.74236513889</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9788,13 +9794,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q139" s="9">
         <v>46233</v>
@@ -9814,7 +9820,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B140" s="5">
         <v>46167.55736211805</v>
@@ -9824,7 +9830,7 @@
         <v>46189.877459745374</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9851,13 +9857,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9867,7 +9873,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B141" s="9">
         <v>46167.55737267361</v>
@@ -9877,7 +9883,7 @@
         <v>46189.87746077546</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9904,13 +9910,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9920,7 +9926,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B142" s="5">
         <v>46167.63325159722</v>
@@ -9930,7 +9936,7 @@
         <v>46189.877455671296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9957,13 +9963,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9973,7 +9979,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B143" s="9">
         <v>46167.63325929398</v>
@@ -9983,7 +9989,7 @@
         <v>46189.87745677083</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10010,13 +10016,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10026,7 +10032,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B144" s="5">
         <v>46167.633274293985</v>
@@ -10036,7 +10042,7 @@
         <v>46189.87745732639</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10063,13 +10069,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10079,7 +10085,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B145" s="9">
         <v>46167.633281875</v>
@@ -10089,7 +10095,7 @@
         <v>46189.877457916664</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10116,13 +10122,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10132,7 +10138,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B146" s="5">
         <v>46167.63332260417</v>
@@ -10142,7 +10148,7 @@
         <v>46189.87745863426</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10169,13 +10175,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10185,7 +10191,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B147" s="9">
         <v>46167.633331689816</v>
@@ -10195,7 +10201,7 @@
         <v>46189.87745917824</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10222,13 +10228,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10238,7 +10244,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B148" s="5">
         <v>46167.557378287034</v>
@@ -10248,7 +10254,7 @@
         <v>46167.742498472224</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10275,13 +10281,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q148" s="5">
         <v>46234</v>
@@ -10301,7 +10307,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B149" s="9">
         <v>46167.55738292824</v>
@@ -10311,7 +10317,7 @@
         <v>46167.742493136575</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10338,13 +10344,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10354,7 +10360,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B150" s="5">
         <v>46167.5573883912</v>
@@ -10364,7 +10370,7 @@
         <v>46167.742490000004</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10391,13 +10397,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10407,7 +10413,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B151" s="9">
         <v>46167.63341660879</v>
@@ -10417,7 +10423,7 @@
         <v>46167.74248716435</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10444,13 +10450,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10460,7 +10466,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B152" s="5">
         <v>46167.63343371528</v>
@@ -10470,7 +10476,7 @@
         <v>46167.74248396991</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10497,13 +10503,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10513,7 +10519,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B153" s="9">
         <v>46167.63344365741</v>
@@ -10523,7 +10529,7 @@
         <v>46167.742481134264</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10550,13 +10556,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10566,7 +10572,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B154" s="5">
         <v>46167.63345188658</v>
@@ -10576,7 +10582,7 @@
         <v>46167.74247835648</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10603,13 +10609,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10619,7 +10625,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B155" s="9">
         <v>46167.633506412036</v>
@@ -10629,7 +10635,7 @@
         <v>46167.74247142361</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10656,13 +10662,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10672,7 +10678,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B156" s="5">
         <v>46167.63351399306</v>
@@ -10682,7 +10688,7 @@
         <v>46167.74247065972</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10709,13 +10715,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10725,7 +10731,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B157" s="9">
         <v>46167.55739407407</v>
@@ -10735,7 +10741,7 @@
         <v>46167.74264841435</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10762,13 +10768,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q157" s="9">
         <v>46238</v>
@@ -10788,7 +10794,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B158" s="5">
         <v>46167.55739920139</v>
@@ -10798,7 +10804,7 @@
         <v>46167.742638298616</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10825,13 +10831,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10841,7 +10847,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B159" s="9">
         <v>46167.5574040162</v>
@@ -10851,7 +10857,7 @@
         <v>46167.74263541667</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10878,13 +10884,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10894,7 +10900,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B160" s="5">
         <v>46167.633843206015</v>
@@ -10904,7 +10910,7 @@
         <v>46167.742632037036</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10931,13 +10937,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10947,7 +10953,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B161" s="9">
         <v>46167.633849895836</v>
@@ -10957,7 +10963,7 @@
         <v>46167.742628935186</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -10984,13 +10990,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11000,7 +11006,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B162" s="5">
         <v>46167.63385791666</v>
@@ -11010,7 +11016,7 @@
         <v>46167.74262635417</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11037,13 +11043,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11053,7 +11059,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B163" s="9">
         <v>46167.633867083336</v>
@@ -11063,7 +11069,7 @@
         <v>46167.74262355324</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11090,13 +11096,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11106,7 +11112,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B164" s="5">
         <v>46167.63391234954</v>
@@ -11116,7 +11122,7 @@
         <v>46167.742617407406</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11143,13 +11149,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11159,7 +11165,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B165" s="9">
         <v>46167.63392017361</v>
@@ -11169,7 +11175,7 @@
         <v>46167.74261677083</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11196,13 +11202,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11212,7 +11218,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B166" s="5">
         <v>46167.557409201385</v>
@@ -11222,7 +11228,7 @@
         <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -11246,7 +11252,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11259,7 +11265,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B167" s="9">
         <v>46167.5574132176</v>
@@ -11269,16 +11275,16 @@
         <v>46167.74284238426</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I167" s="9">
         <v>46230</v>
@@ -11296,13 +11302,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q167" s="9">
         <v>46230</v>
@@ -11322,7 +11328,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B168" s="5">
         <v>46167.55742054398</v>
@@ -11332,16 +11338,16 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I168" s="5">
         <v>46239</v>
@@ -11359,13 +11365,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11375,7 +11381,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B169" s="9">
         <v>46167.557425520834</v>
@@ -11385,16 +11391,16 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I169" s="9">
         <v>46239</v>
@@ -11412,13 +11418,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11428,7 +11434,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B170" s="5">
         <v>46167.55743020833</v>
@@ -11438,16 +11444,16 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I170" s="5">
         <v>46239</v>
@@ -11465,13 +11471,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11481,7 +11487,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B171" s="9">
         <v>46167.557434918985</v>
@@ -11491,16 +11497,16 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I171" s="9">
         <v>46239</v>
@@ -11518,13 +11524,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11534,7 +11540,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B172" s="5">
         <v>46167.636403032404</v>
@@ -11544,16 +11550,16 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I172" s="5">
         <v>46239</v>
@@ -11571,13 +11577,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11587,7 +11593,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B173" s="9">
         <v>46167.63641173611</v>
@@ -11597,16 +11603,16 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I173" s="9">
         <v>46239</v>
@@ -11624,13 +11630,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11640,7 +11646,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B174" s="5">
         <v>46167.636428645834</v>
@@ -11650,16 +11656,16 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I174" s="5">
         <v>46239</v>
@@ -11677,13 +11683,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11693,7 +11699,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B175" s="9">
         <v>46167.636439849535</v>
@@ -11703,16 +11709,16 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I175" s="9">
         <v>46239</v>
@@ -11730,13 +11736,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11746,7 +11752,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B176" s="5">
         <v>46167.636677511575</v>
@@ -11762,10 +11768,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I176" s="5">
         <v>46230</v>
@@ -11783,7 +11789,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>63</v>
@@ -11799,7 +11805,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B177" s="9">
         <v>46167.63669306713</v>
@@ -11815,10 +11821,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I177" s="9">
         <v>46230</v>
@@ -11836,7 +11842,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>63</v>
@@ -11852,7 +11858,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B178" s="5">
         <v>46167.6367015162</v>
@@ -11868,10 +11874,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I178" s="5">
         <v>46230</v>
@@ -11889,7 +11895,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>63</v>
@@ -11905,7 +11911,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B179" s="9">
         <v>46167.6367112963</v>
@@ -11921,10 +11927,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I179" s="9">
         <v>46230</v>
@@ -11942,7 +11948,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>63</v>
@@ -11958,7 +11964,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B180" s="5">
         <v>46167.63672008102</v>
@@ -11974,10 +11980,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I180" s="5">
         <v>46230</v>
@@ -11995,7 +12001,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>63</v>
@@ -12011,7 +12017,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B181" s="9">
         <v>46167.636729247686</v>
@@ -12027,10 +12033,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I181" s="9">
         <v>46230</v>
@@ -12048,7 +12054,7 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O181" s="10" t="s">
         <v>63</v>
@@ -12064,7 +12070,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B182" s="5">
         <v>46167.63683603009</v>
@@ -12080,10 +12086,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I182" s="5">
         <v>46230</v>
@@ -12101,7 +12107,7 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>71</v>
@@ -12117,7 +12123,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B183" s="9">
         <v>46167.636846319445</v>
@@ -12133,10 +12139,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I183" s="9">
         <v>46230</v>
@@ -12154,7 +12160,7 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>71</v>
@@ -12170,7 +12176,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B184" s="5">
         <v>46167.55743945602</v>
@@ -12180,7 +12186,7 @@
         <v>46167.7430450463</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12207,13 +12213,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q184" s="5">
         <v>46231</v>
@@ -12233,7 +12239,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B185" s="9">
         <v>46167.55744423611</v>
@@ -12243,7 +12249,7 @@
         <v>46167.74306620371</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12268,13 +12274,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12284,7 +12290,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B186" s="5">
         <v>46167.55744884259</v>
@@ -12294,7 +12300,7 @@
         <v>46167.74306335648</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12319,13 +12325,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12335,7 +12341,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B187" s="9">
         <v>46167.55745349537</v>
@@ -12345,7 +12351,7 @@
         <v>46167.74306008102</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12370,13 +12376,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12386,7 +12392,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B188" s="5">
         <v>46167.55745777777</v>
@@ -12396,7 +12402,7 @@
         <v>46167.74305738426</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12421,13 +12427,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12437,7 +12443,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B189" s="9">
         <v>46167.637670833334</v>
@@ -12447,7 +12453,7 @@
         <v>46167.74305466435</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12472,13 +12478,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12488,7 +12494,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B190" s="5">
         <v>46167.63768076389</v>
@@ -12498,7 +12504,7 @@
         <v>46167.743051990736</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12523,13 +12529,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12539,7 +12545,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B191" s="9">
         <v>46167.637724016204</v>
@@ -12549,7 +12555,7 @@
         <v>46167.74304920139</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12574,13 +12580,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12590,7 +12596,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B192" s="5">
         <v>46167.63773231482</v>
@@ -12600,7 +12606,7 @@
         <v>46167.743046574076</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12625,13 +12631,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12641,7 +12647,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B193" s="9">
         <v>46167.63788011574</v>
@@ -12678,7 +12684,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>64</v>
@@ -12694,7 +12700,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B194" s="5">
         <v>46167.637888530095</v>
@@ -12731,7 +12737,7 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O194" s="6" t="s">
         <v>63</v>
@@ -12747,7 +12753,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B195" s="9">
         <v>46167.63789722222</v>
@@ -12784,7 +12790,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O195" s="10" t="s">
         <v>63</v>
@@ -12800,7 +12806,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B196" s="5">
         <v>46167.63790768519</v>
@@ -12837,7 +12843,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
@@ -12853,7 +12859,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B197" s="9">
         <v>46167.63791662037</v>
@@ -12890,7 +12896,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>63</v>
@@ -12906,7 +12912,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B198" s="5">
         <v>46167.637946689814</v>
@@ -12943,7 +12949,7 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
@@ -12959,7 +12965,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B199" s="9">
         <v>46167.637995729165</v>
@@ -12996,7 +13002,7 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>71</v>
@@ -13012,7 +13018,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B200" s="5">
         <v>46167.63800420139</v>
@@ -13049,7 +13055,7 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>71</v>
@@ -13065,7 +13071,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B201" s="9">
         <v>46167.55746224537</v>
@@ -13075,16 +13081,16 @@
         <v>46167.74364532407</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13102,13 +13108,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q201" s="9">
         <v>46241</v>
@@ -13128,7 +13134,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B202" s="5">
         <v>46167.55746689815</v>
@@ -13138,16 +13144,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13165,13 +13171,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13181,7 +13187,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B203" s="9">
         <v>46167.55747543981</v>
@@ -13191,16 +13197,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13218,13 +13224,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13234,7 +13240,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B204" s="5">
         <v>46167.557519270835</v>
@@ -13244,16 +13250,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13271,13 +13277,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13287,7 +13293,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B205" s="9">
         <v>46167.5575253125</v>
@@ -13297,16 +13303,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13324,13 +13330,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13340,7 +13346,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B206" s="5">
         <v>46167.6385715162</v>
@@ -13350,16 +13356,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13377,13 +13383,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13393,7 +13399,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B207" s="9">
         <v>46167.63857899306</v>
@@ -13403,16 +13409,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13430,13 +13436,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13446,7 +13452,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B208" s="5">
         <v>46167.638659930555</v>
@@ -13456,16 +13462,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13483,13 +13489,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13499,7 +13505,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B209" s="9">
         <v>46167.638666956016</v>
@@ -13509,16 +13515,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13536,13 +13542,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13552,7 +13558,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B210" s="5">
         <v>46167.6387090162</v>
@@ -13568,10 +13574,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13589,7 +13595,7 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>63</v>
@@ -13605,7 +13611,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B211" s="9">
         <v>46167.63871641204</v>
@@ -13621,10 +13627,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13642,7 +13648,7 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>63</v>
@@ -13658,7 +13664,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B212" s="5">
         <v>46167.638723599535</v>
@@ -13674,10 +13680,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13695,7 +13701,7 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>63</v>
@@ -13711,7 +13717,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B213" s="9">
         <v>46167.63873144676</v>
@@ -13727,10 +13733,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13748,7 +13754,7 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>63</v>
@@ -13764,7 +13770,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B214" s="5">
         <v>46167.6387405787</v>
@@ -13780,10 +13786,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13801,7 +13807,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>63</v>
@@ -13817,7 +13823,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B215" s="9">
         <v>46167.63874844907</v>
@@ -13833,10 +13839,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -13854,7 +13860,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>63</v>
@@ -13870,7 +13876,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B216" s="5">
         <v>46167.638756562505</v>
@@ -13886,10 +13892,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -13907,13 +13913,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13923,7 +13929,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B217" s="9">
         <v>46167.63883428241</v>
@@ -13939,10 +13945,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -13960,13 +13966,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13976,7 +13982,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B218" s="5">
         <v>46167.55752998842</v>
@@ -13986,16 +13992,16 @@
         <v>46167.74382108796</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -14013,13 +14019,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Q218" s="5">
         <v>46244</v>
@@ -14039,7 +14045,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B219" s="9">
         <v>46167.55753614583</v>
@@ -14049,16 +14055,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14076,13 +14082,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14092,7 +14098,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B220" s="5">
         <v>46167.557540381946</v>
@@ -14102,16 +14108,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14129,13 +14135,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14145,7 +14151,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B221" s="9">
         <v>46167.557545069445</v>
@@ -14155,16 +14161,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14182,13 +14188,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14198,7 +14204,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B222" s="5">
         <v>46167.55754895833</v>
@@ -14208,16 +14214,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14235,13 +14241,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14251,7 +14257,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B223" s="9">
         <v>46167.63903770833</v>
@@ -14261,16 +14267,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14288,10 +14294,10 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14304,7 +14310,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B224" s="5">
         <v>46167.639049317135</v>
@@ -14314,16 +14320,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14341,10 +14347,10 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14357,7 +14363,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B225" s="9">
         <v>46167.639172118055</v>
@@ -14367,16 +14373,16 @@
         <v>46167.743832430555</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14394,10 +14400,10 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14410,7 +14416,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B226" s="5">
         <v>46167.63918146991</v>
@@ -14420,16 +14426,16 @@
         <v>46167.74382957176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14447,10 +14453,10 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14463,7 +14469,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B227" s="9">
         <v>46167.63922125</v>
@@ -14479,10 +14485,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14500,7 +14506,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>63</v>
@@ -14516,7 +14522,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B228" s="5">
         <v>46167.63923230324</v>
@@ -14532,10 +14538,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14553,7 +14559,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>63</v>
@@ -14569,7 +14575,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B229" s="9">
         <v>46167.63924049769</v>
@@ -14585,10 +14591,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14606,7 +14612,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>63</v>
@@ -14622,7 +14628,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B230" s="5">
         <v>46167.63924949074</v>
@@ -14638,10 +14644,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14659,7 +14665,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>63</v>
@@ -14675,7 +14681,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B231" s="9">
         <v>46167.639259375</v>
@@ -14691,10 +14697,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14712,7 +14718,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>63</v>
@@ -14728,7 +14734,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B232" s="5">
         <v>46167.63926804398</v>
@@ -14744,10 +14750,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14765,7 +14771,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>63</v>
@@ -14781,7 +14787,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B233" s="9">
         <v>46167.63935532408</v>
@@ -14791,16 +14797,16 @@
         <v>46167.74380655093</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14818,7 +14824,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>71</v>
@@ -14834,7 +14840,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B234" s="5">
         <v>46167.63936689815</v>
@@ -14844,16 +14850,16 @@
         <v>46167.74380591435</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>
@@ -14871,7 +14877,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>71</v>
@@ -14887,7 +14893,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B235" s="9">
         <v>46167.55755266204</v>
@@ -14897,7 +14903,7 @@
         <v>46167.73498962963</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>25</v>
@@ -14921,7 +14927,7 @@
         <v>26</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>26</v>
@@ -14934,7 +14940,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B236" s="5">
         <v>46167.55755585648</v>
@@ -14944,16 +14950,16 @@
         <v>46167.743865428245</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I236" s="5">
         <v>46245</v>
@@ -14971,13 +14977,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Q236" s="5">
         <v>46245</v>
@@ -14997,7 +15003,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B237" s="9">
         <v>46167.55756052083</v>
@@ -15007,7 +15013,7 @@
         <v>46189.872060740745</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15034,13 +15040,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Q237" s="9">
         <v>46245</v>
@@ -15060,7 +15066,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B238" s="5">
         <v>46167.557566296295</v>
@@ -15070,7 +15076,7 @@
         <v>46167.73546241898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>25</v>
@@ -15094,7 +15100,7 @@
         <v>26</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>26</v>
@@ -15113,7 +15119,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B239" s="9">
         <v>46167.55756988426</v>
@@ -15123,7 +15129,7 @@
         <v>46167.743959513886</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15150,13 +15156,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="Q239" s="9">
         <v>46245</v>
@@ -15176,7 +15182,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B240" s="5">
         <v>46167.557574895836</v>
@@ -15186,7 +15192,7 @@
         <v>46167.74395664352</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15213,13 +15219,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="Q240" s="5">
         <v>46254</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -207,70 +207,70 @@
     <t xml:space="preserve">Ingenieria Servicios ,Propuesta Tableros ot 4329 - 4331 </t>
   </si>
   <si>
+    <t>1215103975074444</t>
+  </si>
+  <si>
+    <t>Revision Tableros</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
+    <t>Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215103495723681</t>
+  </si>
+  <si>
+    <t>OT 4329 - TABLERO SS 86 KW</t>
+  </si>
+  <si>
+    <t>OT  4329 - TABLERO SS 86 KW</t>
+  </si>
+  <si>
+    <t>1215103495723683</t>
+  </si>
+  <si>
+    <t>1215103495723684</t>
+  </si>
+  <si>
+    <t>1215103495723685</t>
+  </si>
+  <si>
+    <t>1215103495723686</t>
+  </si>
+  <si>
+    <t>1215103495723687</t>
+  </si>
+  <si>
+    <t>1215103495723688</t>
+  </si>
+  <si>
+    <t>OT 4331- TABLERO SS 63 KW</t>
+  </si>
+  <si>
+    <t>1215103495723689</t>
+  </si>
+  <si>
+    <t>1215118022011727</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215103975074444</t>
-  </si>
-  <si>
-    <t>Revision Tableros</t>
-  </si>
-  <si>
-    <t>sergio saavedra fernandez</t>
-  </si>
-  <si>
-    <t>sergio.saavedra@zitron.com</t>
-  </si>
-  <si>
-    <t>Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215103495723681</t>
-  </si>
-  <si>
-    <t>OT 4329 - TABLERO SS 86 KW</t>
-  </si>
-  <si>
-    <t>OT  4329 - TABLERO SS 86 KW</t>
-  </si>
-  <si>
-    <t>1215103495723683</t>
-  </si>
-  <si>
-    <t>1215103495723684</t>
-  </si>
-  <si>
-    <t>1215103495723685</t>
-  </si>
-  <si>
-    <t>1215103495723686</t>
-  </si>
-  <si>
-    <t>1215103495723687</t>
-  </si>
-  <si>
-    <t>1215103495723688</t>
-  </si>
-  <si>
-    <t>OT 4331- TABLERO SS 63 KW</t>
-  </si>
-  <si>
-    <t>1215103495723689</t>
-  </si>
-  <si>
-    <t>1215118022011727</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
   </si>
   <si>
     <t>1215103975074463</t>
@@ -1587,12 +1587,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.73177047454</v>
+        <v>46198.63710824074</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2562,9 +2562,11 @@
       <c r="B11" s="9">
         <v>46167.55677776621</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46198.637101898144</v>
+      </c>
       <c r="D11" s="9">
-        <v>46175.878151412035</v>
+        <v>46198.637119039355</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2612,15 +2614,15 @@
         <v>33</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46167.55678319444</v>
@@ -2630,16 +2632,16 @@
         <v>46167.73745994213</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I12" s="5">
         <v>46223</v>
@@ -2660,10 +2662,10 @@
         <v>47</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>46223</v>
@@ -2677,13 +2679,13 @@
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="12" t="s">
-        <v>61</v>
+      <c r="U12" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="9">
         <v>46167.63411775463</v>
@@ -2693,16 +2695,16 @@
         <v>46167.73754430556</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I13" s="9">
         <v>46223</v>
@@ -2720,13 +2722,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2736,7 +2738,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46167.63443420139</v>
@@ -2746,16 +2748,16 @@
         <v>46167.7375415162</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I14" s="5">
         <v>46223</v>
@@ -2773,13 +2775,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2789,7 +2791,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" s="9">
         <v>46167.634455694446</v>
@@ -2799,16 +2801,16 @@
         <v>46167.737538692134</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I15" s="9">
         <v>46223</v>
@@ -2826,13 +2828,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2842,7 +2844,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5">
         <v>46167.63446537037</v>
@@ -2852,16 +2854,16 @@
         <v>46167.737535625</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I16" s="5">
         <v>46223</v>
@@ -2879,13 +2881,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2895,7 +2897,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="9">
         <v>46167.6344740162</v>
@@ -2905,16 +2907,16 @@
         <v>46167.73753288195</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I17" s="9">
         <v>46223</v>
@@ -2932,13 +2934,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2948,7 +2950,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="5">
         <v>46167.63448084491</v>
@@ -2958,16 +2960,16 @@
         <v>46167.73753034722</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I18" s="5">
         <v>46223</v>
@@ -2985,13 +2987,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -3001,7 +3003,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="9">
         <v>46167.63453541667</v>
@@ -3011,16 +3013,16 @@
         <v>46167.737524641205</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="I19" s="9">
         <v>46223</v>
@@ -3038,13 +3040,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
@@ -3054,7 +3056,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="5">
         <v>46167.63474393518</v>
@@ -3064,16 +3066,16 @@
         <v>46171.51095925926</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I20" s="5">
         <v>46223</v>
@@ -3091,13 +3093,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
@@ -3107,7 +3109,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="9">
         <v>46167.55662649305</v>
@@ -3117,7 +3119,7 @@
         <v>46189.87207028935</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -3141,7 +3143,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -3150,8 +3152,8 @@
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
-      <c r="U21" s="11" t="s">
-        <v>54</v>
+      <c r="U21" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -3195,7 +3197,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>40</v>
@@ -3260,7 +3262,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>40</v>
@@ -3325,7 +3327,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>40</v>
@@ -3520,8 +3522,8 @@
       <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="11" t="s">
-        <v>54</v>
+      <c r="U27" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3644,7 +3646,7 @@
       <c r="R29" s="9">
         <v>46191</v>
       </c>
-      <c r="S29" s="12" t="s">
+      <c r="S29" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T29" s="10">
@@ -3709,7 +3711,7 @@
       <c r="R30" s="5">
         <v>46191</v>
       </c>
-      <c r="S30" s="12" t="s">
+      <c r="S30" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T30" s="6">
@@ -3774,7 +3776,7 @@
       <c r="R31" s="9">
         <v>46191</v>
       </c>
-      <c r="S31" s="12" t="s">
+      <c r="S31" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T31" s="10">
@@ -3839,7 +3841,7 @@
       <c r="R32" s="5">
         <v>46191</v>
       </c>
-      <c r="S32" s="12" t="s">
+      <c r="S32" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T32" s="6">
@@ -3858,7 +3860,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.87886138889</v>
+        <v>46198.63712021991</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>118</v>
@@ -3909,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -4020,7 +4022,7 @@
       <c r="R35" s="9">
         <v>46167</v>
       </c>
-      <c r="S35" s="12" t="s">
+      <c r="S35" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T35" s="10">
@@ -4085,7 +4087,7 @@
       <c r="R36" s="5">
         <v>46167</v>
       </c>
-      <c r="S36" s="12" t="s">
+      <c r="S36" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T36" s="6">
@@ -4197,7 +4199,7 @@
       <c r="R38" s="5">
         <v>46183</v>
       </c>
-      <c r="S38" s="12" t="s">
+      <c r="S38" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T38" s="6">
@@ -4264,8 +4266,8 @@
       <c r="T39" s="10">
         <v>0</v>
       </c>
-      <c r="U39" s="12" t="s">
-        <v>61</v>
+      <c r="U39" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4325,8 +4327,8 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>61</v>
+      <c r="U40" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4388,8 +4390,8 @@
       <c r="T41" s="10">
         <v>0</v>
       </c>
-      <c r="U41" s="12" t="s">
-        <v>61</v>
+      <c r="U41" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4551,14 +4553,14 @@
       <c r="R44" s="5">
         <v>46204</v>
       </c>
-      <c r="S44" s="11" t="s">
+      <c r="S44" s="12" t="s">
         <v>155</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>61</v>
+      <c r="U44" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4616,8 +4618,8 @@
       <c r="T45" s="10">
         <v>0</v>
       </c>
-      <c r="U45" s="12" t="s">
-        <v>61</v>
+      <c r="U45" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4675,8 +4677,8 @@
       <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="U46" s="12" t="s">
-        <v>61</v>
+      <c r="U46" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4732,14 +4734,14 @@
       <c r="R47" s="9">
         <v>46204</v>
       </c>
-      <c r="S47" s="11" t="s">
+      <c r="S47" s="12" t="s">
         <v>155</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>61</v>
+      <c r="U47" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4907,8 +4909,8 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
-        <v>61</v>
+      <c r="U50" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5123,14 +5125,14 @@
       <c r="R54" s="5">
         <v>46204</v>
       </c>
-      <c r="S54" s="11" t="s">
+      <c r="S54" s="12" t="s">
         <v>155</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>61</v>
+      <c r="U54" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -5341,7 +5343,7 @@
       <c r="R58" s="5">
         <v>46168</v>
       </c>
-      <c r="S58" s="12" t="s">
+      <c r="S58" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T58" s="6">
@@ -5406,7 +5408,7 @@
       <c r="R59" s="9">
         <v>46188</v>
       </c>
-      <c r="S59" s="12" t="s">
+      <c r="S59" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T59" s="10">
@@ -5471,7 +5473,7 @@
       <c r="R60" s="5">
         <v>46189</v>
       </c>
-      <c r="S60" s="12" t="s">
+      <c r="S60" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T60" s="6">
@@ -5540,8 +5542,8 @@
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="12" t="s">
-        <v>61</v>
+      <c r="U61" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -6074,8 +6076,8 @@
       <c r="T71" s="10">
         <v>0</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>61</v>
+      <c r="U71" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -6137,8 +6139,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>61</v>
+      <c r="U72" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6200,8 +6202,8 @@
       <c r="T73" s="10">
         <v>0</v>
       </c>
-      <c r="U73" s="12" t="s">
-        <v>61</v>
+      <c r="U73" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6263,8 +6265,8 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>61</v>
+      <c r="U74" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6326,8 +6328,8 @@
       <c r="T75" s="10">
         <v>0</v>
       </c>
-      <c r="U75" s="12" t="s">
-        <v>61</v>
+      <c r="U75" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6389,8 +6391,8 @@
       <c r="T76" s="6">
         <v>0</v>
       </c>
-      <c r="U76" s="12" t="s">
-        <v>61</v>
+      <c r="U76" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6499,8 +6501,8 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>61</v>
+      <c r="U78" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6986,8 +6988,8 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
-        <v>61</v>
+      <c r="U87" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -7473,8 +7475,8 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="12" t="s">
-        <v>61</v>
+      <c r="U96" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -8001,14 +8003,14 @@
       <c r="R106" s="5">
         <v>46184</v>
       </c>
-      <c r="S106" s="12" t="s">
+      <c r="S106" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="11" t="s">
-        <v>54</v>
+      <c r="U106" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8064,14 +8066,14 @@
       <c r="R107" s="9">
         <v>46167</v>
       </c>
-      <c r="S107" s="12" t="s">
+      <c r="S107" s="11" t="s">
         <v>107</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="11" t="s">
-        <v>54</v>
+      <c r="U107" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -8133,8 +8135,8 @@
       <c r="T108" s="6">
         <v>0</v>
       </c>
-      <c r="U108" s="11" t="s">
-        <v>54</v>
+      <c r="U108" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8196,8 +8198,8 @@
       <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="12" t="s">
-        <v>61</v>
+      <c r="U109" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8212,7 +8214,7 @@
         <v>46167.74163472222</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8259,8 +8261,8 @@
       <c r="T110" s="6">
         <v>0</v>
       </c>
-      <c r="U110" s="12" t="s">
-        <v>61</v>
+      <c r="U110" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -8369,8 +8371,8 @@
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="12" t="s">
-        <v>61</v>
+      <c r="U112" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8856,8 +8858,8 @@
       <c r="T121" s="10">
         <v>0</v>
       </c>
-      <c r="U121" s="12" t="s">
-        <v>61</v>
+      <c r="U121" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -9343,8 +9345,8 @@
       <c r="T130" s="6">
         <v>0</v>
       </c>
-      <c r="U130" s="12" t="s">
-        <v>61</v>
+      <c r="U130" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9814,8 +9816,8 @@
       <c r="T139" s="10">
         <v>0</v>
       </c>
-      <c r="U139" s="12" t="s">
-        <v>61</v>
+      <c r="U139" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
@@ -10301,8 +10303,8 @@
       <c r="T148" s="6">
         <v>0</v>
       </c>
-      <c r="U148" s="12" t="s">
-        <v>61</v>
+      <c r="U148" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
@@ -10788,8 +10790,8 @@
       <c r="T157" s="10">
         <v>0</v>
       </c>
-      <c r="U157" s="12" t="s">
-        <v>61</v>
+      <c r="U157" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
@@ -11322,8 +11324,8 @@
       <c r="T167" s="10">
         <v>0</v>
       </c>
-      <c r="U167" s="12" t="s">
-        <v>61</v>
+      <c r="U167" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11762,7 +11764,7 @@
         <v>46167.742840844905</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11792,10 +11794,10 @@
         <v>389</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11815,7 +11817,7 @@
         <v>46167.742838136575</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11845,10 +11847,10 @@
         <v>389</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11868,7 +11870,7 @@
         <v>46167.742835763886</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11898,10 +11900,10 @@
         <v>389</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11921,7 +11923,7 @@
         <v>46167.74282516204</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11951,10 +11953,10 @@
         <v>389</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11974,7 +11976,7 @@
         <v>46167.742824456014</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12004,10 +12006,10 @@
         <v>389</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12027,7 +12029,7 @@
         <v>46167.74282375</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12057,10 +12059,10 @@
         <v>389</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12080,7 +12082,7 @@
         <v>46167.74282306713</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12110,10 +12112,10 @@
         <v>389</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12133,7 +12135,7 @@
         <v>46167.74282237269</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12163,10 +12165,10 @@
         <v>389</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12233,8 +12235,8 @@
       <c r="T184" s="6">
         <v>0</v>
       </c>
-      <c r="U184" s="12" t="s">
-        <v>61</v>
+      <c r="U184" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
@@ -12657,7 +12659,7 @@
         <v>46167.74304366898</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12687,10 +12689,10 @@
         <v>411</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12710,7 +12712,7 @@
         <v>46167.743040671296</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12740,10 +12742,10 @@
         <v>411</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12763,7 +12765,7 @@
         <v>46167.74303790509</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12793,10 +12795,10 @@
         <v>411</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12816,7 +12818,7 @@
         <v>46167.743035231484</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12846,10 +12848,10 @@
         <v>411</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12869,7 +12871,7 @@
         <v>46167.74302515046</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12899,10 +12901,10 @@
         <v>411</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12922,7 +12924,7 @@
         <v>46167.74302446759</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12952,10 +12954,10 @@
         <v>411</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12975,7 +12977,7 @@
         <v>46167.74302380787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -13005,10 +13007,10 @@
         <v>411</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -13028,7 +13030,7 @@
         <v>46167.74302313657</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13058,10 +13060,10 @@
         <v>411</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13128,8 +13130,8 @@
       <c r="T201" s="10">
         <v>0</v>
       </c>
-      <c r="U201" s="12" t="s">
-        <v>61</v>
+      <c r="U201" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
@@ -13568,7 +13570,7 @@
         <v>46167.74365560185</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13598,10 +13600,10 @@
         <v>432</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13621,7 +13623,7 @@
         <v>46167.74365315972</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13651,10 +13653,10 @@
         <v>432</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13674,7 +13676,7 @@
         <v>46167.74365077546</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13704,10 +13706,10 @@
         <v>432</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13727,7 +13729,7 @@
         <v>46167.7436480787</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13757,10 +13759,10 @@
         <v>432</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13780,7 +13782,7 @@
         <v>46167.74363872685</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13810,10 +13812,10 @@
         <v>432</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13833,7 +13835,7 @@
         <v>46167.74363802084</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13863,10 +13865,10 @@
         <v>432</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13886,7 +13888,7 @@
         <v>46167.74363733796</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13916,7 +13918,7 @@
         <v>432</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>452</v>
@@ -13939,7 +13941,7 @@
         <v>46167.743636666666</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -13969,7 +13971,7 @@
         <v>432</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>452</v>
@@ -14039,8 +14041,8 @@
       <c r="T218" s="6">
         <v>0</v>
       </c>
-      <c r="U218" s="12" t="s">
-        <v>61</v>
+      <c r="U218" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
@@ -14479,7 +14481,7 @@
         <v>46167.74382638889</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14509,7 +14511,7 @@
         <v>455</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P227" s="10" t="s">
         <v>26</v>
@@ -14532,7 +14534,7 @@
         <v>46167.74382362269</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14562,7 +14564,7 @@
         <v>455</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P228" s="6" t="s">
         <v>26</v>
@@ -14585,7 +14587,7 @@
         <v>46167.74381421296</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
@@ -14615,7 +14617,7 @@
         <v>455</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P229" s="10" t="s">
         <v>26</v>
@@ -14638,7 +14640,7 @@
         <v>46167.74381306713</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -14668,7 +14670,7 @@
         <v>455</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P230" s="6" t="s">
         <v>26</v>
@@ -14691,7 +14693,7 @@
         <v>46167.74380835648</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
@@ -14721,7 +14723,7 @@
         <v>455</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P231" s="10" t="s">
         <v>26</v>
@@ -14744,7 +14746,7 @@
         <v>46167.74380726852</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14774,7 +14776,7 @@
         <v>455</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P232" s="6" t="s">
         <v>26</v>
@@ -14827,7 +14829,7 @@
         <v>455</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P233" s="10" t="s">
         <v>26</v>
@@ -14880,7 +14882,7 @@
         <v>455</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>26</v>
@@ -14997,8 +14999,8 @@
       <c r="T236" s="6">
         <v>0</v>
       </c>
-      <c r="U236" s="12" t="s">
-        <v>61</v>
+      <c r="U236" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
@@ -15060,8 +15062,8 @@
       <c r="T237" s="10">
         <v>0</v>
       </c>
-      <c r="U237" s="12" t="s">
-        <v>61</v>
+      <c r="U237" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
@@ -15113,8 +15115,8 @@
       <c r="T238" s="6">
         <v>0</v>
       </c>
-      <c r="U238" s="12" t="s">
-        <v>61</v>
+      <c r="U238" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
@@ -15176,8 +15178,8 @@
       <c r="T239" s="10">
         <v>0</v>
       </c>
-      <c r="U239" s="12" t="s">
-        <v>61</v>
+      <c r="U239" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
@@ -15239,8 +15241,8 @@
       <c r="T240" s="6">
         <v>0</v>
       </c>
-      <c r="U240" s="12" t="s">
-        <v>61</v>
+      <c r="U240" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6026,7 +6026,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46167.74094020833</v>
+        <v>46199.17020613426</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>228</v>
@@ -6070,8 +6070,8 @@
       <c r="R71" s="9">
         <v>46206</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>33</v>
+      <c r="S71" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46167.74093746528</v>
+        <v>46199.17020609954</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>237</v>
@@ -6196,8 +6196,8 @@
       <c r="R73" s="9">
         <v>46206</v>
       </c>
-      <c r="S73" s="7" t="s">
-        <v>33</v>
+      <c r="S73" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46167.740934733796</v>
+        <v>46199.17020608796</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>243</v>
@@ -6322,8 +6322,8 @@
       <c r="R75" s="9">
         <v>46206</v>
       </c>
-      <c r="S75" s="7" t="s">
-        <v>33</v>
+      <c r="S75" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2745" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="490">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46195.93002318287</v>
+        <v>46199.56372103009</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>129</v>
@@ -4142,7 +4142,9 @@
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
-      <c r="U37" s="10"/>
+      <c r="U37" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -4507,9 +4509,11 @@
       <c r="B44" s="5">
         <v>46167.556973784725</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46199.56370100695</v>
+      </c>
       <c r="D44" s="5">
-        <v>46197.202346921295</v>
+        <v>46199.56371440973</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>151</v>
@@ -4557,10 +4561,10 @@
         <v>155</v>
       </c>
       <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4570,9 +4574,11 @@
       <c r="B45" s="9">
         <v>46167.556978611115</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46199.56361858796</v>
+      </c>
       <c r="D45" s="9">
-        <v>46196.64908697917</v>
+        <v>46199.56362072917</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>157</v>
@@ -4629,9 +4635,11 @@
       <c r="B46" s="5">
         <v>46167.55698368055</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46199.56368543982</v>
+      </c>
       <c r="D46" s="5">
-        <v>46169.878329687504</v>
+        <v>46199.563687118054</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>160</v>
@@ -4688,9 +4696,11 @@
       <c r="B47" s="9">
         <v>46167.556988842596</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46199.563824745375</v>
+      </c>
       <c r="D47" s="9">
-        <v>46197.20234700231</v>
+        <v>46199.563835740744</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>163</v>
@@ -4738,10 +4748,10 @@
         <v>155</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4751,9 +4761,11 @@
       <c r="B48" s="5">
         <v>46167.556992708334</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46199.56375501158</v>
+      </c>
       <c r="D48" s="5">
-        <v>46196.64961313657</v>
+        <v>46199.56375667824</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4804,9 +4816,11 @@
       <c r="B49" s="9">
         <v>46167.5569971875</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46199.56381097222</v>
+      </c>
       <c r="D49" s="9">
-        <v>46169.87837792824</v>
+        <v>46199.56447744213</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>168</v>
@@ -5079,9 +5093,11 @@
       <c r="B54" s="5">
         <v>46167.55701769676</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46199.56460204862</v>
+      </c>
       <c r="D54" s="5">
-        <v>46197.202346817125</v>
+        <v>46199.564615462965</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>185</v>
@@ -5129,10 +5145,10 @@
         <v>155</v>
       </c>
       <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -5142,9 +5158,11 @@
       <c r="B55" s="9">
         <v>46167.557021678236</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46199.56439893518</v>
+      </c>
       <c r="D55" s="9">
-        <v>46196.651095995374</v>
+        <v>46199.564400601856</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>113</v>
@@ -5195,9 +5213,11 @@
       <c r="B56" s="5">
         <v>46167.55702634259</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46199.56458818287</v>
+      </c>
       <c r="D56" s="5">
-        <v>46169.87850571759</v>
+        <v>46199.56458967592</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>190</v>
@@ -6026,7 +6046,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46199.17020613426</v>
+        <v>46199.56370296296</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>228</v>
@@ -6076,8 +6096,8 @@
       <c r="T71" s="10">
         <v>0</v>
       </c>
-      <c r="U71" s="11" t="s">
-        <v>60</v>
+      <c r="U71" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -6152,7 +6172,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46199.17020609954</v>
+        <v>46199.563827962964</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>237</v>
@@ -6202,8 +6222,8 @@
       <c r="T73" s="10">
         <v>0</v>
       </c>
-      <c r="U73" s="11" t="s">
-        <v>60</v>
+      <c r="U73" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6278,7 +6298,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46199.17020608796</v>
+        <v>46199.56460534722</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>243</v>
@@ -6328,8 +6348,8 @@
       <c r="T75" s="10">
         <v>0</v>
       </c>
-      <c r="U75" s="11" t="s">
-        <v>60</v>
+      <c r="U75" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46196.6518865625</v>
+        <v>46202.169510775464</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>116</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6109,7 +6109,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46167.7410212963</v>
+        <v>46203.19671185185</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -6153,8 +6153,8 @@
       <c r="R72" s="5">
         <v>46210</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>33</v>
+      <c r="S72" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46167.74101869213</v>
+        <v>46203.19671157407</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>240</v>
@@ -6279,8 +6279,8 @@
       <c r="R74" s="5">
         <v>46210</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>33</v>
+      <c r="S74" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46167.74101563657</v>
+        <v>46203.196711412034</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>244</v>
@@ -6405,8 +6405,8 @@
       <c r="R76" s="5">
         <v>46210</v>
       </c>
-      <c r="S76" s="7" t="s">
-        <v>33</v>
+      <c r="S76" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46167.71426503472</v>
+        <v>46203.50206653935</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>247</v>
@@ -6469,9 +6469,11 @@
       <c r="B78" s="5">
         <v>46167.55717219907</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46203.50206046297</v>
+      </c>
       <c r="D78" s="5">
-        <v>46167.74125046296</v>
+        <v>46203.50223453704</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -6519,10 +6521,10 @@
         <v>33</v>
       </c>
       <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U78" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6532,9 +6534,11 @@
       <c r="B79" s="9">
         <v>46167.557178229166</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9">
+        <v>46203.502226909724</v>
+      </c>
       <c r="D79" s="9">
-        <v>46167.741239525465</v>
+        <v>46203.50222925926</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>213</v>
@@ -6585,9 +6589,11 @@
       <c r="B80" s="5">
         <v>46167.55718505787</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46203.50247417824</v>
+      </c>
       <c r="D80" s="5">
-        <v>46167.74123664352</v>
+        <v>46203.50247613426</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>213</v>
@@ -6638,9 +6644,11 @@
       <c r="B81" s="9">
         <v>46167.629964050924</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="9">
+        <v>46203.50259047454</v>
+      </c>
       <c r="D81" s="9">
-        <v>46167.74123373843</v>
+        <v>46203.50259215278</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>213</v>
@@ -6691,9 +6699,11 @@
       <c r="B82" s="5">
         <v>46167.6299746875</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46203.502671678245</v>
+      </c>
       <c r="D82" s="5">
-        <v>46167.74123071759</v>
+        <v>46203.50267324074</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>213</v>
@@ -6744,9 +6754,11 @@
       <c r="B83" s="9">
         <v>46167.63011578703</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9">
+        <v>46203.50276456018</v>
+      </c>
       <c r="D83" s="9">
-        <v>46167.74122805556</v>
+        <v>46203.50276618055</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>213</v>
@@ -6797,9 +6809,11 @@
       <c r="B84" s="5">
         <v>46167.630126516204</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46203.502881238426</v>
+      </c>
       <c r="D84" s="5">
-        <v>46167.74122546296</v>
+        <v>46203.50288322917</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>213</v>
@@ -6850,9 +6864,11 @@
       <c r="B85" s="9">
         <v>46167.63145555556</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9">
+        <v>46203.503010925924</v>
+      </c>
       <c r="D85" s="9">
-        <v>46167.74121943287</v>
+        <v>46203.503012835645</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>222</v>
@@ -6903,9 +6919,11 @@
       <c r="B86" s="5">
         <v>46167.631772685185</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46203.503100671296</v>
+      </c>
       <c r="D86" s="5">
-        <v>46167.74121879629</v>
+        <v>46203.503102048606</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>222</v>
@@ -7021,7 +7039,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46189.87510653935</v>
+        <v>46203.503963518524</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>213</v>
@@ -7074,7 +7092,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46189.87510706019</v>
+        <v>46203.50410373842</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>213</v>
@@ -7127,7 +7145,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46167.741366435184</v>
+        <v>46203.50259631945</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>213</v>
@@ -7180,7 +7198,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46167.741363622685</v>
+        <v>46203.5026787963</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>213</v>
@@ -7233,7 +7251,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46167.741361215274</v>
+        <v>46203.5027705324</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>213</v>
@@ -7286,7 +7304,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46167.74135855324</v>
+        <v>46203.502887615745</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>213</v>
@@ -7337,9 +7355,11 @@
       <c r="B94" s="5">
         <v>46167.63225591435</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46203.50339400463</v>
+      </c>
       <c r="D94" s="5">
-        <v>46167.74135295139</v>
+        <v>46203.50339560185</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>222</v>
@@ -7390,9 +7410,11 @@
       <c r="B95" s="9">
         <v>46167.63226373843</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="9">
+        <v>46203.50367332176</v>
+      </c>
       <c r="D95" s="9">
-        <v>46167.74135225694</v>
+        <v>46203.50367474537</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>222</v>
@@ -7826,7 +7848,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46167.74150512731</v>
+        <v>46203.50339961806</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>222</v>
@@ -7879,7 +7901,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46167.74150447917</v>
+        <v>46203.503679375004</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>222</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -4871,9 +4871,11 @@
       <c r="B50" s="5">
         <v>46167.55700140046</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46204.595792465276</v>
+      </c>
       <c r="D50" s="5">
-        <v>46169.87797747685</v>
+        <v>46204.59580765046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>171</v>
@@ -4921,10 +4923,10 @@
         <v>33</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4934,9 +4936,11 @@
       <c r="B51" s="9">
         <v>46167.55700519676</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46204.595060011576</v>
+      </c>
       <c r="D51" s="9">
-        <v>46202.169510775464</v>
+        <v>46204.5950621875</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>116</v>
@@ -4987,9 +4991,11 @@
       <c r="B52" s="5">
         <v>46167.557010034725</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46204.59515792824</v>
+      </c>
       <c r="D52" s="5">
-        <v>46169.878430219906</v>
+        <v>46204.59515966436</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>178</v>
@@ -5042,7 +5048,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46169.87844947916</v>
+        <v>46204.59516696759</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>181</v>
@@ -8190,7 +8196,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46167.74163924769</v>
+        <v>46204.59517594907</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>298</v>
@@ -8240,8 +8246,8 @@
       <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="11" t="s">
-        <v>60</v>
+      <c r="U109" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -4875,7 +4875,7 @@
         <v>46204.595792465276</v>
       </c>
       <c r="D50" s="5">
-        <v>46204.59580765046</v>
+        <v>46204.59613972223</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>171</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -516,235 +516,235 @@
     <t>Fabricacion Corte Laser   ot 4328 - 4330,Generación OC materiales corte Laser  ot 4328 - 4330</t>
   </si>
   <si>
+    <t>1215104027582344</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser   ot 4328 - 4330,Materiales corte Laser  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103776711974</t>
+  </si>
+  <si>
+    <t>Fabricacion Corte Laser   ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser  ot 4328 - 4330,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215103776711994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  ot 4328 - 4330 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma   ot 4328 - 4330,Fabricación Corte Plasma  ot 4328 - 4330 </t>
+  </si>
+  <si>
+    <t>1215103776720359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  ot 4328 - 4330 ,Fabricación Corte Plasma  ot 4328 - 4330 </t>
+  </si>
+  <si>
+    <t>1215103776720376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma  ot 4328 - 4330 </t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4328 - 4330 ,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215103875884546</t>
+  </si>
+  <si>
+    <t>Fabricación Externa   ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa  ot 4328 - 4330,Fabricación estructura proveedor externo  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103875884558</t>
+  </si>
+  <si>
+    <t>Fabricación Externa   ot 4328 - 4330,Fabricación estructura proveedor externo  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103875885911</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa   ot 4328 - 4330,Control de calidad fabricación externa   ot 4328 - 4330,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215103875885928</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa   ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215103926634088</t>
+  </si>
+  <si>
+    <t>Mecanizado  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado  ot 4328 - 4330,Generación OC Mecanizado  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103926634100</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado  ot 4328 - 4330,Mecanizado  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103926634117</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103875886339</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215103875886351</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215103776739451</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215103975168124</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Propuesta Mecanizado  ot 4328 - 4330,Propuesta Fabricación externa  ot 4328 - 4330 ,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,propuesta Corte Laser  ot 4328 - 4330,Propuesta Corte plasma   ot 4328 - 4330,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103926643808</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103926643820</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103776749962</t>
+  </si>
+  <si>
+    <t>1215103495723837</t>
+  </si>
+  <si>
+    <t>1215103495723838</t>
+  </si>
+  <si>
+    <t>1215103495723839</t>
+  </si>
+  <si>
+    <t>1215103495723840</t>
+  </si>
+  <si>
+    <t>O 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103495723841</t>
+  </si>
+  <si>
+    <t>OT 4330 - ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1215103495723842</t>
+  </si>
+  <si>
+    <t>1215103776749974</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215103975192169</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215104027582344</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser   ot 4328 - 4330,Materiales corte Laser  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103776711974</t>
-  </si>
-  <si>
-    <t>Fabricacion Corte Laser   ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser  ot 4328 - 4330,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215103776711994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  ot 4328 - 4330 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma   ot 4328 - 4330,Fabricación Corte Plasma  ot 4328 - 4330 </t>
-  </si>
-  <si>
-    <t>1215103776720359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  ot 4328 - 4330 ,Fabricación Corte Plasma  ot 4328 - 4330 </t>
-  </si>
-  <si>
-    <t>1215103776720376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma  ot 4328 - 4330 </t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4328 - 4330 ,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215103875884546</t>
-  </si>
-  <si>
-    <t>Fabricación Externa   ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa  ot 4328 - 4330,Fabricación estructura proveedor externo  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103875884558</t>
-  </si>
-  <si>
-    <t>Fabricación Externa   ot 4328 - 4330,Fabricación estructura proveedor externo  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103875885911</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa   ot 4328 - 4330,Control de calidad fabricación externa   ot 4328 - 4330,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215103875885928</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa   ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215103926634088</t>
-  </si>
-  <si>
-    <t>Mecanizado  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado  ot 4328 - 4330,Generación OC Mecanizado  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103926634100</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado  ot 4328 - 4330,Mecanizado  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103926634117</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103875886339</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215103875886351</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215103776739451</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215103975168124</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Propuesta Mecanizado  ot 4328 - 4330,Propuesta Fabricación externa  ot 4328 - 4330 ,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,propuesta Corte Laser  ot 4328 - 4330,Propuesta Corte plasma   ot 4328 - 4330,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103926643808</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103926643820</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103776749962</t>
-  </si>
-  <si>
-    <t>1215103495723837</t>
-  </si>
-  <si>
-    <t>1215103495723838</t>
-  </si>
-  <si>
-    <t>1215103495723839</t>
-  </si>
-  <si>
-    <t>1215103495723840</t>
-  </si>
-  <si>
-    <t>O 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103495723841</t>
-  </si>
-  <si>
-    <t>OT 4330 - ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1215103495723842</t>
-  </si>
-  <si>
-    <t>1215103776749974</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215103975192169</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1215103975192191</t>
@@ -2145,13 +2145,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46167.55661442129</v>
+        <v>46167.38994775463</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.878143912036</v>
+        <v>46175.71147724537</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87815497685</v>
+        <v>46175.71148831019</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2198,13 +2198,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46167.556757604165</v>
+        <v>46167.3900909375</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.878074479166</v>
+        <v>46175.7114078125</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.87809174768</v>
+        <v>46175.71142508102</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2261,13 +2261,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46167.55676116898</v>
+        <v>46167.39009450232</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87812255787</v>
+        <v>46175.7114558912</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87814511574</v>
+        <v>46175.71147844907</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2324,13 +2324,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46167.5567661574</v>
+        <v>46167.390099490745</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.8781230787</v>
+        <v>46175.71145641204</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.87814434028</v>
+        <v>46175.71147767361</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2387,13 +2387,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46167.55676920139</v>
+        <v>46167.39010253472</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.878123483795</v>
+        <v>46175.71145681713</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.87814564815</v>
+        <v>46175.71147898148</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2450,13 +2450,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46167.556773171294</v>
+        <v>46167.39010650463</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87812405093</v>
+        <v>46175.711457384255</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87814472222</v>
+        <v>46175.71147805556</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2513,11 +2513,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46167.55662017361</v>
+        <v>46167.38995350694</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46198.63710824074</v>
+        <v>46198.47044157407</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2560,13 +2560,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46167.55677776621</v>
+        <v>46167.390111099536</v>
       </c>
       <c r="C11" s="9">
-        <v>46198.637101898144</v>
+        <v>46198.47043523148</v>
       </c>
       <c r="D11" s="9">
-        <v>46198.637119039355</v>
+        <v>46198.47045237268</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2625,11 +2625,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46167.55678319444</v>
+        <v>46167.39011652778</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46167.73745994213</v>
+        <v>46167.57079327546</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2688,11 +2688,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46167.63411775463</v>
+        <v>46167.46745108796</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46167.73754430556</v>
+        <v>46167.57087763889</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2741,11 +2741,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46167.63443420139</v>
+        <v>46167.46776753472</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46167.7375415162</v>
+        <v>46167.57087484954</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2794,11 +2794,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46167.634455694446</v>
+        <v>46167.46778902778</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46167.737538692134</v>
+        <v>46167.57087202546</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>62</v>
@@ -2847,11 +2847,11 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46167.63446537037</v>
+        <v>46167.4677987037</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46167.737535625</v>
+        <v>46167.57086895833</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>62</v>
@@ -2900,11 +2900,11 @@
         <v>67</v>
       </c>
       <c r="B17" s="9">
-        <v>46167.6344740162</v>
+        <v>46167.46780734954</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46167.73753288195</v>
+        <v>46167.570866215276</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>62</v>
@@ -2953,11 +2953,11 @@
         <v>68</v>
       </c>
       <c r="B18" s="5">
-        <v>46167.63448084491</v>
+        <v>46167.46781417824</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46167.73753034722</v>
+        <v>46167.57086368055</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>62</v>
@@ -3006,11 +3006,11 @@
         <v>69</v>
       </c>
       <c r="B19" s="9">
-        <v>46167.63453541667</v>
+        <v>46167.46786875</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46167.737524641205</v>
+        <v>46167.57085797454</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>70</v>
@@ -3059,11 +3059,11 @@
         <v>71</v>
       </c>
       <c r="B20" s="5">
-        <v>46167.63474393518</v>
+        <v>46167.46807726852</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46171.51095925926</v>
+        <v>46171.34429259259</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>70</v>
@@ -3112,11 +3112,11 @@
         <v>72</v>
       </c>
       <c r="B21" s="9">
-        <v>46167.55662649305</v>
+        <v>46167.38995982639</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.87207028935</v>
+        <v>46189.705403622684</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>73</v>
@@ -3161,13 +3161,13 @@
         <v>76</v>
       </c>
       <c r="B22" s="5">
-        <v>46167.55678962963</v>
+        <v>46167.39012296296</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.8711688426</v>
+        <v>46183.704502175926</v>
       </c>
       <c r="D22" s="5">
-        <v>46189.87206064815</v>
+        <v>46189.70539398148</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>77</v>
@@ -3226,13 +3226,13 @@
         <v>82</v>
       </c>
       <c r="B23" s="9">
-        <v>46167.556794918986</v>
+        <v>46167.390128252315</v>
       </c>
       <c r="C23" s="9">
-        <v>46183.87117795139</v>
+        <v>46183.704511284726</v>
       </c>
       <c r="D23" s="9">
-        <v>46189.872060532405</v>
+        <v>46189.70539386574</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>83</v>
@@ -3291,13 +3291,13 @@
         <v>86</v>
       </c>
       <c r="B24" s="5">
-        <v>46167.55680065972</v>
+        <v>46167.39013399306</v>
       </c>
       <c r="C24" s="5">
-        <v>46183.87118480324</v>
+        <v>46183.704518136576</v>
       </c>
       <c r="D24" s="5">
-        <v>46189.872060532405</v>
+        <v>46189.70539386574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>87</v>
@@ -3356,11 +3356,11 @@
         <v>89</v>
       </c>
       <c r="B25" s="9">
-        <v>46167.556633009255</v>
+        <v>46167.38996634259</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46196.64908548611</v>
+        <v>46196.48241881945</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>90</v>
@@ -3403,13 +3403,13 @@
         <v>92</v>
       </c>
       <c r="B26" s="5">
-        <v>46167.556814571755</v>
+        <v>46167.39014790509</v>
       </c>
       <c r="C26" s="5">
-        <v>46189.87262804398</v>
+        <v>46189.705961377316</v>
       </c>
       <c r="D26" s="5">
-        <v>46189.87808604167</v>
+        <v>46189.711419375</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>93</v>
@@ -3468,11 +3468,11 @@
         <v>94</v>
       </c>
       <c r="B27" s="9">
-        <v>46167.55682017361</v>
+        <v>46167.390153506945</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46189.87937197917</v>
+        <v>46189.7127053125</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>95</v>
@@ -3531,13 +3531,13 @@
         <v>97</v>
       </c>
       <c r="B28" s="5">
-        <v>46167.55682586806</v>
+        <v>46167.390159201386</v>
       </c>
       <c r="C28" s="5">
-        <v>46190.64114762731</v>
+        <v>46190.47448096065</v>
       </c>
       <c r="D28" s="5">
-        <v>46190.641165381945</v>
+        <v>46190.47449871528</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>98</v>
@@ -3596,13 +3596,13 @@
         <v>101</v>
       </c>
       <c r="B29" s="9">
-        <v>46167.556831423615</v>
+        <v>46167.390164756944</v>
       </c>
       <c r="C29" s="9">
-        <v>46196.649080138886</v>
+        <v>46196.48241347222</v>
       </c>
       <c r="D29" s="9">
-        <v>46196.64909515047</v>
+        <v>46196.482428483796</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>102</v>
@@ -3661,13 +3661,13 @@
         <v>108</v>
       </c>
       <c r="B30" s="5">
-        <v>46167.55683648148</v>
+        <v>46167.39016981481</v>
       </c>
       <c r="C30" s="5">
-        <v>46196.6496064699</v>
+        <v>46196.482939803245</v>
       </c>
       <c r="D30" s="5">
-        <v>46196.64962321759</v>
+        <v>46196.48295655093</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>109</v>
@@ -3726,13 +3726,13 @@
         <v>111</v>
       </c>
       <c r="B31" s="9">
-        <v>46167.55684075231</v>
+        <v>46167.39017408565</v>
       </c>
       <c r="C31" s="9">
-        <v>46196.651088935185</v>
+        <v>46196.48442226852</v>
       </c>
       <c r="D31" s="9">
-        <v>46196.651105439814</v>
+        <v>46196.48443877314</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>112</v>
@@ -3791,13 +3791,13 @@
         <v>114</v>
       </c>
       <c r="B32" s="5">
-        <v>46167.55684506944</v>
+        <v>46167.39017840278</v>
       </c>
       <c r="C32" s="5">
-        <v>46196.65187996528</v>
+        <v>46196.48521329861</v>
       </c>
       <c r="D32" s="5">
-        <v>46196.65189541667</v>
+        <v>46196.485228749996</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>
@@ -3856,11 +3856,11 @@
         <v>117</v>
       </c>
       <c r="B33" s="9">
-        <v>46167.55684913194</v>
+        <v>46167.39018246528</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46198.63712021991</v>
+        <v>46198.47045355324</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>118</v>
@@ -3919,13 +3919,13 @@
         <v>120</v>
       </c>
       <c r="B34" s="5">
-        <v>46189.87339945602</v>
+        <v>46189.70673278935</v>
       </c>
       <c r="C34" s="5">
-        <v>46190.64358769676</v>
+        <v>46190.47692103009</v>
       </c>
       <c r="D34" s="5">
-        <v>46190.643601261574</v>
+        <v>46190.4769345949</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>121</v>
@@ -3972,13 +3972,13 @@
         <v>122</v>
       </c>
       <c r="B35" s="9">
-        <v>46189.874116527775</v>
+        <v>46189.70744986111</v>
       </c>
       <c r="C35" s="9">
-        <v>46190.643571747685</v>
+        <v>46190.476905081014</v>
       </c>
       <c r="D35" s="9">
-        <v>46190.64358837963</v>
+        <v>46190.476921712965</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>123</v>
@@ -4037,13 +4037,13 @@
         <v>125</v>
       </c>
       <c r="B36" s="5">
-        <v>46189.87428425926</v>
+        <v>46189.70761759259</v>
       </c>
       <c r="C36" s="5">
-        <v>46190.643442395834</v>
+        <v>46190.47677572917</v>
       </c>
       <c r="D36" s="5">
-        <v>46190.643529444445</v>
+        <v>46190.47686277778</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>126</v>
@@ -4102,11 +4102,11 @@
         <v>128</v>
       </c>
       <c r="B37" s="9">
-        <v>46167.556641689815</v>
+        <v>46167.38997502315</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46199.56372103009</v>
+        <v>46199.39705436343</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>129</v>
@@ -4151,13 +4151,13 @@
         <v>131</v>
       </c>
       <c r="B38" s="5">
-        <v>46167.55686952546</v>
+        <v>46167.39020285879</v>
       </c>
       <c r="C38" s="5">
-        <v>46195.93001813657</v>
+        <v>46195.76335146991</v>
       </c>
       <c r="D38" s="5">
-        <v>46195.930020127314</v>
+        <v>46195.76335346064</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>132</v>
@@ -4216,13 +4216,13 @@
         <v>136</v>
       </c>
       <c r="B39" s="9">
-        <v>46167.556874270835</v>
+        <v>46167.39020760417</v>
       </c>
       <c r="C39" s="9">
-        <v>46195.928063217594</v>
+        <v>46195.76139655092</v>
       </c>
       <c r="D39" s="9">
-        <v>46195.92806517361</v>
+        <v>46195.76139850695</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>137</v>
@@ -4277,13 +4277,13 @@
         <v>139</v>
       </c>
       <c r="B40" s="5">
-        <v>46167.55687946759</v>
+        <v>46167.39021280092</v>
       </c>
       <c r="C40" s="5">
-        <v>46195.929883310186</v>
+        <v>46195.76321664352</v>
       </c>
       <c r="D40" s="5">
-        <v>46195.92988494213</v>
+        <v>46195.76321827546</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>140</v>
@@ -4338,11 +4338,11 @@
         <v>142</v>
       </c>
       <c r="B41" s="9">
-        <v>46167.55696103009</v>
+        <v>46167.39029436343</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.87894268519</v>
+        <v>46169.712276018516</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>143</v>
@@ -4401,11 +4401,11 @@
         <v>145</v>
       </c>
       <c r="B42" s="5">
-        <v>46167.556965254626</v>
+        <v>46167.39029858796</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46170.1718400463</v>
+        <v>46170.00517337963</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>119</v>
@@ -4454,11 +4454,11 @@
         <v>147</v>
       </c>
       <c r="B43" s="9">
-        <v>46167.55696965278</v>
+        <v>46167.39030298611</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.87902826389</v>
+        <v>46169.71236159722</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>148</v>
@@ -4507,13 +4507,13 @@
         <v>150</v>
       </c>
       <c r="B44" s="5">
-        <v>46167.556973784725</v>
+        <v>46167.390307118054</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.56370100695</v>
+        <v>46199.397034340276</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.56371440973</v>
+        <v>46205.0023444213</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>151</v>
@@ -4557,8 +4557,8 @@
       <c r="R44" s="5">
         <v>46204</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>155</v>
+      <c r="S44" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4569,19 +4569,19 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46167.390311944444</v>
+      </c>
+      <c r="C45" s="9">
+        <v>46199.3969519213</v>
+      </c>
+      <c r="D45" s="9">
+        <v>46199.3969540625</v>
+      </c>
+      <c r="E45" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="B45" s="9">
-        <v>46167.556978611115</v>
-      </c>
-      <c r="C45" s="9">
-        <v>46199.56361858796</v>
-      </c>
-      <c r="D45" s="9">
-        <v>46199.56362072917</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>157</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4614,7 +4614,7 @@
         <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4630,19 +4630,19 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46167.39031701389</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46199.39701877315</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46199.39702045139</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="B46" s="5">
-        <v>46167.55698368055</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46199.56368543982</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46199.563687118054</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4672,10 +4672,10 @@
         <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4691,19 +4691,19 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46167.390322175925</v>
+      </c>
+      <c r="C47" s="9">
+        <v>46199.397158078704</v>
+      </c>
+      <c r="D47" s="9">
+        <v>46205.0023444213</v>
+      </c>
+      <c r="E47" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="B47" s="9">
-        <v>46167.556988842596</v>
-      </c>
-      <c r="C47" s="9">
-        <v>46199.563824745375</v>
-      </c>
-      <c r="D47" s="9">
-        <v>46199.563835740744</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4733,7 +4733,7 @@
         <v>129</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4744,8 +4744,8 @@
       <c r="R47" s="9">
         <v>46204</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>155</v>
+      <c r="S47" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4756,16 +4756,16 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
-        <v>46167.556992708334</v>
+        <v>46167.39032604167</v>
       </c>
       <c r="C48" s="5">
-        <v>46199.56375501158</v>
+        <v>46199.39708834491</v>
       </c>
       <c r="D48" s="5">
-        <v>46199.56375667824</v>
+        <v>46199.397090011575</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4795,13 +4795,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4811,19 +4811,19 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46167.39033052084</v>
+      </c>
+      <c r="C49" s="9">
+        <v>46199.397144305556</v>
+      </c>
+      <c r="D49" s="9">
+        <v>46199.39781077547</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="B49" s="9">
-        <v>46167.5569971875</v>
-      </c>
-      <c r="C49" s="9">
-        <v>46199.56381097222</v>
-      </c>
-      <c r="D49" s="9">
-        <v>46199.56447744213</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4850,13 +4850,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>110</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4866,28 +4866,28 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" s="5">
+        <v>46167.39033473379</v>
+      </c>
+      <c r="C50" s="5">
+        <v>46204.42912579861</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46204.429473055556</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B50" s="5">
-        <v>46167.55700140046</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46204.595792465276</v>
-      </c>
-      <c r="D50" s="5">
-        <v>46204.59613972223</v>
-      </c>
-      <c r="E50" s="6" t="s">
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4908,7 +4908,7 @@
         <v>129</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4931,16 +4931,16 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B51" s="9">
-        <v>46167.55700519676</v>
+        <v>46167.390338530095</v>
       </c>
       <c r="C51" s="9">
-        <v>46204.595060011576</v>
+        <v>46204.428393344904</v>
       </c>
       <c r="D51" s="9">
-        <v>46204.5950621875</v>
+        <v>46204.42839552084</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>116</v>
@@ -4949,10 +4949,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -4970,13 +4970,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4986,28 +4986,28 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="5">
+        <v>46167.39034336805</v>
+      </c>
+      <c r="C52" s="5">
+        <v>46204.42849126157</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46204.428492997686</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B52" s="5">
-        <v>46167.557010034725</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46204.59515792824</v>
-      </c>
-      <c r="D52" s="5">
-        <v>46204.59515966436</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -5025,13 +5025,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>116</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5041,26 +5041,26 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
-        <v>46167.55701476852</v>
+        <v>46167.39034810185</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46204.59516696759</v>
+        <v>46204.42850030093</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5078,10 +5078,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5094,19 +5094,19 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54" s="5">
+        <v>46167.39035103009</v>
+      </c>
+      <c r="C54" s="5">
+        <v>46199.397935381945</v>
+      </c>
+      <c r="D54" s="5">
+        <v>46205.0023444213</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="B54" s="5">
-        <v>46167.55701769676</v>
-      </c>
-      <c r="C54" s="5">
-        <v>46199.56460204862</v>
-      </c>
-      <c r="D54" s="5">
-        <v>46199.564615462965</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5136,7 +5136,7 @@
         <v>129</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5147,8 +5147,8 @@
       <c r="R54" s="5">
         <v>46204</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>155</v>
+      <c r="S54" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -5159,16 +5159,16 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
-        <v>46167.557021678236</v>
+        <v>46167.39035501158</v>
       </c>
       <c r="C55" s="9">
-        <v>46199.56439893518</v>
+        <v>46199.39773226852</v>
       </c>
       <c r="D55" s="9">
-        <v>46199.564400601856</v>
+        <v>46199.397733935184</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>113</v>
@@ -5198,13 +5198,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5214,19 +5214,19 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B56" s="5">
+        <v>46167.39035967593</v>
+      </c>
+      <c r="C56" s="5">
+        <v>46199.3979215162</v>
+      </c>
+      <c r="D56" s="5">
+        <v>46199.39792300926</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="B56" s="5">
-        <v>46167.55702634259</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46199.56458818287</v>
-      </c>
-      <c r="D56" s="5">
-        <v>46199.56458967592</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5253,13 +5253,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5269,17 +5269,17 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B57" s="9">
-        <v>46167.55703671296</v>
+        <v>46167.3903700463</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46189.891556296294</v>
+        <v>46189.72488962963</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5303,7 +5303,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5316,28 +5316,28 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="5">
+        <v>46167.39037385417</v>
+      </c>
+      <c r="C58" s="5">
+        <v>46184.35049503473</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46197.54840078704</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B58" s="5">
-        <v>46167.557040520835</v>
-      </c>
-      <c r="C58" s="5">
-        <v>46184.517161701384</v>
-      </c>
-      <c r="D58" s="5">
-        <v>46197.715067453704</v>
-      </c>
-      <c r="E58" s="6" t="s">
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="H58" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5355,13 +5355,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5381,28 +5381,28 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B59" s="9">
+        <v>46167.39037918982</v>
+      </c>
+      <c r="C59" s="9">
+        <v>46189.70835143518</v>
+      </c>
+      <c r="D59" s="9">
+        <v>46197.54843625</v>
+      </c>
+      <c r="E59" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B59" s="9">
-        <v>46167.557045856476</v>
-      </c>
-      <c r="C59" s="9">
-        <v>46189.875018101855</v>
-      </c>
-      <c r="D59" s="9">
-        <v>46197.71510291667</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>201</v>
-      </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5420,13 +5420,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5446,16 +5446,16 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46167.5570519676</v>
+        <v>46167.390385300925</v>
       </c>
       <c r="C60" s="5">
-        <v>46189.87508320602</v>
+        <v>46189.70841653935</v>
       </c>
       <c r="D60" s="5">
-        <v>46190.1997147338</v>
+        <v>46190.033048067125</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>105</v>
@@ -5464,10 +5464,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5485,13 +5485,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5511,26 +5511,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
-        <v>46167.55706452546</v>
+        <v>46167.39039785879</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46167.740869988425</v>
+        <v>46167.574203321754</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5548,10 +5548,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5574,26 +5574,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B62" s="5">
-        <v>46167.5570684375</v>
+        <v>46167.390401770834</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46167.74085901621</v>
+        <v>46167.57419234954</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5611,13 +5611,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5627,26 +5627,26 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B63" s="9">
-        <v>46167.55707274306</v>
+        <v>46167.39040607639</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46167.74085574074</v>
+        <v>46167.574189074076</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5664,13 +5664,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>213</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>214</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5680,26 +5680,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46167.65975748842</v>
+        <v>46167.49309082176</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46167.74085291667</v>
+        <v>46167.57418625</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5717,13 +5717,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5733,26 +5733,26 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B65" s="9">
-        <v>46167.65976925926</v>
+        <v>46167.49310259259</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46167.74085050926</v>
+        <v>46167.57418384259</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5770,13 +5770,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5786,26 +5786,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B66" s="5">
-        <v>46167.65978199074</v>
+        <v>46167.493115324076</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46167.74084565972</v>
+        <v>46167.574178993054</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5823,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5839,26 +5839,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B67" s="9">
-        <v>46167.659797824075</v>
+        <v>46167.493131157404</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46167.74084013889</v>
+        <v>46167.574173472225</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5876,13 +5876,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5892,26 +5892,26 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B68" s="5">
-        <v>46167.65987638889</v>
+        <v>46167.49320972222</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46167.740839074075</v>
+        <v>46167.5741724074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5929,13 +5929,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5945,26 +5945,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B69" s="9">
-        <v>46167.65988679398</v>
+        <v>46167.49322012732</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46167.740838356476</v>
+        <v>46167.57417168982</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -5982,13 +5982,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5998,17 +5998,17 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B70" s="5">
-        <v>46167.5570771412</v>
+        <v>46167.39041047454</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46167.629188032406</v>
+        <v>46167.46252136574</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6032,7 +6032,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6045,26 +6045,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B71" s="9">
-        <v>46167.55708079861</v>
+        <v>46167.39041413194</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46199.56370296296</v>
+        <v>46199.3970362963</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="H71" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6082,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6097,7 +6097,7 @@
         <v>46206</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -6111,11 +6111,11 @@
         <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46167.5570859838</v>
+        <v>46167.39041931713</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46203.19671185185</v>
+        <v>46203.03004518518</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -6124,10 +6124,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6145,7 +6145,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>234</v>
@@ -6160,7 +6160,7 @@
         <v>46210</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -6174,11 +6174,11 @@
         <v>236</v>
       </c>
       <c r="B73" s="9">
-        <v>46167.55709181713</v>
+        <v>46167.390425150465</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46199.563827962964</v>
+        <v>46199.39716129629</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>237</v>
@@ -6187,10 +6187,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6208,10 +6208,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>238</v>
@@ -6223,7 +6223,7 @@
         <v>46206</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -6237,11 +6237,11 @@
         <v>239</v>
       </c>
       <c r="B74" s="5">
-        <v>46167.55709682871</v>
+        <v>46167.390430162035</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46203.19671157407</v>
+        <v>46203.030044907406</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>240</v>
@@ -6250,10 +6250,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6271,7 +6271,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>237</v>
@@ -6286,7 +6286,7 @@
         <v>46210</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -6300,11 +6300,11 @@
         <v>242</v>
       </c>
       <c r="B75" s="9">
-        <v>46167.55715278935</v>
+        <v>46167.390486122684</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46199.56460534722</v>
+        <v>46199.39793868056</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>243</v>
@@ -6313,10 +6313,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6334,10 +6334,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>244</v>
@@ -6349,7 +6349,7 @@
         <v>46206</v>
       </c>
       <c r="S75" s="12" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>
@@ -6363,11 +6363,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46167.55716416667</v>
+        <v>46167.390497500004</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46203.196711412034</v>
+        <v>46203.03004474537</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>244</v>
@@ -6376,10 +6376,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6397,7 +6397,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>243</v>
@@ -6412,7 +6412,7 @@
         <v>46210</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -6426,11 +6426,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46167.557168680556</v>
+        <v>46167.39050201389</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46203.50206653935</v>
+        <v>46203.33539987268</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>247</v>
@@ -6473,13 +6473,13 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <v>46167.55717219907</v>
+        <v>46167.39050553241</v>
       </c>
       <c r="C78" s="5">
-        <v>46203.50206046297</v>
+        <v>46203.3353937963</v>
       </c>
       <c r="D78" s="5">
-        <v>46203.50223453704</v>
+        <v>46203.33556787037</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -6538,16 +6538,16 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46167.557178229166</v>
+        <v>46167.390511562495</v>
       </c>
       <c r="C79" s="9">
-        <v>46203.502226909724</v>
+        <v>46203.33556024305</v>
       </c>
       <c r="D79" s="9">
-        <v>46203.50222925926</v>
+        <v>46203.33556259259</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6593,16 +6593,16 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46167.55718505787</v>
+        <v>46167.3905183912</v>
       </c>
       <c r="C80" s="5">
-        <v>46203.50247417824</v>
+        <v>46203.335807511576</v>
       </c>
       <c r="D80" s="5">
-        <v>46203.50247613426</v>
+        <v>46203.33580946759</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6635,7 +6635,7 @@
         <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6648,16 +6648,16 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46167.629964050924</v>
+        <v>46167.46329738426</v>
       </c>
       <c r="C81" s="9">
-        <v>46203.50259047454</v>
+        <v>46203.33592380787</v>
       </c>
       <c r="D81" s="9">
-        <v>46203.50259215278</v>
+        <v>46203.33592548611</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6690,7 +6690,7 @@
         <v>260</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6703,16 +6703,16 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46167.6299746875</v>
+        <v>46167.46330802083</v>
       </c>
       <c r="C82" s="5">
-        <v>46203.502671678245</v>
+        <v>46203.33600501157</v>
       </c>
       <c r="D82" s="5">
-        <v>46203.50267324074</v>
+        <v>46203.33600657407</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6745,7 +6745,7 @@
         <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6758,16 +6758,16 @@
         <v>262</v>
       </c>
       <c r="B83" s="9">
-        <v>46167.63011578703</v>
+        <v>46167.46344912037</v>
       </c>
       <c r="C83" s="9">
-        <v>46203.50276456018</v>
+        <v>46203.33609789352</v>
       </c>
       <c r="D83" s="9">
-        <v>46203.50276618055</v>
+        <v>46203.336099513894</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6800,7 +6800,7 @@
         <v>260</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6813,16 +6813,16 @@
         <v>263</v>
       </c>
       <c r="B84" s="5">
-        <v>46167.630126516204</v>
+        <v>46167.46345984953</v>
       </c>
       <c r="C84" s="5">
-        <v>46203.502881238426</v>
+        <v>46203.336214571755</v>
       </c>
       <c r="D84" s="5">
-        <v>46203.50288322917</v>
+        <v>46203.3362165625</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6855,7 +6855,7 @@
         <v>260</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6868,16 +6868,16 @@
         <v>264</v>
       </c>
       <c r="B85" s="9">
-        <v>46167.63145555556</v>
+        <v>46167.46478888889</v>
       </c>
       <c r="C85" s="9">
-        <v>46203.503010925924</v>
+        <v>46203.33634425926</v>
       </c>
       <c r="D85" s="9">
-        <v>46203.503012835645</v>
+        <v>46203.33634616898</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6910,7 +6910,7 @@
         <v>260</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6923,16 +6923,16 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46167.631772685185</v>
+        <v>46167.46510601851</v>
       </c>
       <c r="C86" s="5">
-        <v>46203.503100671296</v>
+        <v>46203.336434004625</v>
       </c>
       <c r="D86" s="5">
-        <v>46203.503102048606</v>
+        <v>46203.33643538195</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6965,7 +6965,7 @@
         <v>260</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6978,11 +6978,11 @@
         <v>266</v>
       </c>
       <c r="B87" s="9">
-        <v>46167.557190844906</v>
+        <v>46167.39052417824</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46167.74138710648</v>
+        <v>46167.574720439814</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>267</v>
@@ -7015,7 +7015,7 @@
         <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>247</v>
@@ -7041,14 +7041,14 @@
         <v>268</v>
       </c>
       <c r="B88" s="5">
-        <v>46167.557195092595</v>
+        <v>46167.39052842592</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46203.503963518524</v>
+        <v>46203.33729685185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7094,14 +7094,14 @@
         <v>271</v>
       </c>
       <c r="B89" s="9">
-        <v>46167.557200995376</v>
+        <v>46167.390534328704</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46203.50410373842</v>
+        <v>46203.33743707176</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -7147,14 +7147,14 @@
         <v>272</v>
       </c>
       <c r="B90" s="5">
-        <v>46167.63214916667</v>
+        <v>46167.4654825</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46203.50259631945</v>
+        <v>46203.33592965278</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7184,10 +7184,10 @@
         <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7200,14 +7200,14 @@
         <v>273</v>
       </c>
       <c r="B91" s="9">
-        <v>46167.63219107639</v>
+        <v>46167.46552440972</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46203.5026787963</v>
+        <v>46203.33601212963</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7237,10 +7237,10 @@
         <v>267</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7253,14 +7253,14 @@
         <v>274</v>
       </c>
       <c r="B92" s="5">
-        <v>46167.63220099537</v>
+        <v>46167.4655343287</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46203.5027705324</v>
+        <v>46203.336103865746</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7290,10 +7290,10 @@
         <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7306,14 +7306,14 @@
         <v>275</v>
       </c>
       <c r="B93" s="9">
-        <v>46167.63220839121</v>
+        <v>46167.46554172454</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46203.502887615745</v>
+        <v>46203.33622094907</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7343,10 +7343,10 @@
         <v>267</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7359,16 +7359,16 @@
         <v>276</v>
       </c>
       <c r="B94" s="5">
-        <v>46167.63225591435</v>
+        <v>46167.46558924769</v>
       </c>
       <c r="C94" s="5">
-        <v>46203.50339400463</v>
+        <v>46203.33672733796</v>
       </c>
       <c r="D94" s="5">
-        <v>46203.50339560185</v>
+        <v>46203.33672893519</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7398,10 +7398,10 @@
         <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7414,16 +7414,16 @@
         <v>277</v>
       </c>
       <c r="B95" s="9">
-        <v>46167.63226373843</v>
+        <v>46167.46559707176</v>
       </c>
       <c r="C95" s="9">
-        <v>46203.50367332176</v>
+        <v>46203.33700665509</v>
       </c>
       <c r="D95" s="9">
-        <v>46203.50367474537</v>
+        <v>46203.3370080787</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7453,10 +7453,10 @@
         <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7469,11 +7469,11 @@
         <v>278</v>
       </c>
       <c r="B96" s="5">
-        <v>46167.5572065625</v>
+        <v>46167.39053989583</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46167.74153292824</v>
+        <v>46167.57486626157</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>279</v>
@@ -7482,10 +7482,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7506,7 +7506,7 @@
         <v>247</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>247</v>
@@ -7532,23 +7532,23 @@
         <v>280</v>
       </c>
       <c r="B97" s="9">
-        <v>46167.557210914354</v>
+        <v>46167.39054424768</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46189.87509809028</v>
+        <v>46189.70843142361</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7585,23 +7585,23 @@
         <v>282</v>
       </c>
       <c r="B98" s="5">
-        <v>46167.55721697917</v>
+        <v>46167.3905503125</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46189.87509940972</v>
+        <v>46189.70843274306</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7638,23 +7638,23 @@
         <v>283</v>
       </c>
       <c r="B99" s="9">
-        <v>46167.632342048615</v>
+        <v>46167.46567538194</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46167.74151755787</v>
+        <v>46167.57485089121</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7675,7 +7675,7 @@
         <v>279</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7691,23 +7691,23 @@
         <v>284</v>
       </c>
       <c r="B100" s="5">
-        <v>46167.63235868055</v>
+        <v>46167.46569201389</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46167.74151503472</v>
+        <v>46167.57484836805</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7728,10 +7728,10 @@
         <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7744,23 +7744,23 @@
         <v>285</v>
       </c>
       <c r="B101" s="9">
-        <v>46167.63236590278</v>
+        <v>46167.46569923611</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46167.74151262731</v>
+        <v>46167.57484596065</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7781,10 +7781,10 @@
         <v>279</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7797,23 +7797,23 @@
         <v>286</v>
       </c>
       <c r="B102" s="5">
-        <v>46167.63237413194</v>
+        <v>46167.46570746528</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46167.7415103588</v>
+        <v>46167.57484369213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7834,10 +7834,10 @@
         <v>279</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7850,23 +7850,23 @@
         <v>287</v>
       </c>
       <c r="B103" s="9">
-        <v>46167.63244320602</v>
+        <v>46167.46577653935</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46203.50339961806</v>
+        <v>46203.336732951386</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7887,10 +7887,10 @@
         <v>279</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7903,23 +7903,23 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46167.63245268518</v>
+        <v>46167.46578601852</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46203.503679375004</v>
+        <v>46203.33701270833</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -7940,10 +7940,10 @@
         <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7956,14 +7956,14 @@
         <v>289</v>
       </c>
       <c r="B105" s="9">
-        <v>46167.55722248842</v>
+        <v>46167.39055582176</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46189.87746019676</v>
+        <v>46189.71079353009</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -8003,11 +8003,11 @@
         <v>291</v>
       </c>
       <c r="B106" s="5">
-        <v>46167.557225682875</v>
+        <v>46167.3905590162</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46195.92990200232</v>
+        <v>46195.763235335646</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>292</v>
@@ -8016,10 +8016,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -8037,7 +8037,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>140</v>
@@ -8066,11 +8066,11 @@
         <v>294</v>
       </c>
       <c r="B107" s="9">
-        <v>46167.557231493054</v>
+        <v>46167.39056482639</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46190.64346133102</v>
+        <v>46190.476794664355</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>127</v>
@@ -8079,10 +8079,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8100,7 +8100,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>126</v>
@@ -8129,11 +8129,11 @@
         <v>295</v>
       </c>
       <c r="B108" s="5">
-        <v>46167.55723746528</v>
+        <v>46167.39057079861</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46189.87818384259</v>
+        <v>46189.71151717592</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>124</v>
@@ -8142,10 +8142,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8163,7 +8163,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
@@ -8192,11 +8192,11 @@
         <v>297</v>
       </c>
       <c r="B109" s="9">
-        <v>46167.55724847222</v>
+        <v>46167.39058180556</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46204.59517594907</v>
+        <v>46204.42850928241</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>298</v>
@@ -8205,10 +8205,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8226,10 +8226,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>299</v>
@@ -8255,11 +8255,11 @@
         <v>300</v>
       </c>
       <c r="B110" s="5">
-        <v>46167.55725353009</v>
+        <v>46167.390586863425</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46167.74163472222</v>
+        <v>46167.57496805556</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>58</v>
@@ -8268,10 +8268,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8289,7 +8289,7 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>148</v>
@@ -8318,11 +8318,11 @@
         <v>302</v>
       </c>
       <c r="B111" s="9">
-        <v>46167.5572591088</v>
+        <v>46167.39059244213</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46167.73130032407</v>
+        <v>46167.56463365741</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>303</v>
@@ -8365,11 +8365,11 @@
         <v>305</v>
       </c>
       <c r="B112" s="5">
-        <v>46167.557262685186</v>
+        <v>46167.39059601852</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46167.741924999995</v>
+        <v>46167.57525833334</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>306</v>
@@ -8428,14 +8428,14 @@
         <v>308</v>
       </c>
       <c r="B113" s="9">
-        <v>46167.55727085649</v>
+        <v>46167.390604189815</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46167.74190891204</v>
+        <v>46167.575242245366</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8481,14 +8481,14 @@
         <v>310</v>
       </c>
       <c r="B114" s="5">
-        <v>46167.55727532407</v>
+        <v>46167.390608657406</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46167.74190642362</v>
+        <v>46167.575239756945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8534,14 +8534,14 @@
         <v>311</v>
       </c>
       <c r="B115" s="9">
-        <v>46167.632606053245</v>
+        <v>46167.46593938657</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46167.7419037037</v>
+        <v>46167.57523703703</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8571,10 +8571,10 @@
         <v>306</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8587,14 +8587,14 @@
         <v>312</v>
       </c>
       <c r="B116" s="5">
-        <v>46167.63261443287</v>
+        <v>46167.465947766206</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46167.74190121528</v>
+        <v>46167.57523454861</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8624,10 +8624,10 @@
         <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8640,14 +8640,14 @@
         <v>313</v>
       </c>
       <c r="B117" s="9">
-        <v>46167.63262241898</v>
+        <v>46167.46595575231</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46167.74189892361</v>
+        <v>46167.575232256946</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8677,10 +8677,10 @@
         <v>306</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8693,14 +8693,14 @@
         <v>314</v>
       </c>
       <c r="B118" s="5">
-        <v>46167.63263039352</v>
+        <v>46167.46596372685</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46167.74189655093</v>
+        <v>46167.575229884256</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8730,10 +8730,10 @@
         <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8746,14 +8746,14 @@
         <v>315</v>
       </c>
       <c r="B119" s="9">
-        <v>46167.63269008102</v>
+        <v>46167.46602341435</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46167.74189145833</v>
+        <v>46167.57522479167</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8783,10 +8783,10 @@
         <v>306</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8799,14 +8799,14 @@
         <v>316</v>
       </c>
       <c r="B120" s="5">
-        <v>46167.632698738424</v>
+        <v>46167.46603207176</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46167.74189078704</v>
+        <v>46167.57522412037</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8836,10 +8836,10 @@
         <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8852,11 +8852,11 @@
         <v>317</v>
       </c>
       <c r="B121" s="9">
-        <v>46167.55727960648</v>
+        <v>46167.39061293982</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46167.74207511574</v>
+        <v>46167.575408449076</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>318</v>
@@ -8889,7 +8889,7 @@
         <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>303</v>
@@ -8915,14 +8915,14 @@
         <v>319</v>
       </c>
       <c r="B122" s="5">
-        <v>46167.557284375</v>
+        <v>46167.39061770833</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46189.87510767361</v>
+        <v>46189.708441006944</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8968,14 +8968,14 @@
         <v>322</v>
       </c>
       <c r="B123" s="9">
-        <v>46167.55729009259</v>
+        <v>46167.39062342593</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46189.87510009259</v>
+        <v>46189.70843342593</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9021,14 +9021,14 @@
         <v>323</v>
       </c>
       <c r="B124" s="5">
-        <v>46167.6328130787</v>
+        <v>46167.466146412036</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46189.87508946759</v>
+        <v>46189.708422800926</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9061,7 +9061,7 @@
         <v>324</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9074,14 +9074,14 @@
         <v>325</v>
       </c>
       <c r="B125" s="9">
-        <v>46167.63283585648</v>
+        <v>46167.466169189815</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46189.87509015047</v>
+        <v>46189.7084234838</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9114,7 +9114,7 @@
         <v>326</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9127,14 +9127,14 @@
         <v>327</v>
       </c>
       <c r="B126" s="5">
-        <v>46167.63284336806</v>
+        <v>46167.46617670139</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46189.87509105324</v>
+        <v>46189.708424386576</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9167,7 +9167,7 @@
         <v>326</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9180,14 +9180,14 @@
         <v>328</v>
       </c>
       <c r="B127" s="9">
-        <v>46167.63285163195</v>
+        <v>46167.46618496528</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46189.87509177084</v>
+        <v>46189.70842510417</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9220,7 +9220,7 @@
         <v>326</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9233,14 +9233,14 @@
         <v>329</v>
       </c>
       <c r="B128" s="5">
-        <v>46167.63289178241</v>
+        <v>46167.46622511574</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46189.87509244213</v>
+        <v>46189.70842577546</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9273,7 +9273,7 @@
         <v>330</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9286,14 +9286,14 @@
         <v>331</v>
       </c>
       <c r="B129" s="9">
-        <v>46167.632899212964</v>
+        <v>46167.4662325463</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46189.8750930324</v>
+        <v>46189.708426365745</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9326,7 +9326,7 @@
         <v>330</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9339,11 +9339,11 @@
         <v>332</v>
       </c>
       <c r="B130" s="5">
-        <v>46167.55733736111</v>
+        <v>46167.39067069444</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46167.74221776621</v>
+        <v>46167.57555109954</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>333</v>
@@ -9376,7 +9376,7 @@
         <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>303</v>
@@ -9402,14 +9402,14 @@
         <v>334</v>
       </c>
       <c r="B131" s="9">
-        <v>46167.557343645836</v>
+        <v>46167.390676979165</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46189.87510797454</v>
+        <v>46189.70844130787</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9453,14 +9453,14 @@
         <v>337</v>
       </c>
       <c r="B132" s="5">
-        <v>46167.55735079861</v>
+        <v>46167.39068413194</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46189.87510071759</v>
+        <v>46189.708434050925</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9504,14 +9504,14 @@
         <v>338</v>
       </c>
       <c r="B133" s="9">
-        <v>46167.63302359954</v>
+        <v>46167.46635693287</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46189.875093634255</v>
+        <v>46189.7084269676</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9542,7 +9542,7 @@
         <v>335</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9555,14 +9555,14 @@
         <v>339</v>
       </c>
       <c r="B134" s="5">
-        <v>46167.63303486111</v>
+        <v>46167.466368194444</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46189.8750941551</v>
+        <v>46189.708427488426</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9593,7 +9593,7 @@
         <v>335</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9606,14 +9606,14 @@
         <v>340</v>
       </c>
       <c r="B135" s="9">
-        <v>46167.633050648146</v>
+        <v>46167.46638398148</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46189.87509472222</v>
+        <v>46189.70842805556</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9644,7 +9644,7 @@
         <v>335</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9657,14 +9657,14 @@
         <v>341</v>
       </c>
       <c r="B136" s="5">
-        <v>46167.633060671295</v>
+        <v>46167.46639400463</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46189.87509519676</v>
+        <v>46189.708428530095</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9695,7 +9695,7 @@
         <v>335</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9708,14 +9708,14 @@
         <v>342</v>
       </c>
       <c r="B137" s="9">
-        <v>46167.633115185185</v>
+        <v>46167.46644851852</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46189.87509570602</v>
+        <v>46189.708429039354</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9746,7 +9746,7 @@
         <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9759,14 +9759,14 @@
         <v>344</v>
       </c>
       <c r="B138" s="5">
-        <v>46167.6331228125</v>
+        <v>46167.466456145834</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46189.87509615741</v>
+        <v>46189.70842949074</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9797,7 +9797,7 @@
         <v>345</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9810,11 +9810,11 @@
         <v>346</v>
       </c>
       <c r="B139" s="9">
-        <v>46167.557357488426</v>
+        <v>46167.39069082176</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46167.74236513889</v>
+        <v>46167.575698472225</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>347</v>
@@ -9847,7 +9847,7 @@
         <v>303</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>303</v>
@@ -9873,14 +9873,14 @@
         <v>348</v>
       </c>
       <c r="B140" s="5">
-        <v>46167.55736211805</v>
+        <v>46167.39069545139</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46189.877459745374</v>
+        <v>46189.7107930787</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9926,14 +9926,14 @@
         <v>351</v>
       </c>
       <c r="B141" s="9">
-        <v>46167.55737267361</v>
+        <v>46167.39070600695</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46189.87746077546</v>
+        <v>46189.710794108796</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9979,14 +9979,14 @@
         <v>352</v>
       </c>
       <c r="B142" s="5">
-        <v>46167.63325159722</v>
+        <v>46167.46658493056</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46189.877455671296</v>
+        <v>46189.71078900463</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10019,7 +10019,7 @@
         <v>353</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10032,14 +10032,14 @@
         <v>354</v>
       </c>
       <c r="B143" s="9">
-        <v>46167.63325929398</v>
+        <v>46167.466592627316</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46189.87745677083</v>
+        <v>46189.71079010417</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10072,7 +10072,7 @@
         <v>355</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10085,14 +10085,14 @@
         <v>356</v>
       </c>
       <c r="B144" s="5">
-        <v>46167.633274293985</v>
+        <v>46167.46660762731</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46189.87745732639</v>
+        <v>46189.71079065972</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10125,7 +10125,7 @@
         <v>349</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10138,14 +10138,14 @@
         <v>357</v>
       </c>
       <c r="B145" s="9">
-        <v>46167.633281875</v>
+        <v>46167.46661520834</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46189.877457916664</v>
+        <v>46189.71079125</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10178,7 +10178,7 @@
         <v>358</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10191,14 +10191,14 @@
         <v>359</v>
       </c>
       <c r="B146" s="5">
-        <v>46167.63332260417</v>
+        <v>46167.466655937504</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46189.87745863426</v>
+        <v>46189.71079196759</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10231,7 +10231,7 @@
         <v>360</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10244,14 +10244,14 @@
         <v>361</v>
       </c>
       <c r="B147" s="9">
-        <v>46167.633331689816</v>
+        <v>46167.46666502315</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46189.87745917824</v>
+        <v>46189.71079251157</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10284,7 +10284,7 @@
         <v>360</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10297,11 +10297,11 @@
         <v>362</v>
       </c>
       <c r="B148" s="5">
-        <v>46167.557378287034</v>
+        <v>46167.39071162037</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46167.742498472224</v>
+        <v>46167.57583180556</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>363</v>
@@ -10334,7 +10334,7 @@
         <v>303</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>303</v>
@@ -10360,14 +10360,14 @@
         <v>364</v>
       </c>
       <c r="B149" s="9">
-        <v>46167.55738292824</v>
+        <v>46167.39071626157</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46167.742493136575</v>
+        <v>46167.57582646991</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10397,7 +10397,7 @@
         <v>363</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>365</v>
@@ -10413,14 +10413,14 @@
         <v>366</v>
       </c>
       <c r="B150" s="5">
-        <v>46167.5573883912</v>
+        <v>46167.390721724536</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46167.742490000004</v>
+        <v>46167.57582333333</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10450,7 +10450,7 @@
         <v>363</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>365</v>
@@ -10466,14 +10466,14 @@
         <v>367</v>
       </c>
       <c r="B151" s="9">
-        <v>46167.63341660879</v>
+        <v>46167.466749942134</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46167.74248716435</v>
+        <v>46167.57582049769</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10503,10 +10503,10 @@
         <v>363</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10519,14 +10519,14 @@
         <v>368</v>
       </c>
       <c r="B152" s="5">
-        <v>46167.63343371528</v>
+        <v>46167.46676704861</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46167.74248396991</v>
+        <v>46167.57581730324</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10556,10 +10556,10 @@
         <v>363</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10572,14 +10572,14 @@
         <v>369</v>
       </c>
       <c r="B153" s="9">
-        <v>46167.63344365741</v>
+        <v>46167.46677699074</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46167.742481134264</v>
+        <v>46167.57581446759</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10609,10 +10609,10 @@
         <v>363</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10625,14 +10625,14 @@
         <v>370</v>
       </c>
       <c r="B154" s="5">
-        <v>46167.63345188658</v>
+        <v>46167.466785219905</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46167.74247835648</v>
+        <v>46167.575811689814</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10662,10 +10662,10 @@
         <v>363</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10678,14 +10678,14 @@
         <v>371</v>
       </c>
       <c r="B155" s="9">
-        <v>46167.633506412036</v>
+        <v>46167.46683974537</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46167.74247142361</v>
+        <v>46167.57580475694</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10715,10 +10715,10 @@
         <v>363</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10731,14 +10731,14 @@
         <v>372</v>
       </c>
       <c r="B156" s="5">
-        <v>46167.63351399306</v>
+        <v>46167.46684732639</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46167.74247065972</v>
+        <v>46167.57580399305</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10768,10 +10768,10 @@
         <v>363</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10784,11 +10784,11 @@
         <v>373</v>
       </c>
       <c r="B157" s="9">
-        <v>46167.55739407407</v>
+        <v>46167.39072740741</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46167.74264841435</v>
+        <v>46167.57598174769</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>374</v>
@@ -10821,7 +10821,7 @@
         <v>303</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>375</v>
@@ -10847,14 +10847,14 @@
         <v>376</v>
       </c>
       <c r="B158" s="5">
-        <v>46167.55739920139</v>
+        <v>46167.390732534725</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46167.742638298616</v>
+        <v>46167.575971631944</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10884,7 +10884,7 @@
         <v>374</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>377</v>
@@ -10900,14 +10900,14 @@
         <v>378</v>
       </c>
       <c r="B159" s="9">
-        <v>46167.5574040162</v>
+        <v>46167.39073734954</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46167.74263541667</v>
+        <v>46167.575968749996</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10937,7 +10937,7 @@
         <v>374</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>377</v>
@@ -10953,14 +10953,14 @@
         <v>379</v>
       </c>
       <c r="B160" s="5">
-        <v>46167.633843206015</v>
+        <v>46167.46717653935</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46167.742632037036</v>
+        <v>46167.57596537037</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -10990,10 +10990,10 @@
         <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11006,14 +11006,14 @@
         <v>380</v>
       </c>
       <c r="B161" s="9">
-        <v>46167.633849895836</v>
+        <v>46167.467183229164</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46167.742628935186</v>
+        <v>46167.575962268515</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11043,10 +11043,10 @@
         <v>374</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11059,14 +11059,14 @@
         <v>381</v>
       </c>
       <c r="B162" s="5">
-        <v>46167.63385791666</v>
+        <v>46167.467191250005</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46167.74262635417</v>
+        <v>46167.5759596875</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11096,10 +11096,10 @@
         <v>374</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11112,14 +11112,14 @@
         <v>382</v>
       </c>
       <c r="B163" s="9">
-        <v>46167.633867083336</v>
+        <v>46167.467200416664</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46167.74262355324</v>
+        <v>46167.575956886576</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11149,10 +11149,10 @@
         <v>374</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11165,14 +11165,14 @@
         <v>383</v>
       </c>
       <c r="B164" s="5">
-        <v>46167.63391234954</v>
+        <v>46167.46724568287</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46167.742617407406</v>
+        <v>46167.57595074074</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11202,10 +11202,10 @@
         <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11218,14 +11218,14 @@
         <v>384</v>
       </c>
       <c r="B165" s="9">
-        <v>46167.63392017361</v>
+        <v>46167.46725350694</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46167.74261677083</v>
+        <v>46167.57595010417</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11255,10 +11255,10 @@
         <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11271,11 +11271,11 @@
         <v>385</v>
       </c>
       <c r="B166" s="5">
-        <v>46167.557409201385</v>
+        <v>46167.39074253472</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46167.734742650464</v>
+        <v>46167.5680759838</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>386</v>
@@ -11318,11 +11318,11 @@
         <v>388</v>
       </c>
       <c r="B167" s="9">
-        <v>46167.5574132176</v>
+        <v>46167.390746550926</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46167.74284238426</v>
+        <v>46167.57617571759</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>389</v>
@@ -11381,14 +11381,14 @@
         <v>393</v>
       </c>
       <c r="B168" s="5">
-        <v>46167.55742054398</v>
+        <v>46167.39075387732</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46167.74286244213</v>
+        <v>46167.57619577546</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11418,7 +11418,7 @@
         <v>389</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>394</v>
@@ -11434,14 +11434,14 @@
         <v>395</v>
       </c>
       <c r="B169" s="9">
-        <v>46167.557425520834</v>
+        <v>46167.39075885416</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46167.742859606486</v>
+        <v>46167.576192939814</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11471,7 +11471,7 @@
         <v>389</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>394</v>
@@ -11487,14 +11487,14 @@
         <v>396</v>
       </c>
       <c r="B170" s="5">
-        <v>46167.55743020833</v>
+        <v>46167.39076354167</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46167.74285702546</v>
+        <v>46167.5761903588</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11524,7 +11524,7 @@
         <v>389</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>394</v>
@@ -11540,14 +11540,14 @@
         <v>397</v>
       </c>
       <c r="B171" s="9">
-        <v>46167.557434918985</v>
+        <v>46167.39076825231</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46167.742854375</v>
+        <v>46167.576187708335</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11577,7 +11577,7 @@
         <v>389</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>394</v>
@@ -11593,14 +11593,14 @@
         <v>398</v>
       </c>
       <c r="B172" s="5">
-        <v>46167.636403032404</v>
+        <v>46167.46973636574</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46167.74285166667</v>
+        <v>46167.576185</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11630,10 +11630,10 @@
         <v>389</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11646,14 +11646,14 @@
         <v>399</v>
       </c>
       <c r="B173" s="9">
-        <v>46167.63641173611</v>
+        <v>46167.469745069444</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46167.74284892361</v>
+        <v>46167.57618225695</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11683,10 +11683,10 @@
         <v>389</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11699,14 +11699,14 @@
         <v>400</v>
       </c>
       <c r="B174" s="5">
-        <v>46167.636428645834</v>
+        <v>46167.46976197917</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46167.742846469904</v>
+        <v>46167.57617980324</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11736,10 +11736,10 @@
         <v>389</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11752,14 +11752,14 @@
         <v>401</v>
       </c>
       <c r="B175" s="9">
-        <v>46167.636439849535</v>
+        <v>46167.46977318287</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46167.74284369213</v>
+        <v>46167.57617702546</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11789,10 +11789,10 @@
         <v>389</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11805,11 +11805,11 @@
         <v>402</v>
       </c>
       <c r="B176" s="5">
-        <v>46167.636677511575</v>
+        <v>46167.4700108449</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46167.742840844905</v>
+        <v>46167.57617417824</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>63</v>
@@ -11858,11 +11858,11 @@
         <v>403</v>
       </c>
       <c r="B177" s="9">
-        <v>46167.63669306713</v>
+        <v>46167.470026400464</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46167.742838136575</v>
+        <v>46167.576171469904</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>62</v>
@@ -11911,11 +11911,11 @@
         <v>404</v>
       </c>
       <c r="B178" s="5">
-        <v>46167.6367015162</v>
+        <v>46167.47003484954</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46167.742835763886</v>
+        <v>46167.57616909722</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>62</v>
@@ -11964,11 +11964,11 @@
         <v>405</v>
       </c>
       <c r="B179" s="9">
-        <v>46167.6367112963</v>
+        <v>46167.470044629634</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46167.74282516204</v>
+        <v>46167.57615849537</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>62</v>
@@ -12017,11 +12017,11 @@
         <v>406</v>
       </c>
       <c r="B180" s="5">
-        <v>46167.63672008102</v>
+        <v>46167.47005341435</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46167.742824456014</v>
+        <v>46167.57615778936</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>62</v>
@@ -12070,11 +12070,11 @@
         <v>407</v>
       </c>
       <c r="B181" s="9">
-        <v>46167.636729247686</v>
+        <v>46167.47006258102</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46167.74282375</v>
+        <v>46167.576157083335</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>62</v>
@@ -12123,11 +12123,11 @@
         <v>408</v>
       </c>
       <c r="B182" s="5">
-        <v>46167.63683603009</v>
+        <v>46167.47016936343</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46167.74282306713</v>
+        <v>46167.576156400464</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>70</v>
@@ -12176,11 +12176,11 @@
         <v>409</v>
       </c>
       <c r="B183" s="9">
-        <v>46167.636846319445</v>
+        <v>46167.47017965278</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46167.74282237269</v>
+        <v>46167.57615570602</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>70</v>
@@ -12229,11 +12229,11 @@
         <v>410</v>
       </c>
       <c r="B184" s="5">
-        <v>46167.55743945602</v>
+        <v>46167.39077278935</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46167.7430450463</v>
+        <v>46167.57637837963</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>411</v>
@@ -12292,14 +12292,14 @@
         <v>413</v>
       </c>
       <c r="B185" s="9">
-        <v>46167.55744423611</v>
+        <v>46167.390777569446</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46167.74306620371</v>
+        <v>46167.576399537036</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12327,7 +12327,7 @@
         <v>411</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P185" s="10" t="s">
         <v>414</v>
@@ -12343,14 +12343,14 @@
         <v>415</v>
       </c>
       <c r="B186" s="5">
-        <v>46167.55744884259</v>
+        <v>46167.39078217593</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46167.74306335648</v>
+        <v>46167.576396689816</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12378,7 +12378,7 @@
         <v>411</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>416</v>
@@ -12394,14 +12394,14 @@
         <v>417</v>
       </c>
       <c r="B187" s="9">
-        <v>46167.55745349537</v>
+        <v>46167.390786828706</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46167.74306008102</v>
+        <v>46167.57639341435</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12429,7 +12429,7 @@
         <v>411</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>416</v>
@@ -12445,14 +12445,14 @@
         <v>418</v>
       </c>
       <c r="B188" s="5">
-        <v>46167.55745777777</v>
+        <v>46167.39079111112</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46167.74305738426</v>
+        <v>46167.57639071759</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12480,7 +12480,7 @@
         <v>411</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>416</v>
@@ -12496,14 +12496,14 @@
         <v>419</v>
       </c>
       <c r="B189" s="9">
-        <v>46167.637670833334</v>
+        <v>46167.47100416667</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46167.74305466435</v>
+        <v>46167.57638799769</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12531,10 +12531,10 @@
         <v>411</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12547,14 +12547,14 @@
         <v>420</v>
       </c>
       <c r="B190" s="5">
-        <v>46167.63768076389</v>
+        <v>46167.471014097224</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46167.743051990736</v>
+        <v>46167.57638532408</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12582,10 +12582,10 @@
         <v>411</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12598,14 +12598,14 @@
         <v>421</v>
       </c>
       <c r="B191" s="9">
-        <v>46167.637724016204</v>
+        <v>46167.47105734954</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46167.74304920139</v>
+        <v>46167.576382534724</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12633,10 +12633,10 @@
         <v>411</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12649,14 +12649,14 @@
         <v>422</v>
       </c>
       <c r="B192" s="5">
-        <v>46167.63773231482</v>
+        <v>46167.47106564815</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46167.743046574076</v>
+        <v>46167.576379907405</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12684,10 +12684,10 @@
         <v>411</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12700,11 +12700,11 @@
         <v>423</v>
       </c>
       <c r="B193" s="9">
-        <v>46167.63788011574</v>
+        <v>46167.47121344907</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46167.74304366898</v>
+        <v>46167.57637700232</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>62</v>
@@ -12753,11 +12753,11 @@
         <v>424</v>
       </c>
       <c r="B194" s="5">
-        <v>46167.637888530095</v>
+        <v>46167.47122186342</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46167.743040671296</v>
+        <v>46167.57637400463</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>62</v>
@@ -12806,11 +12806,11 @@
         <v>425</v>
       </c>
       <c r="B195" s="9">
-        <v>46167.63789722222</v>
+        <v>46167.47123055556</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46167.74303790509</v>
+        <v>46167.57637123842</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>62</v>
@@ -12859,11 +12859,11 @@
         <v>426</v>
       </c>
       <c r="B196" s="5">
-        <v>46167.63790768519</v>
+        <v>46167.47124101852</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46167.743035231484</v>
+        <v>46167.57636856481</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>62</v>
@@ -12912,11 +12912,11 @@
         <v>427</v>
       </c>
       <c r="B197" s="9">
-        <v>46167.63791662037</v>
+        <v>46167.471249953705</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46167.74302515046</v>
+        <v>46167.5763584838</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>62</v>
@@ -12965,11 +12965,11 @@
         <v>428</v>
       </c>
       <c r="B198" s="5">
-        <v>46167.637946689814</v>
+        <v>46167.47128002315</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46167.74302446759</v>
+        <v>46167.57635780092</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>62</v>
@@ -13018,11 +13018,11 @@
         <v>429</v>
       </c>
       <c r="B199" s="9">
-        <v>46167.637995729165</v>
+        <v>46167.4713290625</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46167.74302380787</v>
+        <v>46167.5763571412</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>70</v>
@@ -13071,11 +13071,11 @@
         <v>430</v>
       </c>
       <c r="B200" s="5">
-        <v>46167.63800420139</v>
+        <v>46167.47133753472</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46167.74302313657</v>
+        <v>46167.57635646991</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>70</v>
@@ -13124,11 +13124,11 @@
         <v>431</v>
       </c>
       <c r="B201" s="9">
-        <v>46167.55746224537</v>
+        <v>46167.3907955787</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46167.74364532407</v>
+        <v>46167.57697865741</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>432</v>
@@ -13187,14 +13187,14 @@
         <v>433</v>
       </c>
       <c r="B202" s="5">
-        <v>46167.55746689815</v>
+        <v>46167.390800231486</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46167.74367725695</v>
+        <v>46167.57701059028</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
@@ -13224,7 +13224,7 @@
         <v>432</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>434</v>
@@ -13240,14 +13240,14 @@
         <v>435</v>
       </c>
       <c r="B203" s="9">
-        <v>46167.55747543981</v>
+        <v>46167.39080877315</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46167.743674363424</v>
+        <v>46167.57700769676</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
@@ -13277,7 +13277,7 @@
         <v>432</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P203" s="10" t="s">
         <v>436</v>
@@ -13293,14 +13293,14 @@
         <v>437</v>
       </c>
       <c r="B204" s="5">
-        <v>46167.557519270835</v>
+        <v>46167.39085260416</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46167.743671840275</v>
+        <v>46167.57700517361</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13330,7 +13330,7 @@
         <v>432</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>438</v>
@@ -13346,14 +13346,14 @@
         <v>439</v>
       </c>
       <c r="B205" s="9">
-        <v>46167.5575253125</v>
+        <v>46167.390858645835</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46167.74366940973</v>
+        <v>46167.577002743055</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
@@ -13383,7 +13383,7 @@
         <v>432</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P205" s="10" t="s">
         <v>438</v>
@@ -13399,14 +13399,14 @@
         <v>440</v>
       </c>
       <c r="B206" s="5">
-        <v>46167.6385715162</v>
+        <v>46167.47190484953</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46167.74366684028</v>
+        <v>46167.57700017361</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13436,10 +13436,10 @@
         <v>432</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13452,14 +13452,14 @@
         <v>441</v>
       </c>
       <c r="B207" s="9">
-        <v>46167.63857899306</v>
+        <v>46167.47191232639</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46167.74366416667</v>
+        <v>46167.5769975</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
@@ -13489,10 +13489,10 @@
         <v>432</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13505,14 +13505,14 @@
         <v>442</v>
       </c>
       <c r="B208" s="5">
-        <v>46167.638659930555</v>
+        <v>46167.47199326388</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46167.74366101852</v>
+        <v>46167.57699435185</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
@@ -13542,7 +13542,7 @@
         <v>432</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>443</v>
@@ -13558,14 +13558,14 @@
         <v>444</v>
       </c>
       <c r="B209" s="9">
-        <v>46167.638666956016</v>
+        <v>46167.47200028935</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46167.743658402775</v>
+        <v>46167.57699173611</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
@@ -13595,7 +13595,7 @@
         <v>432</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>443</v>
@@ -13611,11 +13611,11 @@
         <v>445</v>
       </c>
       <c r="B210" s="5">
-        <v>46167.6387090162</v>
+        <v>46167.47204234954</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46167.74365560185</v>
+        <v>46167.57698893519</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>62</v>
@@ -13664,11 +13664,11 @@
         <v>446</v>
       </c>
       <c r="B211" s="9">
-        <v>46167.63871641204</v>
+        <v>46167.47204974537</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46167.74365315972</v>
+        <v>46167.576986493055</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>62</v>
@@ -13717,11 +13717,11 @@
         <v>447</v>
       </c>
       <c r="B212" s="5">
-        <v>46167.638723599535</v>
+        <v>46167.47205693287</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46167.74365077546</v>
+        <v>46167.5769841088</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>62</v>
@@ -13770,11 +13770,11 @@
         <v>448</v>
       </c>
       <c r="B213" s="9">
-        <v>46167.63873144676</v>
+        <v>46167.47206478009</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46167.7436480787</v>
+        <v>46167.576981412036</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>62</v>
@@ -13823,11 +13823,11 @@
         <v>449</v>
       </c>
       <c r="B214" s="5">
-        <v>46167.6387405787</v>
+        <v>46167.47207391204</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46167.74363872685</v>
+        <v>46167.57697206018</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>62</v>
@@ -13876,11 +13876,11 @@
         <v>450</v>
       </c>
       <c r="B215" s="9">
-        <v>46167.63874844907</v>
+        <v>46167.47208178241</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46167.74363802084</v>
+        <v>46167.57697135417</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>62</v>
@@ -13929,11 +13929,11 @@
         <v>451</v>
       </c>
       <c r="B216" s="5">
-        <v>46167.638756562505</v>
+        <v>46167.47208989583</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46167.74363733796</v>
+        <v>46167.576970671296</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>70</v>
@@ -13982,11 +13982,11 @@
         <v>453</v>
       </c>
       <c r="B217" s="9">
-        <v>46167.63883428241</v>
+        <v>46167.47216761574</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46167.743636666666</v>
+        <v>46167.576969999995</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>70</v>
@@ -14035,11 +14035,11 @@
         <v>454</v>
       </c>
       <c r="B218" s="5">
-        <v>46167.55752998842</v>
+        <v>46167.39086332176</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46167.74382108796</v>
+        <v>46167.57715442129</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>455</v>
@@ -14098,14 +14098,14 @@
         <v>457</v>
       </c>
       <c r="B219" s="9">
-        <v>46167.55753614583</v>
+        <v>46167.39086947917</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46167.74384899306</v>
+        <v>46167.57718232639</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
@@ -14135,7 +14135,7 @@
         <v>455</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>455</v>
@@ -14151,14 +14151,14 @@
         <v>458</v>
       </c>
       <c r="B220" s="5">
-        <v>46167.557540381946</v>
+        <v>46167.39087371528</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46167.74384597222</v>
+        <v>46167.57717930556</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
@@ -14188,7 +14188,7 @@
         <v>455</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>455</v>
@@ -14204,14 +14204,14 @@
         <v>459</v>
       </c>
       <c r="B221" s="9">
-        <v>46167.557545069445</v>
+        <v>46167.39087840277</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46167.743843414355</v>
+        <v>46167.57717674768</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
@@ -14241,7 +14241,7 @@
         <v>455</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>455</v>
@@ -14257,14 +14257,14 @@
         <v>460</v>
       </c>
       <c r="B222" s="5">
-        <v>46167.55754895833</v>
+        <v>46167.39088229167</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46167.7438406713</v>
+        <v>46167.57717400463</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
@@ -14294,7 +14294,7 @@
         <v>455</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>455</v>
@@ -14310,14 +14310,14 @@
         <v>461</v>
       </c>
       <c r="B223" s="9">
-        <v>46167.63903770833</v>
+        <v>46167.472371041666</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46167.743837939815</v>
+        <v>46167.57717127315</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
@@ -14347,7 +14347,7 @@
         <v>455</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14363,14 +14363,14 @@
         <v>462</v>
       </c>
       <c r="B224" s="5">
-        <v>46167.639049317135</v>
+        <v>46167.47238265046</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46167.74383519676</v>
+        <v>46167.57716853009</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
@@ -14400,7 +14400,7 @@
         <v>455</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14416,11 +14416,11 @@
         <v>463</v>
       </c>
       <c r="B225" s="9">
-        <v>46167.639172118055</v>
+        <v>46167.472505451384</v>
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46167.743832430555</v>
+        <v>46167.57716576389</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>443</v>
@@ -14453,7 +14453,7 @@
         <v>455</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14469,11 +14469,11 @@
         <v>464</v>
       </c>
       <c r="B226" s="5">
-        <v>46167.63918146991</v>
+        <v>46167.472514803245</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46167.74382957176</v>
+        <v>46167.577162905094</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>443</v>
@@ -14506,7 +14506,7 @@
         <v>455</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14522,11 +14522,11 @@
         <v>465</v>
       </c>
       <c r="B227" s="9">
-        <v>46167.63922125</v>
+        <v>46167.472554583335</v>
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46167.74382638889</v>
+        <v>46167.57715972222</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>62</v>
@@ -14575,11 +14575,11 @@
         <v>466</v>
       </c>
       <c r="B228" s="5">
-        <v>46167.63923230324</v>
+        <v>46167.47256563658</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46167.74382362269</v>
+        <v>46167.57715695602</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>62</v>
@@ -14628,11 +14628,11 @@
         <v>467</v>
       </c>
       <c r="B229" s="9">
-        <v>46167.63924049769</v>
+        <v>46167.47257383102</v>
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46167.74381421296</v>
+        <v>46167.5771475463</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>62</v>
@@ -14681,11 +14681,11 @@
         <v>468</v>
       </c>
       <c r="B230" s="5">
-        <v>46167.63924949074</v>
+        <v>46167.47258282408</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46167.74381306713</v>
+        <v>46167.577146400465</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>62</v>
@@ -14734,11 +14734,11 @@
         <v>469</v>
       </c>
       <c r="B231" s="9">
-        <v>46167.639259375</v>
+        <v>46167.472592708335</v>
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46167.74380835648</v>
+        <v>46167.57714168981</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>62</v>
@@ -14787,11 +14787,11 @@
         <v>470</v>
       </c>
       <c r="B232" s="5">
-        <v>46167.63926804398</v>
+        <v>46167.47260137732</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46167.74380726852</v>
+        <v>46167.57714060185</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>62</v>
@@ -14840,11 +14840,11 @@
         <v>471</v>
       </c>
       <c r="B233" s="9">
-        <v>46167.63935532408</v>
+        <v>46167.472688657406</v>
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46167.74380655093</v>
+        <v>46167.57713988426</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>452</v>
@@ -14893,11 +14893,11 @@
         <v>472</v>
       </c>
       <c r="B234" s="5">
-        <v>46167.63936689815</v>
+        <v>46167.47270023148</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46167.74380591435</v>
+        <v>46167.57713924769</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>452</v>
@@ -14946,11 +14946,11 @@
         <v>473</v>
       </c>
       <c r="B235" s="9">
-        <v>46167.55755266204</v>
+        <v>46167.390885995366</v>
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46167.73498962963</v>
+        <v>46167.568322962965</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>474</v>
@@ -14993,11 +14993,11 @@
         <v>476</v>
       </c>
       <c r="B236" s="5">
-        <v>46167.55755585648</v>
+        <v>46167.39088918982</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46167.743865428245</v>
+        <v>46167.57719876157</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>477</v>
@@ -15056,11 +15056,11 @@
         <v>480</v>
       </c>
       <c r="B237" s="9">
-        <v>46167.55756052083</v>
+        <v>46167.39089385417</v>
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46189.872060740745</v>
+        <v>46189.70539407407</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>481</v>
@@ -15119,11 +15119,11 @@
         <v>482</v>
       </c>
       <c r="B238" s="5">
-        <v>46167.557566296295</v>
+        <v>46167.39089962963</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46167.73546241898</v>
+        <v>46167.56879575232</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>483</v>
@@ -15172,11 +15172,11 @@
         <v>485</v>
       </c>
       <c r="B239" s="9">
-        <v>46167.55756988426</v>
+        <v>46167.390903217594</v>
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46167.743959513886</v>
+        <v>46167.57729284722</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>486</v>
@@ -15235,11 +15235,11 @@
         <v>488</v>
       </c>
       <c r="B240" s="5">
-        <v>46167.557574895836</v>
+        <v>46167.390908229165</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46167.74395664352</v>
+        <v>46167.57728997685</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>489</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -2145,13 +2145,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46167.38994775463</v>
+        <v>46167.55661442129</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.71147724537</v>
+        <v>46175.878143912036</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.71148831019</v>
+        <v>46175.87815497685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2198,13 +2198,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46167.3900909375</v>
+        <v>46167.556757604165</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.7114078125</v>
+        <v>46175.878074479166</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.71142508102</v>
+        <v>46175.87809174768</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2261,13 +2261,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46167.39009450232</v>
+        <v>46167.55676116898</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.7114558912</v>
+        <v>46175.87812255787</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.71147844907</v>
+        <v>46175.87814511574</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2324,13 +2324,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46167.390099490745</v>
+        <v>46167.5567661574</v>
       </c>
       <c r="C7" s="9">
-        <v>46175.71145641204</v>
+        <v>46175.8781230787</v>
       </c>
       <c r="D7" s="9">
-        <v>46175.71147767361</v>
+        <v>46175.87814434028</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2387,13 +2387,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46167.39010253472</v>
+        <v>46167.55676920139</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.71145681713</v>
+        <v>46175.878123483795</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.71147898148</v>
+        <v>46175.87814564815</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2450,13 +2450,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46167.39010650463</v>
+        <v>46167.556773171294</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.711457384255</v>
+        <v>46175.87812405093</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.71147805556</v>
+        <v>46175.87814472222</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2513,11 +2513,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46167.38995350694</v>
+        <v>46167.55662017361</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46198.47044157407</v>
+        <v>46198.63710824074</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2560,13 +2560,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46167.390111099536</v>
+        <v>46167.55677776621</v>
       </c>
       <c r="C11" s="9">
-        <v>46198.47043523148</v>
+        <v>46198.637101898144</v>
       </c>
       <c r="D11" s="9">
-        <v>46198.47045237268</v>
+        <v>46198.637119039355</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2625,11 +2625,11 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46167.39011652778</v>
+        <v>46167.55678319444</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46167.57079327546</v>
+        <v>46167.73745994213</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2688,11 +2688,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46167.46745108796</v>
+        <v>46167.63411775463</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46167.57087763889</v>
+        <v>46167.73754430556</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2741,11 +2741,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46167.46776753472</v>
+        <v>46167.63443420139</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46167.57087484954</v>
+        <v>46167.7375415162</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2794,11 +2794,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="9">
-        <v>46167.46778902778</v>
+        <v>46167.634455694446</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46167.57087202546</v>
+        <v>46167.737538692134</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>62</v>
@@ -2847,11 +2847,11 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46167.4677987037</v>
+        <v>46167.63446537037</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46167.57086895833</v>
+        <v>46167.737535625</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>62</v>
@@ -2900,11 +2900,11 @@
         <v>67</v>
       </c>
       <c r="B17" s="9">
-        <v>46167.46780734954</v>
+        <v>46167.6344740162</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46167.570866215276</v>
+        <v>46167.73753288195</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>62</v>
@@ -2953,11 +2953,11 @@
         <v>68</v>
       </c>
       <c r="B18" s="5">
-        <v>46167.46781417824</v>
+        <v>46167.63448084491</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46167.57086368055</v>
+        <v>46167.73753034722</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>62</v>
@@ -3006,11 +3006,11 @@
         <v>69</v>
       </c>
       <c r="B19" s="9">
-        <v>46167.46786875</v>
+        <v>46167.63453541667</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46167.57085797454</v>
+        <v>46167.737524641205</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>70</v>
@@ -3059,11 +3059,11 @@
         <v>71</v>
       </c>
       <c r="B20" s="5">
-        <v>46167.46807726852</v>
+        <v>46167.63474393518</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46171.34429259259</v>
+        <v>46171.51095925926</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>70</v>
@@ -3112,11 +3112,11 @@
         <v>72</v>
       </c>
       <c r="B21" s="9">
-        <v>46167.38995982639</v>
+        <v>46167.55662649305</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46189.705403622684</v>
+        <v>46189.87207028935</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>73</v>
@@ -3161,13 +3161,13 @@
         <v>76</v>
       </c>
       <c r="B22" s="5">
-        <v>46167.39012296296</v>
+        <v>46167.55678962963</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.704502175926</v>
+        <v>46183.8711688426</v>
       </c>
       <c r="D22" s="5">
-        <v>46189.70539398148</v>
+        <v>46189.87206064815</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>77</v>
@@ -3226,13 +3226,13 @@
         <v>82</v>
       </c>
       <c r="B23" s="9">
-        <v>46167.390128252315</v>
+        <v>46167.556794918986</v>
       </c>
       <c r="C23" s="9">
-        <v>46183.704511284726</v>
+        <v>46183.87117795139</v>
       </c>
       <c r="D23" s="9">
-        <v>46189.70539386574</v>
+        <v>46189.872060532405</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>83</v>
@@ -3291,13 +3291,13 @@
         <v>86</v>
       </c>
       <c r="B24" s="5">
-        <v>46167.39013399306</v>
+        <v>46167.55680065972</v>
       </c>
       <c r="C24" s="5">
-        <v>46183.704518136576</v>
+        <v>46183.87118480324</v>
       </c>
       <c r="D24" s="5">
-        <v>46189.70539386574</v>
+        <v>46189.872060532405</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>87</v>
@@ -3356,11 +3356,11 @@
         <v>89</v>
       </c>
       <c r="B25" s="9">
-        <v>46167.38996634259</v>
+        <v>46167.556633009255</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46196.48241881945</v>
+        <v>46196.64908548611</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>90</v>
@@ -3403,13 +3403,13 @@
         <v>92</v>
       </c>
       <c r="B26" s="5">
-        <v>46167.39014790509</v>
+        <v>46167.556814571755</v>
       </c>
       <c r="C26" s="5">
-        <v>46189.705961377316</v>
+        <v>46189.87262804398</v>
       </c>
       <c r="D26" s="5">
-        <v>46189.711419375</v>
+        <v>46189.87808604167</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>93</v>
@@ -3468,11 +3468,11 @@
         <v>94</v>
       </c>
       <c r="B27" s="9">
-        <v>46167.390153506945</v>
+        <v>46167.55682017361</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46189.7127053125</v>
+        <v>46189.87937197917</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>95</v>
@@ -3531,13 +3531,13 @@
         <v>97</v>
       </c>
       <c r="B28" s="5">
-        <v>46167.390159201386</v>
+        <v>46167.55682586806</v>
       </c>
       <c r="C28" s="5">
-        <v>46190.47448096065</v>
+        <v>46190.64114762731</v>
       </c>
       <c r="D28" s="5">
-        <v>46190.47449871528</v>
+        <v>46190.641165381945</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>98</v>
@@ -3596,13 +3596,13 @@
         <v>101</v>
       </c>
       <c r="B29" s="9">
-        <v>46167.390164756944</v>
+        <v>46167.556831423615</v>
       </c>
       <c r="C29" s="9">
-        <v>46196.48241347222</v>
+        <v>46196.649080138886</v>
       </c>
       <c r="D29" s="9">
-        <v>46196.482428483796</v>
+        <v>46196.64909515047</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>102</v>
@@ -3661,13 +3661,13 @@
         <v>108</v>
       </c>
       <c r="B30" s="5">
-        <v>46167.39016981481</v>
+        <v>46167.55683648148</v>
       </c>
       <c r="C30" s="5">
-        <v>46196.482939803245</v>
+        <v>46196.6496064699</v>
       </c>
       <c r="D30" s="5">
-        <v>46196.48295655093</v>
+        <v>46196.64962321759</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>109</v>
@@ -3726,13 +3726,13 @@
         <v>111</v>
       </c>
       <c r="B31" s="9">
-        <v>46167.39017408565</v>
+        <v>46167.55684075231</v>
       </c>
       <c r="C31" s="9">
-        <v>46196.48442226852</v>
+        <v>46196.651088935185</v>
       </c>
       <c r="D31" s="9">
-        <v>46196.48443877314</v>
+        <v>46196.651105439814</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>112</v>
@@ -3791,13 +3791,13 @@
         <v>114</v>
       </c>
       <c r="B32" s="5">
-        <v>46167.39017840278</v>
+        <v>46167.55684506944</v>
       </c>
       <c r="C32" s="5">
-        <v>46196.48521329861</v>
+        <v>46196.65187996528</v>
       </c>
       <c r="D32" s="5">
-        <v>46196.485228749996</v>
+        <v>46196.65189541667</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>115</v>
@@ -3856,11 +3856,11 @@
         <v>117</v>
       </c>
       <c r="B33" s="9">
-        <v>46167.39018246528</v>
+        <v>46167.55684913194</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46198.47045355324</v>
+        <v>46198.63712021991</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>118</v>
@@ -3919,13 +3919,13 @@
         <v>120</v>
       </c>
       <c r="B34" s="5">
-        <v>46189.70673278935</v>
+        <v>46189.87339945602</v>
       </c>
       <c r="C34" s="5">
-        <v>46190.47692103009</v>
+        <v>46190.64358769676</v>
       </c>
       <c r="D34" s="5">
-        <v>46190.4769345949</v>
+        <v>46190.643601261574</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>121</v>
@@ -3972,13 +3972,13 @@
         <v>122</v>
       </c>
       <c r="B35" s="9">
-        <v>46189.70744986111</v>
+        <v>46189.874116527775</v>
       </c>
       <c r="C35" s="9">
-        <v>46190.476905081014</v>
+        <v>46190.643571747685</v>
       </c>
       <c r="D35" s="9">
-        <v>46190.476921712965</v>
+        <v>46190.64358837963</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>123</v>
@@ -4037,13 +4037,13 @@
         <v>125</v>
       </c>
       <c r="B36" s="5">
-        <v>46189.70761759259</v>
+        <v>46189.87428425926</v>
       </c>
       <c r="C36" s="5">
-        <v>46190.47677572917</v>
+        <v>46190.643442395834</v>
       </c>
       <c r="D36" s="5">
-        <v>46190.47686277778</v>
+        <v>46190.643529444445</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>126</v>
@@ -4102,11 +4102,11 @@
         <v>128</v>
       </c>
       <c r="B37" s="9">
-        <v>46167.38997502315</v>
+        <v>46167.556641689815</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46199.39705436343</v>
+        <v>46199.56372103009</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>129</v>
@@ -4151,13 +4151,13 @@
         <v>131</v>
       </c>
       <c r="B38" s="5">
-        <v>46167.39020285879</v>
+        <v>46167.55686952546</v>
       </c>
       <c r="C38" s="5">
-        <v>46195.76335146991</v>
+        <v>46195.93001813657</v>
       </c>
       <c r="D38" s="5">
-        <v>46195.76335346064</v>
+        <v>46195.930020127314</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>132</v>
@@ -4216,13 +4216,13 @@
         <v>136</v>
       </c>
       <c r="B39" s="9">
-        <v>46167.39020760417</v>
+        <v>46167.556874270835</v>
       </c>
       <c r="C39" s="9">
-        <v>46195.76139655092</v>
+        <v>46195.928063217594</v>
       </c>
       <c r="D39" s="9">
-        <v>46195.76139850695</v>
+        <v>46195.92806517361</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>137</v>
@@ -4277,13 +4277,13 @@
         <v>139</v>
       </c>
       <c r="B40" s="5">
-        <v>46167.39021280092</v>
+        <v>46167.55687946759</v>
       </c>
       <c r="C40" s="5">
-        <v>46195.76321664352</v>
+        <v>46195.929883310186</v>
       </c>
       <c r="D40" s="5">
-        <v>46195.76321827546</v>
+        <v>46195.92988494213</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>140</v>
@@ -4338,11 +4338,11 @@
         <v>142</v>
       </c>
       <c r="B41" s="9">
-        <v>46167.39029436343</v>
+        <v>46167.55696103009</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.712276018516</v>
+        <v>46169.87894268519</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>143</v>
@@ -4401,11 +4401,11 @@
         <v>145</v>
       </c>
       <c r="B42" s="5">
-        <v>46167.39029858796</v>
+        <v>46167.556965254626</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46170.00517337963</v>
+        <v>46170.1718400463</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>119</v>
@@ -4454,11 +4454,11 @@
         <v>147</v>
       </c>
       <c r="B43" s="9">
-        <v>46167.39030298611</v>
+        <v>46167.55696965278</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.71236159722</v>
+        <v>46169.87902826389</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>148</v>
@@ -4507,13 +4507,13 @@
         <v>150</v>
       </c>
       <c r="B44" s="5">
-        <v>46167.390307118054</v>
+        <v>46167.556973784725</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.397034340276</v>
+        <v>46199.56370100695</v>
       </c>
       <c r="D44" s="5">
-        <v>46205.0023444213</v>
+        <v>46205.169011087964</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>151</v>
@@ -4572,13 +4572,13 @@
         <v>155</v>
       </c>
       <c r="B45" s="9">
-        <v>46167.390311944444</v>
+        <v>46167.556978611115</v>
       </c>
       <c r="C45" s="9">
-        <v>46199.3969519213</v>
+        <v>46199.56361858796</v>
       </c>
       <c r="D45" s="9">
-        <v>46199.3969540625</v>
+        <v>46199.56362072917</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>156</v>
@@ -4633,13 +4633,13 @@
         <v>158</v>
       </c>
       <c r="B46" s="5">
-        <v>46167.39031701389</v>
+        <v>46167.55698368055</v>
       </c>
       <c r="C46" s="5">
-        <v>46199.39701877315</v>
+        <v>46199.56368543982</v>
       </c>
       <c r="D46" s="5">
-        <v>46199.39702045139</v>
+        <v>46199.563687118054</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>159</v>
@@ -4694,13 +4694,13 @@
         <v>161</v>
       </c>
       <c r="B47" s="9">
-        <v>46167.390322175925</v>
+        <v>46167.556988842596</v>
       </c>
       <c r="C47" s="9">
-        <v>46199.397158078704</v>
+        <v>46199.563824745375</v>
       </c>
       <c r="D47" s="9">
-        <v>46205.0023444213</v>
+        <v>46205.169011087964</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>162</v>
@@ -4759,13 +4759,13 @@
         <v>164</v>
       </c>
       <c r="B48" s="5">
-        <v>46167.39032604167</v>
+        <v>46167.556992708334</v>
       </c>
       <c r="C48" s="5">
-        <v>46199.39708834491</v>
+        <v>46199.56375501158</v>
       </c>
       <c r="D48" s="5">
-        <v>46199.397090011575</v>
+        <v>46199.56375667824</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4814,13 +4814,13 @@
         <v>166</v>
       </c>
       <c r="B49" s="9">
-        <v>46167.39033052084</v>
+        <v>46167.5569971875</v>
       </c>
       <c r="C49" s="9">
-        <v>46199.397144305556</v>
+        <v>46199.56381097222</v>
       </c>
       <c r="D49" s="9">
-        <v>46199.39781077547</v>
+        <v>46199.56447744213</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>167</v>
@@ -4869,13 +4869,13 @@
         <v>169</v>
       </c>
       <c r="B50" s="5">
-        <v>46167.39033473379</v>
+        <v>46167.55700140046</v>
       </c>
       <c r="C50" s="5">
-        <v>46204.42912579861</v>
+        <v>46204.595792465276</v>
       </c>
       <c r="D50" s="5">
-        <v>46204.429473055556</v>
+        <v>46204.59613972223</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>
@@ -4934,13 +4934,13 @@
         <v>174</v>
       </c>
       <c r="B51" s="9">
-        <v>46167.390338530095</v>
+        <v>46167.55700519676</v>
       </c>
       <c r="C51" s="9">
-        <v>46204.428393344904</v>
+        <v>46204.595060011576</v>
       </c>
       <c r="D51" s="9">
-        <v>46204.42839552084</v>
+        <v>46204.5950621875</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>116</v>
@@ -4989,13 +4989,13 @@
         <v>176</v>
       </c>
       <c r="B52" s="5">
-        <v>46167.39034336805</v>
+        <v>46167.557010034725</v>
       </c>
       <c r="C52" s="5">
-        <v>46204.42849126157</v>
+        <v>46204.59515792824</v>
       </c>
       <c r="D52" s="5">
-        <v>46204.428492997686</v>
+        <v>46204.59515966436</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>177</v>
@@ -5044,11 +5044,11 @@
         <v>179</v>
       </c>
       <c r="B53" s="9">
-        <v>46167.39034810185</v>
+        <v>46167.55701476852</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46204.42850030093</v>
+        <v>46204.59516696759</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>180</v>
@@ -5097,13 +5097,13 @@
         <v>183</v>
       </c>
       <c r="B54" s="5">
-        <v>46167.39035103009</v>
+        <v>46167.55701769676</v>
       </c>
       <c r="C54" s="5">
-        <v>46199.397935381945</v>
+        <v>46199.56460204862</v>
       </c>
       <c r="D54" s="5">
-        <v>46205.0023444213</v>
+        <v>46205.169011087964</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>184</v>
@@ -5162,13 +5162,13 @@
         <v>186</v>
       </c>
       <c r="B55" s="9">
-        <v>46167.39035501158</v>
+        <v>46167.557021678236</v>
       </c>
       <c r="C55" s="9">
-        <v>46199.39773226852</v>
+        <v>46199.56439893518</v>
       </c>
       <c r="D55" s="9">
-        <v>46199.397733935184</v>
+        <v>46199.564400601856</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>113</v>
@@ -5217,13 +5217,13 @@
         <v>188</v>
       </c>
       <c r="B56" s="5">
-        <v>46167.39035967593</v>
+        <v>46167.55702634259</v>
       </c>
       <c r="C56" s="5">
-        <v>46199.3979215162</v>
+        <v>46199.56458818287</v>
       </c>
       <c r="D56" s="5">
-        <v>46199.39792300926</v>
+        <v>46199.56458967592</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>189</v>
@@ -5272,11 +5272,11 @@
         <v>191</v>
       </c>
       <c r="B57" s="9">
-        <v>46167.3903700463</v>
+        <v>46167.55703671296</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46189.72488962963</v>
+        <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>192</v>
@@ -5319,13 +5319,13 @@
         <v>194</v>
       </c>
       <c r="B58" s="5">
-        <v>46167.39037385417</v>
+        <v>46167.557040520835</v>
       </c>
       <c r="C58" s="5">
-        <v>46184.35049503473</v>
+        <v>46184.517161701384</v>
       </c>
       <c r="D58" s="5">
-        <v>46197.54840078704</v>
+        <v>46197.715067453704</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>195</v>
@@ -5384,13 +5384,13 @@
         <v>199</v>
       </c>
       <c r="B59" s="9">
-        <v>46167.39037918982</v>
+        <v>46167.557045856476</v>
       </c>
       <c r="C59" s="9">
-        <v>46189.70835143518</v>
+        <v>46189.875018101855</v>
       </c>
       <c r="D59" s="9">
-        <v>46197.54843625</v>
+        <v>46197.71510291667</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>200</v>
@@ -5449,13 +5449,13 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46167.390385300925</v>
+        <v>46167.5570519676</v>
       </c>
       <c r="C60" s="5">
-        <v>46189.70841653935</v>
+        <v>46189.87508320602</v>
       </c>
       <c r="D60" s="5">
-        <v>46190.033048067125</v>
+        <v>46190.1997147338</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>105</v>
@@ -5514,11 +5514,11 @@
         <v>206</v>
       </c>
       <c r="B61" s="9">
-        <v>46167.39039785879</v>
+        <v>46167.55706452546</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46167.574203321754</v>
+        <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>207</v>
@@ -5577,11 +5577,11 @@
         <v>211</v>
       </c>
       <c r="B62" s="5">
-        <v>46167.390401770834</v>
+        <v>46167.5570684375</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46167.57419234954</v>
+        <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>212</v>
@@ -5630,11 +5630,11 @@
         <v>214</v>
       </c>
       <c r="B63" s="9">
-        <v>46167.39040607639</v>
+        <v>46167.55707274306</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46167.574189074076</v>
+        <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5683,11 +5683,11 @@
         <v>215</v>
       </c>
       <c r="B64" s="5">
-        <v>46167.49309082176</v>
+        <v>46167.65975748842</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46167.57418625</v>
+        <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5736,11 +5736,11 @@
         <v>216</v>
       </c>
       <c r="B65" s="9">
-        <v>46167.49310259259</v>
+        <v>46167.65976925926</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46167.57418384259</v>
+        <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>212</v>
@@ -5789,11 +5789,11 @@
         <v>217</v>
       </c>
       <c r="B66" s="5">
-        <v>46167.493115324076</v>
+        <v>46167.65978199074</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46167.574178993054</v>
+        <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>212</v>
@@ -5842,11 +5842,11 @@
         <v>218</v>
       </c>
       <c r="B67" s="9">
-        <v>46167.493131157404</v>
+        <v>46167.659797824075</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46167.574173472225</v>
+        <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>212</v>
@@ -5895,11 +5895,11 @@
         <v>220</v>
       </c>
       <c r="B68" s="5">
-        <v>46167.49320972222</v>
+        <v>46167.65987638889</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46167.5741724074</v>
+        <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>221</v>
@@ -5948,11 +5948,11 @@
         <v>222</v>
       </c>
       <c r="B69" s="9">
-        <v>46167.49322012732</v>
+        <v>46167.65988679398</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46167.57417168982</v>
+        <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>221</v>
@@ -6001,11 +6001,11 @@
         <v>223</v>
       </c>
       <c r="B70" s="5">
-        <v>46167.39041047454</v>
+        <v>46167.5570771412</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46167.46252136574</v>
+        <v>46167.629188032406</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>224</v>
@@ -6048,11 +6048,11 @@
         <v>226</v>
       </c>
       <c r="B71" s="9">
-        <v>46167.39041413194</v>
+        <v>46167.55708079861</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46199.3970362963</v>
+        <v>46199.56370296296</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>227</v>
@@ -6111,11 +6111,11 @@
         <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46167.39041931713</v>
+        <v>46167.5570859838</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46203.03004518518</v>
+        <v>46203.19671185185</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -6174,11 +6174,11 @@
         <v>236</v>
       </c>
       <c r="B73" s="9">
-        <v>46167.390425150465</v>
+        <v>46167.55709181713</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46199.39716129629</v>
+        <v>46199.563827962964</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>237</v>
@@ -6237,11 +6237,11 @@
         <v>239</v>
       </c>
       <c r="B74" s="5">
-        <v>46167.390430162035</v>
+        <v>46167.55709682871</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46203.030044907406</v>
+        <v>46203.19671157407</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>240</v>
@@ -6300,11 +6300,11 @@
         <v>242</v>
       </c>
       <c r="B75" s="9">
-        <v>46167.390486122684</v>
+        <v>46167.55715278935</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46199.39793868056</v>
+        <v>46199.56460534722</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>243</v>
@@ -6363,11 +6363,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46167.390497500004</v>
+        <v>46167.55716416667</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46203.03004474537</v>
+        <v>46203.196711412034</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>244</v>
@@ -6426,11 +6426,11 @@
         <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46167.39050201389</v>
+        <v>46167.557168680556</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46203.33539987268</v>
+        <v>46203.50206653935</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>247</v>
@@ -6473,13 +6473,13 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <v>46167.39050553241</v>
+        <v>46167.55717219907</v>
       </c>
       <c r="C78" s="5">
-        <v>46203.3353937963</v>
+        <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46203.33556787037</v>
+        <v>46203.50223453704</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -6538,13 +6538,13 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46167.390511562495</v>
+        <v>46167.557178229166</v>
       </c>
       <c r="C79" s="9">
-        <v>46203.33556024305</v>
+        <v>46203.502226909724</v>
       </c>
       <c r="D79" s="9">
-        <v>46203.33556259259</v>
+        <v>46203.50222925926</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>212</v>
@@ -6593,13 +6593,13 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46167.3905183912</v>
+        <v>46167.55718505787</v>
       </c>
       <c r="C80" s="5">
-        <v>46203.335807511576</v>
+        <v>46203.50247417824</v>
       </c>
       <c r="D80" s="5">
-        <v>46203.33580946759</v>
+        <v>46203.50247613426</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>212</v>
@@ -6648,13 +6648,13 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46167.46329738426</v>
+        <v>46167.629964050924</v>
       </c>
       <c r="C81" s="9">
-        <v>46203.33592380787</v>
+        <v>46203.50259047454</v>
       </c>
       <c r="D81" s="9">
-        <v>46203.33592548611</v>
+        <v>46203.50259215278</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>212</v>
@@ -6703,13 +6703,13 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46167.46330802083</v>
+        <v>46167.6299746875</v>
       </c>
       <c r="C82" s="5">
-        <v>46203.33600501157</v>
+        <v>46203.502671678245</v>
       </c>
       <c r="D82" s="5">
-        <v>46203.33600657407</v>
+        <v>46203.50267324074</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>212</v>
@@ -6758,13 +6758,13 @@
         <v>262</v>
       </c>
       <c r="B83" s="9">
-        <v>46167.46344912037</v>
+        <v>46167.63011578703</v>
       </c>
       <c r="C83" s="9">
-        <v>46203.33609789352</v>
+        <v>46203.50276456018</v>
       </c>
       <c r="D83" s="9">
-        <v>46203.336099513894</v>
+        <v>46203.50276618055</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>212</v>
@@ -6813,13 +6813,13 @@
         <v>263</v>
       </c>
       <c r="B84" s="5">
-        <v>46167.46345984953</v>
+        <v>46167.630126516204</v>
       </c>
       <c r="C84" s="5">
-        <v>46203.336214571755</v>
+        <v>46203.502881238426</v>
       </c>
       <c r="D84" s="5">
-        <v>46203.3362165625</v>
+        <v>46203.50288322917</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>212</v>
@@ -6868,13 +6868,13 @@
         <v>264</v>
       </c>
       <c r="B85" s="9">
-        <v>46167.46478888889</v>
+        <v>46167.63145555556</v>
       </c>
       <c r="C85" s="9">
-        <v>46203.33634425926</v>
+        <v>46203.503010925924</v>
       </c>
       <c r="D85" s="9">
-        <v>46203.33634616898</v>
+        <v>46203.503012835645</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>221</v>
@@ -6923,13 +6923,13 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46167.46510601851</v>
+        <v>46167.631772685185</v>
       </c>
       <c r="C86" s="5">
-        <v>46203.336434004625</v>
+        <v>46203.503100671296</v>
       </c>
       <c r="D86" s="5">
-        <v>46203.33643538195</v>
+        <v>46203.503102048606</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>221</v>
@@ -6978,11 +6978,11 @@
         <v>266</v>
       </c>
       <c r="B87" s="9">
-        <v>46167.39052417824</v>
+        <v>46167.557190844906</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46167.574720439814</v>
+        <v>46167.74138710648</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>267</v>
@@ -7041,11 +7041,11 @@
         <v>268</v>
       </c>
       <c r="B88" s="5">
-        <v>46167.39052842592</v>
+        <v>46167.557195092595</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46203.33729685185</v>
+        <v>46203.503963518524</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>212</v>
@@ -7094,11 +7094,11 @@
         <v>271</v>
       </c>
       <c r="B89" s="9">
-        <v>46167.390534328704</v>
+        <v>46167.557200995376</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46203.33743707176</v>
+        <v>46203.50410373842</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>212</v>
@@ -7147,11 +7147,11 @@
         <v>272</v>
       </c>
       <c r="B90" s="5">
-        <v>46167.4654825</v>
+        <v>46167.63214916667</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46203.33592965278</v>
+        <v>46203.50259631945</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>212</v>
@@ -7200,11 +7200,11 @@
         <v>273</v>
       </c>
       <c r="B91" s="9">
-        <v>46167.46552440972</v>
+        <v>46167.63219107639</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46203.33601212963</v>
+        <v>46203.5026787963</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>212</v>
@@ -7253,11 +7253,11 @@
         <v>274</v>
       </c>
       <c r="B92" s="5">
-        <v>46167.4655343287</v>
+        <v>46167.63220099537</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46203.336103865746</v>
+        <v>46203.5027705324</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>212</v>
@@ -7306,11 +7306,11 @@
         <v>275</v>
       </c>
       <c r="B93" s="9">
-        <v>46167.46554172454</v>
+        <v>46167.63220839121</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46203.33622094907</v>
+        <v>46203.502887615745</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>212</v>
@@ -7359,13 +7359,13 @@
         <v>276</v>
       </c>
       <c r="B94" s="5">
-        <v>46167.46558924769</v>
+        <v>46167.63225591435</v>
       </c>
       <c r="C94" s="5">
-        <v>46203.33672733796</v>
+        <v>46203.50339400463</v>
       </c>
       <c r="D94" s="5">
-        <v>46203.33672893519</v>
+        <v>46203.50339560185</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>221</v>
@@ -7414,13 +7414,13 @@
         <v>277</v>
       </c>
       <c r="B95" s="9">
-        <v>46167.46559707176</v>
+        <v>46167.63226373843</v>
       </c>
       <c r="C95" s="9">
-        <v>46203.33700665509</v>
+        <v>46203.50367332176</v>
       </c>
       <c r="D95" s="9">
-        <v>46203.3370080787</v>
+        <v>46203.50367474537</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>221</v>
@@ -7469,11 +7469,11 @@
         <v>278</v>
       </c>
       <c r="B96" s="5">
-        <v>46167.39053989583</v>
+        <v>46167.5572065625</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46167.57486626157</v>
+        <v>46167.74153292824</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>279</v>
@@ -7532,11 +7532,11 @@
         <v>280</v>
       </c>
       <c r="B97" s="9">
-        <v>46167.39054424768</v>
+        <v>46167.557210914354</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46189.70843142361</v>
+        <v>46189.87509809028</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>212</v>
@@ -7585,11 +7585,11 @@
         <v>282</v>
       </c>
       <c r="B98" s="5">
-        <v>46167.3905503125</v>
+        <v>46167.55721697917</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46189.70843274306</v>
+        <v>46189.87509940972</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>212</v>
@@ -7638,11 +7638,11 @@
         <v>283</v>
       </c>
       <c r="B99" s="9">
-        <v>46167.46567538194</v>
+        <v>46167.632342048615</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46167.57485089121</v>
+        <v>46167.74151755787</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>212</v>
@@ -7691,11 +7691,11 @@
         <v>284</v>
       </c>
       <c r="B100" s="5">
-        <v>46167.46569201389</v>
+        <v>46167.63235868055</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46167.57484836805</v>
+        <v>46167.74151503472</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7744,11 +7744,11 @@
         <v>285</v>
       </c>
       <c r="B101" s="9">
-        <v>46167.46569923611</v>
+        <v>46167.63236590278</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46167.57484596065</v>
+        <v>46167.74151262731</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>212</v>
@@ -7797,11 +7797,11 @@
         <v>286</v>
       </c>
       <c r="B102" s="5">
-        <v>46167.46570746528</v>
+        <v>46167.63237413194</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46167.57484369213</v>
+        <v>46167.7415103588</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>212</v>
@@ -7850,11 +7850,11 @@
         <v>287</v>
       </c>
       <c r="B103" s="9">
-        <v>46167.46577653935</v>
+        <v>46167.63244320602</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46203.336732951386</v>
+        <v>46203.50339961806</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>221</v>
@@ -7903,11 +7903,11 @@
         <v>288</v>
       </c>
       <c r="B104" s="5">
-        <v>46167.46578601852</v>
+        <v>46167.63245268518</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46203.33701270833</v>
+        <v>46203.503679375004</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>221</v>
@@ -7956,11 +7956,11 @@
         <v>289</v>
       </c>
       <c r="B105" s="9">
-        <v>46167.39055582176</v>
+        <v>46167.55722248842</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46189.71079353009</v>
+        <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>224</v>
@@ -8003,11 +8003,11 @@
         <v>291</v>
       </c>
       <c r="B106" s="5">
-        <v>46167.3905590162</v>
+        <v>46167.557225682875</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46195.763235335646</v>
+        <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>292</v>
@@ -8066,11 +8066,11 @@
         <v>294</v>
       </c>
       <c r="B107" s="9">
-        <v>46167.39056482639</v>
+        <v>46167.557231493054</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46190.476794664355</v>
+        <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>127</v>
@@ -8129,11 +8129,11 @@
         <v>295</v>
       </c>
       <c r="B108" s="5">
-        <v>46167.39057079861</v>
+        <v>46167.55723746528</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46189.71151717592</v>
+        <v>46189.87818384259</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>124</v>
@@ -8192,11 +8192,11 @@
         <v>297</v>
       </c>
       <c r="B109" s="9">
-        <v>46167.39058180556</v>
+        <v>46167.55724847222</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46204.42850928241</v>
+        <v>46204.59517594907</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>298</v>
@@ -8255,11 +8255,11 @@
         <v>300</v>
       </c>
       <c r="B110" s="5">
-        <v>46167.390586863425</v>
+        <v>46167.55725353009</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46167.57496805556</v>
+        <v>46167.74163472222</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>58</v>
@@ -8318,11 +8318,11 @@
         <v>302</v>
       </c>
       <c r="B111" s="9">
-        <v>46167.39059244213</v>
+        <v>46167.5572591088</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46167.56463365741</v>
+        <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>303</v>
@@ -8365,11 +8365,11 @@
         <v>305</v>
       </c>
       <c r="B112" s="5">
-        <v>46167.39059601852</v>
+        <v>46167.557262685186</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46167.57525833334</v>
+        <v>46167.741924999995</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>306</v>
@@ -8428,11 +8428,11 @@
         <v>308</v>
       </c>
       <c r="B113" s="9">
-        <v>46167.390604189815</v>
+        <v>46167.55727085649</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46167.575242245366</v>
+        <v>46167.74190891204</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>212</v>
@@ -8481,11 +8481,11 @@
         <v>310</v>
       </c>
       <c r="B114" s="5">
-        <v>46167.390608657406</v>
+        <v>46167.55727532407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46167.575239756945</v>
+        <v>46167.74190642362</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>212</v>
@@ -8534,11 +8534,11 @@
         <v>311</v>
       </c>
       <c r="B115" s="9">
-        <v>46167.46593938657</v>
+        <v>46167.632606053245</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46167.57523703703</v>
+        <v>46167.7419037037</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>212</v>
@@ -8587,11 +8587,11 @@
         <v>312</v>
       </c>
       <c r="B116" s="5">
-        <v>46167.465947766206</v>
+        <v>46167.63261443287</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46167.57523454861</v>
+        <v>46167.74190121528</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>212</v>
@@ -8640,11 +8640,11 @@
         <v>313</v>
       </c>
       <c r="B117" s="9">
-        <v>46167.46595575231</v>
+        <v>46167.63262241898</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46167.575232256946</v>
+        <v>46167.74189892361</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>212</v>
@@ -8693,11 +8693,11 @@
         <v>314</v>
       </c>
       <c r="B118" s="5">
-        <v>46167.46596372685</v>
+        <v>46167.63263039352</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46167.575229884256</v>
+        <v>46167.74189655093</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>212</v>
@@ -8746,11 +8746,11 @@
         <v>315</v>
       </c>
       <c r="B119" s="9">
-        <v>46167.46602341435</v>
+        <v>46167.63269008102</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46167.57522479167</v>
+        <v>46167.74189145833</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>221</v>
@@ -8799,11 +8799,11 @@
         <v>316</v>
       </c>
       <c r="B120" s="5">
-        <v>46167.46603207176</v>
+        <v>46167.632698738424</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46167.57522412037</v>
+        <v>46167.74189078704</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>221</v>
@@ -8852,11 +8852,11 @@
         <v>317</v>
       </c>
       <c r="B121" s="9">
-        <v>46167.39061293982</v>
+        <v>46167.55727960648</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46167.575408449076</v>
+        <v>46167.74207511574</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>318</v>
@@ -8915,11 +8915,11 @@
         <v>319</v>
       </c>
       <c r="B122" s="5">
-        <v>46167.39061770833</v>
+        <v>46167.557284375</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46189.708441006944</v>
+        <v>46189.87510767361</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>212</v>
@@ -8968,11 +8968,11 @@
         <v>322</v>
       </c>
       <c r="B123" s="9">
-        <v>46167.39062342593</v>
+        <v>46167.55729009259</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46189.70843342593</v>
+        <v>46189.87510009259</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>212</v>
@@ -9021,11 +9021,11 @@
         <v>323</v>
       </c>
       <c r="B124" s="5">
-        <v>46167.466146412036</v>
+        <v>46167.6328130787</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46189.708422800926</v>
+        <v>46189.87508946759</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -9074,11 +9074,11 @@
         <v>325</v>
       </c>
       <c r="B125" s="9">
-        <v>46167.466169189815</v>
+        <v>46167.63283585648</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46189.7084234838</v>
+        <v>46189.87509015047</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>212</v>
@@ -9127,11 +9127,11 @@
         <v>327</v>
       </c>
       <c r="B126" s="5">
-        <v>46167.46617670139</v>
+        <v>46167.63284336806</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46189.708424386576</v>
+        <v>46189.87509105324</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>212</v>
@@ -9180,11 +9180,11 @@
         <v>328</v>
       </c>
       <c r="B127" s="9">
-        <v>46167.46618496528</v>
+        <v>46167.63285163195</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46189.70842510417</v>
+        <v>46189.87509177084</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>212</v>
@@ -9233,11 +9233,11 @@
         <v>329</v>
       </c>
       <c r="B128" s="5">
-        <v>46167.46622511574</v>
+        <v>46167.63289178241</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46189.70842577546</v>
+        <v>46189.87509244213</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>221</v>
@@ -9286,11 +9286,11 @@
         <v>331</v>
       </c>
       <c r="B129" s="9">
-        <v>46167.4662325463</v>
+        <v>46167.632899212964</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46189.708426365745</v>
+        <v>46189.8750930324</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>221</v>
@@ -9339,11 +9339,11 @@
         <v>332</v>
       </c>
       <c r="B130" s="5">
-        <v>46167.39067069444</v>
+        <v>46167.55733736111</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46167.57555109954</v>
+        <v>46167.74221776621</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>333</v>
@@ -9402,11 +9402,11 @@
         <v>334</v>
       </c>
       <c r="B131" s="9">
-        <v>46167.390676979165</v>
+        <v>46167.557343645836</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46189.70844130787</v>
+        <v>46189.87510797454</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>212</v>
@@ -9453,11 +9453,11 @@
         <v>337</v>
       </c>
       <c r="B132" s="5">
-        <v>46167.39068413194</v>
+        <v>46167.55735079861</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46189.708434050925</v>
+        <v>46189.87510071759</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>212</v>
@@ -9504,11 +9504,11 @@
         <v>338</v>
       </c>
       <c r="B133" s="9">
-        <v>46167.46635693287</v>
+        <v>46167.63302359954</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46189.7084269676</v>
+        <v>46189.875093634255</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>212</v>
@@ -9555,11 +9555,11 @@
         <v>339</v>
       </c>
       <c r="B134" s="5">
-        <v>46167.466368194444</v>
+        <v>46167.63303486111</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46189.708427488426</v>
+        <v>46189.8750941551</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>212</v>
@@ -9606,11 +9606,11 @@
         <v>340</v>
       </c>
       <c r="B135" s="9">
-        <v>46167.46638398148</v>
+        <v>46167.633050648146</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46189.70842805556</v>
+        <v>46189.87509472222</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>212</v>
@@ -9657,11 +9657,11 @@
         <v>341</v>
       </c>
       <c r="B136" s="5">
-        <v>46167.46639400463</v>
+        <v>46167.633060671295</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46189.708428530095</v>
+        <v>46189.87509519676</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>212</v>
@@ -9708,11 +9708,11 @@
         <v>342</v>
       </c>
       <c r="B137" s="9">
-        <v>46167.46644851852</v>
+        <v>46167.633115185185</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46189.708429039354</v>
+        <v>46189.87509570602</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>221</v>
@@ -9759,11 +9759,11 @@
         <v>344</v>
       </c>
       <c r="B138" s="5">
-        <v>46167.466456145834</v>
+        <v>46167.6331228125</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46189.70842949074</v>
+        <v>46189.87509615741</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>221</v>
@@ -9810,11 +9810,11 @@
         <v>346</v>
       </c>
       <c r="B139" s="9">
-        <v>46167.39069082176</v>
+        <v>46167.557357488426</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46167.575698472225</v>
+        <v>46167.74236513889</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>347</v>
@@ -9873,11 +9873,11 @@
         <v>348</v>
       </c>
       <c r="B140" s="5">
-        <v>46167.39069545139</v>
+        <v>46167.55736211805</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46189.7107930787</v>
+        <v>46189.877459745374</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>212</v>
@@ -9926,11 +9926,11 @@
         <v>351</v>
       </c>
       <c r="B141" s="9">
-        <v>46167.39070600695</v>
+        <v>46167.55737267361</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46189.710794108796</v>
+        <v>46189.87746077546</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>212</v>
@@ -9979,11 +9979,11 @@
         <v>352</v>
       </c>
       <c r="B142" s="5">
-        <v>46167.46658493056</v>
+        <v>46167.63325159722</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46189.71078900463</v>
+        <v>46189.877455671296</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>212</v>
@@ -10032,11 +10032,11 @@
         <v>354</v>
       </c>
       <c r="B143" s="9">
-        <v>46167.466592627316</v>
+        <v>46167.63325929398</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46189.71079010417</v>
+        <v>46189.87745677083</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>212</v>
@@ -10085,11 +10085,11 @@
         <v>356</v>
       </c>
       <c r="B144" s="5">
-        <v>46167.46660762731</v>
+        <v>46167.633274293985</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46189.71079065972</v>
+        <v>46189.87745732639</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>212</v>
@@ -10138,11 +10138,11 @@
         <v>357</v>
       </c>
       <c r="B145" s="9">
-        <v>46167.46661520834</v>
+        <v>46167.633281875</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46189.71079125</v>
+        <v>46189.877457916664</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>212</v>
@@ -10191,11 +10191,11 @@
         <v>359</v>
       </c>
       <c r="B146" s="5">
-        <v>46167.466655937504</v>
+        <v>46167.63332260417</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46189.71079196759</v>
+        <v>46189.87745863426</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>221</v>
@@ -10244,11 +10244,11 @@
         <v>361</v>
       </c>
       <c r="B147" s="9">
-        <v>46167.46666502315</v>
+        <v>46167.633331689816</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46189.71079251157</v>
+        <v>46189.87745917824</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>221</v>
@@ -10297,11 +10297,11 @@
         <v>362</v>
       </c>
       <c r="B148" s="5">
-        <v>46167.39071162037</v>
+        <v>46167.557378287034</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46167.57583180556</v>
+        <v>46167.742498472224</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>363</v>
@@ -10360,11 +10360,11 @@
         <v>364</v>
       </c>
       <c r="B149" s="9">
-        <v>46167.39071626157</v>
+        <v>46167.55738292824</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46167.57582646991</v>
+        <v>46167.742493136575</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>212</v>
@@ -10413,11 +10413,11 @@
         <v>366</v>
       </c>
       <c r="B150" s="5">
-        <v>46167.390721724536</v>
+        <v>46167.5573883912</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46167.57582333333</v>
+        <v>46167.742490000004</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>212</v>
@@ -10466,11 +10466,11 @@
         <v>367</v>
       </c>
       <c r="B151" s="9">
-        <v>46167.466749942134</v>
+        <v>46167.63341660879</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46167.57582049769</v>
+        <v>46167.74248716435</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>212</v>
@@ -10519,11 +10519,11 @@
         <v>368</v>
       </c>
       <c r="B152" s="5">
-        <v>46167.46676704861</v>
+        <v>46167.63343371528</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46167.57581730324</v>
+        <v>46167.74248396991</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>212</v>
@@ -10572,11 +10572,11 @@
         <v>369</v>
       </c>
       <c r="B153" s="9">
-        <v>46167.46677699074</v>
+        <v>46167.63344365741</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46167.57581446759</v>
+        <v>46167.742481134264</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>212</v>
@@ -10625,11 +10625,11 @@
         <v>370</v>
       </c>
       <c r="B154" s="5">
-        <v>46167.466785219905</v>
+        <v>46167.63345188658</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46167.575811689814</v>
+        <v>46167.74247835648</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>212</v>
@@ -10678,11 +10678,11 @@
         <v>371</v>
       </c>
       <c r="B155" s="9">
-        <v>46167.46683974537</v>
+        <v>46167.633506412036</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46167.57580475694</v>
+        <v>46167.74247142361</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>221</v>
@@ -10731,11 +10731,11 @@
         <v>372</v>
       </c>
       <c r="B156" s="5">
-        <v>46167.46684732639</v>
+        <v>46167.63351399306</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46167.57580399305</v>
+        <v>46167.74247065972</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>221</v>
@@ -10784,11 +10784,11 @@
         <v>373</v>
       </c>
       <c r="B157" s="9">
-        <v>46167.39072740741</v>
+        <v>46167.55739407407</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46167.57598174769</v>
+        <v>46167.74264841435</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>374</v>
@@ -10847,11 +10847,11 @@
         <v>376</v>
       </c>
       <c r="B158" s="5">
-        <v>46167.390732534725</v>
+        <v>46167.55739920139</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46167.575971631944</v>
+        <v>46167.742638298616</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>212</v>
@@ -10900,11 +10900,11 @@
         <v>378</v>
       </c>
       <c r="B159" s="9">
-        <v>46167.39073734954</v>
+        <v>46167.5574040162</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46167.575968749996</v>
+        <v>46167.74263541667</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>212</v>
@@ -10953,11 +10953,11 @@
         <v>379</v>
       </c>
       <c r="B160" s="5">
-        <v>46167.46717653935</v>
+        <v>46167.633843206015</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46167.57596537037</v>
+        <v>46167.742632037036</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>212</v>
@@ -11006,11 +11006,11 @@
         <v>380</v>
       </c>
       <c r="B161" s="9">
-        <v>46167.467183229164</v>
+        <v>46167.633849895836</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46167.575962268515</v>
+        <v>46167.742628935186</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>212</v>
@@ -11059,11 +11059,11 @@
         <v>381</v>
       </c>
       <c r="B162" s="5">
-        <v>46167.467191250005</v>
+        <v>46167.63385791666</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46167.5759596875</v>
+        <v>46167.74262635417</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>212</v>
@@ -11112,11 +11112,11 @@
         <v>382</v>
       </c>
       <c r="B163" s="9">
-        <v>46167.467200416664</v>
+        <v>46167.633867083336</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46167.575956886576</v>
+        <v>46167.74262355324</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>219</v>
@@ -11165,11 +11165,11 @@
         <v>383</v>
       </c>
       <c r="B164" s="5">
-        <v>46167.46724568287</v>
+        <v>46167.63391234954</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46167.57595074074</v>
+        <v>46167.742617407406</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>221</v>
@@ -11218,11 +11218,11 @@
         <v>384</v>
       </c>
       <c r="B165" s="9">
-        <v>46167.46725350694</v>
+        <v>46167.63392017361</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46167.57595010417</v>
+        <v>46167.74261677083</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>221</v>
@@ -11271,11 +11271,11 @@
         <v>385</v>
       </c>
       <c r="B166" s="5">
-        <v>46167.39074253472</v>
+        <v>46167.557409201385</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46167.5680759838</v>
+        <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>386</v>
@@ -11318,11 +11318,11 @@
         <v>388</v>
       </c>
       <c r="B167" s="9">
-        <v>46167.390746550926</v>
+        <v>46167.5574132176</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46167.57617571759</v>
+        <v>46167.74284238426</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>389</v>
@@ -11381,11 +11381,11 @@
         <v>393</v>
       </c>
       <c r="B168" s="5">
-        <v>46167.39075387732</v>
+        <v>46167.55742054398</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46167.57619577546</v>
+        <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>212</v>
@@ -11434,11 +11434,11 @@
         <v>395</v>
       </c>
       <c r="B169" s="9">
-        <v>46167.39075885416</v>
+        <v>46167.557425520834</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46167.576192939814</v>
+        <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>212</v>
@@ -11487,11 +11487,11 @@
         <v>396</v>
       </c>
       <c r="B170" s="5">
-        <v>46167.39076354167</v>
+        <v>46167.55743020833</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46167.5761903588</v>
+        <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>212</v>
@@ -11540,11 +11540,11 @@
         <v>397</v>
       </c>
       <c r="B171" s="9">
-        <v>46167.39076825231</v>
+        <v>46167.557434918985</v>
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46167.576187708335</v>
+        <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>212</v>
@@ -11593,11 +11593,11 @@
         <v>398</v>
       </c>
       <c r="B172" s="5">
-        <v>46167.46973636574</v>
+        <v>46167.636403032404</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46167.576185</v>
+        <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>212</v>
@@ -11646,11 +11646,11 @@
         <v>399</v>
       </c>
       <c r="B173" s="9">
-        <v>46167.469745069444</v>
+        <v>46167.63641173611</v>
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46167.57618225695</v>
+        <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>212</v>
@@ -11699,11 +11699,11 @@
         <v>400</v>
       </c>
       <c r="B174" s="5">
-        <v>46167.46976197917</v>
+        <v>46167.636428645834</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46167.57617980324</v>
+        <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>221</v>
@@ -11752,11 +11752,11 @@
         <v>401</v>
       </c>
       <c r="B175" s="9">
-        <v>46167.46977318287</v>
+        <v>46167.636439849535</v>
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46167.57617702546</v>
+        <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>221</v>
@@ -11805,11 +11805,11 @@
         <v>402</v>
       </c>
       <c r="B176" s="5">
-        <v>46167.4700108449</v>
+        <v>46167.636677511575</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46167.57617417824</v>
+        <v>46167.742840844905</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>63</v>
@@ -11858,11 +11858,11 @@
         <v>403</v>
       </c>
       <c r="B177" s="9">
-        <v>46167.470026400464</v>
+        <v>46167.63669306713</v>
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46167.576171469904</v>
+        <v>46167.742838136575</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>62</v>
@@ -11911,11 +11911,11 @@
         <v>404</v>
       </c>
       <c r="B178" s="5">
-        <v>46167.47003484954</v>
+        <v>46167.6367015162</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46167.57616909722</v>
+        <v>46167.742835763886</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>62</v>
@@ -11964,11 +11964,11 @@
         <v>405</v>
       </c>
       <c r="B179" s="9">
-        <v>46167.470044629634</v>
+        <v>46167.6367112963</v>
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46167.57615849537</v>
+        <v>46167.74282516204</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>62</v>
@@ -12017,11 +12017,11 @@
         <v>406</v>
       </c>
       <c r="B180" s="5">
-        <v>46167.47005341435</v>
+        <v>46167.63672008102</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46167.57615778936</v>
+        <v>46167.742824456014</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>62</v>
@@ -12070,11 +12070,11 @@
         <v>407</v>
       </c>
       <c r="B181" s="9">
-        <v>46167.47006258102</v>
+        <v>46167.636729247686</v>
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46167.576157083335</v>
+        <v>46167.74282375</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>62</v>
@@ -12123,11 +12123,11 @@
         <v>408</v>
       </c>
       <c r="B182" s="5">
-        <v>46167.47016936343</v>
+        <v>46167.63683603009</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46167.576156400464</v>
+        <v>46167.74282306713</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>70</v>
@@ -12176,11 +12176,11 @@
         <v>409</v>
       </c>
       <c r="B183" s="9">
-        <v>46167.47017965278</v>
+        <v>46167.636846319445</v>
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46167.57615570602</v>
+        <v>46167.74282237269</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>70</v>
@@ -12229,11 +12229,11 @@
         <v>410</v>
       </c>
       <c r="B184" s="5">
-        <v>46167.39077278935</v>
+        <v>46167.55743945602</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46167.57637837963</v>
+        <v>46167.7430450463</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>411</v>
@@ -12292,11 +12292,11 @@
         <v>413</v>
       </c>
       <c r="B185" s="9">
-        <v>46167.390777569446</v>
+        <v>46167.55744423611</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46167.576399537036</v>
+        <v>46167.74306620371</v>
       </c>
       <c r="E185" s="10" t="s">
         <v>212</v>
@@ -12343,11 +12343,11 @@
         <v>415</v>
       </c>
       <c r="B186" s="5">
-        <v>46167.39078217593</v>
+        <v>46167.55744884259</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46167.576396689816</v>
+        <v>46167.74306335648</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>212</v>
@@ -12394,11 +12394,11 @@
         <v>417</v>
       </c>
       <c r="B187" s="9">
-        <v>46167.390786828706</v>
+        <v>46167.55745349537</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46167.57639341435</v>
+        <v>46167.74306008102</v>
       </c>
       <c r="E187" s="10" t="s">
         <v>212</v>
@@ -12445,11 +12445,11 @@
         <v>418</v>
       </c>
       <c r="B188" s="5">
-        <v>46167.39079111112</v>
+        <v>46167.55745777777</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46167.57639071759</v>
+        <v>46167.74305738426</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>212</v>
@@ -12496,11 +12496,11 @@
         <v>419</v>
       </c>
       <c r="B189" s="9">
-        <v>46167.47100416667</v>
+        <v>46167.637670833334</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46167.57638799769</v>
+        <v>46167.74305466435</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>212</v>
@@ -12547,11 +12547,11 @@
         <v>420</v>
       </c>
       <c r="B190" s="5">
-        <v>46167.471014097224</v>
+        <v>46167.63768076389</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46167.57638532408</v>
+        <v>46167.743051990736</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>212</v>
@@ -12598,11 +12598,11 @@
         <v>421</v>
       </c>
       <c r="B191" s="9">
-        <v>46167.47105734954</v>
+        <v>46167.637724016204</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46167.576382534724</v>
+        <v>46167.74304920139</v>
       </c>
       <c r="E191" s="10" t="s">
         <v>221</v>
@@ -12649,11 +12649,11 @@
         <v>422</v>
       </c>
       <c r="B192" s="5">
-        <v>46167.47106564815</v>
+        <v>46167.63773231482</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46167.576379907405</v>
+        <v>46167.743046574076</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>221</v>
@@ -12700,11 +12700,11 @@
         <v>423</v>
       </c>
       <c r="B193" s="9">
-        <v>46167.47121344907</v>
+        <v>46167.63788011574</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46167.57637700232</v>
+        <v>46167.74304366898</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>62</v>
@@ -12753,11 +12753,11 @@
         <v>424</v>
       </c>
       <c r="B194" s="5">
-        <v>46167.47122186342</v>
+        <v>46167.637888530095</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46167.57637400463</v>
+        <v>46167.743040671296</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>62</v>
@@ -12806,11 +12806,11 @@
         <v>425</v>
       </c>
       <c r="B195" s="9">
-        <v>46167.47123055556</v>
+        <v>46167.63789722222</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46167.57637123842</v>
+        <v>46167.74303790509</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>62</v>
@@ -12859,11 +12859,11 @@
         <v>426</v>
       </c>
       <c r="B196" s="5">
-        <v>46167.47124101852</v>
+        <v>46167.63790768519</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46167.57636856481</v>
+        <v>46167.743035231484</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>62</v>
@@ -12912,11 +12912,11 @@
         <v>427</v>
       </c>
       <c r="B197" s="9">
-        <v>46167.471249953705</v>
+        <v>46167.63791662037</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46167.5763584838</v>
+        <v>46167.74302515046</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>62</v>
@@ -12965,11 +12965,11 @@
         <v>428</v>
       </c>
       <c r="B198" s="5">
-        <v>46167.47128002315</v>
+        <v>46167.637946689814</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46167.57635780092</v>
+        <v>46167.74302446759</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>62</v>
@@ -13018,11 +13018,11 @@
         <v>429</v>
       </c>
       <c r="B199" s="9">
-        <v>46167.4713290625</v>
+        <v>46167.637995729165</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46167.5763571412</v>
+        <v>46167.74302380787</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>70</v>
@@ -13071,11 +13071,11 @@
         <v>430</v>
       </c>
       <c r="B200" s="5">
-        <v>46167.47133753472</v>
+        <v>46167.63800420139</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46167.57635646991</v>
+        <v>46167.74302313657</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>70</v>
@@ -13124,11 +13124,11 @@
         <v>431</v>
       </c>
       <c r="B201" s="9">
-        <v>46167.3907955787</v>
+        <v>46167.55746224537</v>
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46167.57697865741</v>
+        <v>46167.74364532407</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>432</v>
@@ -13187,11 +13187,11 @@
         <v>433</v>
       </c>
       <c r="B202" s="5">
-        <v>46167.390800231486</v>
+        <v>46167.55746689815</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46167.57701059028</v>
+        <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>212</v>
@@ -13240,11 +13240,11 @@
         <v>435</v>
       </c>
       <c r="B203" s="9">
-        <v>46167.39080877315</v>
+        <v>46167.55747543981</v>
       </c>
       <c r="C203" s="10"/>
       <c r="D203" s="9">
-        <v>46167.57700769676</v>
+        <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
         <v>212</v>
@@ -13293,11 +13293,11 @@
         <v>437</v>
       </c>
       <c r="B204" s="5">
-        <v>46167.39085260416</v>
+        <v>46167.557519270835</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46167.57700517361</v>
+        <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>212</v>
@@ -13346,11 +13346,11 @@
         <v>439</v>
       </c>
       <c r="B205" s="9">
-        <v>46167.390858645835</v>
+        <v>46167.5575253125</v>
       </c>
       <c r="C205" s="10"/>
       <c r="D205" s="9">
-        <v>46167.577002743055</v>
+        <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
         <v>212</v>
@@ -13399,11 +13399,11 @@
         <v>440</v>
       </c>
       <c r="B206" s="5">
-        <v>46167.47190484953</v>
+        <v>46167.6385715162</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46167.57700017361</v>
+        <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>212</v>
@@ -13452,11 +13452,11 @@
         <v>441</v>
       </c>
       <c r="B207" s="9">
-        <v>46167.47191232639</v>
+        <v>46167.63857899306</v>
       </c>
       <c r="C207" s="10"/>
       <c r="D207" s="9">
-        <v>46167.5769975</v>
+        <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
         <v>212</v>
@@ -13505,11 +13505,11 @@
         <v>442</v>
       </c>
       <c r="B208" s="5">
-        <v>46167.47199326388</v>
+        <v>46167.638659930555</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46167.57699435185</v>
+        <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>221</v>
@@ -13558,11 +13558,11 @@
         <v>444</v>
       </c>
       <c r="B209" s="9">
-        <v>46167.47200028935</v>
+        <v>46167.638666956016</v>
       </c>
       <c r="C209" s="10"/>
       <c r="D209" s="9">
-        <v>46167.57699173611</v>
+        <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
         <v>221</v>
@@ -13611,11 +13611,11 @@
         <v>445</v>
       </c>
       <c r="B210" s="5">
-        <v>46167.47204234954</v>
+        <v>46167.6387090162</v>
       </c>
       <c r="C210" s="6"/>
       <c r="D210" s="5">
-        <v>46167.57698893519</v>
+        <v>46167.74365560185</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>62</v>
@@ -13664,11 +13664,11 @@
         <v>446</v>
       </c>
       <c r="B211" s="9">
-        <v>46167.47204974537</v>
+        <v>46167.63871641204</v>
       </c>
       <c r="C211" s="10"/>
       <c r="D211" s="9">
-        <v>46167.576986493055</v>
+        <v>46167.74365315972</v>
       </c>
       <c r="E211" s="10" t="s">
         <v>62</v>
@@ -13717,11 +13717,11 @@
         <v>447</v>
       </c>
       <c r="B212" s="5">
-        <v>46167.47205693287</v>
+        <v>46167.638723599535</v>
       </c>
       <c r="C212" s="6"/>
       <c r="D212" s="5">
-        <v>46167.5769841088</v>
+        <v>46167.74365077546</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>62</v>
@@ -13770,11 +13770,11 @@
         <v>448</v>
       </c>
       <c r="B213" s="9">
-        <v>46167.47206478009</v>
+        <v>46167.63873144676</v>
       </c>
       <c r="C213" s="10"/>
       <c r="D213" s="9">
-        <v>46167.576981412036</v>
+        <v>46167.7436480787</v>
       </c>
       <c r="E213" s="10" t="s">
         <v>62</v>
@@ -13823,11 +13823,11 @@
         <v>449</v>
       </c>
       <c r="B214" s="5">
-        <v>46167.47207391204</v>
+        <v>46167.6387405787</v>
       </c>
       <c r="C214" s="6"/>
       <c r="D214" s="5">
-        <v>46167.57697206018</v>
+        <v>46167.74363872685</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>62</v>
@@ -13876,11 +13876,11 @@
         <v>450</v>
       </c>
       <c r="B215" s="9">
-        <v>46167.47208178241</v>
+        <v>46167.63874844907</v>
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46167.57697135417</v>
+        <v>46167.74363802084</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>62</v>
@@ -13929,11 +13929,11 @@
         <v>451</v>
       </c>
       <c r="B216" s="5">
-        <v>46167.47208989583</v>
+        <v>46167.638756562505</v>
       </c>
       <c r="C216" s="6"/>
       <c r="D216" s="5">
-        <v>46167.576970671296</v>
+        <v>46167.74363733796</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>70</v>
@@ -13982,11 +13982,11 @@
         <v>453</v>
       </c>
       <c r="B217" s="9">
-        <v>46167.47216761574</v>
+        <v>46167.63883428241</v>
       </c>
       <c r="C217" s="10"/>
       <c r="D217" s="9">
-        <v>46167.576969999995</v>
+        <v>46167.743636666666</v>
       </c>
       <c r="E217" s="10" t="s">
         <v>70</v>
@@ -14035,11 +14035,11 @@
         <v>454</v>
       </c>
       <c r="B218" s="5">
-        <v>46167.39086332176</v>
+        <v>46167.55752998842</v>
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46167.57715442129</v>
+        <v>46167.74382108796</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>455</v>
@@ -14098,11 +14098,11 @@
         <v>457</v>
       </c>
       <c r="B219" s="9">
-        <v>46167.39086947917</v>
+        <v>46167.55753614583</v>
       </c>
       <c r="C219" s="10"/>
       <c r="D219" s="9">
-        <v>46167.57718232639</v>
+        <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
         <v>212</v>
@@ -14151,11 +14151,11 @@
         <v>458</v>
       </c>
       <c r="B220" s="5">
-        <v>46167.39087371528</v>
+        <v>46167.557540381946</v>
       </c>
       <c r="C220" s="6"/>
       <c r="D220" s="5">
-        <v>46167.57717930556</v>
+        <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>212</v>
@@ -14204,11 +14204,11 @@
         <v>459</v>
       </c>
       <c r="B221" s="9">
-        <v>46167.39087840277</v>
+        <v>46167.557545069445</v>
       </c>
       <c r="C221" s="10"/>
       <c r="D221" s="9">
-        <v>46167.57717674768</v>
+        <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
         <v>212</v>
@@ -14257,11 +14257,11 @@
         <v>460</v>
       </c>
       <c r="B222" s="5">
-        <v>46167.39088229167</v>
+        <v>46167.55754895833</v>
       </c>
       <c r="C222" s="6"/>
       <c r="D222" s="5">
-        <v>46167.57717400463</v>
+        <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
         <v>212</v>
@@ -14310,11 +14310,11 @@
         <v>461</v>
       </c>
       <c r="B223" s="9">
-        <v>46167.472371041666</v>
+        <v>46167.63903770833</v>
       </c>
       <c r="C223" s="10"/>
       <c r="D223" s="9">
-        <v>46167.57717127315</v>
+        <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
         <v>212</v>
@@ -14363,11 +14363,11 @@
         <v>462</v>
       </c>
       <c r="B224" s="5">
-        <v>46167.47238265046</v>
+        <v>46167.639049317135</v>
       </c>
       <c r="C224" s="6"/>
       <c r="D224" s="5">
-        <v>46167.57716853009</v>
+        <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>212</v>
@@ -14416,11 +14416,11 @@
         <v>463</v>
       </c>
       <c r="B225" s="9">
-        <v>46167.472505451384</v>
+        <v>46167.639172118055</v>
       </c>
       <c r="C225" s="10"/>
       <c r="D225" s="9">
-        <v>46167.57716576389</v>
+        <v>46167.743832430555</v>
       </c>
       <c r="E225" s="10" t="s">
         <v>443</v>
@@ -14469,11 +14469,11 @@
         <v>464</v>
       </c>
       <c r="B226" s="5">
-        <v>46167.472514803245</v>
+        <v>46167.63918146991</v>
       </c>
       <c r="C226" s="6"/>
       <c r="D226" s="5">
-        <v>46167.577162905094</v>
+        <v>46167.74382957176</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>443</v>
@@ -14522,11 +14522,11 @@
         <v>465</v>
       </c>
       <c r="B227" s="9">
-        <v>46167.472554583335</v>
+        <v>46167.63922125</v>
       </c>
       <c r="C227" s="10"/>
       <c r="D227" s="9">
-        <v>46167.57715972222</v>
+        <v>46167.74382638889</v>
       </c>
       <c r="E227" s="10" t="s">
         <v>62</v>
@@ -14575,11 +14575,11 @@
         <v>466</v>
       </c>
       <c r="B228" s="5">
-        <v>46167.47256563658</v>
+        <v>46167.63923230324</v>
       </c>
       <c r="C228" s="6"/>
       <c r="D228" s="5">
-        <v>46167.57715695602</v>
+        <v>46167.74382362269</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>62</v>
@@ -14628,11 +14628,11 @@
         <v>467</v>
       </c>
       <c r="B229" s="9">
-        <v>46167.47257383102</v>
+        <v>46167.63924049769</v>
       </c>
       <c r="C229" s="10"/>
       <c r="D229" s="9">
-        <v>46167.5771475463</v>
+        <v>46167.74381421296</v>
       </c>
       <c r="E229" s="10" t="s">
         <v>62</v>
@@ -14681,11 +14681,11 @@
         <v>468</v>
       </c>
       <c r="B230" s="5">
-        <v>46167.47258282408</v>
+        <v>46167.63924949074</v>
       </c>
       <c r="C230" s="6"/>
       <c r="D230" s="5">
-        <v>46167.577146400465</v>
+        <v>46167.74381306713</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>62</v>
@@ -14734,11 +14734,11 @@
         <v>469</v>
       </c>
       <c r="B231" s="9">
-        <v>46167.472592708335</v>
+        <v>46167.639259375</v>
       </c>
       <c r="C231" s="10"/>
       <c r="D231" s="9">
-        <v>46167.57714168981</v>
+        <v>46167.74380835648</v>
       </c>
       <c r="E231" s="10" t="s">
         <v>62</v>
@@ -14787,11 +14787,11 @@
         <v>470</v>
       </c>
       <c r="B232" s="5">
-        <v>46167.47260137732</v>
+        <v>46167.63926804398</v>
       </c>
       <c r="C232" s="6"/>
       <c r="D232" s="5">
-        <v>46167.57714060185</v>
+        <v>46167.74380726852</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>62</v>
@@ -14840,11 +14840,11 @@
         <v>471</v>
       </c>
       <c r="B233" s="9">
-        <v>46167.472688657406</v>
+        <v>46167.63935532408</v>
       </c>
       <c r="C233" s="10"/>
       <c r="D233" s="9">
-        <v>46167.57713988426</v>
+        <v>46167.74380655093</v>
       </c>
       <c r="E233" s="10" t="s">
         <v>452</v>
@@ -14893,11 +14893,11 @@
         <v>472</v>
       </c>
       <c r="B234" s="5">
-        <v>46167.47270023148</v>
+        <v>46167.63936689815</v>
       </c>
       <c r="C234" s="6"/>
       <c r="D234" s="5">
-        <v>46167.57713924769</v>
+        <v>46167.74380591435</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>452</v>
@@ -14946,11 +14946,11 @@
         <v>473</v>
       </c>
       <c r="B235" s="9">
-        <v>46167.390885995366</v>
+        <v>46167.55755266204</v>
       </c>
       <c r="C235" s="10"/>
       <c r="D235" s="9">
-        <v>46167.568322962965</v>
+        <v>46167.73498962963</v>
       </c>
       <c r="E235" s="10" t="s">
         <v>474</v>
@@ -14993,11 +14993,11 @@
         <v>476</v>
       </c>
       <c r="B236" s="5">
-        <v>46167.39088918982</v>
+        <v>46167.55755585648</v>
       </c>
       <c r="C236" s="6"/>
       <c r="D236" s="5">
-        <v>46167.57719876157</v>
+        <v>46167.743865428245</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>477</v>
@@ -15056,11 +15056,11 @@
         <v>480</v>
       </c>
       <c r="B237" s="9">
-        <v>46167.39089385417</v>
+        <v>46167.55756052083</v>
       </c>
       <c r="C237" s="10"/>
       <c r="D237" s="9">
-        <v>46189.70539407407</v>
+        <v>46189.872060740745</v>
       </c>
       <c r="E237" s="10" t="s">
         <v>481</v>
@@ -15119,11 +15119,11 @@
         <v>482</v>
       </c>
       <c r="B238" s="5">
-        <v>46167.39089962963</v>
+        <v>46167.557566296295</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="5">
-        <v>46167.56879575232</v>
+        <v>46167.73546241898</v>
       </c>
       <c r="E238" s="6" t="s">
         <v>483</v>
@@ -15172,11 +15172,11 @@
         <v>485</v>
       </c>
       <c r="B239" s="9">
-        <v>46167.390903217594</v>
+        <v>46167.55756988426</v>
       </c>
       <c r="C239" s="10"/>
       <c r="D239" s="9">
-        <v>46167.57729284722</v>
+        <v>46167.743959513886</v>
       </c>
       <c r="E239" s="10" t="s">
         <v>486</v>
@@ -15235,11 +15235,11 @@
         <v>488</v>
       </c>
       <c r="B240" s="5">
-        <v>46167.390908229165</v>
+        <v>46167.557574895836</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="5">
-        <v>46167.57728997685</v>
+        <v>46167.74395664352</v>
       </c>
       <c r="E240" s="6" t="s">
         <v>489</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46199.56370296296</v>
+        <v>46206.16887833334</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>227</v>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46199.563827962964</v>
+        <v>46206.16887974537</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>237</v>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46199.56460534722</v>
+        <v>46206.168873993054</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>243</v>
@@ -6479,7 +6479,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46203.50223453704</v>
+        <v>46206.16856959491</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -6523,8 +6523,8 @@
       <c r="R78" s="5">
         <v>46213</v>
       </c>
-      <c r="S78" s="7" t="s">
-        <v>33</v>
+      <c r="S78" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -744,19 +744,19 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1215103975192191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Bodega:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215103975192191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Bodega:</t>
   </si>
   <si>
     <t>1215103975192341</t>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46206.16887833334</v>
+        <v>46207.17045002315</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>227</v>
@@ -6096,8 +6096,8 @@
       <c r="R71" s="9">
         <v>46206</v>
       </c>
-      <c r="S71" s="12" t="s">
-        <v>231</v>
+      <c r="S71" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6118,7 +6118,7 @@
         <v>46203.19671185185</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -6148,10 +6148,10 @@
         <v>224</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6160,7 +6160,7 @@
         <v>46210</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46206.16887974537</v>
+        <v>46207.17044986111</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>237</v>
@@ -6222,8 +6222,8 @@
       <c r="R73" s="9">
         <v>46206</v>
       </c>
-      <c r="S73" s="12" t="s">
-        <v>231</v>
+      <c r="S73" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T73" s="10">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>46210</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46206.168873993054</v>
+        <v>46207.17044987269</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>243</v>
@@ -6348,8 +6348,8 @@
       <c r="R75" s="9">
         <v>46206</v>
       </c>
-      <c r="S75" s="12" t="s">
-        <v>231</v>
+      <c r="S75" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T75" s="10">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         <v>46210</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -6524,7 +6524,7 @@
         <v>46213</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -8106,7 +8106,7 @@
         <v>126</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="490">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -3358,9 +3358,11 @@
       <c r="B25" s="9">
         <v>46167.556633009255</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46209.56444690972</v>
+      </c>
       <c r="D25" s="9">
-        <v>46196.64908548611</v>
+        <v>46209.56446100694</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>90</v>
@@ -3395,8 +3397,12 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
+      <c r="T25" s="10">
+        <v>1</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -3470,9 +3476,11 @@
       <c r="B27" s="9">
         <v>46167.55682017361</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46209.56392407407</v>
+      </c>
       <c r="D27" s="9">
-        <v>46189.87937197917</v>
+        <v>46209.563948483796</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>95</v>
@@ -3520,10 +3528,10 @@
         <v>33</v>
       </c>
       <c r="T27" s="10">
-        <v>0</v>
-      </c>
-      <c r="U27" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U27" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3858,9 +3866,11 @@
       <c r="B33" s="9">
         <v>46167.55684913194</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9">
+        <v>46209.564430046295</v>
+      </c>
       <c r="D33" s="9">
-        <v>46198.63712021991</v>
+        <v>46209.564447372686</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>118</v>
@@ -3908,10 +3918,10 @@
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="12" t="s">
-        <v>75</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -4043,7 +4053,7 @@
         <v>46190.643442395834</v>
       </c>
       <c r="D36" s="5">
-        <v>46190.643529444445</v>
+        <v>46209.56394472222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>126</v>
@@ -4093,8 +4103,8 @@
       <c r="T36" s="6">
         <v>1</v>
       </c>
-      <c r="U36" s="7" t="s">
-        <v>27</v>
+      <c r="U36" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4405,7 +4415,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46170.1718400463</v>
+        <v>46209.56443627315</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>119</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46167.74138710648</v>
+        <v>46209.72517689815</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>267</v>
@@ -7042,8 +7042,8 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="11" t="s">
-        <v>60</v>
+      <c r="U87" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -7053,9 +7053,11 @@
       <c r="B88" s="5">
         <v>46167.557195092595</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46209.72503165509</v>
+      </c>
       <c r="D88" s="5">
-        <v>46203.503963518524</v>
+        <v>46209.725033622686</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>212</v>
@@ -7106,9 +7108,11 @@
       <c r="B89" s="9">
         <v>46167.557200995376</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="9">
+        <v>46209.72515854167</v>
+      </c>
       <c r="D89" s="9">
-        <v>46203.50410373842</v>
+        <v>46209.72516011574</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>212</v>
@@ -7159,9 +7163,11 @@
       <c r="B90" s="5">
         <v>46167.63214916667</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46209.72517012732</v>
+      </c>
       <c r="D90" s="5">
-        <v>46203.50259631945</v>
+        <v>46209.725171666665</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>212</v>
@@ -7212,9 +7218,11 @@
       <c r="B91" s="9">
         <v>46167.63219107639</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9">
+        <v>46209.72518462963</v>
+      </c>
       <c r="D91" s="9">
-        <v>46203.5026787963</v>
+        <v>46209.72518666666</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>212</v>
@@ -7265,9 +7273,11 @@
       <c r="B92" s="5">
         <v>46167.63220099537</v>
       </c>
-      <c r="C92" s="6"/>
+      <c r="C92" s="5">
+        <v>46209.72520350694</v>
+      </c>
       <c r="D92" s="5">
-        <v>46203.5027705324</v>
+        <v>46209.725205462964</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>212</v>
@@ -7483,7 +7493,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46167.74153292824</v>
+        <v>46209.72590972223</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>279</v>
@@ -7533,8 +7543,8 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="11" t="s">
-        <v>60</v>
+      <c r="U96" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7544,9 +7554,11 @@
       <c r="B97" s="9">
         <v>46167.557210914354</v>
       </c>
-      <c r="C97" s="10"/>
+      <c r="C97" s="9">
+        <v>46209.72589184028</v>
+      </c>
       <c r="D97" s="9">
-        <v>46189.87509809028</v>
+        <v>46209.725893599534</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>212</v>
@@ -7597,9 +7609,11 @@
       <c r="B98" s="5">
         <v>46167.55721697917</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46209.72588532408</v>
+      </c>
       <c r="D98" s="5">
-        <v>46189.87509940972</v>
+        <v>46209.725886851855</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>212</v>
@@ -7650,9 +7664,11 @@
       <c r="B99" s="9">
         <v>46167.632342048615</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="9">
+        <v>46209.72588054398</v>
+      </c>
       <c r="D99" s="9">
-        <v>46167.74151755787</v>
+        <v>46209.72588194444</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>212</v>
@@ -7703,9 +7719,11 @@
       <c r="B100" s="5">
         <v>46167.63235868055</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46209.72587407407</v>
+      </c>
       <c r="D100" s="5">
-        <v>46167.74151503472</v>
+        <v>46209.72587559027</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7756,9 +7774,11 @@
       <c r="B101" s="9">
         <v>46167.63236590278</v>
       </c>
-      <c r="C101" s="10"/>
+      <c r="C101" s="9">
+        <v>46209.72586827546</v>
+      </c>
       <c r="D101" s="9">
-        <v>46167.74151262731</v>
+        <v>46209.725869594906</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>212</v>
@@ -7862,9 +7882,11 @@
       <c r="B103" s="9">
         <v>46167.63244320602</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9">
+        <v>46209.72585559028</v>
+      </c>
       <c r="D103" s="9">
-        <v>46203.50339961806</v>
+        <v>46209.7258571875</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>221</v>
@@ -7915,9 +7937,11 @@
       <c r="B104" s="5">
         <v>46167.63245268518</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46209.725846574074</v>
+      </c>
       <c r="D104" s="5">
-        <v>46203.503679375004</v>
+        <v>46209.725848692135</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>221</v>
@@ -8379,7 +8403,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46167.741924999995</v>
+        <v>46209.72590130787</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>306</v>
@@ -8442,7 +8466,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46167.74190891204</v>
+        <v>46209.725901666665</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>212</v>
@@ -8495,7 +8519,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46167.74190642362</v>
+        <v>46209.72589265046</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>212</v>
@@ -8548,7 +8572,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46167.7419037037</v>
+        <v>46209.72518126157</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>212</v>
@@ -8601,7 +8625,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46167.74190121528</v>
+        <v>46209.72588013889</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>212</v>
@@ -8654,7 +8678,7 @@
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46167.74189892361</v>
+        <v>46209.72587407407</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>212</v>
@@ -8760,7 +8784,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46167.74189145833</v>
+        <v>46209.72586340278</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>221</v>
@@ -8813,7 +8837,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46167.74189078704</v>
+        <v>46209.72585412037</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>221</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6125,7 +6125,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46203.19671185185</v>
+        <v>46210.16981278935</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>232</v>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46203.19671157407</v>
+        <v>46210.1698080787</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>240</v>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46203.196711412034</v>
+        <v>46210.16981091435</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>244</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -756,61 +756,61 @@
     <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Bodega:</t>
   </si>
   <si>
+    <t>1215103975192341</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215103776754403</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103875866783</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215103875866800</t>
+  </si>
+  <si>
+    <t>1215103776789924</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Preparación Materiales,Armado</t>
+  </si>
+  <si>
+    <t>1215103776789936</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215103975192341</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215103776754403</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103875866783</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215103875866800</t>
-  </si>
-  <si>
-    <t>1215103776789924</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Preparación Materiales,Armado</t>
-  </si>
-  <si>
-    <t>1215103776789936</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46210.16981278935</v>
+        <v>46211.19534319444</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>232</v>
@@ -6169,8 +6169,8 @@
       <c r="R72" s="5">
         <v>46210</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>235</v>
+      <c r="S72" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6191,7 +6191,7 @@
         <v>46207.17044986111</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -6224,7 +6224,7 @@
         <v>167</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6244,17 +6244,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46210.1698080787</v>
+        <v>46211.19534318287</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6284,10 +6284,10 @@
         <v>224</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6295,8 +6295,8 @@
       <c r="R74" s="5">
         <v>46210</v>
       </c>
-      <c r="S74" s="12" t="s">
-        <v>235</v>
+      <c r="S74" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6317,7 +6317,7 @@
         <v>46207.17044987269</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6350,7 +6350,7 @@
         <v>189</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6370,17 +6370,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46210.16981091435</v>
+        <v>46211.195343217594</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6410,10 +6410,10 @@
         <v>224</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6421,8 +6421,8 @@
       <c r="R76" s="5">
         <v>46210</v>
       </c>
-      <c r="S76" s="12" t="s">
-        <v>235</v>
+      <c r="S76" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6443,7 +6443,7 @@
         <v>46203.50206653935</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6467,7 +6467,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6492,16 +6492,16 @@
         <v>46206.16856959491</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6519,13 +6519,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6534,7 +6534,7 @@
         <v>46213</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6563,10 +6563,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6584,7 +6584,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>255</v>
@@ -6618,10 +6618,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6639,7 +6639,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>258</v>
@@ -6673,10 +6673,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6694,7 +6694,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>260</v>
@@ -6728,10 +6728,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6749,7 +6749,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>260</v>
@@ -6783,10 +6783,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6804,7 +6804,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>260</v>
@@ -6838,10 +6838,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6859,7 +6859,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>260</v>
@@ -6893,10 +6893,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6914,7 +6914,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>260</v>
@@ -6948,10 +6948,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -6969,7 +6969,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>260</v>
@@ -7001,10 +7001,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -7022,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>210</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -7066,10 +7066,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7121,10 +7121,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7176,10 +7176,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7231,10 +7231,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7286,10 +7286,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7339,10 +7339,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7394,10 +7394,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7449,10 +7449,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7523,13 +7523,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>210</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -13171,10 +13171,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13234,10 +13234,10 @@
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13287,10 +13287,10 @@
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13340,10 +13340,10 @@
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13393,10 +13393,10 @@
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H205" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13446,10 +13446,10 @@
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13499,10 +13499,10 @@
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13552,10 +13552,10 @@
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13605,10 +13605,10 @@
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13658,10 +13658,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13711,10 +13711,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H211" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13764,10 +13764,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13817,10 +13817,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H213" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13870,10 +13870,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13923,10 +13923,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H215" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -13976,10 +13976,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -14029,10 +14029,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -14082,10 +14082,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -14145,10 +14145,10 @@
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H219" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H219" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14198,10 +14198,10 @@
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14251,10 +14251,10 @@
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14304,10 +14304,10 @@
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14357,10 +14357,10 @@
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14410,10 +14410,10 @@
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14463,10 +14463,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14516,10 +14516,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14569,10 +14569,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14622,10 +14622,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14675,10 +14675,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14728,10 +14728,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14781,10 +14781,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H231" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H231" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14834,10 +14834,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H232" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14887,10 +14887,10 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>252</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14940,10 +14940,10 @@
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -486,6 +486,9 @@
     <t xml:space="preserve">Generación OC   ot 4329 - 4331 ,fabricación tableros  ot 4329 - 4331 </t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215103776708404</t>
   </si>
   <si>
@@ -808,9 +811,6 @@
   </si>
   <si>
     <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.87894268519</v>
+        <v>46212.18989069444</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>143</v>
@@ -4396,8 +4396,8 @@
       <c r="R41" s="9">
         <v>46219</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>33</v>
+      <c r="S41" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B42" s="5">
         <v>46167.556965254626</v>
@@ -4451,7 +4451,7 @@
         <v>118</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B43" s="9">
         <v>46167.55696965278</v>
@@ -4471,7 +4471,7 @@
         <v>46169.87902826389</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4504,7 +4504,7 @@
         <v>119</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B44" s="5">
         <v>46167.556973784725</v>
@@ -4526,16 +4526,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46192</v>
@@ -4556,7 +4556,7 @@
         <v>129</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>129</v>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" s="9">
         <v>46167.556978611115</v>
@@ -4591,16 +4591,16 @@
         <v>46199.56362072917</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I45" s="9">
         <v>46192</v>
@@ -4618,13 +4618,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B46" s="5">
         <v>46167.55698368055</v>
@@ -4652,16 +4652,16 @@
         <v>46199.563687118054</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46196</v>
@@ -4679,13 +4679,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B47" s="9">
         <v>46167.556988842596</v>
@@ -4713,16 +4713,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I47" s="9">
         <v>46192</v>
@@ -4743,7 +4743,7 @@
         <v>129</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B48" s="5">
         <v>46167.556992708334</v>
@@ -4784,10 +4784,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I48" s="5">
         <v>46192</v>
@@ -4805,13 +4805,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4821,7 +4821,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B49" s="9">
         <v>46167.5569971875</v>
@@ -4833,16 +4833,16 @@
         <v>46199.56447744213</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I49" s="9">
         <v>46196</v>
@@ -4860,13 +4860,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>110</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46167.55700140046</v>
@@ -4888,16 +4888,16 @@
         <v>46204.59613972223</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4918,7 +4918,7 @@
         <v>129</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4941,7 +4941,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" s="9">
         <v>46167.55700519676</v>
@@ -4959,10 +4959,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -4980,13 +4980,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46167.557010034725</v>
@@ -5008,16 +5008,16 @@
         <v>46204.59515966436</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -5035,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>116</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B53" s="9">
         <v>46167.55701476852</v>
@@ -5061,16 +5061,16 @@
         <v>46204.59516696759</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5088,10 +5088,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="5">
         <v>46167.55701769676</v>
@@ -5116,16 +5116,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I54" s="5">
         <v>46192</v>
@@ -5146,7 +5146,7 @@
         <v>129</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" s="9">
         <v>46167.557021678236</v>
@@ -5187,10 +5187,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I55" s="9">
         <v>46192</v>
@@ -5208,13 +5208,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B56" s="5">
         <v>46167.55702634259</v>
@@ -5236,16 +5236,16 @@
         <v>46199.56458967592</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I56" s="5">
         <v>46196</v>
@@ -5263,13 +5263,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B57" s="9">
         <v>46167.55703671296</v>
@@ -5289,7 +5289,7 @@
         <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5313,7 +5313,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46167.557040520835</v>
@@ -5338,16 +5338,16 @@
         <v>46197.715067453704</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5365,13 +5365,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46167.557045856476</v>
@@ -5403,16 +5403,16 @@
         <v>46197.71510291667</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5430,13 +5430,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46167.5570519676</v>
@@ -5474,10 +5474,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5495,13 +5495,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
@@ -5531,16 +5531,16 @@
         <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5558,10 +5558,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5594,16 +5594,16 @@
         <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5621,13 +5621,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5647,16 +5647,16 @@
         <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5674,13 +5674,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5700,16 +5700,16 @@
         <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5727,13 +5727,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5743,7 +5743,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5753,16 +5753,16 @@
         <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5780,13 +5780,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5796,7 +5796,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5806,16 +5806,16 @@
         <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5833,13 +5833,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5859,16 +5859,16 @@
         <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5886,13 +5886,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5902,7 +5902,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5912,16 +5912,16 @@
         <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5939,13 +5939,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5955,7 +5955,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5965,16 +5965,16 @@
         <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -5992,13 +5992,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -6018,7 +6018,7 @@
         <v>46167.629188032406</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6042,7 +6042,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6065,16 +6065,16 @@
         <v>46207.17045002315</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6092,13 +6092,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6118,7 +6118,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6128,16 +6128,16 @@
         <v>46211.19534319444</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6155,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6181,7 +6181,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6191,16 +6191,16 @@
         <v>46207.17044986111</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6218,13 +6218,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6244,7 +6244,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6254,16 +6254,16 @@
         <v>46211.19534318287</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6281,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6317,16 +6317,16 @@
         <v>46207.17044987269</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6344,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6380,16 +6380,16 @@
         <v>46211.195343217594</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6407,13 +6407,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6443,7 +6443,7 @@
         <v>46203.50206653935</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6467,7 +6467,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6480,7 +6480,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6492,16 +6492,16 @@
         <v>46206.16856959491</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6519,13 +6519,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6534,7 +6534,7 @@
         <v>46213</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>253</v>
+        <v>145</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6557,16 +6557,16 @@
         <v>46203.50222925926</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6584,7 +6584,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>255</v>
@@ -6612,16 +6612,16 @@
         <v>46203.50247613426</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6639,13 +6639,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6667,16 +6667,16 @@
         <v>46203.50259215278</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6694,13 +6694,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>260</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6722,16 +6722,16 @@
         <v>46203.50267324074</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6749,13 +6749,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6777,16 +6777,16 @@
         <v>46203.50276618055</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6804,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>260</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6832,16 +6832,16 @@
         <v>46203.50288322917</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6859,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>260</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6887,16 +6887,16 @@
         <v>46203.503012835645</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6914,13 +6914,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>260</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6942,16 +6942,16 @@
         <v>46203.503102048606</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -6969,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>260</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7001,10 +7001,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -7022,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -7060,16 +7060,16 @@
         <v>46209.725033622686</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7115,16 +7115,16 @@
         <v>46209.72516011574</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7170,16 +7170,16 @@
         <v>46209.725171666665</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7200,10 +7200,10 @@
         <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7225,16 +7225,16 @@
         <v>46209.72518666666</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7255,10 +7255,10 @@
         <v>267</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7280,16 +7280,16 @@
         <v>46209.725205462964</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7310,10 +7310,10 @@
         <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7333,16 +7333,16 @@
         <v>46203.502887615745</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7363,10 +7363,10 @@
         <v>267</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7388,16 +7388,16 @@
         <v>46203.50339560185</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7418,10 +7418,10 @@
         <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7443,16 +7443,16 @@
         <v>46203.50367474537</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7473,10 +7473,10 @@
         <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7502,10 +7502,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7523,13 +7523,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7561,16 +7561,16 @@
         <v>46209.725893599534</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7616,16 +7616,16 @@
         <v>46209.725886851855</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7671,16 +7671,16 @@
         <v>46209.72588194444</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7701,7 +7701,7 @@
         <v>279</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7726,16 +7726,16 @@
         <v>46209.72587559027</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7756,10 +7756,10 @@
         <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7781,16 +7781,16 @@
         <v>46209.725869594906</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7811,10 +7811,10 @@
         <v>279</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7834,16 +7834,16 @@
         <v>46167.7415103588</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7864,10 +7864,10 @@
         <v>279</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7889,16 +7889,16 @@
         <v>46209.7258571875</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7919,10 +7919,10 @@
         <v>279</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7944,16 +7944,16 @@
         <v>46209.725848692135</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -7974,10 +7974,10 @@
         <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7997,7 +7997,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -8050,10 +8050,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -8071,7 +8071,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>140</v>
@@ -8113,10 +8113,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8134,13 +8134,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>126</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8176,10 +8176,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8197,7 +8197,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
@@ -8239,10 +8239,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8260,10 +8260,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>299</v>
@@ -8302,10 +8302,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8323,10 +8323,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>301</v>
@@ -8469,7 +8469,7 @@
         <v>46209.725901666665</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8522,7 +8522,7 @@
         <v>46209.72589265046</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8575,7 +8575,7 @@
         <v>46209.72518126157</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8605,10 +8605,10 @@
         <v>306</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8628,7 +8628,7 @@
         <v>46209.72588013889</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8658,10 +8658,10 @@
         <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8681,7 +8681,7 @@
         <v>46209.72587407407</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8711,10 +8711,10 @@
         <v>306</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8734,7 +8734,7 @@
         <v>46167.74189655093</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8764,10 +8764,10 @@
         <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8787,7 +8787,7 @@
         <v>46209.72586340278</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8817,10 +8817,10 @@
         <v>306</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8840,7 +8840,7 @@
         <v>46209.72585412037</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8870,10 +8870,10 @@
         <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8923,7 +8923,7 @@
         <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>303</v>
@@ -8956,7 +8956,7 @@
         <v>46189.87510767361</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9009,7 +9009,7 @@
         <v>46189.87510009259</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9062,7 +9062,7 @@
         <v>46189.87508946759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9095,7 +9095,7 @@
         <v>324</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9115,7 +9115,7 @@
         <v>46189.87509015047</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9148,7 +9148,7 @@
         <v>326</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9168,7 +9168,7 @@
         <v>46189.87509105324</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9201,7 +9201,7 @@
         <v>326</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9221,7 +9221,7 @@
         <v>46189.87509177084</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9254,7 +9254,7 @@
         <v>326</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9274,7 +9274,7 @@
         <v>46189.87509244213</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9307,7 +9307,7 @@
         <v>330</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9327,7 +9327,7 @@
         <v>46189.8750930324</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9360,7 +9360,7 @@
         <v>330</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9410,7 +9410,7 @@
         <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>303</v>
@@ -9443,7 +9443,7 @@
         <v>46189.87510797454</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9494,7 +9494,7 @@
         <v>46189.87510071759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9545,7 +9545,7 @@
         <v>46189.875093634255</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9576,7 +9576,7 @@
         <v>335</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9596,7 +9596,7 @@
         <v>46189.8750941551</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9627,7 +9627,7 @@
         <v>335</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9647,7 +9647,7 @@
         <v>46189.87509472222</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9678,7 +9678,7 @@
         <v>335</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9698,7 +9698,7 @@
         <v>46189.87509519676</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9729,7 +9729,7 @@
         <v>335</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9749,7 +9749,7 @@
         <v>46189.87509570602</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9780,7 +9780,7 @@
         <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9800,7 +9800,7 @@
         <v>46189.87509615741</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9831,7 +9831,7 @@
         <v>345</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9881,7 +9881,7 @@
         <v>303</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>303</v>
@@ -9914,7 +9914,7 @@
         <v>46189.877459745374</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9967,7 +9967,7 @@
         <v>46189.87746077546</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10020,7 +10020,7 @@
         <v>46189.877455671296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10053,7 +10053,7 @@
         <v>353</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10073,7 +10073,7 @@
         <v>46189.87745677083</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10106,7 +10106,7 @@
         <v>355</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10126,7 +10126,7 @@
         <v>46189.87745732639</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10159,7 +10159,7 @@
         <v>349</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10179,7 +10179,7 @@
         <v>46189.877457916664</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10212,7 +10212,7 @@
         <v>358</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10232,7 +10232,7 @@
         <v>46189.87745863426</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10265,7 +10265,7 @@
         <v>360</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10285,7 +10285,7 @@
         <v>46189.87745917824</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10318,7 +10318,7 @@
         <v>360</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10368,7 +10368,7 @@
         <v>303</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>303</v>
@@ -10401,7 +10401,7 @@
         <v>46167.742493136575</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10431,7 +10431,7 @@
         <v>363</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>365</v>
@@ -10454,7 +10454,7 @@
         <v>46167.742490000004</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10484,7 +10484,7 @@
         <v>363</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>365</v>
@@ -10507,7 +10507,7 @@
         <v>46167.74248716435</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10537,10 +10537,10 @@
         <v>363</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10560,7 +10560,7 @@
         <v>46167.74248396991</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10590,10 +10590,10 @@
         <v>363</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10613,7 +10613,7 @@
         <v>46167.742481134264</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10643,10 +10643,10 @@
         <v>363</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10666,7 +10666,7 @@
         <v>46167.74247835648</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10696,10 +10696,10 @@
         <v>363</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10719,7 +10719,7 @@
         <v>46167.74247142361</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10749,10 +10749,10 @@
         <v>363</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10772,7 +10772,7 @@
         <v>46167.74247065972</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10802,10 +10802,10 @@
         <v>363</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10855,7 +10855,7 @@
         <v>303</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>375</v>
@@ -10888,7 +10888,7 @@
         <v>46167.742638298616</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10918,7 +10918,7 @@
         <v>374</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>377</v>
@@ -10941,7 +10941,7 @@
         <v>46167.74263541667</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -10971,7 +10971,7 @@
         <v>374</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>377</v>
@@ -10994,7 +10994,7 @@
         <v>46167.742632037036</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11024,10 +11024,10 @@
         <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11047,7 +11047,7 @@
         <v>46167.742628935186</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11077,10 +11077,10 @@
         <v>374</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11100,7 +11100,7 @@
         <v>46167.74262635417</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11130,10 +11130,10 @@
         <v>374</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11153,7 +11153,7 @@
         <v>46167.74262355324</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11183,10 +11183,10 @@
         <v>374</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11206,7 +11206,7 @@
         <v>46167.742617407406</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11236,10 +11236,10 @@
         <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11259,7 +11259,7 @@
         <v>46167.74261677083</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11289,10 +11289,10 @@
         <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11422,7 +11422,7 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11452,7 +11452,7 @@
         <v>389</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>394</v>
@@ -11475,7 +11475,7 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11505,7 +11505,7 @@
         <v>389</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>394</v>
@@ -11528,7 +11528,7 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11558,7 +11558,7 @@
         <v>389</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>394</v>
@@ -11581,7 +11581,7 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11611,7 +11611,7 @@
         <v>389</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>394</v>
@@ -11634,7 +11634,7 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11664,10 +11664,10 @@
         <v>389</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11687,7 +11687,7 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11717,10 +11717,10 @@
         <v>389</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11740,7 +11740,7 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11770,10 +11770,10 @@
         <v>389</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11793,7 +11793,7 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11823,10 +11823,10 @@
         <v>389</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -12333,7 +12333,7 @@
         <v>46167.74306620371</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12361,7 +12361,7 @@
         <v>411</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P185" s="10" t="s">
         <v>414</v>
@@ -12384,7 +12384,7 @@
         <v>46167.74306335648</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12412,7 +12412,7 @@
         <v>411</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>416</v>
@@ -12435,7 +12435,7 @@
         <v>46167.74306008102</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12463,7 +12463,7 @@
         <v>411</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>416</v>
@@ -12486,7 +12486,7 @@
         <v>46167.74305738426</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12514,7 +12514,7 @@
         <v>411</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>416</v>
@@ -12537,7 +12537,7 @@
         <v>46167.74305466435</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12565,10 +12565,10 @@
         <v>411</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12588,7 +12588,7 @@
         <v>46167.743051990736</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12616,10 +12616,10 @@
         <v>411</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12639,7 +12639,7 @@
         <v>46167.74304920139</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12667,10 +12667,10 @@
         <v>411</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12690,7 +12690,7 @@
         <v>46167.743046574076</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12718,10 +12718,10 @@
         <v>411</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13171,10 +13171,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13228,16 +13228,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13258,7 +13258,7 @@
         <v>432</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>434</v>
@@ -13281,16 +13281,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13311,7 +13311,7 @@
         <v>432</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P203" s="10" t="s">
         <v>436</v>
@@ -13334,16 +13334,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13364,7 +13364,7 @@
         <v>432</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>438</v>
@@ -13387,16 +13387,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13417,7 +13417,7 @@
         <v>432</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P205" s="10" t="s">
         <v>438</v>
@@ -13440,16 +13440,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13470,10 +13470,10 @@
         <v>432</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13493,16 +13493,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13523,10 +13523,10 @@
         <v>432</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13546,16 +13546,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13576,7 +13576,7 @@
         <v>432</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>443</v>
@@ -13599,16 +13599,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13629,7 +13629,7 @@
         <v>432</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>443</v>
@@ -13658,10 +13658,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13711,10 +13711,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13764,10 +13764,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13817,10 +13817,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13870,10 +13870,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13923,10 +13923,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -13976,10 +13976,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -14029,10 +14029,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -14082,10 +14082,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -14139,16 +14139,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14169,7 +14169,7 @@
         <v>455</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>455</v>
@@ -14192,16 +14192,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14222,7 +14222,7 @@
         <v>455</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>455</v>
@@ -14245,16 +14245,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14275,7 +14275,7 @@
         <v>455</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>455</v>
@@ -14298,16 +14298,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14328,7 +14328,7 @@
         <v>455</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>455</v>
@@ -14351,16 +14351,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14381,7 +14381,7 @@
         <v>455</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14404,16 +14404,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14434,7 +14434,7 @@
         <v>455</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14463,10 +14463,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14487,7 +14487,7 @@
         <v>455</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14516,10 +14516,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14540,7 +14540,7 @@
         <v>455</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14569,10 +14569,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14622,10 +14622,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14675,10 +14675,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14728,10 +14728,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14781,10 +14781,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14834,10 +14834,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14887,10 +14887,10 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14940,10 +14940,10 @@
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -222,7 +222,7 @@
     <t>Recepcion Tableros</t>
   </si>
   <si>
-    <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
+    <t>Ingenieria Servicios ,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -795,7 +795,7 @@
     <t>Caldereria:</t>
   </si>
   <si>
-    <t>Control de calidad Armado,Preparación Materiales,Armado</t>
+    <t>OT 4328  Control de calidad Armado,Preparación Materiales,OT 4328 Armado</t>
   </si>
   <si>
     <t>1215103776789936</t>
@@ -852,7 +852,7 @@
     <t>1215103875953948</t>
   </si>
   <si>
-    <t>Armado</t>
+    <t>OT 4328 Armado</t>
   </si>
   <si>
     <t>1215103926669155</t>
@@ -861,7 +861,7 @@
     <t>OT 4328 - ZVN 1-9-86/2,check planos</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Armado</t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 Armado</t>
   </si>
   <si>
     <t>1215103926669273</t>
@@ -888,13 +888,13 @@
     <t>1215103926669295</t>
   </si>
   <si>
-    <t>Control de calidad Armado</t>
+    <t>OT 4328  Control de calidad Armado</t>
   </si>
   <si>
     <t>1215103776817021</t>
   </si>
   <si>
-    <t>Control de calidad Armado,Revestimiento,OT 4328 - ZVN 1-9-86/2</t>
+    <t>OT 4328  Control de calidad Armado,ot 4328 - 4330 Revestimiento,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215103875982913</t>
@@ -948,7 +948,7 @@
     <t xml:space="preserve">Recepcion fabricación externa </t>
   </si>
   <si>
-    <t>Revestimiento,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
+    <t>ot 4328 - 4330 Revestimiento,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215103975280667</t>
@@ -963,13 +963,13 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>Montaje motor,Revestimiento,Montaje Alabe,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+    <t>ot 4328 - 4330 Montaje motor,ot 4328 - 4330 Revestimiento,ot 4328 - 4330 Montaje Alabe,ot 4328 - 4330 Montaje Rodete,ot 4328 - 4330 Pruebas FAT,ot 4328 - 4330 RE-PINTADO</t>
   </si>
   <si>
     <t>1215103975290017</t>
   </si>
   <si>
-    <t>Revestimiento</t>
+    <t>ot 4328 - 4330 Revestimiento</t>
   </si>
   <si>
     <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Recepcion fabricación externa </t>
@@ -1005,7 +1005,7 @@
     <t>1215103975291300</t>
   </si>
   <si>
-    <t>Montaje Alabe</t>
+    <t>ot 4328 - 4330 Montaje Alabe</t>
   </si>
   <si>
     <t>1215103926689693</t>
@@ -1014,7 +1014,7 @@
     <t>Recepcion Alabe ot 4328 - 4330,check planos</t>
   </si>
   <si>
-    <t>Montaje Alabe,OT 4328 - ZVN 1-9-86/2</t>
+    <t>ot 4328 - 4330 Montaje Alabe,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215103875995330</t>
@@ -1050,7 +1050,7 @@
     <t>1215103875882313</t>
   </si>
   <si>
-    <t>Montaje Rodete</t>
+    <t>ot 4328 - 4330 Montaje Rodete</t>
   </si>
   <si>
     <t>1215103926715037</t>
@@ -1059,7 +1059,7 @@
     <t>OT 4328 - ZVN 1-9-86/2,Recepcion Rodete,check planos</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Montaje Rodete</t>
+    <t>OT 4328 - ZVN 1-9-86/2,ot 4328 - 4330 Montaje Rodete</t>
   </si>
   <si>
     <t>1215103876023928</t>
@@ -1092,7 +1092,7 @@
     <t>1215103776870737</t>
   </si>
   <si>
-    <t>Montaje motor</t>
+    <t>ot 4328 - 4330 Montaje motor</t>
   </si>
   <si>
     <t>1215103776870754</t>
@@ -1101,7 +1101,7 @@
     <t>OT 4328 - ZVN 1-9-86/2,Recepcion motor ot 4328 - 4330,check planos</t>
   </si>
   <si>
-    <t>Montaje motor,OT 4328 - ZVN 1-9-86/2</t>
+    <t>ot 4328 - 4330 Montaje motor,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215103975325192</t>
@@ -1140,13 +1140,13 @@
     <t>1215103975325214</t>
   </si>
   <si>
-    <t>Pruebas FAT</t>
+    <t>ot 4328 - 4330 Pruebas FAT</t>
   </si>
   <si>
     <t>1215103975335574</t>
   </si>
   <si>
-    <t>Pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
+    <t>ot 4328 - 4330 Pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215104027758696</t>
@@ -1173,16 +1173,16 @@
     <t>1215104027758718</t>
   </si>
   <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+    <t>ot 4328 - 4330 RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1215103975335766</t>
   </si>
   <si>
-    <t>RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
+    <t>ot 4328 - 4330 RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215103975335783</t>
@@ -1212,13 +1212,13 @@
     <t>Logistica:</t>
   </si>
   <si>
-    <t>Embalaje,Despacho,PACKING LIST,Coordinacion Entrega con Cliente</t>
+    <t>ot 4328 - 4330- 4329  Embalaje,ot 4328 - 4330- 4329   Despacho,ot 4328 - 4330- 4329 PACKING LIST,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1215103876049076</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente</t>
+    <t>ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>Karin Pinto</t>
@@ -1227,13 +1227,13 @@
     <t>kpinto@zitron.com</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Revision Tableros,RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Revision Tableros,ot 4328 - 4330 RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215104027762191</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Coordinacion Entrega con Cliente</t>
+    <t>OT 4328 - ZVN 1-9-86/2,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1215103926750927</t>
@@ -1284,7 +1284,7 @@
     <t>1215103975344524</t>
   </si>
   <si>
-    <t>Embalaje</t>
+    <t>ot 4328 - 4330- 4329  Embalaje</t>
   </si>
   <si>
     <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
@@ -1293,13 +1293,13 @@
     <t>1215103776901789</t>
   </si>
   <si>
-    <t>Embalaje,OT 4328 - ZVN 1-9-86/2</t>
+    <t>ot 4328 - 4330- 4329  Embalaje,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215103776901806</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Embalaje</t>
+    <t>OT 4328 - ZVN 1-9-86/2,ot 4328 - 4330- 4329  Embalaje</t>
   </si>
   <si>
     <t>1215103926753336</t>
@@ -1347,25 +1347,25 @@
     <t>1215103926762638</t>
   </si>
   <si>
-    <t>PACKING LIST</t>
+    <t>ot 4328 - 4330- 4329 PACKING LIST</t>
   </si>
   <si>
     <t>1215103926762655</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,PACKING LIST,Planos Preliminar</t>
+    <t>OT 4328 - ZVN 1-9-86/2,ot 4328 - 4330- 4329 PACKING LIST,Planos Preliminar</t>
   </si>
   <si>
     <t>1215103876053133</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Planos Preliminar,PACKING LIST</t>
+    <t>OT 4328 - ZVN 1-9-86/2,Planos Preliminar,ot 4328 - 4330- 4329 PACKING LIST</t>
   </si>
   <si>
     <t>1215103875983062</t>
   </si>
   <si>
-    <t>PACKING LIST,OT 4328 - ZVN 1-9-86/2</t>
+    <t>ot 4328 - 4330- 4329 PACKING LIST,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215103776950002</t>
@@ -1416,7 +1416,7 @@
     <t>1215103776950019</t>
   </si>
   <si>
-    <t>Despacho</t>
+    <t>ot 4328 - 4330- 4329   Despacho</t>
   </si>
   <si>
     <t>Logistica:,Gestion,Costos,Instalación componentes</t>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46209.72517689815</v>
+        <v>46212.62563253472</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>267</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46209.72590972223</v>
+        <v>46212.62569252314</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>279</v>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46209.72590130787</v>
+        <v>46212.62486408565</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>306</v>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46167.74207511574</v>
+        <v>46212.62488043982</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>318</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46167.74221776621</v>
+        <v>46212.62489320602</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>333</v>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46167.74236513889</v>
+        <v>46212.624909606486</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>347</v>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46167.742498472224</v>
+        <v>46212.62492555556</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>363</v>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46167.74264841435</v>
+        <v>46212.624938865745</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>374</v>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46167.74284238426</v>
+        <v>46212.62539956019</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>389</v>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46167.7430450463</v>
+        <v>46212.6251847338</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>411</v>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46167.74364532407</v>
+        <v>46212.62523481481</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>432</v>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46167.74382108796</v>
+        <v>46212.62527664352</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>455</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -408,7 +408,7 @@
     <t xml:space="preserve">Propuesta Tableros ot 4329 - 4331 </t>
   </si>
   <si>
-    <t xml:space="preserve">Generación OC   ot 4329 - 4331 </t>
+    <t xml:space="preserve">Generación OC Tableros  ot 4329 - 4331 </t>
   </si>
   <si>
     <t>1215768600270734</t>
@@ -483,7 +483,7 @@
     <t xml:space="preserve">Tableros  ot 4329 - 4331 </t>
   </si>
   <si>
-    <t xml:space="preserve">Generación OC   ot 4329 - 4331 ,fabricación tableros  ot 4329 - 4331 </t>
+    <t xml:space="preserve">Generación OC Tableros  ot 4329 - 4331 ,fabricación tableros  ot 4329 - 4331 </t>
   </si>
   <si>
     <t>Media</t>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46209.56443627315</v>
+        <v>46212.654553368055</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>119</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46212.62563253472</v>
+        <v>46213.18677706018</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>267</v>
@@ -7036,8 +7036,8 @@
       <c r="R87" s="9">
         <v>46220</v>
       </c>
-      <c r="S87" s="7" t="s">
-        <v>33</v>
+      <c r="S87" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46167.74163472222</v>
+        <v>46213.18677655092</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>58</v>
@@ -8337,8 +8337,8 @@
       <c r="R110" s="5">
         <v>46220</v>
       </c>
-      <c r="S110" s="7" t="s">
-        <v>33</v>
+      <c r="S110" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
@@ -8570,9 +8570,11 @@
       <c r="B115" s="9">
         <v>46167.632606053245</v>
       </c>
-      <c r="C115" s="10"/>
+      <c r="C115" s="9">
+        <v>46213.50676451389</v>
+      </c>
       <c r="D115" s="9">
-        <v>46209.72518126157</v>
+        <v>46213.506766238424</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>213</v>
@@ -8623,9 +8625,11 @@
       <c r="B116" s="5">
         <v>46167.63261443287</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46213.50677003472</v>
+      </c>
       <c r="D116" s="5">
-        <v>46209.72588013889</v>
+        <v>46213.506771631946</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>213</v>
@@ -8676,9 +8680,11 @@
       <c r="B117" s="9">
         <v>46167.63262241898</v>
       </c>
-      <c r="C117" s="10"/>
+      <c r="C117" s="9">
+        <v>46213.506775752314</v>
+      </c>
       <c r="D117" s="9">
-        <v>46209.72587407407</v>
+        <v>46213.50677731482</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>213</v>
@@ -8782,9 +8788,11 @@
       <c r="B119" s="9">
         <v>46167.63269008102</v>
       </c>
-      <c r="C119" s="10"/>
+      <c r="C119" s="9">
+        <v>46213.50678833333</v>
+      </c>
       <c r="D119" s="9">
-        <v>46209.72586340278</v>
+        <v>46213.5067896875</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>222</v>
@@ -8835,9 +8843,11 @@
       <c r="B120" s="5">
         <v>46167.632698738424</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46213.50679619213</v>
+      </c>
       <c r="D120" s="5">
-        <v>46209.72585412037</v>
+        <v>46213.50679762731</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>222</v>
@@ -9059,7 +9069,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46189.87508946759</v>
+        <v>46213.50676993055</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>213</v>
@@ -9112,7 +9122,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46189.87509015047</v>
+        <v>46213.50677655093</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>213</v>
@@ -9165,7 +9175,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46189.87509105324</v>
+        <v>46213.50678052084</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>213</v>
@@ -9271,7 +9281,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46189.87509244213</v>
+        <v>46213.50679318287</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>222</v>
@@ -9324,7 +9334,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46189.8750930324</v>
+        <v>46213.50680238426</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>222</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6517,7 +6517,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46206.16856959491</v>
+        <v>46214.19770118056</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>251</v>
@@ -6561,8 +6561,8 @@
       <c r="R78" s="5">
         <v>46213</v>
       </c>
-      <c r="S78" s="12" t="s">
-        <v>146</v>
+      <c r="S78" s="11" t="s">
+        <v>108</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -7521,7 +7521,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46212.62569252314</v>
+        <v>46216.20187390046</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>280</v>
@@ -7565,8 +7565,8 @@
       <c r="R96" s="5">
         <v>46223</v>
       </c>
-      <c r="S96" s="7" t="s">
-        <v>33</v>
+      <c r="S96" s="12" t="s">
+        <v>146</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46167.629188032406</v>
+        <v>46216.68609471065</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>226</v>
@@ -6088,9 +6088,11 @@
       <c r="B71" s="9">
         <v>46167.55708079861</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="9">
+        <v>46216.68608863426</v>
+      </c>
       <c r="D71" s="9">
-        <v>46207.17045002315</v>
+        <v>46216.686107546295</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>229</v>
@@ -6138,10 +6140,10 @@
         <v>108</v>
       </c>
       <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="12" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="U71" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -6153,7 +6155,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46211.19534319444</v>
+        <v>46216.68612402778</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>234</v>
@@ -6203,8 +6205,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="11" t="s">
-        <v>61</v>
+      <c r="U72" s="12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6214,9 +6216,11 @@
       <c r="B73" s="9">
         <v>46167.55709181713</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9">
+        <v>46216.68610497685</v>
+      </c>
       <c r="D73" s="9">
-        <v>46207.17044986111</v>
+        <v>46216.68612113426</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>238</v>
@@ -6264,10 +6268,10 @@
         <v>108</v>
       </c>
       <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6279,7 +6283,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46211.19534318287</v>
+        <v>46216.68612297454</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>241</v>
@@ -6329,8 +6333,8 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="11" t="s">
-        <v>61</v>
+      <c r="U74" s="12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6340,9 +6344,11 @@
       <c r="B75" s="9">
         <v>46167.55715278935</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46216.68611923611</v>
+      </c>
       <c r="D75" s="9">
-        <v>46207.17044987269</v>
+        <v>46216.68613528935</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>244</v>
@@ -6390,10 +6396,10 @@
         <v>108</v>
       </c>
       <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="12" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="U75" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6405,7 +6411,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46211.195343217594</v>
+        <v>46216.6861346875</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>245</v>
@@ -6455,8 +6461,8 @@
       <c r="T76" s="6">
         <v>0</v>
       </c>
-      <c r="U76" s="11" t="s">
-        <v>61</v>
+      <c r="U76" s="12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="491">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -6041,9 +6041,11 @@
       <c r="B70" s="5">
         <v>46167.5570771412</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46216.801943796294</v>
+      </c>
       <c r="D70" s="5">
-        <v>46216.68609471065</v>
+        <v>46216.8019547338</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>226</v>
@@ -6078,8 +6080,12 @@
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
+      <c r="T70" s="6">
+        <v>1</v>
+      </c>
+      <c r="U70" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
@@ -6153,9 +6159,11 @@
       <c r="B72" s="5">
         <v>46167.5570859838</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46216.801912118055</v>
+      </c>
       <c r="D72" s="5">
-        <v>46216.68612402778</v>
+        <v>46216.802392673606</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>234</v>
@@ -6203,10 +6211,10 @@
         <v>108</v>
       </c>
       <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="12" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="U72" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6281,9 +6289,11 @@
       <c r="B74" s="5">
         <v>46167.55709682871</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46216.80191915509</v>
+      </c>
       <c r="D74" s="5">
-        <v>46216.68612297454</v>
+        <v>46216.801934849536</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>241</v>
@@ -6331,10 +6341,10 @@
         <v>108</v>
       </c>
       <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="12" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="U74" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6409,9 +6419,11 @@
       <c r="B76" s="5">
         <v>46167.55716416667</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46216.80192825232</v>
+      </c>
       <c r="D76" s="5">
-        <v>46216.6861346875</v>
+        <v>46216.801944085644</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>245</v>
@@ -6459,10 +6471,10 @@
         <v>108</v>
       </c>
       <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="12" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="U76" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6588,7 +6600,7 @@
         <v>46203.502226909724</v>
       </c>
       <c r="D79" s="9">
-        <v>46203.50222925926</v>
+        <v>46216.80193877315</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>214</v>
@@ -6643,7 +6655,7 @@
         <v>46203.50247417824</v>
       </c>
       <c r="D80" s="5">
-        <v>46203.50247613426</v>
+        <v>46216.80193822917</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>214</v>
@@ -6698,7 +6710,7 @@
         <v>46203.50259047454</v>
       </c>
       <c r="D81" s="9">
-        <v>46203.50259215278</v>
+        <v>46216.801934814815</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>214</v>
@@ -6753,7 +6765,7 @@
         <v>46203.502671678245</v>
       </c>
       <c r="D82" s="5">
-        <v>46203.50267324074</v>
+        <v>46216.80193553241</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>214</v>
@@ -6808,7 +6820,7 @@
         <v>46203.50276456018</v>
       </c>
       <c r="D83" s="9">
-        <v>46203.50276618055</v>
+        <v>46216.80193606482</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>214</v>
@@ -6863,7 +6875,7 @@
         <v>46203.502881238426</v>
       </c>
       <c r="D84" s="5">
-        <v>46203.50288322917</v>
+        <v>46216.801936585645</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>214</v>
@@ -6918,7 +6930,7 @@
         <v>46203.503010925924</v>
       </c>
       <c r="D85" s="9">
-        <v>46203.503012835645</v>
+        <v>46216.801937083335</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>223</v>
@@ -6973,7 +6985,7 @@
         <v>46203.503100671296</v>
       </c>
       <c r="D86" s="5">
-        <v>46203.503102048606</v>
+        <v>46216.801937592594</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>223</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="488">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -376,9 +376,6 @@
     <t>propuesta nucleo rodete  ot 4328 - 4330</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete  ot 4328 - 4330,Propuesta compras:</t>
   </si>
   <si>
@@ -386,12 +383,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser  ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -3582,11 +3573,9 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="5">
         <v>46156</v>
       </c>
@@ -3609,7 +3598,7 @@
         <v>84</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q28" s="5">
         <v>46156</v>
@@ -3629,7 +3618,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" s="9">
         <v>46167.556831423615</v>
@@ -3641,17 +3630,15 @@
         <v>46196.64909515047</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>105</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H29" s="10"/>
       <c r="I29" s="9">
         <v>46190</v>
       </c>
@@ -3671,10 +3658,10 @@
         <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q29" s="9">
         <v>46190</v>
@@ -3683,7 +3670,7 @@
         <v>46191</v>
       </c>
       <c r="S29" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3694,7 +3681,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B30" s="5">
         <v>46167.55683648148</v>
@@ -3706,17 +3693,15 @@
         <v>46196.64962321759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>105</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="5">
         <v>46190</v>
       </c>
@@ -3736,10 +3721,10 @@
         <v>91</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q30" s="5">
         <v>46190</v>
@@ -3748,7 +3733,7 @@
         <v>46191</v>
       </c>
       <c r="S30" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3759,7 +3744,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B31" s="9">
         <v>46167.55684075231</v>
@@ -3771,17 +3756,15 @@
         <v>46196.651105439814</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>105</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H31" s="10"/>
       <c r="I31" s="9">
         <v>46190</v>
       </c>
@@ -3801,10 +3784,10 @@
         <v>91</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q31" s="9">
         <v>46190</v>
@@ -3813,7 +3796,7 @@
         <v>46191</v>
       </c>
       <c r="S31" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3824,7 +3807,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B32" s="5">
         <v>46167.55684506944</v>
@@ -3836,17 +3819,15 @@
         <v>46196.65189541667</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>105</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H32" s="6"/>
       <c r="I32" s="5">
         <v>46190</v>
       </c>
@@ -3866,10 +3847,10 @@
         <v>91</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Q32" s="5">
         <v>46190</v>
@@ -3878,7 +3859,7 @@
         <v>46191</v>
       </c>
       <c r="S32" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3889,7 +3870,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B33" s="9">
         <v>46167.55684913194</v>
@@ -3901,7 +3882,7 @@
         <v>46209.564447372686</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3934,7 +3915,7 @@
         <v>51</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q33" s="9">
         <v>46157</v>
@@ -3954,7 +3935,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B34" s="5">
         <v>46189.87339945602</v>
@@ -3966,7 +3947,7 @@
         <v>46190.643601261574</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -4007,7 +3988,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B35" s="9">
         <v>46189.874116527775</v>
@@ -4019,17 +4000,15 @@
         <v>46190.64358837963</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H35" s="10"/>
       <c r="I35" s="9">
         <v>46160</v>
       </c>
@@ -4046,10 +4025,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O35" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4061,7 +4040,7 @@
         <v>46167</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -4072,7 +4051,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B36" s="5">
         <v>46189.87428425926</v>
@@ -4084,17 +4063,15 @@
         <v>46209.56394472222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H36" s="6"/>
       <c r="I36" s="5">
         <v>46160</v>
       </c>
@@ -4111,13 +4088,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q36" s="5">
         <v>46160</v>
@@ -4126,7 +4103,7 @@
         <v>46167</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4137,7 +4114,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B37" s="9">
         <v>46167.556641689815</v>
@@ -4147,7 +4124,7 @@
         <v>46199.56372103009</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>25</v>
@@ -4171,7 +4148,7 @@
         <v>26</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4186,7 +4163,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B38" s="5">
         <v>46167.55686952546</v>
@@ -4198,16 +4175,16 @@
         <v>46195.930020127314</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I38" s="5">
         <v>46160</v>
@@ -4225,13 +4202,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q38" s="5">
         <v>46160</v>
@@ -4240,7 +4217,7 @@
         <v>46183</v>
       </c>
       <c r="S38" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -4251,7 +4228,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B39" s="9">
         <v>46167.556874270835</v>
@@ -4263,16 +4240,16 @@
         <v>46195.92806517361</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I39" s="9">
         <v>46160</v>
@@ -4290,13 +4267,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>99</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4312,7 +4289,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B40" s="5">
         <v>46167.55687946759</v>
@@ -4324,16 +4301,16 @@
         <v>46195.92988494213</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I40" s="5">
         <v>46162</v>
@@ -4351,13 +4328,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4373,7 +4350,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B41" s="9">
         <v>46167.55696103009</v>
@@ -4383,16 +4360,16 @@
         <v>46212.18989069444</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I41" s="9">
         <v>46160</v>
@@ -4410,10 +4387,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4425,7 +4402,7 @@
         <v>46219</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -4436,7 +4413,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B42" s="5">
         <v>46167.556965254626</v>
@@ -4446,16 +4423,16 @@
         <v>46212.654553368055</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I42" s="5">
         <v>46161</v>
@@ -4473,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4489,7 +4466,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B43" s="9">
         <v>46167.55696965278</v>
@@ -4499,16 +4476,16 @@
         <v>46169.87902826389</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I43" s="9">
         <v>46171</v>
@@ -4526,13 +4503,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4542,7 +4519,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B44" s="5">
         <v>46167.556973784725</v>
@@ -4554,16 +4531,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I44" s="5">
         <v>46192</v>
@@ -4581,13 +4558,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q44" s="5">
         <v>46192</v>
@@ -4596,7 +4573,7 @@
         <v>46204</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4607,7 +4584,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B45" s="9">
         <v>46167.556978611115</v>
@@ -4619,16 +4596,16 @@
         <v>46199.56362072917</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I45" s="9">
         <v>46192</v>
@@ -4646,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4668,7 +4645,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B46" s="5">
         <v>46167.55698368055</v>
@@ -4680,16 +4657,16 @@
         <v>46199.563687118054</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I46" s="5">
         <v>46196</v>
@@ -4707,13 +4684,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4729,7 +4706,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B47" s="9">
         <v>46167.556988842596</v>
@@ -4741,16 +4718,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I47" s="9">
         <v>46192</v>
@@ -4768,10 +4745,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4783,7 +4760,7 @@
         <v>46204</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4794,7 +4771,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B48" s="5">
         <v>46167.556992708334</v>
@@ -4806,16 +4783,16 @@
         <v>46199.56375667824</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I48" s="5">
         <v>46192</v>
@@ -4833,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4849,7 +4826,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B49" s="9">
         <v>46167.5569971875</v>
@@ -4861,16 +4838,16 @@
         <v>46199.56447744213</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I49" s="9">
         <v>46196</v>
@@ -4888,13 +4865,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4904,7 +4881,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B50" s="5">
         <v>46167.55700140046</v>
@@ -4916,16 +4893,16 @@
         <v>46204.59613972223</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4943,10 +4920,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4969,7 +4946,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B51" s="9">
         <v>46167.55700519676</v>
@@ -4981,16 +4958,16 @@
         <v>46204.5950621875</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -5008,13 +4985,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5024,7 +5001,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B52" s="5">
         <v>46167.557010034725</v>
@@ -5036,16 +5013,16 @@
         <v>46204.59515966436</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -5063,13 +5040,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5079,7 +5056,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B53" s="9">
         <v>46167.55701476852</v>
@@ -5089,16 +5066,16 @@
         <v>46204.59516696759</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5116,10 +5093,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5132,7 +5109,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B54" s="5">
         <v>46167.55701769676</v>
@@ -5144,16 +5121,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I54" s="5">
         <v>46192</v>
@@ -5171,10 +5148,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5186,7 +5163,7 @@
         <v>46204</v>
       </c>
       <c r="S54" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -5197,7 +5174,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B55" s="9">
         <v>46167.557021678236</v>
@@ -5209,16 +5186,16 @@
         <v>46199.564400601856</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I55" s="9">
         <v>46192</v>
@@ -5236,13 +5213,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5252,7 +5229,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B56" s="5">
         <v>46167.55702634259</v>
@@ -5264,16 +5241,16 @@
         <v>46199.56458967592</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I56" s="5">
         <v>46196</v>
@@ -5291,13 +5268,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5307,7 +5284,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B57" s="9">
         <v>46167.55703671296</v>
@@ -5317,7 +5294,7 @@
         <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5341,7 +5318,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5354,7 +5331,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B58" s="5">
         <v>46167.557040520835</v>
@@ -5366,16 +5343,16 @@
         <v>46197.715067453704</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5393,13 +5370,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5408,7 +5385,7 @@
         <v>46168</v>
       </c>
       <c r="S58" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5419,7 +5396,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B59" s="9">
         <v>46167.557045856476</v>
@@ -5431,16 +5408,16 @@
         <v>46197.71510291667</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5458,13 +5435,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="O59" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="O59" s="10" t="s">
-        <v>197</v>
-      </c>
       <c r="P59" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5473,7 +5450,7 @@
         <v>46188</v>
       </c>
       <c r="S59" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5484,7 +5461,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46167.5570519676</v>
@@ -5496,16 +5473,16 @@
         <v>46190.1997147338</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5523,13 +5500,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5538,7 +5515,7 @@
         <v>46189</v>
       </c>
       <c r="S60" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5549,7 +5526,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
@@ -5559,16 +5536,16 @@
         <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5586,10 +5563,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5612,7 +5589,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5622,16 +5599,16 @@
         <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5649,13 +5626,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5665,7 +5642,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5675,16 +5652,16 @@
         <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5702,13 +5679,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5718,7 +5695,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5728,16 +5705,16 @@
         <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5755,13 +5732,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5771,7 +5748,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5781,16 +5758,16 @@
         <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5808,13 +5785,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5824,7 +5801,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5834,16 +5811,16 @@
         <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5861,13 +5838,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5877,7 +5854,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5887,16 +5864,16 @@
         <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5914,13 +5891,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5930,7 +5907,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5940,16 +5917,16 @@
         <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5967,13 +5944,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5983,7 +5960,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5993,16 +5970,16 @@
         <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -6020,13 +5997,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -6036,7 +6013,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -6048,7 +6025,7 @@
         <v>46216.8019547338</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6072,7 +6049,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6089,7 +6066,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6101,16 +6078,16 @@
         <v>46216.686107546295</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6128,13 +6105,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6143,7 +6120,7 @@
         <v>46206</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -6154,7 +6131,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6166,16 +6143,16 @@
         <v>46216.802392673606</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6193,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6208,7 +6185,7 @@
         <v>46210</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6219,7 +6196,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6231,16 +6208,16 @@
         <v>46216.68612113426</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6258,13 +6235,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6273,7 +6250,7 @@
         <v>46206</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T73" s="10">
         <v>1</v>
@@ -6284,7 +6261,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6296,16 +6273,16 @@
         <v>46216.801934849536</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6323,13 +6300,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6338,7 +6315,7 @@
         <v>46210</v>
       </c>
       <c r="S74" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6349,7 +6326,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6361,16 +6338,16 @@
         <v>46216.68613528935</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6388,13 +6365,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6403,7 +6380,7 @@
         <v>46206</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6414,7 +6391,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6426,16 +6403,16 @@
         <v>46216.801944085644</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6453,13 +6430,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6468,7 +6445,7 @@
         <v>46210</v>
       </c>
       <c r="S76" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6479,7 +6456,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6489,7 +6466,7 @@
         <v>46203.50206653935</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6513,7 +6490,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6526,7 +6503,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6538,16 +6515,16 @@
         <v>46214.19770118056</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6565,13 +6542,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6580,7 +6557,7 @@
         <v>46213</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6591,7 +6568,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46167.557178229166</v>
@@ -6603,16 +6580,16 @@
         <v>46216.80193877315</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6630,13 +6607,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6646,7 +6623,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46167.55718505787</v>
@@ -6658,16 +6635,16 @@
         <v>46216.80193822917</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6685,13 +6662,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6701,7 +6678,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46167.629964050924</v>
@@ -6713,16 +6690,16 @@
         <v>46216.801934814815</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6740,13 +6717,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6756,7 +6733,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46167.6299746875</v>
@@ -6768,16 +6745,16 @@
         <v>46216.80193553241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6795,13 +6772,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6811,7 +6788,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B83" s="9">
         <v>46167.63011578703</v>
@@ -6823,16 +6800,16 @@
         <v>46216.80193606482</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6850,13 +6827,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6866,7 +6843,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46167.630126516204</v>
@@ -6878,16 +6855,16 @@
         <v>46216.801936585645</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6905,13 +6882,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6921,7 +6898,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B85" s="9">
         <v>46167.63145555556</v>
@@ -6933,16 +6910,16 @@
         <v>46216.801937083335</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6960,13 +6937,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6976,7 +6953,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
         <v>46167.631772685185</v>
@@ -6988,16 +6965,16 @@
         <v>46216.801937592594</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -7015,13 +6992,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7031,7 +7008,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B87" s="9">
         <v>46167.557190844906</v>
@@ -7041,16 +7018,16 @@
         <v>46213.18677706018</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -7068,13 +7045,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -7083,7 +7060,7 @@
         <v>46220</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -7094,7 +7071,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5">
         <v>46167.557195092595</v>
@@ -7106,16 +7083,16 @@
         <v>46209.725033622686</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7133,13 +7110,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7149,7 +7126,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B89" s="9">
         <v>46167.557200995376</v>
@@ -7161,16 +7138,16 @@
         <v>46209.72516011574</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7188,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7204,7 +7181,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B90" s="5">
         <v>46167.63214916667</v>
@@ -7216,16 +7193,16 @@
         <v>46209.725171666665</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7243,13 +7220,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7259,7 +7236,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B91" s="9">
         <v>46167.63219107639</v>
@@ -7271,16 +7248,16 @@
         <v>46209.72518666666</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7298,13 +7275,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7314,7 +7291,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B92" s="5">
         <v>46167.63220099537</v>
@@ -7326,16 +7303,16 @@
         <v>46209.725205462964</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7353,13 +7330,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7369,7 +7346,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B93" s="9">
         <v>46167.63220839121</v>
@@ -7379,16 +7356,16 @@
         <v>46203.502887615745</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7406,13 +7383,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7422,7 +7399,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B94" s="5">
         <v>46167.63225591435</v>
@@ -7434,16 +7411,16 @@
         <v>46203.50339560185</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7461,13 +7438,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7477,7 +7454,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B95" s="9">
         <v>46167.63226373843</v>
@@ -7489,16 +7466,16 @@
         <v>46203.50367474537</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7516,13 +7493,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7532,7 +7509,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B96" s="5">
         <v>46167.5572065625</v>
@@ -7542,16 +7519,16 @@
         <v>46216.20187390046</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7569,13 +7546,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7584,7 +7561,7 @@
         <v>46223</v>
       </c>
       <c r="S96" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
@@ -7595,7 +7572,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B97" s="9">
         <v>46167.557210914354</v>
@@ -7607,16 +7584,16 @@
         <v>46209.725893599534</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7634,13 +7611,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7650,7 +7627,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B98" s="5">
         <v>46167.55721697917</v>
@@ -7662,16 +7639,16 @@
         <v>46209.725886851855</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7689,13 +7666,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7705,7 +7682,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B99" s="9">
         <v>46167.632342048615</v>
@@ -7717,16 +7694,16 @@
         <v>46209.72588194444</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7744,10 +7721,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7760,7 +7737,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B100" s="5">
         <v>46167.63235868055</v>
@@ -7772,16 +7749,16 @@
         <v>46209.72587559027</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7799,13 +7776,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7815,7 +7792,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B101" s="9">
         <v>46167.63236590278</v>
@@ -7827,16 +7804,16 @@
         <v>46209.725869594906</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7854,13 +7831,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7870,7 +7847,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B102" s="5">
         <v>46167.63237413194</v>
@@ -7880,16 +7857,16 @@
         <v>46167.7415103588</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7907,13 +7884,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7923,7 +7900,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B103" s="9">
         <v>46167.63244320602</v>
@@ -7935,16 +7912,16 @@
         <v>46209.7258571875</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7962,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7978,7 +7955,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B104" s="5">
         <v>46167.63245268518</v>
@@ -7990,16 +7967,16 @@
         <v>46209.725848692135</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -8017,13 +7994,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8033,7 +8010,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B105" s="9">
         <v>46167.55722248842</v>
@@ -8043,7 +8020,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -8067,7 +8044,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -8080,7 +8057,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46167.557225682875</v>
@@ -8090,16 +8067,16 @@
         <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -8117,13 +8094,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="5">
         <v>46184</v>
@@ -8132,7 +8109,7 @@
         <v>46184</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8143,7 +8120,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46167.557231493054</v>
@@ -8153,16 +8130,16 @@
         <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8180,13 +8157,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8195,7 +8172,7 @@
         <v>46167</v>
       </c>
       <c r="S107" s="11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
@@ -8206,7 +8183,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B108" s="5">
         <v>46167.55723746528</v>
@@ -8216,16 +8193,16 @@
         <v>46189.87818384259</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8243,13 +8220,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q108" s="5">
         <v>46168</v>
@@ -8269,7 +8246,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B109" s="9">
         <v>46167.55724847222</v>
@@ -8279,16 +8256,16 @@
         <v>46204.59517594907</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8306,13 +8283,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q109" s="9">
         <v>46265</v>
@@ -8332,7 +8309,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B110" s="5">
         <v>46167.55725353009</v>
@@ -8348,10 +8325,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8369,13 +8346,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q110" s="5">
         <v>46220</v>
@@ -8384,7 +8361,7 @@
         <v>46220</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
@@ -8395,7 +8372,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B111" s="9">
         <v>46167.5572591088</v>
@@ -8405,7 +8382,7 @@
         <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8429,7 +8406,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8442,7 +8419,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B112" s="5">
         <v>46167.557262685186</v>
@@ -8452,17 +8429,15 @@
         <v>46212.62486408565</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="5">
         <v>46224</v>
       </c>
@@ -8479,13 +8454,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q112" s="5">
         <v>46224</v>
@@ -8505,7 +8480,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B113" s="9">
         <v>46167.55727085649</v>
@@ -8515,17 +8490,15 @@
         <v>46209.725901666665</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="10"/>
       <c r="I113" s="9">
         <v>46224</v>
       </c>
@@ -8542,10 +8515,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="O113" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="O113" s="10" t="s">
-        <v>310</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8558,7 +8531,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B114" s="5">
         <v>46167.55727532407</v>
@@ -8568,17 +8541,15 @@
         <v>46209.72589265046</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H114" s="6"/>
       <c r="I114" s="5">
         <v>46224</v>
       </c>
@@ -8595,10 +8566,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="O114" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8611,7 +8582,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B115" s="9">
         <v>46167.632606053245</v>
@@ -8623,17 +8594,15 @@
         <v>46213.506766238424</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H115" s="10"/>
       <c r="I115" s="9">
         <v>46224</v>
       </c>
@@ -8650,13 +8619,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8666,7 +8635,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B116" s="5">
         <v>46167.63261443287</v>
@@ -8678,17 +8647,15 @@
         <v>46213.506771631946</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H116" s="6"/>
       <c r="I116" s="5">
         <v>46224</v>
       </c>
@@ -8705,13 +8672,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8721,7 +8688,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B117" s="9">
         <v>46167.63262241898</v>
@@ -8733,17 +8700,15 @@
         <v>46213.50677731482</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H117" s="10"/>
       <c r="I117" s="9">
         <v>46224</v>
       </c>
@@ -8760,13 +8725,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8776,7 +8741,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B118" s="5">
         <v>46167.63263039352</v>
@@ -8786,17 +8751,15 @@
         <v>46167.74189655093</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="5">
         <v>46224</v>
       </c>
@@ -8813,13 +8776,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8829,7 +8792,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B119" s="9">
         <v>46167.63269008102</v>
@@ -8841,17 +8804,15 @@
         <v>46213.5067896875</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="10"/>
       <c r="I119" s="9">
         <v>46224</v>
       </c>
@@ -8868,13 +8829,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8884,7 +8845,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B120" s="5">
         <v>46167.632698738424</v>
@@ -8896,17 +8857,15 @@
         <v>46213.50679762731</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="5">
         <v>46224</v>
       </c>
@@ -8923,13 +8882,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8939,7 +8898,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B121" s="9">
         <v>46167.55727960648</v>
@@ -8949,17 +8908,15 @@
         <v>46212.62488043982</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="10"/>
       <c r="I121" s="9">
         <v>46231</v>
       </c>
@@ -8976,13 +8933,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q121" s="9">
         <v>46231</v>
@@ -9002,7 +8959,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B122" s="5">
         <v>46167.557284375</v>
@@ -9012,17 +8969,15 @@
         <v>46189.87510767361</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="5">
         <v>46231</v>
       </c>
@@ -9039,13 +8994,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="P122" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="O122" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>322</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9055,7 +9010,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B123" s="9">
         <v>46167.55729009259</v>
@@ -9065,17 +9020,15 @@
         <v>46189.87510009259</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="10"/>
       <c r="I123" s="9">
         <v>46231</v>
       </c>
@@ -9092,13 +9045,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="O123" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="P123" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="O123" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="P123" s="10" t="s">
-        <v>322</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9108,7 +9061,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B124" s="5">
         <v>46167.6328130787</v>
@@ -9118,17 +9071,15 @@
         <v>46213.50676993055</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="5">
         <v>46231</v>
       </c>
@@ -9145,13 +9096,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9161,7 +9112,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B125" s="9">
         <v>46167.63283585648</v>
@@ -9171,17 +9122,15 @@
         <v>46213.50677655093</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="10"/>
       <c r="I125" s="9">
         <v>46231</v>
       </c>
@@ -9198,13 +9147,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9214,7 +9163,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B126" s="5">
         <v>46167.63284336806</v>
@@ -9224,17 +9173,15 @@
         <v>46213.50678052084</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
       <c r="I126" s="5">
         <v>46231</v>
       </c>
@@ -9251,13 +9198,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9267,7 +9214,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B127" s="9">
         <v>46167.63285163195</v>
@@ -9277,17 +9224,15 @@
         <v>46189.87509177084</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H127" s="10"/>
       <c r="I127" s="9">
         <v>46231</v>
       </c>
@@ -9304,13 +9249,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9320,7 +9265,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B128" s="5">
         <v>46167.63289178241</v>
@@ -9330,17 +9275,15 @@
         <v>46213.50679318287</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H128" s="6"/>
       <c r="I128" s="5">
         <v>46231</v>
       </c>
@@ -9357,13 +9300,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9373,7 +9316,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B129" s="9">
         <v>46167.632899212964</v>
@@ -9383,17 +9326,15 @@
         <v>46213.50680238426</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H129" s="10"/>
       <c r="I129" s="9">
         <v>46231</v>
       </c>
@@ -9410,13 +9351,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9426,7 +9367,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B130" s="5">
         <v>46167.55733736111</v>
@@ -9436,17 +9377,15 @@
         <v>46212.62489320602</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H130" s="6"/>
       <c r="I130" s="5">
         <v>46232</v>
       </c>
@@ -9463,13 +9402,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q130" s="5">
         <v>46232</v>
@@ -9489,7 +9428,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B131" s="9">
         <v>46167.557343645836</v>
@@ -9499,17 +9438,15 @@
         <v>46189.87510797454</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H131" s="10"/>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
         <v>46232</v>
@@ -9524,13 +9461,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="O131" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="P131" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="O131" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="P131" s="10" t="s">
-        <v>337</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9540,7 +9477,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B132" s="5">
         <v>46167.55735079861</v>
@@ -9550,17 +9487,15 @@
         <v>46189.87510071759</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H132" s="6"/>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
         <v>46232</v>
@@ -9575,13 +9510,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="O132" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="O132" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9591,7 +9526,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B133" s="9">
         <v>46167.63302359954</v>
@@ -9601,17 +9536,15 @@
         <v>46189.875093634255</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H133" s="10"/>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
         <v>46232</v>
@@ -9626,13 +9559,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9642,7 +9575,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B134" s="5">
         <v>46167.63303486111</v>
@@ -9652,17 +9585,15 @@
         <v>46189.8750941551</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H134" s="6"/>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
         <v>46232</v>
@@ -9677,13 +9608,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9693,7 +9624,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B135" s="9">
         <v>46167.633050648146</v>
@@ -9703,17 +9634,15 @@
         <v>46189.87509472222</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H135" s="10"/>
       <c r="I135" s="10"/>
       <c r="J135" s="9">
         <v>46232</v>
@@ -9728,13 +9657,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9744,7 +9673,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B136" s="5">
         <v>46167.633060671295</v>
@@ -9754,17 +9683,15 @@
         <v>46189.87509519676</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H136" s="6"/>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
         <v>46232</v>
@@ -9779,13 +9706,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9795,7 +9722,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B137" s="9">
         <v>46167.633115185185</v>
@@ -9805,17 +9732,15 @@
         <v>46189.87509570602</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H137" s="10"/>
       <c r="I137" s="10"/>
       <c r="J137" s="9">
         <v>46232</v>
@@ -9830,13 +9755,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9846,7 +9771,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B138" s="5">
         <v>46167.6331228125</v>
@@ -9856,17 +9781,15 @@
         <v>46189.87509615741</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H138" s="6"/>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
         <v>46232</v>
@@ -9881,13 +9804,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9897,7 +9820,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B139" s="9">
         <v>46167.557357488426</v>
@@ -9907,17 +9830,15 @@
         <v>46212.624909606486</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H139" s="10"/>
       <c r="I139" s="9">
         <v>46233</v>
       </c>
@@ -9934,13 +9855,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q139" s="9">
         <v>46233</v>
@@ -9960,7 +9881,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B140" s="5">
         <v>46167.55736211805</v>
@@ -9970,17 +9891,15 @@
         <v>46189.877459745374</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H140" s="6"/>
       <c r="I140" s="5">
         <v>46233</v>
       </c>
@@ -9997,13 +9916,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="O140" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="P140" s="6" t="s">
         <v>348</v>
-      </c>
-      <c r="O140" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10013,7 +9932,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B141" s="9">
         <v>46167.55737267361</v>
@@ -10023,17 +9942,15 @@
         <v>46189.87746077546</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H141" s="10"/>
       <c r="I141" s="9">
         <v>46233</v>
       </c>
@@ -10050,13 +9967,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="O141" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="P141" s="10" t="s">
         <v>348</v>
-      </c>
-      <c r="O141" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="P141" s="10" t="s">
-        <v>351</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -10066,7 +9983,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B142" s="5">
         <v>46167.63325159722</v>
@@ -10076,17 +9993,15 @@
         <v>46189.877455671296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H142" s="6"/>
       <c r="I142" s="5">
         <v>46233</v>
       </c>
@@ -10103,13 +10018,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10119,7 +10034,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B143" s="9">
         <v>46167.63325929398</v>
@@ -10129,17 +10044,15 @@
         <v>46189.87745677083</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H143" s="10"/>
       <c r="I143" s="9">
         <v>46233</v>
       </c>
@@ -10156,13 +10069,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10172,7 +10085,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B144" s="5">
         <v>46167.633274293985</v>
@@ -10182,17 +10095,15 @@
         <v>46189.87745732639</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H144" s="6"/>
       <c r="I144" s="5">
         <v>46233</v>
       </c>
@@ -10209,13 +10120,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10225,7 +10136,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B145" s="9">
         <v>46167.633281875</v>
@@ -10235,17 +10146,15 @@
         <v>46189.877457916664</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H145" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H145" s="10"/>
       <c r="I145" s="9">
         <v>46233</v>
       </c>
@@ -10262,13 +10171,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10278,7 +10187,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B146" s="5">
         <v>46167.63332260417</v>
@@ -10288,17 +10197,15 @@
         <v>46189.87745863426</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H146" s="6"/>
       <c r="I146" s="5">
         <v>46233</v>
       </c>
@@ -10315,13 +10222,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10331,7 +10238,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B147" s="9">
         <v>46167.633331689816</v>
@@ -10341,17 +10248,15 @@
         <v>46189.87745917824</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H147" s="10"/>
       <c r="I147" s="9">
         <v>46233</v>
       </c>
@@ -10368,13 +10273,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10384,7 +10289,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B148" s="5">
         <v>46167.557378287034</v>
@@ -10394,17 +10299,15 @@
         <v>46212.62492555556</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H148" s="6"/>
       <c r="I148" s="5">
         <v>46234</v>
       </c>
@@ -10421,13 +10324,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q148" s="5">
         <v>46234</v>
@@ -10447,7 +10350,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B149" s="9">
         <v>46167.55738292824</v>
@@ -10457,17 +10360,15 @@
         <v>46167.742493136575</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H149" s="10"/>
       <c r="I149" s="9">
         <v>46234</v>
       </c>
@@ -10484,13 +10385,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10500,7 +10401,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B150" s="5">
         <v>46167.5573883912</v>
@@ -10510,17 +10411,15 @@
         <v>46167.742490000004</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H150" s="6"/>
       <c r="I150" s="5">
         <v>46234</v>
       </c>
@@ -10537,13 +10436,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10553,7 +10452,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B151" s="9">
         <v>46167.63341660879</v>
@@ -10563,17 +10462,15 @@
         <v>46167.74248716435</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H151" s="10"/>
       <c r="I151" s="9">
         <v>46234</v>
       </c>
@@ -10590,13 +10487,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10606,7 +10503,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B152" s="5">
         <v>46167.63343371528</v>
@@ -10616,17 +10513,15 @@
         <v>46167.74248396991</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H152" s="6"/>
       <c r="I152" s="5">
         <v>46234</v>
       </c>
@@ -10643,13 +10538,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10659,7 +10554,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B153" s="9">
         <v>46167.63344365741</v>
@@ -10669,17 +10564,15 @@
         <v>46167.742481134264</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H153" s="10"/>
       <c r="I153" s="9">
         <v>46234</v>
       </c>
@@ -10696,13 +10589,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10712,7 +10605,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B154" s="5">
         <v>46167.63345188658</v>
@@ -10722,17 +10615,15 @@
         <v>46167.74247835648</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H154" s="6"/>
       <c r="I154" s="5">
         <v>46234</v>
       </c>
@@ -10749,13 +10640,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10765,7 +10656,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B155" s="9">
         <v>46167.633506412036</v>
@@ -10775,17 +10666,15 @@
         <v>46167.74247142361</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H155" s="10"/>
       <c r="I155" s="9">
         <v>46234</v>
       </c>
@@ -10802,13 +10691,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10818,7 +10707,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B156" s="5">
         <v>46167.63351399306</v>
@@ -10828,17 +10717,15 @@
         <v>46167.74247065972</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H156" s="6"/>
       <c r="I156" s="5">
         <v>46234</v>
       </c>
@@ -10855,13 +10742,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10871,7 +10758,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B157" s="9">
         <v>46167.55739407407</v>
@@ -10881,17 +10768,15 @@
         <v>46212.624938865745</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H157" s="10"/>
       <c r="I157" s="9">
         <v>46238</v>
       </c>
@@ -10908,13 +10793,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Q157" s="9">
         <v>46238</v>
@@ -10934,7 +10819,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B158" s="5">
         <v>46167.55739920139</v>
@@ -10944,17 +10829,15 @@
         <v>46167.742638298616</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H158" s="6"/>
       <c r="I158" s="5">
         <v>46238</v>
       </c>
@@ -10971,13 +10854,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="O158" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="P158" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="O158" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="P158" s="6" t="s">
-        <v>378</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10987,7 +10870,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B159" s="9">
         <v>46167.5574040162</v>
@@ -10997,17 +10880,15 @@
         <v>46167.74263541667</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H159" s="10"/>
       <c r="I159" s="9">
         <v>46238</v>
       </c>
@@ -11024,13 +10905,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="O159" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="P159" s="10" t="s">
         <v>375</v>
-      </c>
-      <c r="O159" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="P159" s="10" t="s">
-        <v>378</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -11040,7 +10921,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B160" s="5">
         <v>46167.633843206015</v>
@@ -11050,17 +10931,15 @@
         <v>46167.742632037036</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H160" s="6"/>
       <c r="I160" s="5">
         <v>46238</v>
       </c>
@@ -11077,13 +10956,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11093,7 +10972,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B161" s="9">
         <v>46167.633849895836</v>
@@ -11103,17 +10982,15 @@
         <v>46167.742628935186</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H161" s="10"/>
       <c r="I161" s="9">
         <v>46238</v>
       </c>
@@ -11130,13 +11007,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11146,7 +11023,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B162" s="5">
         <v>46167.63385791666</v>
@@ -11156,17 +11033,15 @@
         <v>46167.74262635417</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H162" s="6"/>
       <c r="I162" s="5">
         <v>46238</v>
       </c>
@@ -11183,13 +11058,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11199,7 +11074,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B163" s="9">
         <v>46167.633867083336</v>
@@ -11209,17 +11084,15 @@
         <v>46167.74262355324</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H163" s="10"/>
       <c r="I163" s="9">
         <v>46238</v>
       </c>
@@ -11236,13 +11109,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11252,7 +11125,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B164" s="5">
         <v>46167.63391234954</v>
@@ -11262,17 +11135,15 @@
         <v>46167.742617407406</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H164" s="6"/>
       <c r="I164" s="5">
         <v>46238</v>
       </c>
@@ -11289,13 +11160,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11305,7 +11176,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B165" s="9">
         <v>46167.63392017361</v>
@@ -11315,17 +11186,15 @@
         <v>46167.74261677083</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H165" s="10"/>
       <c r="I165" s="9">
         <v>46238</v>
       </c>
@@ -11342,13 +11211,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11358,7 +11227,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B166" s="5">
         <v>46167.557409201385</v>
@@ -11368,7 +11237,7 @@
         <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -11392,7 +11261,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11405,7 +11274,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B167" s="9">
         <v>46167.5574132176</v>
@@ -11415,16 +11284,16 @@
         <v>46212.62539956019</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I167" s="9">
         <v>46230</v>
@@ -11442,13 +11311,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q167" s="9">
         <v>46230</v>
@@ -11468,7 +11337,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B168" s="5">
         <v>46167.55742054398</v>
@@ -11478,16 +11347,16 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I168" s="5">
         <v>46239</v>
@@ -11505,13 +11374,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11521,7 +11390,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B169" s="9">
         <v>46167.557425520834</v>
@@ -11531,16 +11400,16 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I169" s="9">
         <v>46239</v>
@@ -11558,13 +11427,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11574,7 +11443,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B170" s="5">
         <v>46167.55743020833</v>
@@ -11584,16 +11453,16 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I170" s="5">
         <v>46239</v>
@@ -11611,13 +11480,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11627,7 +11496,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B171" s="9">
         <v>46167.557434918985</v>
@@ -11637,16 +11506,16 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I171" s="9">
         <v>46239</v>
@@ -11664,13 +11533,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11680,7 +11549,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B172" s="5">
         <v>46167.636403032404</v>
@@ -11690,16 +11559,16 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I172" s="5">
         <v>46239</v>
@@ -11717,13 +11586,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11733,7 +11602,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B173" s="9">
         <v>46167.63641173611</v>
@@ -11743,16 +11612,16 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I173" s="9">
         <v>46239</v>
@@ -11770,13 +11639,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11786,7 +11655,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B174" s="5">
         <v>46167.636428645834</v>
@@ -11796,16 +11665,16 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I174" s="5">
         <v>46239</v>
@@ -11823,13 +11692,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11839,7 +11708,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B175" s="9">
         <v>46167.636439849535</v>
@@ -11849,16 +11718,16 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I175" s="9">
         <v>46239</v>
@@ -11876,13 +11745,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11892,7 +11761,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B176" s="5">
         <v>46167.636677511575</v>
@@ -11908,10 +11777,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I176" s="5">
         <v>46230</v>
@@ -11929,7 +11798,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>63</v>
@@ -11945,7 +11814,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B177" s="9">
         <v>46167.63669306713</v>
@@ -11961,10 +11830,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I177" s="9">
         <v>46230</v>
@@ -11982,7 +11851,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>63</v>
@@ -11998,7 +11867,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B178" s="5">
         <v>46167.6367015162</v>
@@ -12014,10 +11883,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I178" s="5">
         <v>46230</v>
@@ -12035,7 +11904,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>63</v>
@@ -12051,7 +11920,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B179" s="9">
         <v>46167.6367112963</v>
@@ -12067,10 +11936,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I179" s="9">
         <v>46230</v>
@@ -12088,7 +11957,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>63</v>
@@ -12104,7 +11973,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B180" s="5">
         <v>46167.63672008102</v>
@@ -12120,10 +11989,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I180" s="5">
         <v>46230</v>
@@ -12141,7 +12010,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>63</v>
@@ -12157,7 +12026,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B181" s="9">
         <v>46167.636729247686</v>
@@ -12173,10 +12042,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I181" s="9">
         <v>46230</v>
@@ -12194,7 +12063,7 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O181" s="10" t="s">
         <v>63</v>
@@ -12210,7 +12079,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B182" s="5">
         <v>46167.63683603009</v>
@@ -12226,10 +12095,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I182" s="5">
         <v>46230</v>
@@ -12247,7 +12116,7 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>71</v>
@@ -12263,7 +12132,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B183" s="9">
         <v>46167.636846319445</v>
@@ -12279,10 +12148,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I183" s="9">
         <v>46230</v>
@@ -12300,7 +12169,7 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>71</v>
@@ -12316,7 +12185,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B184" s="5">
         <v>46167.55743945602</v>
@@ -12326,17 +12195,15 @@
         <v>46212.6251847338</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H184" s="6"/>
       <c r="I184" s="5">
         <v>46170</v>
       </c>
@@ -12353,13 +12220,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q184" s="5">
         <v>46231</v>
@@ -12379,7 +12246,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B185" s="9">
         <v>46167.55744423611</v>
@@ -12389,17 +12256,15 @@
         <v>46167.74306620371</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H185" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H185" s="10"/>
       <c r="I185" s="10"/>
       <c r="J185" s="9">
         <v>46240</v>
@@ -12414,13 +12279,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="O185" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="P185" s="10" t="s">
         <v>412</v>
-      </c>
-      <c r="O185" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="P185" s="10" t="s">
-        <v>415</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12430,7 +12295,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B186" s="5">
         <v>46167.55744884259</v>
@@ -12440,17 +12305,15 @@
         <v>46167.74306335648</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H186" s="6"/>
       <c r="I186" s="6"/>
       <c r="J186" s="5">
         <v>46240</v>
@@ -12465,13 +12328,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12481,7 +12344,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B187" s="9">
         <v>46167.55745349537</v>
@@ -12491,17 +12354,15 @@
         <v>46167.74306008102</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H187" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H187" s="10"/>
       <c r="I187" s="10"/>
       <c r="J187" s="9">
         <v>46240</v>
@@ -12516,13 +12377,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12532,7 +12393,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B188" s="5">
         <v>46167.55745777777</v>
@@ -12542,17 +12403,15 @@
         <v>46167.74305738426</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H188" s="6"/>
       <c r="I188" s="6"/>
       <c r="J188" s="5">
         <v>46240</v>
@@ -12567,13 +12426,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12583,7 +12442,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B189" s="9">
         <v>46167.637670833334</v>
@@ -12593,17 +12452,15 @@
         <v>46167.74305466435</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H189" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H189" s="10"/>
       <c r="I189" s="10"/>
       <c r="J189" s="9">
         <v>46240</v>
@@ -12618,13 +12475,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12634,7 +12491,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B190" s="5">
         <v>46167.63768076389</v>
@@ -12644,17 +12501,15 @@
         <v>46167.743051990736</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H190" s="6"/>
       <c r="I190" s="6"/>
       <c r="J190" s="5">
         <v>46240</v>
@@ -12669,13 +12524,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12685,7 +12540,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B191" s="9">
         <v>46167.637724016204</v>
@@ -12695,17 +12550,15 @@
         <v>46167.74304920139</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H191" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H191" s="10"/>
       <c r="I191" s="10"/>
       <c r="J191" s="9">
         <v>46240</v>
@@ -12720,13 +12573,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12736,7 +12589,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B192" s="5">
         <v>46167.63773231482</v>
@@ -12746,17 +12599,15 @@
         <v>46167.743046574076</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H192" s="6"/>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
         <v>46240</v>
@@ -12771,13 +12622,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12787,7 +12638,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B193" s="9">
         <v>46167.63788011574</v>
@@ -12803,11 +12654,9 @@
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H193" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H193" s="10"/>
       <c r="I193" s="9">
         <v>46231</v>
       </c>
@@ -12824,7 +12673,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>64</v>
@@ -12840,7 +12689,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B194" s="5">
         <v>46167.637888530095</v>
@@ -12856,11 +12705,9 @@
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H194" s="6"/>
       <c r="I194" s="5">
         <v>46231</v>
       </c>
@@ -12877,7 +12724,7 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O194" s="6" t="s">
         <v>63</v>
@@ -12893,7 +12740,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B195" s="9">
         <v>46167.63789722222</v>
@@ -12909,11 +12756,9 @@
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H195" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H195" s="10"/>
       <c r="I195" s="9">
         <v>46231</v>
       </c>
@@ -12930,7 +12775,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O195" s="10" t="s">
         <v>63</v>
@@ -12946,7 +12791,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B196" s="5">
         <v>46167.63790768519</v>
@@ -12962,11 +12807,9 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H196" s="6"/>
       <c r="I196" s="5">
         <v>46231</v>
       </c>
@@ -12983,7 +12826,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
@@ -12999,7 +12842,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B197" s="9">
         <v>46167.63791662037</v>
@@ -13015,11 +12858,9 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H197" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H197" s="10"/>
       <c r="I197" s="9">
         <v>46231</v>
       </c>
@@ -13036,7 +12877,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>63</v>
@@ -13052,7 +12893,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B198" s="5">
         <v>46167.637946689814</v>
@@ -13068,11 +12909,9 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H198" s="6"/>
       <c r="I198" s="5">
         <v>46231</v>
       </c>
@@ -13089,7 +12928,7 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
@@ -13105,7 +12944,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B199" s="9">
         <v>46167.637995729165</v>
@@ -13121,11 +12960,9 @@
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H199" s="10"/>
       <c r="I199" s="9">
         <v>46231</v>
       </c>
@@ -13142,7 +12979,7 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>71</v>
@@ -13158,7 +12995,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B200" s="5">
         <v>46167.63800420139</v>
@@ -13174,11 +13011,9 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H200" s="6"/>
       <c r="I200" s="5">
         <v>46231</v>
       </c>
@@ -13195,7 +13030,7 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>71</v>
@@ -13211,7 +13046,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B201" s="9">
         <v>46167.55746224537</v>
@@ -13221,16 +13056,16 @@
         <v>46212.62523481481</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13248,13 +13083,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q201" s="9">
         <v>46241</v>
@@ -13274,7 +13109,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B202" s="5">
         <v>46167.55746689815</v>
@@ -13284,16 +13119,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13311,13 +13146,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13327,7 +13162,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B203" s="9">
         <v>46167.55747543981</v>
@@ -13337,16 +13172,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13364,13 +13199,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13380,7 +13215,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B204" s="5">
         <v>46167.557519270835</v>
@@ -13390,16 +13225,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13417,13 +13252,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13433,7 +13268,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B205" s="9">
         <v>46167.5575253125</v>
@@ -13443,16 +13278,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13470,13 +13305,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13486,7 +13321,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B206" s="5">
         <v>46167.6385715162</v>
@@ -13496,16 +13331,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13523,13 +13358,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13539,7 +13374,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B207" s="9">
         <v>46167.63857899306</v>
@@ -13549,16 +13384,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13576,13 +13411,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13592,7 +13427,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B208" s="5">
         <v>46167.638659930555</v>
@@ -13602,16 +13437,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13629,13 +13464,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13645,7 +13480,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B209" s="9">
         <v>46167.638666956016</v>
@@ -13655,16 +13490,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13682,13 +13517,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13698,7 +13533,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B210" s="5">
         <v>46167.6387090162</v>
@@ -13714,10 +13549,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13735,7 +13570,7 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>63</v>
@@ -13751,7 +13586,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B211" s="9">
         <v>46167.63871641204</v>
@@ -13767,10 +13602,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13788,7 +13623,7 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>63</v>
@@ -13804,7 +13639,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B212" s="5">
         <v>46167.638723599535</v>
@@ -13820,10 +13655,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13841,7 +13676,7 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>63</v>
@@ -13857,7 +13692,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B213" s="9">
         <v>46167.63873144676</v>
@@ -13873,10 +13708,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13894,7 +13729,7 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>63</v>
@@ -13910,7 +13745,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B214" s="5">
         <v>46167.6387405787</v>
@@ -13926,10 +13761,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13947,7 +13782,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>63</v>
@@ -13963,7 +13798,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B215" s="9">
         <v>46167.63874844907</v>
@@ -13979,10 +13814,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -14000,7 +13835,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>63</v>
@@ -14016,7 +13851,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B216" s="5">
         <v>46167.638756562505</v>
@@ -14032,10 +13867,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -14053,13 +13888,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -14069,7 +13904,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B217" s="9">
         <v>46167.63883428241</v>
@@ -14085,10 +13920,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -14106,13 +13941,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -14122,7 +13957,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B218" s="5">
         <v>46167.55752998842</v>
@@ -14132,16 +13967,16 @@
         <v>46212.62527664352</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -14159,13 +13994,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q218" s="5">
         <v>46244</v>
@@ -14185,7 +14020,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B219" s="9">
         <v>46167.55753614583</v>
@@ -14195,16 +14030,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14222,13 +14057,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14238,7 +14073,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B220" s="5">
         <v>46167.557540381946</v>
@@ -14248,16 +14083,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14275,13 +14110,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14291,7 +14126,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B221" s="9">
         <v>46167.557545069445</v>
@@ -14301,16 +14136,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14328,13 +14163,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14344,7 +14179,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B222" s="5">
         <v>46167.55754895833</v>
@@ -14354,16 +14189,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14381,13 +14216,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14397,7 +14232,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B223" s="9">
         <v>46167.63903770833</v>
@@ -14407,16 +14242,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14434,10 +14269,10 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14450,7 +14285,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B224" s="5">
         <v>46167.639049317135</v>
@@ -14460,16 +14295,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14487,10 +14322,10 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14503,7 +14338,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B225" s="9">
         <v>46167.639172118055</v>
@@ -14513,16 +14348,16 @@
         <v>46167.743832430555</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14540,10 +14375,10 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14556,7 +14391,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B226" s="5">
         <v>46167.63918146991</v>
@@ -14566,16 +14401,16 @@
         <v>46167.74382957176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14593,10 +14428,10 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14609,7 +14444,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B227" s="9">
         <v>46167.63922125</v>
@@ -14625,10 +14460,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14646,7 +14481,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>63</v>
@@ -14662,7 +14497,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B228" s="5">
         <v>46167.63923230324</v>
@@ -14678,10 +14513,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14699,7 +14534,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>63</v>
@@ -14715,7 +14550,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B229" s="9">
         <v>46167.63924049769</v>
@@ -14731,10 +14566,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14752,7 +14587,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>63</v>
@@ -14768,7 +14603,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B230" s="5">
         <v>46167.63924949074</v>
@@ -14784,10 +14619,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14805,7 +14640,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>63</v>
@@ -14821,7 +14656,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B231" s="9">
         <v>46167.639259375</v>
@@ -14837,10 +14672,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14858,7 +14693,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>63</v>
@@ -14874,7 +14709,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B232" s="5">
         <v>46167.63926804398</v>
@@ -14890,10 +14725,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14911,7 +14746,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>63</v>
@@ -14927,7 +14762,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B233" s="9">
         <v>46167.63935532408</v>
@@ -14937,16 +14772,16 @@
         <v>46167.74380655093</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14964,7 +14799,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>71</v>
@@ -14980,7 +14815,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B234" s="5">
         <v>46167.63936689815</v>
@@ -14990,16 +14825,16 @@
         <v>46167.74380591435</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>
@@ -15017,7 +14852,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>71</v>
@@ -15033,7 +14868,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B235" s="9">
         <v>46167.55755266204</v>
@@ -15043,7 +14878,7 @@
         <v>46167.73498962963</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>25</v>
@@ -15067,7 +14902,7 @@
         <v>26</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>26</v>
@@ -15080,7 +14915,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B236" s="5">
         <v>46167.55755585648</v>
@@ -15090,16 +14925,16 @@
         <v>46167.743865428245</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="I236" s="5">
         <v>46245</v>
@@ -15117,13 +14952,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="Q236" s="5">
         <v>46245</v>
@@ -15143,7 +14978,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B237" s="9">
         <v>46167.55756052083</v>
@@ -15153,7 +14988,7 @@
         <v>46189.872060740745</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15180,13 +15015,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="Q237" s="9">
         <v>46245</v>
@@ -15206,7 +15041,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B238" s="5">
         <v>46167.557566296295</v>
@@ -15216,7 +15051,7 @@
         <v>46167.73546241898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>25</v>
@@ -15240,7 +15075,7 @@
         <v>26</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>26</v>
@@ -15259,7 +15094,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B239" s="9">
         <v>46167.55756988426</v>
@@ -15269,7 +15104,7 @@
         <v>46167.743959513886</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15296,13 +15131,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="Q239" s="9">
         <v>46245</v>
@@ -15322,7 +15157,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B240" s="5">
         <v>46167.557574895836</v>
@@ -15332,7 +15167,7 @@
         <v>46167.74395664352</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15359,13 +15194,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="O240" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="O240" s="6" t="s">
-        <v>487</v>
-      </c>
       <c r="P240" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q240" s="5">
         <v>46254</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46212.18989069444</v>
+        <v>46219.16843181713</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>141</v>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.87902826389</v>
+        <v>46219.16843491898</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>147</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -253,6 +253,9 @@
     <t>Ingenieria Servicios ,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -503,9 +506,6 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC Tableros  ot 4329 - 4331 ,fabricación tableros  ot 4329 - 4331 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215103776708404</t>
@@ -1606,12 +1606,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
   </fills>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46167.73745994213</v>
+        <v>46220.20472001158</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2692,19 +2692,19 @@
       <c r="R12" s="5">
         <v>46227</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>33</v>
+      <c r="S12" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="11" t="s">
-        <v>61</v>
+      <c r="U12" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" s="9">
         <v>46167.63411775463</v>
@@ -2714,7 +2714,7 @@
         <v>46167.73754430556</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2747,7 +2747,7 @@
         <v>59</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="5">
         <v>46167.63443420139</v>
@@ -2767,7 +2767,7 @@
         <v>46167.7375415162</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2800,7 +2800,7 @@
         <v>59</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" s="9">
         <v>46167.634455694446</v>
@@ -2820,7 +2820,7 @@
         <v>46167.737538692134</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2853,7 +2853,7 @@
         <v>59</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2863,7 +2863,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46167.63446537037</v>
@@ -2873,7 +2873,7 @@
         <v>46167.737535625</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2906,7 +2906,7 @@
         <v>59</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="9">
         <v>46167.6344740162</v>
@@ -2926,7 +2926,7 @@
         <v>46167.73753288195</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2959,7 +2959,7 @@
         <v>59</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5">
         <v>46167.63448084491</v>
@@ -2979,7 +2979,7 @@
         <v>46167.73753034722</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -3012,7 +3012,7 @@
         <v>59</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="9">
         <v>46167.63453541667</v>
@@ -3032,7 +3032,7 @@
         <v>46167.737524641205</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -3065,7 +3065,7 @@
         <v>59</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5">
         <v>46167.63474393518</v>
@@ -3085,7 +3085,7 @@
         <v>46171.51095925926</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3118,7 +3118,7 @@
         <v>59</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" s="9">
         <v>46167.55662649305</v>
@@ -3138,7 +3138,7 @@
         <v>46189.87207028935</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -3162,7 +3162,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -3171,13 +3171,13 @@
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
-      <c r="U21" s="12" t="s">
-        <v>76</v>
+      <c r="U21" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B22" s="5">
         <v>46167.55678962963</v>
@@ -3189,16 +3189,16 @@
         <v>46189.87206064815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I22" s="5">
         <v>46154</v>
@@ -3210,19 +3210,19 @@
         <v>26</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="5">
         <v>46154</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B23" s="9">
         <v>46167.556794918986</v>
@@ -3254,16 +3254,16 @@
         <v>46189.872060532405</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I23" s="9">
         <v>46154</v>
@@ -3275,19 +3275,19 @@
         <v>26</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>41</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q23" s="9">
         <v>46154</v>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="5">
         <v>46167.55680065972</v>
@@ -3319,16 +3319,16 @@
         <v>46189.872060532405</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
@@ -3346,13 +3346,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q24" s="5">
         <v>46154</v>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="9">
         <v>46167.556633009255</v>
@@ -3384,7 +3384,7 @@
         <v>46209.56446100694</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3408,7 +3408,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="5">
         <v>46167.556814571755</v>
@@ -3437,16 +3437,16 @@
         <v>46189.87808604167</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I26" s="5">
         <v>46156</v>
@@ -3464,13 +3464,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46156</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B27" s="9">
         <v>46167.55682017361</v>
@@ -3502,16 +3502,16 @@
         <v>46209.563948483796</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I27" s="9">
         <v>46156</v>
@@ -3529,13 +3529,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q27" s="9">
         <v>46156</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" s="5">
         <v>46167.55682586806</v>
@@ -3567,7 +3567,7 @@
         <v>46190.641165381945</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3592,13 +3592,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q28" s="5">
         <v>46156</v>
@@ -3618,7 +3618,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" s="9">
         <v>46167.556831423615</v>
@@ -3630,7 +3630,7 @@
         <v>46196.64909515047</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3655,13 +3655,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q29" s="9">
         <v>46190</v>
@@ -3669,8 +3669,8 @@
       <c r="R29" s="9">
         <v>46191</v>
       </c>
-      <c r="S29" s="11" t="s">
-        <v>105</v>
+      <c r="S29" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5">
         <v>46167.55683648148</v>
@@ -3693,7 +3693,7 @@
         <v>46196.64962321759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3718,13 +3718,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="5">
         <v>46190</v>
@@ -3732,8 +3732,8 @@
       <c r="R30" s="5">
         <v>46191</v>
       </c>
-      <c r="S30" s="11" t="s">
-        <v>105</v>
+      <c r="S30" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="9">
         <v>46167.55684075231</v>
@@ -3756,7 +3756,7 @@
         <v>46196.651105439814</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3781,13 +3781,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q31" s="9">
         <v>46190</v>
@@ -3795,8 +3795,8 @@
       <c r="R31" s="9">
         <v>46191</v>
       </c>
-      <c r="S31" s="11" t="s">
-        <v>105</v>
+      <c r="S31" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3807,7 +3807,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="5">
         <v>46167.55684506944</v>
@@ -3819,7 +3819,7 @@
         <v>46196.65189541667</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3844,13 +3844,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q32" s="5">
         <v>46190</v>
@@ -3858,8 +3858,8 @@
       <c r="R32" s="5">
         <v>46191</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>105</v>
+      <c r="S32" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" s="9">
         <v>46167.55684913194</v>
@@ -3882,16 +3882,16 @@
         <v>46209.564447372686</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I33" s="9">
         <v>46157</v>
@@ -3909,13 +3909,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>51</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="9">
         <v>46157</v>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34" s="5">
         <v>46189.87339945602</v>
@@ -3947,7 +3947,7 @@
         <v>46190.643601261574</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B35" s="9">
         <v>46189.874116527775</v>
@@ -4000,7 +4000,7 @@
         <v>46190.64358837963</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -4025,10 +4025,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4039,8 +4039,8 @@
       <c r="R35" s="9">
         <v>46167</v>
       </c>
-      <c r="S35" s="11" t="s">
-        <v>105</v>
+      <c r="S35" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="5">
         <v>46189.87428425926</v>
@@ -4063,7 +4063,7 @@
         <v>46209.56394472222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -4088,13 +4088,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q36" s="5">
         <v>46160</v>
@@ -4102,19 +4102,19 @@
       <c r="R36" s="5">
         <v>46167</v>
       </c>
-      <c r="S36" s="11" t="s">
-        <v>105</v>
+      <c r="S36" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>76</v>
+      <c r="U36" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B37" s="9">
         <v>46167.556641689815</v>
@@ -4124,7 +4124,7 @@
         <v>46199.56372103009</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>25</v>
@@ -4148,7 +4148,7 @@
         <v>26</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4157,13 +4157,13 @@
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
-      <c r="U37" s="12" t="s">
-        <v>76</v>
+      <c r="U37" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B38" s="5">
         <v>46167.55686952546</v>
@@ -4175,16 +4175,16 @@
         <v>46195.930020127314</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46160</v>
@@ -4202,13 +4202,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q38" s="5">
         <v>46160</v>
@@ -4216,8 +4216,8 @@
       <c r="R38" s="5">
         <v>46183</v>
       </c>
-      <c r="S38" s="11" t="s">
-        <v>105</v>
+      <c r="S38" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -4228,7 +4228,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B39" s="9">
         <v>46167.556874270835</v>
@@ -4240,16 +4240,16 @@
         <v>46195.92806517361</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I39" s="9">
         <v>46160</v>
@@ -4267,13 +4267,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4283,13 +4283,13 @@
       <c r="T39" s="10">
         <v>0</v>
       </c>
-      <c r="U39" s="11" t="s">
-        <v>61</v>
+      <c r="U39" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B40" s="5">
         <v>46167.55687946759</v>
@@ -4301,16 +4301,16 @@
         <v>46195.92988494213</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I40" s="5">
         <v>46162</v>
@@ -4328,13 +4328,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4344,32 +4344,32 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="11" t="s">
-        <v>61</v>
+      <c r="U40" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B41" s="9">
         <v>46167.55696103009</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46219.16843181713</v>
+        <v>46220.1910684375</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I41" s="9">
         <v>46160</v>
@@ -4387,10 +4387,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4402,13 +4402,13 @@
         <v>46219</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
       </c>
-      <c r="U41" s="11" t="s">
-        <v>61</v>
+      <c r="U41" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4423,16 +4423,16 @@
         <v>46212.654553368055</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I42" s="5">
         <v>46161</v>
@@ -4450,10 +4450,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>145</v>
@@ -4482,10 +4482,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I43" s="9">
         <v>46171</v>
@@ -4503,10 +4503,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>148</v>
@@ -4558,13 +4558,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q44" s="5">
         <v>46192</v>
@@ -4572,8 +4572,8 @@
       <c r="R44" s="5">
         <v>46204</v>
       </c>
-      <c r="S44" s="11" t="s">
-        <v>105</v>
+      <c r="S44" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4626,7 +4626,7 @@
         <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>156</v>
@@ -4639,8 +4639,8 @@
       <c r="T45" s="10">
         <v>0</v>
       </c>
-      <c r="U45" s="11" t="s">
-        <v>61</v>
+      <c r="U45" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4700,8 +4700,8 @@
       <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="U46" s="11" t="s">
-        <v>61</v>
+      <c r="U46" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4745,7 +4745,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>162</v>
@@ -4759,8 +4759,8 @@
       <c r="R47" s="9">
         <v>46204</v>
       </c>
-      <c r="S47" s="11" t="s">
-        <v>105</v>
+      <c r="S47" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4783,7 +4783,7 @@
         <v>46199.56375667824</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4813,7 +4813,7 @@
         <v>161</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>164</v>
@@ -4868,7 +4868,7 @@
         <v>161</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>167</v>
@@ -4920,7 +4920,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>172</v>
@@ -4958,7 +4958,7 @@
         <v>46204.5950621875</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4988,7 +4988,7 @@
         <v>169</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>174</v>
@@ -5043,7 +5043,7 @@
         <v>169</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>177</v>
@@ -5148,7 +5148,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>184</v>
@@ -5162,8 +5162,8 @@
       <c r="R54" s="5">
         <v>46204</v>
       </c>
-      <c r="S54" s="11" t="s">
-        <v>105</v>
+      <c r="S54" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -5186,7 +5186,7 @@
         <v>46199.564400601856</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -5216,7 +5216,7 @@
         <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>186</v>
@@ -5271,7 +5271,7 @@
         <v>183</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>189</v>
@@ -5373,7 +5373,7 @@
         <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>197</v>
@@ -5384,8 +5384,8 @@
       <c r="R58" s="5">
         <v>46168</v>
       </c>
-      <c r="S58" s="11" t="s">
-        <v>105</v>
+      <c r="S58" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5449,8 +5449,8 @@
       <c r="R59" s="9">
         <v>46188</v>
       </c>
-      <c r="S59" s="11" t="s">
-        <v>105</v>
+      <c r="S59" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5473,7 +5473,7 @@
         <v>46190.1997147338</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5514,8 +5514,8 @@
       <c r="R60" s="5">
         <v>46189</v>
       </c>
-      <c r="S60" s="11" t="s">
-        <v>105</v>
+      <c r="S60" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5583,8 +5583,8 @@
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="11" t="s">
-        <v>61</v>
+      <c r="U61" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -6119,8 +6119,8 @@
       <c r="R71" s="9">
         <v>46206</v>
       </c>
-      <c r="S71" s="11" t="s">
-        <v>105</v>
+      <c r="S71" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -6184,8 +6184,8 @@
       <c r="R72" s="5">
         <v>46210</v>
       </c>
-      <c r="S72" s="11" t="s">
-        <v>105</v>
+      <c r="S72" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6249,8 +6249,8 @@
       <c r="R73" s="9">
         <v>46206</v>
       </c>
-      <c r="S73" s="11" t="s">
-        <v>105</v>
+      <c r="S73" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T73" s="10">
         <v>1</v>
@@ -6314,8 +6314,8 @@
       <c r="R74" s="5">
         <v>46210</v>
       </c>
-      <c r="S74" s="11" t="s">
-        <v>105</v>
+      <c r="S74" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6379,8 +6379,8 @@
       <c r="R75" s="9">
         <v>46206</v>
       </c>
-      <c r="S75" s="11" t="s">
-        <v>105</v>
+      <c r="S75" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6444,8 +6444,8 @@
       <c r="R76" s="5">
         <v>46210</v>
       </c>
-      <c r="S76" s="11" t="s">
-        <v>105</v>
+      <c r="S76" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6556,8 +6556,8 @@
       <c r="R78" s="5">
         <v>46213</v>
       </c>
-      <c r="S78" s="11" t="s">
-        <v>105</v>
+      <c r="S78" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46213.18677706018</v>
+        <v>46220.16910630787</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>265</v>
@@ -7059,14 +7059,14 @@
       <c r="R87" s="9">
         <v>46220</v>
       </c>
-      <c r="S87" s="12" t="s">
-        <v>143</v>
+      <c r="S87" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
-        <v>76</v>
+      <c r="U87" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46203.502887615745</v>
+        <v>46220.16910454861</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>211</v>
@@ -7560,14 +7560,14 @@
       <c r="R96" s="5">
         <v>46223</v>
       </c>
-      <c r="S96" s="12" t="s">
-        <v>143</v>
+      <c r="S96" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="12" t="s">
-        <v>76</v>
+      <c r="U96" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -8097,7 +8097,7 @@
         <v>223</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>291</v>
@@ -8108,14 +8108,14 @@
       <c r="R106" s="5">
         <v>46184</v>
       </c>
-      <c r="S106" s="11" t="s">
-        <v>105</v>
+      <c r="S106" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="12" t="s">
-        <v>76</v>
+      <c r="U106" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8130,7 +8130,7 @@
         <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -8160,7 +8160,7 @@
         <v>223</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>233</v>
@@ -8171,14 +8171,14 @@
       <c r="R107" s="9">
         <v>46167</v>
       </c>
-      <c r="S107" s="11" t="s">
-        <v>105</v>
+      <c r="S107" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="12" t="s">
-        <v>76</v>
+      <c r="U107" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -8193,7 +8193,7 @@
         <v>46189.87818384259</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8240,8 +8240,8 @@
       <c r="T108" s="6">
         <v>0</v>
       </c>
-      <c r="U108" s="12" t="s">
-        <v>76</v>
+      <c r="U108" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8303,8 +8303,8 @@
       <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="12" t="s">
-        <v>76</v>
+      <c r="U109" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46213.18677655092</v>
+        <v>46220.16910866898</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>59</v>
@@ -8360,14 +8360,14 @@
       <c r="R110" s="5">
         <v>46220</v>
       </c>
-      <c r="S110" s="12" t="s">
-        <v>143</v>
+      <c r="S110" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
       </c>
-      <c r="U110" s="11" t="s">
-        <v>61</v>
+      <c r="U110" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -8474,8 +8474,8 @@
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="11" t="s">
-        <v>61</v>
+      <c r="U112" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8953,8 +8953,8 @@
       <c r="T121" s="10">
         <v>0</v>
       </c>
-      <c r="U121" s="11" t="s">
-        <v>61</v>
+      <c r="U121" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -9422,8 +9422,8 @@
       <c r="T130" s="6">
         <v>0</v>
       </c>
-      <c r="U130" s="11" t="s">
-        <v>61</v>
+      <c r="U130" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9875,8 +9875,8 @@
       <c r="T139" s="10">
         <v>0</v>
       </c>
-      <c r="U139" s="11" t="s">
-        <v>61</v>
+      <c r="U139" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
@@ -10344,8 +10344,8 @@
       <c r="T148" s="6">
         <v>0</v>
       </c>
-      <c r="U148" s="11" t="s">
-        <v>61</v>
+      <c r="U148" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
@@ -10813,8 +10813,8 @@
       <c r="T157" s="10">
         <v>0</v>
       </c>
-      <c r="U157" s="11" t="s">
-        <v>61</v>
+      <c r="U157" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
@@ -11331,8 +11331,8 @@
       <c r="T167" s="10">
         <v>0</v>
       </c>
-      <c r="U167" s="11" t="s">
-        <v>61</v>
+      <c r="U167" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11771,7 +11771,7 @@
         <v>46167.742840844905</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11801,10 +11801,10 @@
         <v>387</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11824,7 +11824,7 @@
         <v>46167.742838136575</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11854,10 +11854,10 @@
         <v>387</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11877,7 +11877,7 @@
         <v>46167.742835763886</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -11907,10 +11907,10 @@
         <v>387</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -11930,7 +11930,7 @@
         <v>46167.74282516204</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
@@ -11960,10 +11960,10 @@
         <v>387</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11983,7 +11983,7 @@
         <v>46167.742824456014</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12013,10 +12013,10 @@
         <v>387</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12036,7 +12036,7 @@
         <v>46167.74282375</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
@@ -12066,10 +12066,10 @@
         <v>387</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12089,7 +12089,7 @@
         <v>46167.74282306713</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12119,10 +12119,10 @@
         <v>387</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12142,7 +12142,7 @@
         <v>46167.74282237269</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
@@ -12172,10 +12172,10 @@
         <v>387</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12240,8 +12240,8 @@
       <c r="T184" s="6">
         <v>0</v>
       </c>
-      <c r="U184" s="11" t="s">
-        <v>61</v>
+      <c r="U184" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
@@ -12648,7 +12648,7 @@
         <v>46167.74304366898</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
@@ -12676,10 +12676,10 @@
         <v>409</v>
       </c>
       <c r="O193" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P193" s="10" t="s">
         <v>64</v>
-      </c>
-      <c r="P193" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12699,7 +12699,7 @@
         <v>46167.743040671296</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -12727,10 +12727,10 @@
         <v>409</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12750,7 +12750,7 @@
         <v>46167.74303790509</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
@@ -12778,10 +12778,10 @@
         <v>409</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12801,7 +12801,7 @@
         <v>46167.743035231484</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -12829,10 +12829,10 @@
         <v>409</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12852,7 +12852,7 @@
         <v>46167.74302515046</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
@@ -12880,10 +12880,10 @@
         <v>409</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12903,7 +12903,7 @@
         <v>46167.74302446759</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -12931,10 +12931,10 @@
         <v>409</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -12954,7 +12954,7 @@
         <v>46167.74302380787</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
@@ -12982,10 +12982,10 @@
         <v>409</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q199" s="10"/>
       <c r="R199" s="10"/>
@@ -13005,7 +13005,7 @@
         <v>46167.74302313657</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13033,10 +13033,10 @@
         <v>409</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13103,8 +13103,8 @@
       <c r="T201" s="10">
         <v>0</v>
       </c>
-      <c r="U201" s="11" t="s">
-        <v>61</v>
+      <c r="U201" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
@@ -13543,7 +13543,7 @@
         <v>46167.74365560185</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>26</v>
@@ -13573,10 +13573,10 @@
         <v>430</v>
       </c>
       <c r="O210" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q210" s="6"/>
       <c r="R210" s="6"/>
@@ -13596,7 +13596,7 @@
         <v>46167.74365315972</v>
       </c>
       <c r="E211" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>26</v>
@@ -13626,10 +13626,10 @@
         <v>430</v>
       </c>
       <c r="O211" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P211" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q211" s="10"/>
       <c r="R211" s="10"/>
@@ -13649,7 +13649,7 @@
         <v>46167.74365077546</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>26</v>
@@ -13679,10 +13679,10 @@
         <v>430</v>
       </c>
       <c r="O212" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q212" s="6"/>
       <c r="R212" s="6"/>
@@ -13702,7 +13702,7 @@
         <v>46167.7436480787</v>
       </c>
       <c r="E213" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F213" s="10" t="s">
         <v>26</v>
@@ -13732,10 +13732,10 @@
         <v>430</v>
       </c>
       <c r="O213" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P213" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q213" s="10"/>
       <c r="R213" s="10"/>
@@ -13755,7 +13755,7 @@
         <v>46167.74363872685</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>26</v>
@@ -13785,10 +13785,10 @@
         <v>430</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q214" s="6"/>
       <c r="R214" s="6"/>
@@ -13808,7 +13808,7 @@
         <v>46167.74363802084</v>
       </c>
       <c r="E215" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>26</v>
@@ -13838,10 +13838,10 @@
         <v>430</v>
       </c>
       <c r="O215" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P215" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q215" s="10"/>
       <c r="R215" s="10"/>
@@ -13861,7 +13861,7 @@
         <v>46167.74363733796</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>26</v>
@@ -13891,7 +13891,7 @@
         <v>430</v>
       </c>
       <c r="O216" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P216" s="6" t="s">
         <v>450</v>
@@ -13914,7 +13914,7 @@
         <v>46167.743636666666</v>
       </c>
       <c r="E217" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>26</v>
@@ -13944,7 +13944,7 @@
         <v>430</v>
       </c>
       <c r="O217" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P217" s="10" t="s">
         <v>450</v>
@@ -14014,8 +14014,8 @@
       <c r="T218" s="6">
         <v>0</v>
       </c>
-      <c r="U218" s="11" t="s">
-        <v>61</v>
+      <c r="U218" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
@@ -14454,7 +14454,7 @@
         <v>46167.74382638889</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F227" s="10" t="s">
         <v>26</v>
@@ -14484,7 +14484,7 @@
         <v>453</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P227" s="10" t="s">
         <v>26</v>
@@ -14507,7 +14507,7 @@
         <v>46167.74382362269</v>
       </c>
       <c r="E228" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>26</v>
@@ -14537,7 +14537,7 @@
         <v>453</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P228" s="6" t="s">
         <v>26</v>
@@ -14560,7 +14560,7 @@
         <v>46167.74381421296</v>
       </c>
       <c r="E229" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F229" s="10" t="s">
         <v>26</v>
@@ -14590,7 +14590,7 @@
         <v>453</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P229" s="10" t="s">
         <v>26</v>
@@ -14613,7 +14613,7 @@
         <v>46167.74381306713</v>
       </c>
       <c r="E230" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>26</v>
@@ -14643,7 +14643,7 @@
         <v>453</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P230" s="6" t="s">
         <v>26</v>
@@ -14666,7 +14666,7 @@
         <v>46167.74380835648</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>26</v>
@@ -14696,7 +14696,7 @@
         <v>453</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P231" s="10" t="s">
         <v>26</v>
@@ -14719,7 +14719,7 @@
         <v>46167.74380726852</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>26</v>
@@ -14749,7 +14749,7 @@
         <v>453</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P232" s="6" t="s">
         <v>26</v>
@@ -14802,7 +14802,7 @@
         <v>453</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P233" s="10" t="s">
         <v>26</v>
@@ -14855,7 +14855,7 @@
         <v>453</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>26</v>
@@ -14972,8 +14972,8 @@
       <c r="T236" s="6">
         <v>0</v>
       </c>
-      <c r="U236" s="11" t="s">
-        <v>61</v>
+      <c r="U236" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
@@ -14994,10 +14994,10 @@
         <v>26</v>
       </c>
       <c r="G237" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H237" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I237" s="9">
         <v>46245</v>
@@ -15035,8 +15035,8 @@
       <c r="T237" s="10">
         <v>0</v>
       </c>
-      <c r="U237" s="11" t="s">
-        <v>61</v>
+      <c r="U237" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
@@ -15088,8 +15088,8 @@
       <c r="T238" s="6">
         <v>0</v>
       </c>
-      <c r="U238" s="11" t="s">
-        <v>61</v>
+      <c r="U238" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
@@ -15151,8 +15151,8 @@
       <c r="T239" s="10">
         <v>0</v>
       </c>
-      <c r="U239" s="11" t="s">
-        <v>61</v>
+      <c r="U239" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
@@ -15214,8 +15214,8 @@
       <c r="T240" s="6">
         <v>0</v>
       </c>
-      <c r="U240" s="11" t="s">
-        <v>61</v>
+      <c r="U240" s="12" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46220.16910630787</v>
+        <v>46221.17198219907</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>265</v>
@@ -7059,8 +7059,8 @@
       <c r="R87" s="9">
         <v>46220</v>
       </c>
-      <c r="S87" s="11" t="s">
-        <v>61</v>
+      <c r="S87" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46220.16910866898</v>
+        <v>46221.171982141204</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>59</v>
@@ -8360,8 +8360,8 @@
       <c r="R110" s="5">
         <v>46220</v>
       </c>
-      <c r="S110" s="11" t="s">
-        <v>61</v>
+      <c r="S110" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="489">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete  ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Generación OC Rodete  ot 4328 - 4330,Propuesta compras:</t>
@@ -3564,7 +3567,7 @@
         <v>46190.64114762731</v>
       </c>
       <c r="D28" s="5">
-        <v>46190.641165381945</v>
+        <v>46223.57338140046</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>100</v>
@@ -3573,9 +3576,11 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I28" s="5">
         <v>46156</v>
       </c>
@@ -3598,7 +3603,7 @@
         <v>85</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q28" s="5">
         <v>46156</v>
@@ -3618,7 +3623,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" s="9">
         <v>46167.556831423615</v>
@@ -3627,18 +3632,20 @@
         <v>46196.649080138886</v>
       </c>
       <c r="D29" s="9">
-        <v>46196.64909515047</v>
+        <v>46223.57337745371</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I29" s="9">
         <v>46190</v>
       </c>
@@ -3658,10 +3665,10 @@
         <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q29" s="9">
         <v>46190</v>
@@ -3670,7 +3677,7 @@
         <v>46191</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3681,7 +3688,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46167.55683648148</v>
@@ -3690,18 +3697,20 @@
         <v>46196.6496064699</v>
       </c>
       <c r="D30" s="5">
-        <v>46196.64962321759</v>
+        <v>46223.57337341435</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I30" s="5">
         <v>46190</v>
       </c>
@@ -3721,10 +3730,10 @@
         <v>92</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="5">
         <v>46190</v>
@@ -3733,7 +3742,7 @@
         <v>46191</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3744,7 +3753,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="9">
         <v>46167.55684075231</v>
@@ -3753,18 +3762,20 @@
         <v>46196.651088935185</v>
       </c>
       <c r="D31" s="9">
-        <v>46196.651105439814</v>
+        <v>46223.573370266204</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I31" s="9">
         <v>46190</v>
       </c>
@@ -3784,10 +3795,10 @@
         <v>92</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q31" s="9">
         <v>46190</v>
@@ -3796,7 +3807,7 @@
         <v>46191</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3807,7 +3818,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B32" s="5">
         <v>46167.55684506944</v>
@@ -3816,18 +3827,20 @@
         <v>46196.65187996528</v>
       </c>
       <c r="D32" s="5">
-        <v>46196.65189541667</v>
+        <v>46223.573365069446</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I32" s="5">
         <v>46190</v>
       </c>
@@ -3847,10 +3860,10 @@
         <v>92</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q32" s="5">
         <v>46190</v>
@@ -3859,7 +3872,7 @@
         <v>46191</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3870,7 +3883,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B33" s="9">
         <v>46167.55684913194</v>
@@ -3882,7 +3895,7 @@
         <v>46209.564447372686</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3915,7 +3928,7 @@
         <v>51</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q33" s="9">
         <v>46157</v>
@@ -3935,7 +3948,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B34" s="5">
         <v>46189.87339945602</v>
@@ -3947,7 +3960,7 @@
         <v>46190.643601261574</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -3988,7 +4001,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B35" s="9">
         <v>46189.874116527775</v>
@@ -3997,18 +4010,20 @@
         <v>46190.643571747685</v>
       </c>
       <c r="D35" s="9">
-        <v>46190.64358837963</v>
+        <v>46223.573449062504</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I35" s="9">
         <v>46160</v>
       </c>
@@ -4025,10 +4040,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4040,7 +4055,7 @@
         <v>46167</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -4051,7 +4066,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="5">
         <v>46189.87428425926</v>
@@ -4060,18 +4075,20 @@
         <v>46190.643442395834</v>
       </c>
       <c r="D36" s="5">
-        <v>46209.56394472222</v>
+        <v>46223.57344547454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I36" s="5">
         <v>46160</v>
       </c>
@@ -4088,13 +4105,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q36" s="5">
         <v>46160</v>
@@ -4103,7 +4120,7 @@
         <v>46167</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4114,7 +4131,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B37" s="9">
         <v>46167.556641689815</v>
@@ -4124,7 +4141,7 @@
         <v>46199.56372103009</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>25</v>
@@ -4148,7 +4165,7 @@
         <v>26</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4163,7 +4180,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B38" s="5">
         <v>46167.55686952546</v>
@@ -4175,16 +4192,16 @@
         <v>46195.930020127314</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I38" s="5">
         <v>46160</v>
@@ -4202,13 +4219,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q38" s="5">
         <v>46160</v>
@@ -4217,7 +4234,7 @@
         <v>46183</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -4228,7 +4245,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B39" s="9">
         <v>46167.556874270835</v>
@@ -4240,16 +4257,16 @@
         <v>46195.92806517361</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I39" s="9">
         <v>46160</v>
@@ -4267,13 +4284,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4289,7 +4306,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B40" s="5">
         <v>46167.55687946759</v>
@@ -4301,16 +4318,16 @@
         <v>46195.92988494213</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I40" s="5">
         <v>46162</v>
@@ -4328,13 +4345,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4350,7 +4367,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B41" s="9">
         <v>46167.55696103009</v>
@@ -4360,16 +4377,16 @@
         <v>46220.1910684375</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I41" s="9">
         <v>46160</v>
@@ -4387,10 +4404,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4402,7 +4419,7 @@
         <v>46219</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -4413,7 +4430,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B42" s="5">
         <v>46167.556965254626</v>
@@ -4423,16 +4440,16 @@
         <v>46212.654553368055</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I42" s="5">
         <v>46161</v>
@@ -4450,13 +4467,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4466,7 +4483,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B43" s="9">
         <v>46167.55696965278</v>
@@ -4476,16 +4493,16 @@
         <v>46219.16843491898</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I43" s="9">
         <v>46171</v>
@@ -4503,13 +4520,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4519,7 +4536,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B44" s="5">
         <v>46167.556973784725</v>
@@ -4531,16 +4548,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I44" s="5">
         <v>46192</v>
@@ -4558,13 +4575,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q44" s="5">
         <v>46192</v>
@@ -4573,7 +4590,7 @@
         <v>46204</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4584,7 +4601,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B45" s="9">
         <v>46167.556978611115</v>
@@ -4596,16 +4613,16 @@
         <v>46199.56362072917</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I45" s="9">
         <v>46192</v>
@@ -4623,13 +4640,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4645,7 +4662,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B46" s="5">
         <v>46167.55698368055</v>
@@ -4657,16 +4674,16 @@
         <v>46199.563687118054</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I46" s="5">
         <v>46196</v>
@@ -4684,13 +4701,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4706,7 +4723,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B47" s="9">
         <v>46167.556988842596</v>
@@ -4718,16 +4735,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I47" s="9">
         <v>46192</v>
@@ -4745,10 +4762,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4760,7 +4777,7 @@
         <v>46204</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4771,7 +4788,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
         <v>46167.556992708334</v>
@@ -4783,16 +4800,16 @@
         <v>46199.56375667824</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I48" s="5">
         <v>46192</v>
@@ -4810,13 +4827,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4826,7 +4843,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B49" s="9">
         <v>46167.5569971875</v>
@@ -4838,16 +4855,16 @@
         <v>46199.56447744213</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I49" s="9">
         <v>46196</v>
@@ -4865,13 +4882,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4881,7 +4898,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5">
         <v>46167.55700140046</v>
@@ -4893,16 +4910,16 @@
         <v>46204.59613972223</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4920,10 +4937,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4946,7 +4963,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B51" s="9">
         <v>46167.55700519676</v>
@@ -4958,16 +4975,16 @@
         <v>46204.5950621875</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -4985,13 +5002,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5001,7 +5018,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B52" s="5">
         <v>46167.557010034725</v>
@@ -5013,16 +5030,16 @@
         <v>46204.59515966436</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -5040,13 +5057,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5056,7 +5073,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
         <v>46167.55701476852</v>
@@ -5066,16 +5083,16 @@
         <v>46204.59516696759</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5093,10 +5110,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5109,7 +5126,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B54" s="5">
         <v>46167.55701769676</v>
@@ -5121,16 +5138,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I54" s="5">
         <v>46192</v>
@@ -5148,10 +5165,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5163,7 +5180,7 @@
         <v>46204</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -5174,7 +5191,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46167.557021678236</v>
@@ -5186,16 +5203,16 @@
         <v>46199.564400601856</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I55" s="9">
         <v>46192</v>
@@ -5213,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5229,7 +5246,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B56" s="5">
         <v>46167.55702634259</v>
@@ -5241,16 +5258,16 @@
         <v>46199.56458967592</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I56" s="5">
         <v>46196</v>
@@ -5268,13 +5285,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5284,7 +5301,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B57" s="9">
         <v>46167.55703671296</v>
@@ -5294,7 +5311,7 @@
         <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5318,7 +5335,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5331,7 +5348,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46167.557040520835</v>
@@ -5343,16 +5360,16 @@
         <v>46197.715067453704</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5370,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5385,7 +5402,7 @@
         <v>46168</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5396,7 +5413,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46167.557045856476</v>
@@ -5408,16 +5425,16 @@
         <v>46197.71510291667</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5435,13 +5452,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5450,7 +5467,7 @@
         <v>46188</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5461,7 +5478,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46167.5570519676</v>
@@ -5473,16 +5490,16 @@
         <v>46190.1997147338</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5500,13 +5517,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5515,7 +5532,7 @@
         <v>46189</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5526,7 +5543,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
@@ -5536,16 +5553,16 @@
         <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5563,10 +5580,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5589,7 +5606,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5599,16 +5616,16 @@
         <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5626,13 +5643,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5642,7 +5659,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5652,16 +5669,16 @@
         <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5679,13 +5696,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5695,7 +5712,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5705,16 +5722,16 @@
         <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5732,13 +5749,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5748,7 +5765,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5758,16 +5775,16 @@
         <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5785,13 +5802,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5801,7 +5818,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5811,16 +5828,16 @@
         <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5838,13 +5855,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5854,7 +5871,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5864,16 +5881,16 @@
         <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5891,13 +5908,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5907,7 +5924,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5917,16 +5934,16 @@
         <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5944,13 +5961,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5960,7 +5977,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5970,16 +5987,16 @@
         <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -5997,13 +6014,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -6013,7 +6030,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -6025,7 +6042,7 @@
         <v>46216.8019547338</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6049,7 +6066,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6066,7 +6083,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6078,16 +6095,16 @@
         <v>46216.686107546295</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6105,13 +6122,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6120,7 +6137,7 @@
         <v>46206</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -6131,7 +6148,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6143,16 +6160,16 @@
         <v>46216.802392673606</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6170,13 +6187,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6185,7 +6202,7 @@
         <v>46210</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6196,7 +6213,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6208,16 +6225,16 @@
         <v>46216.68612113426</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6235,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6250,7 +6267,7 @@
         <v>46206</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T73" s="10">
         <v>1</v>
@@ -6261,7 +6278,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6273,16 +6290,16 @@
         <v>46216.801934849536</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6300,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6315,7 +6332,7 @@
         <v>46210</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6326,7 +6343,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6338,16 +6355,16 @@
         <v>46216.68613528935</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6365,13 +6382,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6380,7 +6397,7 @@
         <v>46206</v>
       </c>
       <c r="S75" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6391,7 +6408,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6403,16 +6420,16 @@
         <v>46216.801944085644</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6430,13 +6447,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6445,7 +6462,7 @@
         <v>46210</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6456,7 +6473,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6466,7 +6483,7 @@
         <v>46203.50206653935</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6490,7 +6507,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6503,7 +6520,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6515,16 +6532,16 @@
         <v>46214.19770118056</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6542,13 +6559,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6557,7 +6574,7 @@
         <v>46213</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6568,7 +6585,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46167.557178229166</v>
@@ -6580,16 +6597,16 @@
         <v>46216.80193877315</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6607,13 +6624,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6623,7 +6640,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46167.55718505787</v>
@@ -6635,16 +6652,16 @@
         <v>46216.80193822917</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6662,13 +6679,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6678,7 +6695,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46167.629964050924</v>
@@ -6690,16 +6707,16 @@
         <v>46216.801934814815</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6717,13 +6734,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6733,7 +6750,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46167.6299746875</v>
@@ -6745,16 +6762,16 @@
         <v>46216.80193553241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6772,13 +6789,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6788,7 +6805,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B83" s="9">
         <v>46167.63011578703</v>
@@ -6800,16 +6817,16 @@
         <v>46216.80193606482</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6827,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6843,7 +6860,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46167.630126516204</v>
@@ -6855,16 +6872,16 @@
         <v>46216.801936585645</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6882,13 +6899,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6898,7 +6915,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B85" s="9">
         <v>46167.63145555556</v>
@@ -6910,16 +6927,16 @@
         <v>46216.801937083335</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6937,13 +6954,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6953,7 +6970,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
         <v>46167.631772685185</v>
@@ -6965,16 +6982,16 @@
         <v>46216.801937592594</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -6992,13 +7009,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7008,7 +7025,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B87" s="9">
         <v>46167.557190844906</v>
@@ -7018,16 +7035,16 @@
         <v>46221.17198219907</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -7045,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -7060,7 +7077,7 @@
         <v>46220</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -7071,7 +7088,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B88" s="5">
         <v>46167.557195092595</v>
@@ -7083,16 +7100,16 @@
         <v>46209.725033622686</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7110,13 +7127,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7126,7 +7143,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B89" s="9">
         <v>46167.557200995376</v>
@@ -7138,16 +7155,16 @@
         <v>46209.72516011574</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7165,13 +7182,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7181,7 +7198,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
         <v>46167.63214916667</v>
@@ -7193,16 +7210,16 @@
         <v>46209.725171666665</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7220,13 +7237,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7236,7 +7253,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B91" s="9">
         <v>46167.63219107639</v>
@@ -7248,16 +7265,16 @@
         <v>46209.72518666666</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7275,13 +7292,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7291,7 +7308,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B92" s="5">
         <v>46167.63220099537</v>
@@ -7303,16 +7320,16 @@
         <v>46209.725205462964</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7330,13 +7347,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7346,7 +7363,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B93" s="9">
         <v>46167.63220839121</v>
@@ -7356,16 +7373,16 @@
         <v>46220.16910454861</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7383,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7399,7 +7416,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B94" s="5">
         <v>46167.63225591435</v>
@@ -7411,16 +7428,16 @@
         <v>46203.50339560185</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7438,13 +7455,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7454,7 +7471,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B95" s="9">
         <v>46167.63226373843</v>
@@ -7466,16 +7483,16 @@
         <v>46203.50367474537</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7493,13 +7510,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7509,26 +7526,26 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B96" s="5">
         <v>46167.5572065625</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46216.20187390046</v>
+        <v>46223.16902545139</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7546,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7572,7 +7589,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B97" s="9">
         <v>46167.557210914354</v>
@@ -7584,16 +7601,16 @@
         <v>46209.725893599534</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7611,13 +7628,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7627,7 +7644,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B98" s="5">
         <v>46167.55721697917</v>
@@ -7639,16 +7656,16 @@
         <v>46209.725886851855</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7666,13 +7683,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7682,7 +7699,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B99" s="9">
         <v>46167.632342048615</v>
@@ -7694,16 +7711,16 @@
         <v>46209.72588194444</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7721,10 +7738,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7737,7 +7754,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B100" s="5">
         <v>46167.63235868055</v>
@@ -7749,16 +7766,16 @@
         <v>46209.72587559027</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7776,13 +7793,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7792,7 +7809,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B101" s="9">
         <v>46167.63236590278</v>
@@ -7804,16 +7821,16 @@
         <v>46209.725869594906</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7831,13 +7848,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7847,26 +7864,26 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B102" s="5">
         <v>46167.63237413194</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46167.7415103588</v>
+        <v>46223.16901707176</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7884,13 +7901,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7900,7 +7917,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B103" s="9">
         <v>46167.63244320602</v>
@@ -7912,16 +7929,16 @@
         <v>46209.7258571875</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7939,13 +7956,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7955,7 +7972,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B104" s="5">
         <v>46167.63245268518</v>
@@ -7967,16 +7984,16 @@
         <v>46209.725848692135</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -7994,13 +8011,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8010,7 +8027,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B105" s="9">
         <v>46167.55722248842</v>
@@ -8020,7 +8037,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -8044,7 +8061,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -8057,7 +8074,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B106" s="5">
         <v>46167.557225682875</v>
@@ -8067,16 +8084,16 @@
         <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -8094,13 +8111,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q106" s="5">
         <v>46184</v>
@@ -8109,7 +8126,7 @@
         <v>46184</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8120,7 +8137,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B107" s="9">
         <v>46167.557231493054</v>
@@ -8130,16 +8147,16 @@
         <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8157,13 +8174,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8172,7 +8189,7 @@
         <v>46167</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
@@ -8183,7 +8200,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B108" s="5">
         <v>46167.55723746528</v>
@@ -8193,16 +8210,16 @@
         <v>46189.87818384259</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8220,13 +8237,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q108" s="5">
         <v>46168</v>
@@ -8246,7 +8263,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B109" s="9">
         <v>46167.55724847222</v>
@@ -8256,16 +8273,16 @@
         <v>46204.59517594907</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8283,13 +8300,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q109" s="9">
         <v>46265</v>
@@ -8309,7 +8326,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B110" s="5">
         <v>46167.55725353009</v>
@@ -8325,10 +8342,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8346,13 +8363,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q110" s="5">
         <v>46220</v>
@@ -8361,7 +8378,7 @@
         <v>46220</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
@@ -8372,7 +8389,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B111" s="9">
         <v>46167.5572591088</v>
@@ -8382,7 +8399,7 @@
         <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8406,7 +8423,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8419,25 +8436,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B112" s="5">
         <v>46167.557262685186</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46212.62486408565</v>
+        <v>46223.57427424769</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I112" s="5">
         <v>46224</v>
       </c>
@@ -8454,13 +8473,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q112" s="5">
         <v>46224</v>
@@ -8468,8 +8487,8 @@
       <c r="R112" s="5">
         <v>46230</v>
       </c>
-      <c r="S112" s="7" t="s">
-        <v>33</v>
+      <c r="S112" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -8480,25 +8499,27 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B113" s="9">
         <v>46167.55727085649</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46209.725901666665</v>
+        <v>46223.57360364583</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I113" s="9">
         <v>46224</v>
       </c>
@@ -8515,10 +8536,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8531,25 +8552,27 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B114" s="5">
         <v>46167.55727532407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46209.72589265046</v>
+        <v>46223.57360296296</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I114" s="5">
         <v>46224</v>
       </c>
@@ -8566,10 +8589,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8582,7 +8605,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B115" s="9">
         <v>46167.632606053245</v>
@@ -8591,18 +8614,20 @@
         <v>46213.50676451389</v>
       </c>
       <c r="D115" s="9">
-        <v>46213.506766238424</v>
+        <v>46223.573618090275</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I115" s="9">
         <v>46224</v>
       </c>
@@ -8619,13 +8644,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8635,7 +8660,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B116" s="5">
         <v>46167.63261443287</v>
@@ -8644,18 +8669,20 @@
         <v>46213.50677003472</v>
       </c>
       <c r="D116" s="5">
-        <v>46213.506771631946</v>
+        <v>46223.57361446759</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I116" s="5">
         <v>46224</v>
       </c>
@@ -8672,13 +8699,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8688,7 +8715,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B117" s="9">
         <v>46167.63262241898</v>
@@ -8697,18 +8724,20 @@
         <v>46213.506775752314</v>
       </c>
       <c r="D117" s="9">
-        <v>46213.50677731482</v>
+        <v>46223.57361017361</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I117" s="9">
         <v>46224</v>
       </c>
@@ -8725,13 +8754,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8741,25 +8770,27 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B118" s="5">
         <v>46167.63263039352</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46167.74189655093</v>
+        <v>46223.573600034724</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I118" s="5">
         <v>46224</v>
       </c>
@@ -8776,13 +8807,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8792,7 +8823,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B119" s="9">
         <v>46167.63269008102</v>
@@ -8801,18 +8832,20 @@
         <v>46213.50678833333</v>
       </c>
       <c r="D119" s="9">
-        <v>46213.5067896875</v>
+        <v>46223.57359932871</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I119" s="9">
         <v>46224</v>
       </c>
@@ -8829,13 +8862,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8845,7 +8878,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B120" s="5">
         <v>46167.632698738424</v>
@@ -8854,18 +8887,20 @@
         <v>46213.50679619213</v>
       </c>
       <c r="D120" s="5">
-        <v>46213.50679762731</v>
+        <v>46223.57359854167</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I120" s="5">
         <v>46224</v>
       </c>
@@ -8882,13 +8917,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8898,25 +8933,27 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B121" s="9">
         <v>46167.55727960648</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46212.62488043982</v>
+        <v>46223.5742734838</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I121" s="9">
         <v>46231</v>
       </c>
@@ -8933,13 +8970,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q121" s="9">
         <v>46231</v>
@@ -8959,25 +8996,27 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B122" s="5">
         <v>46167.557284375</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46189.87510767361</v>
+        <v>46223.5737202662</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I122" s="5">
         <v>46231</v>
       </c>
@@ -8994,13 +9033,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9010,25 +9049,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B123" s="9">
         <v>46167.55729009259</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46189.87510009259</v>
+        <v>46223.573719583335</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I123" s="9">
         <v>46231</v>
       </c>
@@ -9045,13 +9086,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9061,25 +9102,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B124" s="5">
         <v>46167.6328130787</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46213.50676993055</v>
+        <v>46223.57371890046</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I124" s="5">
         <v>46231</v>
       </c>
@@ -9096,13 +9139,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9112,25 +9155,27 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B125" s="9">
         <v>46167.63283585648</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46213.50677655093</v>
+        <v>46223.57371819444</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I125" s="9">
         <v>46231</v>
       </c>
@@ -9147,13 +9192,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9163,25 +9208,27 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B126" s="5">
         <v>46167.63284336806</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46213.50678052084</v>
+        <v>46223.5737175463</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I126" s="5">
         <v>46231</v>
       </c>
@@ -9198,13 +9245,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9214,25 +9261,27 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B127" s="9">
         <v>46167.63285163195</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46189.87509177084</v>
+        <v>46223.57371685185</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I127" s="9">
         <v>46231</v>
       </c>
@@ -9249,13 +9298,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9265,25 +9314,27 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B128" s="5">
         <v>46167.63289178241</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46213.50679318287</v>
+        <v>46223.57371615741</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I128" s="5">
         <v>46231</v>
       </c>
@@ -9300,13 +9351,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9316,25 +9367,27 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B129" s="9">
         <v>46167.632899212964</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46213.50680238426</v>
+        <v>46223.57371547454</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I129" s="9">
         <v>46231</v>
       </c>
@@ -9351,13 +9404,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9367,25 +9420,27 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B130" s="5">
         <v>46167.55733736111</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46212.62489320602</v>
+        <v>46223.57427283565</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I130" s="5">
         <v>46232</v>
       </c>
@@ -9402,13 +9457,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q130" s="5">
         <v>46232</v>
@@ -9428,25 +9483,27 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B131" s="9">
         <v>46167.557343645836</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46189.87510797454</v>
+        <v>46223.573848125</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
         <v>46232</v>
@@ -9461,13 +9518,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9477,25 +9534,27 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B132" s="5">
         <v>46167.55735079861</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46189.87510071759</v>
+        <v>46223.57384737268</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
         <v>46232</v>
@@ -9510,13 +9569,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9526,25 +9585,27 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B133" s="9">
         <v>46167.63302359954</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46189.875093634255</v>
+        <v>46223.5738466551</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H133" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
         <v>46232</v>
@@ -9559,13 +9620,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9575,25 +9636,27 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B134" s="5">
         <v>46167.63303486111</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46189.8750941551</v>
+        <v>46223.573846018524</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
         <v>46232</v>
@@ -9608,13 +9671,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9624,25 +9687,27 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B135" s="9">
         <v>46167.633050648146</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46189.87509472222</v>
+        <v>46223.5738453588</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I135" s="10"/>
       <c r="J135" s="9">
         <v>46232</v>
@@ -9657,13 +9722,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9673,25 +9738,27 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B136" s="5">
         <v>46167.633060671295</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46189.87509519676</v>
+        <v>46223.573844687504</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
         <v>46232</v>
@@ -9706,13 +9773,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9722,25 +9789,27 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B137" s="9">
         <v>46167.633115185185</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46189.87509570602</v>
+        <v>46223.57384399306</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H137" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I137" s="10"/>
       <c r="J137" s="9">
         <v>46232</v>
@@ -9755,13 +9824,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9771,25 +9840,27 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B138" s="5">
         <v>46167.6331228125</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46189.87509615741</v>
+        <v>46223.57384329861</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H138" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
         <v>46232</v>
@@ -9804,13 +9875,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9820,25 +9891,27 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B139" s="9">
         <v>46167.557357488426</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46212.624909606486</v>
+        <v>46223.5742721875</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H139" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I139" s="9">
         <v>46233</v>
       </c>
@@ -9855,13 +9928,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q139" s="9">
         <v>46233</v>
@@ -9881,25 +9954,27 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B140" s="5">
         <v>46167.55736211805</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46189.877459745374</v>
+        <v>46223.573953645835</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H140" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I140" s="5">
         <v>46233</v>
       </c>
@@ -9916,13 +9991,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9932,25 +10007,27 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B141" s="9">
         <v>46167.55737267361</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46189.87746077546</v>
+        <v>46223.573953009254</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H141" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H141" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I141" s="9">
         <v>46233</v>
       </c>
@@ -9967,13 +10044,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9983,25 +10060,27 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B142" s="5">
         <v>46167.63325159722</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46189.877455671296</v>
+        <v>46223.57395239583</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H142" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I142" s="5">
         <v>46233</v>
       </c>
@@ -10018,13 +10097,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10034,25 +10113,27 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B143" s="9">
         <v>46167.63325929398</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46189.87745677083</v>
+        <v>46223.57395174769</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H143" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I143" s="9">
         <v>46233</v>
       </c>
@@ -10069,13 +10150,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10085,25 +10166,27 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B144" s="5">
         <v>46167.633274293985</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46189.87745732639</v>
+        <v>46223.57395109953</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H144" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I144" s="5">
         <v>46233</v>
       </c>
@@ -10120,13 +10203,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10136,25 +10219,27 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B145" s="9">
         <v>46167.633281875</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46189.877457916664</v>
+        <v>46223.57395048611</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H145" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I145" s="9">
         <v>46233</v>
       </c>
@@ -10171,13 +10256,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10187,25 +10272,27 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B146" s="5">
         <v>46167.63332260417</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46189.87745863426</v>
+        <v>46223.57394983796</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H146" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I146" s="5">
         <v>46233</v>
       </c>
@@ -10222,13 +10309,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10238,25 +10325,27 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B147" s="9">
         <v>46167.633331689816</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46189.87745917824</v>
+        <v>46223.57394920139</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H147" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I147" s="9">
         <v>46233</v>
       </c>
@@ -10273,13 +10362,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10289,25 +10378,27 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B148" s="5">
         <v>46167.557378287034</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46212.62492555556</v>
+        <v>46223.574271527774</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H148" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I148" s="5">
         <v>46234</v>
       </c>
@@ -10324,13 +10415,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q148" s="5">
         <v>46234</v>
@@ -10350,25 +10441,27 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B149" s="9">
         <v>46167.55738292824</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46167.742493136575</v>
+        <v>46223.57407541666</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H149" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I149" s="9">
         <v>46234</v>
       </c>
@@ -10385,13 +10478,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10401,25 +10494,27 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B150" s="5">
         <v>46167.5573883912</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46167.742490000004</v>
+        <v>46223.5740747338</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H150" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I150" s="5">
         <v>46234</v>
       </c>
@@ -10436,13 +10531,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10452,25 +10547,27 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B151" s="9">
         <v>46167.63341660879</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46167.74248716435</v>
+        <v>46223.57407407407</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H151" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I151" s="9">
         <v>46234</v>
       </c>
@@ -10487,13 +10584,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10503,25 +10600,27 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B152" s="5">
         <v>46167.63343371528</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46167.74248396991</v>
+        <v>46223.5740733912</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H152" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I152" s="5">
         <v>46234</v>
       </c>
@@ -10538,13 +10637,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10554,25 +10653,27 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B153" s="9">
         <v>46167.63344365741</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46167.742481134264</v>
+        <v>46223.57407268518</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H153" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H153" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I153" s="9">
         <v>46234</v>
       </c>
@@ -10589,13 +10690,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10605,25 +10706,27 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B154" s="5">
         <v>46167.63345188658</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46167.74247835648</v>
+        <v>46223.574072013886</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H154" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I154" s="5">
         <v>46234</v>
       </c>
@@ -10640,13 +10743,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10656,25 +10759,27 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B155" s="9">
         <v>46167.633506412036</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46167.74247142361</v>
+        <v>46223.57407130787</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H155" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I155" s="9">
         <v>46234</v>
       </c>
@@ -10691,13 +10796,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10707,25 +10812,27 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B156" s="5">
         <v>46167.63351399306</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46167.74247065972</v>
+        <v>46223.574070648145</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H156" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I156" s="5">
         <v>46234</v>
       </c>
@@ -10742,13 +10849,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10758,25 +10865,27 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B157" s="9">
         <v>46167.55739407407</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46212.624938865745</v>
+        <v>46223.57427081019</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H157" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H157" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I157" s="9">
         <v>46238</v>
       </c>
@@ -10793,13 +10902,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q157" s="9">
         <v>46238</v>
@@ -10819,25 +10928,27 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B158" s="5">
         <v>46167.55739920139</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46167.742638298616</v>
+        <v>46223.57418311342</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H158" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I158" s="5">
         <v>46238</v>
       </c>
@@ -10854,13 +10965,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10870,25 +10981,27 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B159" s="9">
         <v>46167.5574040162</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46167.74263541667</v>
+        <v>46223.574182488424</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H159" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I159" s="9">
         <v>46238</v>
       </c>
@@ -10905,13 +11018,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10921,25 +11034,27 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B160" s="5">
         <v>46167.633843206015</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46167.742632037036</v>
+        <v>46223.57418185185</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H160" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I160" s="5">
         <v>46238</v>
       </c>
@@ -10956,13 +11071,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10972,25 +11087,27 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B161" s="9">
         <v>46167.633849895836</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46167.742628935186</v>
+        <v>46223.57418118056</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H161" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I161" s="9">
         <v>46238</v>
       </c>
@@ -11007,13 +11124,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11023,25 +11140,27 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B162" s="5">
         <v>46167.63385791666</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46167.74262635417</v>
+        <v>46223.57418053241</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H162" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I162" s="5">
         <v>46238</v>
       </c>
@@ -11058,13 +11177,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11074,25 +11193,27 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B163" s="9">
         <v>46167.633867083336</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46167.74262355324</v>
+        <v>46223.57417979167</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H163" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H163" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I163" s="9">
         <v>46238</v>
       </c>
@@ -11109,13 +11230,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11125,25 +11246,27 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B164" s="5">
         <v>46167.63391234954</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46167.742617407406</v>
+        <v>46223.57417917824</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H164" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I164" s="5">
         <v>46238</v>
       </c>
@@ -11160,13 +11283,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11176,25 +11299,27 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B165" s="9">
         <v>46167.63392017361</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46167.74261677083</v>
+        <v>46223.57417856481</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H165" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H165" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I165" s="9">
         <v>46238</v>
       </c>
@@ -11211,13 +11336,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11227,7 +11352,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B166" s="5">
         <v>46167.557409201385</v>
@@ -11237,7 +11362,7 @@
         <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -11261,7 +11386,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11274,7 +11399,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B167" s="9">
         <v>46167.5574132176</v>
@@ -11284,16 +11409,16 @@
         <v>46212.62539956019</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I167" s="9">
         <v>46230</v>
@@ -11311,13 +11436,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q167" s="9">
         <v>46230</v>
@@ -11337,7 +11462,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B168" s="5">
         <v>46167.55742054398</v>
@@ -11347,16 +11472,16 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I168" s="5">
         <v>46239</v>
@@ -11374,13 +11499,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11390,7 +11515,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B169" s="9">
         <v>46167.557425520834</v>
@@ -11400,16 +11525,16 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I169" s="9">
         <v>46239</v>
@@ -11427,13 +11552,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11443,7 +11568,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B170" s="5">
         <v>46167.55743020833</v>
@@ -11453,16 +11578,16 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I170" s="5">
         <v>46239</v>
@@ -11480,13 +11605,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11496,7 +11621,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B171" s="9">
         <v>46167.557434918985</v>
@@ -11506,16 +11631,16 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I171" s="9">
         <v>46239</v>
@@ -11533,13 +11658,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11549,7 +11674,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B172" s="5">
         <v>46167.636403032404</v>
@@ -11559,16 +11684,16 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I172" s="5">
         <v>46239</v>
@@ -11586,13 +11711,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11602,7 +11727,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B173" s="9">
         <v>46167.63641173611</v>
@@ -11612,16 +11737,16 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I173" s="9">
         <v>46239</v>
@@ -11639,13 +11764,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11655,7 +11780,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B174" s="5">
         <v>46167.636428645834</v>
@@ -11665,16 +11790,16 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I174" s="5">
         <v>46239</v>
@@ -11692,13 +11817,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11708,7 +11833,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B175" s="9">
         <v>46167.636439849535</v>
@@ -11718,16 +11843,16 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I175" s="9">
         <v>46239</v>
@@ -11745,13 +11870,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11761,7 +11886,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B176" s="5">
         <v>46167.636677511575</v>
@@ -11777,10 +11902,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I176" s="5">
         <v>46230</v>
@@ -11798,7 +11923,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>64</v>
@@ -11814,7 +11939,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B177" s="9">
         <v>46167.63669306713</v>
@@ -11830,10 +11955,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I177" s="9">
         <v>46230</v>
@@ -11851,7 +11976,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>64</v>
@@ -11867,7 +11992,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B178" s="5">
         <v>46167.6367015162</v>
@@ -11883,10 +12008,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I178" s="5">
         <v>46230</v>
@@ -11904,7 +12029,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>64</v>
@@ -11920,7 +12045,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B179" s="9">
         <v>46167.6367112963</v>
@@ -11936,10 +12061,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I179" s="9">
         <v>46230</v>
@@ -11957,7 +12082,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>64</v>
@@ -11973,7 +12098,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B180" s="5">
         <v>46167.63672008102</v>
@@ -11989,10 +12114,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I180" s="5">
         <v>46230</v>
@@ -12010,7 +12135,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>64</v>
@@ -12026,7 +12151,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B181" s="9">
         <v>46167.636729247686</v>
@@ -12042,10 +12167,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I181" s="9">
         <v>46230</v>
@@ -12063,7 +12188,7 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O181" s="10" t="s">
         <v>64</v>
@@ -12079,7 +12204,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B182" s="5">
         <v>46167.63683603009</v>
@@ -12095,10 +12220,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I182" s="5">
         <v>46230</v>
@@ -12116,7 +12241,7 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>72</v>
@@ -12132,7 +12257,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B183" s="9">
         <v>46167.636846319445</v>
@@ -12148,10 +12273,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I183" s="9">
         <v>46230</v>
@@ -12169,7 +12294,7 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>72</v>
@@ -12185,25 +12310,27 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B184" s="5">
         <v>46167.55743945602</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46212.6251847338</v>
+        <v>46223.57466138889</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H184" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H184" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I184" s="5">
         <v>46170</v>
       </c>
@@ -12220,13 +12347,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q184" s="5">
         <v>46231</v>
@@ -12246,25 +12373,27 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B185" s="9">
         <v>46167.55744423611</v>
       </c>
       <c r="C185" s="10"/>
       <c r="D185" s="9">
-        <v>46167.74306620371</v>
+        <v>46223.57463326389</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H185" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H185" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I185" s="10"/>
       <c r="J185" s="9">
         <v>46240</v>
@@ -12279,13 +12408,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12295,25 +12424,27 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B186" s="5">
         <v>46167.55744884259</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46167.74306335648</v>
+        <v>46223.57463260417</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H186" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H186" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I186" s="6"/>
       <c r="J186" s="5">
         <v>46240</v>
@@ -12328,13 +12459,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12344,25 +12475,27 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B187" s="9">
         <v>46167.55745349537</v>
       </c>
       <c r="C187" s="10"/>
       <c r="D187" s="9">
-        <v>46167.74306008102</v>
+        <v>46223.57463199074</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H187" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H187" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I187" s="10"/>
       <c r="J187" s="9">
         <v>46240</v>
@@ -12377,13 +12510,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12393,25 +12526,27 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B188" s="5">
         <v>46167.55745777777</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46167.74305738426</v>
+        <v>46223.57463131944</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H188" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H188" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I188" s="6"/>
       <c r="J188" s="5">
         <v>46240</v>
@@ -12426,13 +12561,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12442,25 +12577,27 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B189" s="9">
         <v>46167.637670833334</v>
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46167.74305466435</v>
+        <v>46223.5746305787</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H189" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H189" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I189" s="10"/>
       <c r="J189" s="9">
         <v>46240</v>
@@ -12475,13 +12612,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12491,25 +12628,27 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B190" s="5">
         <v>46167.63768076389</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46167.743051990736</v>
+        <v>46223.574629849536</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H190" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H190" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I190" s="6"/>
       <c r="J190" s="5">
         <v>46240</v>
@@ -12524,13 +12663,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12540,25 +12679,27 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B191" s="9">
         <v>46167.637724016204</v>
       </c>
       <c r="C191" s="10"/>
       <c r="D191" s="9">
-        <v>46167.74304920139</v>
+        <v>46223.57462922454</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H191" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H191" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I191" s="10"/>
       <c r="J191" s="9">
         <v>46240</v>
@@ -12573,13 +12714,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12589,25 +12730,27 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B192" s="5">
         <v>46167.63773231482</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46167.743046574076</v>
+        <v>46223.574628622686</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H192" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
         <v>46240</v>
@@ -12622,13 +12765,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12638,14 +12781,14 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B193" s="9">
         <v>46167.63788011574</v>
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46167.74304366898</v>
+        <v>46223.574627974536</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>64</v>
@@ -12654,9 +12797,11 @@
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H193" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H193" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I193" s="9">
         <v>46231</v>
       </c>
@@ -12673,7 +12818,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>65</v>
@@ -12689,14 +12834,14 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B194" s="5">
         <v>46167.637888530095</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46167.743040671296</v>
+        <v>46223.57462730324</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>64</v>
@@ -12705,9 +12850,11 @@
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H194" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H194" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I194" s="5">
         <v>46231</v>
       </c>
@@ -12724,7 +12871,7 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O194" s="6" t="s">
         <v>64</v>
@@ -12740,14 +12887,14 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B195" s="9">
         <v>46167.63789722222</v>
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46167.74303790509</v>
+        <v>46223.57462666667</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>64</v>
@@ -12756,9 +12903,11 @@
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H195" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H195" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I195" s="9">
         <v>46231</v>
       </c>
@@ -12775,7 +12924,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O195" s="10" t="s">
         <v>64</v>
@@ -12791,14 +12940,14 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B196" s="5">
         <v>46167.63790768519</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46167.743035231484</v>
+        <v>46223.574626030095</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>64</v>
@@ -12807,9 +12956,11 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H196" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H196" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I196" s="5">
         <v>46231</v>
       </c>
@@ -12826,7 +12977,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>64</v>
@@ -12842,14 +12993,14 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B197" s="9">
         <v>46167.63791662037</v>
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46167.74302515046</v>
+        <v>46223.574625416666</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>64</v>
@@ -12858,9 +13009,11 @@
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H197" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H197" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I197" s="9">
         <v>46231</v>
       </c>
@@ -12877,7 +13030,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>64</v>
@@ -12893,14 +13046,14 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B198" s="5">
         <v>46167.637946689814</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46167.74302446759</v>
+        <v>46223.57462474537</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>64</v>
@@ -12909,9 +13062,11 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H198" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H198" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I198" s="5">
         <v>46231</v>
       </c>
@@ -12928,7 +13083,7 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>64</v>
@@ -12944,14 +13099,14 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B199" s="9">
         <v>46167.637995729165</v>
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46167.74302380787</v>
+        <v>46223.57462407407</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>72</v>
@@ -12960,9 +13115,11 @@
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H199" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="H199" s="10" t="s">
+        <v>101</v>
+      </c>
       <c r="I199" s="9">
         <v>46231</v>
       </c>
@@ -12979,7 +13136,7 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>72</v>
@@ -12995,14 +13152,14 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B200" s="5">
         <v>46167.63800420139</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46167.74302313657</v>
+        <v>46223.574623402776</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>72</v>
@@ -13011,9 +13168,11 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H200" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H200" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="I200" s="5">
         <v>46231</v>
       </c>
@@ -13030,7 +13189,7 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>72</v>
@@ -13046,7 +13205,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B201" s="9">
         <v>46167.55746224537</v>
@@ -13056,16 +13215,16 @@
         <v>46212.62523481481</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13083,13 +13242,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q201" s="9">
         <v>46241</v>
@@ -13109,7 +13268,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B202" s="5">
         <v>46167.55746689815</v>
@@ -13119,16 +13278,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13146,13 +13305,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13162,7 +13321,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B203" s="9">
         <v>46167.55747543981</v>
@@ -13172,16 +13331,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13199,13 +13358,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13215,7 +13374,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B204" s="5">
         <v>46167.557519270835</v>
@@ -13225,16 +13384,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13252,13 +13411,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13268,7 +13427,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B205" s="9">
         <v>46167.5575253125</v>
@@ -13278,16 +13437,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13305,13 +13464,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13321,7 +13480,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B206" s="5">
         <v>46167.6385715162</v>
@@ -13331,16 +13490,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13358,13 +13517,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13374,7 +13533,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B207" s="9">
         <v>46167.63857899306</v>
@@ -13384,16 +13543,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13411,13 +13570,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13427,7 +13586,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B208" s="5">
         <v>46167.638659930555</v>
@@ -13437,16 +13596,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13464,13 +13623,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13480,7 +13639,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B209" s="9">
         <v>46167.638666956016</v>
@@ -13490,16 +13649,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13517,13 +13676,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13533,7 +13692,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B210" s="5">
         <v>46167.6387090162</v>
@@ -13549,10 +13708,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13570,7 +13729,7 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>64</v>
@@ -13586,7 +13745,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B211" s="9">
         <v>46167.63871641204</v>
@@ -13602,10 +13761,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13623,7 +13782,7 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>64</v>
@@ -13639,7 +13798,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B212" s="5">
         <v>46167.638723599535</v>
@@ -13655,10 +13814,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13676,7 +13835,7 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>64</v>
@@ -13692,7 +13851,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B213" s="9">
         <v>46167.63873144676</v>
@@ -13708,10 +13867,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13729,7 +13888,7 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>64</v>
@@ -13745,7 +13904,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B214" s="5">
         <v>46167.6387405787</v>
@@ -13761,10 +13920,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13782,7 +13941,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>64</v>
@@ -13798,7 +13957,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B215" s="9">
         <v>46167.63874844907</v>
@@ -13814,10 +13973,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -13835,7 +13994,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>64</v>
@@ -13851,7 +14010,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B216" s="5">
         <v>46167.638756562505</v>
@@ -13867,10 +14026,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -13888,13 +14047,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -13904,7 +14063,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B217" s="9">
         <v>46167.63883428241</v>
@@ -13920,10 +14079,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -13941,13 +14100,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -13957,7 +14116,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B218" s="5">
         <v>46167.55752998842</v>
@@ -13967,16 +14126,16 @@
         <v>46212.62527664352</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -13994,13 +14153,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q218" s="5">
         <v>46244</v>
@@ -14020,7 +14179,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B219" s="9">
         <v>46167.55753614583</v>
@@ -14030,16 +14189,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14057,13 +14216,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14073,7 +14232,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B220" s="5">
         <v>46167.557540381946</v>
@@ -14083,16 +14242,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14110,13 +14269,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14126,7 +14285,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B221" s="9">
         <v>46167.557545069445</v>
@@ -14136,16 +14295,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14163,13 +14322,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14179,7 +14338,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B222" s="5">
         <v>46167.55754895833</v>
@@ -14189,16 +14348,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14216,13 +14375,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14232,7 +14391,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B223" s="9">
         <v>46167.63903770833</v>
@@ -14242,16 +14401,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14269,10 +14428,10 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14285,7 +14444,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B224" s="5">
         <v>46167.639049317135</v>
@@ -14295,16 +14454,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14322,10 +14481,10 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14338,7 +14497,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B225" s="9">
         <v>46167.639172118055</v>
@@ -14348,16 +14507,16 @@
         <v>46167.743832430555</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14375,10 +14534,10 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14391,7 +14550,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B226" s="5">
         <v>46167.63918146991</v>
@@ -14401,16 +14560,16 @@
         <v>46167.74382957176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14428,10 +14587,10 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14444,7 +14603,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B227" s="9">
         <v>46167.63922125</v>
@@ -14460,10 +14619,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14481,7 +14640,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>64</v>
@@ -14497,7 +14656,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B228" s="5">
         <v>46167.63923230324</v>
@@ -14513,10 +14672,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14534,7 +14693,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>64</v>
@@ -14550,7 +14709,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B229" s="9">
         <v>46167.63924049769</v>
@@ -14566,10 +14725,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14587,7 +14746,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>64</v>
@@ -14603,7 +14762,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B230" s="5">
         <v>46167.63924949074</v>
@@ -14619,10 +14778,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14640,7 +14799,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>64</v>
@@ -14656,7 +14815,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B231" s="9">
         <v>46167.639259375</v>
@@ -14672,10 +14831,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14693,7 +14852,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>64</v>
@@ -14709,7 +14868,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B232" s="5">
         <v>46167.63926804398</v>
@@ -14725,10 +14884,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14746,7 +14905,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>64</v>
@@ -14762,7 +14921,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B233" s="9">
         <v>46167.63935532408</v>
@@ -14772,16 +14931,16 @@
         <v>46167.74380655093</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14799,7 +14958,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>72</v>
@@ -14815,7 +14974,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B234" s="5">
         <v>46167.63936689815</v>
@@ -14825,16 +14984,16 @@
         <v>46167.74380591435</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>
@@ -14852,7 +15011,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>72</v>
@@ -14868,7 +15027,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B235" s="9">
         <v>46167.55755266204</v>
@@ -14878,7 +15037,7 @@
         <v>46167.73498962963</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>25</v>
@@ -14902,7 +15061,7 @@
         <v>26</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>26</v>
@@ -14915,7 +15074,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B236" s="5">
         <v>46167.55755585648</v>
@@ -14925,16 +15084,16 @@
         <v>46167.743865428245</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I236" s="5">
         <v>46245</v>
@@ -14952,13 +15111,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q236" s="5">
         <v>46245</v>
@@ -14978,7 +15137,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B237" s="9">
         <v>46167.55756052083</v>
@@ -14988,7 +15147,7 @@
         <v>46189.872060740745</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15015,13 +15174,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q237" s="9">
         <v>46245</v>
@@ -15041,7 +15200,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B238" s="5">
         <v>46167.557566296295</v>
@@ -15051,7 +15210,7 @@
         <v>46167.73546241898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>25</v>
@@ -15075,7 +15234,7 @@
         <v>26</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>26</v>
@@ -15094,7 +15253,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B239" s="9">
         <v>46167.55756988426</v>
@@ -15104,7 +15263,7 @@
         <v>46167.743959513886</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15131,13 +15290,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q239" s="9">
         <v>46245</v>
@@ -15157,7 +15316,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B240" s="5">
         <v>46167.557574895836</v>
@@ -15167,7 +15326,7 @@
         <v>46167.74395664352</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15194,13 +15353,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q240" s="5">
         <v>46254</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46223.16902545139</v>
+        <v>46224.20563896991</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>278</v>
@@ -7577,8 +7577,8 @@
       <c r="R96" s="5">
         <v>46223</v>
       </c>
-      <c r="S96" s="11" t="s">
-        <v>61</v>
+      <c r="S96" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46223.5742734838</v>
+        <v>46224.18997180555</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>317</v>
@@ -8984,8 +8984,8 @@
       <c r="R121" s="9">
         <v>46231</v>
       </c>
-      <c r="S121" s="7" t="s">
-        <v>33</v>
+      <c r="S121" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T121" s="10">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -832,7 +832,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 </t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -6529,7 +6529,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46214.19770118056</v>
+        <v>46224.878386111115</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>249</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -832,7 +832,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -6529,7 +6529,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46224.878386111115</v>
+        <v>46225.009614490744</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>249</v>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46223.57427283565</v>
+        <v>46225.195242835645</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>332</v>
@@ -9471,8 +9471,8 @@
       <c r="R130" s="5">
         <v>46232</v>
       </c>
-      <c r="S130" s="7" t="s">
-        <v>33</v>
+      <c r="S130" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -832,7 +832,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -6529,7 +6529,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46225.009614490744</v>
+        <v>46225.58945462963</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>249</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="490">
   <si>
     <t>50001554 - MAPIMI</t>
   </si>
@@ -379,6 +379,9 @@
     <t>propuesta nucleo rodete  ot 4328 - 4330</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -832,7 +835,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -3579,7 +3582,7 @@
         <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46156</v>
@@ -3603,7 +3606,7 @@
         <v>85</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q28" s="5">
         <v>46156</v>
@@ -3623,7 +3626,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" s="9">
         <v>46167.556831423615</v>
@@ -3635,7 +3638,7 @@
         <v>46223.57337745371</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3644,7 +3647,7 @@
         <v>101</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="9">
         <v>46190</v>
@@ -3665,10 +3668,10 @@
         <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q29" s="9">
         <v>46190</v>
@@ -3677,7 +3680,7 @@
         <v>46191</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3688,7 +3691,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46167.55683648148</v>
@@ -3700,7 +3703,7 @@
         <v>46223.57337341435</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3709,7 +3712,7 @@
         <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46190</v>
@@ -3730,10 +3733,10 @@
         <v>92</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="5">
         <v>46190</v>
@@ -3742,7 +3745,7 @@
         <v>46191</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3753,7 +3756,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46167.55684075231</v>
@@ -3765,7 +3768,7 @@
         <v>46223.573370266204</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3774,7 +3777,7 @@
         <v>101</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="9">
         <v>46190</v>
@@ -3795,10 +3798,10 @@
         <v>92</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q31" s="9">
         <v>46190</v>
@@ -3807,7 +3810,7 @@
         <v>46191</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3818,7 +3821,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46167.55684506944</v>
@@ -3830,7 +3833,7 @@
         <v>46223.573365069446</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3839,7 +3842,7 @@
         <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46190</v>
@@ -3860,10 +3863,10 @@
         <v>92</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q32" s="5">
         <v>46190</v>
@@ -3872,7 +3875,7 @@
         <v>46191</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3883,7 +3886,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B33" s="9">
         <v>46167.55684913194</v>
@@ -3895,7 +3898,7 @@
         <v>46209.564447372686</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3928,7 +3931,7 @@
         <v>51</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="9">
         <v>46157</v>
@@ -3948,7 +3951,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" s="5">
         <v>46189.87339945602</v>
@@ -3960,7 +3963,7 @@
         <v>46190.643601261574</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -4001,7 +4004,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="9">
         <v>46189.874116527775</v>
@@ -4013,7 +4016,7 @@
         <v>46223.573449062504</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -4022,7 +4025,7 @@
         <v>101</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I35" s="9">
         <v>46160</v>
@@ -4040,10 +4043,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4055,7 +4058,7 @@
         <v>46167</v>
       </c>
       <c r="S35" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -4066,7 +4069,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B36" s="5">
         <v>46189.87428425926</v>
@@ -4078,7 +4081,7 @@
         <v>46223.57344547454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -4087,7 +4090,7 @@
         <v>101</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I36" s="5">
         <v>46160</v>
@@ -4105,13 +4108,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q36" s="5">
         <v>46160</v>
@@ -4120,7 +4123,7 @@
         <v>46167</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4131,7 +4134,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B37" s="9">
         <v>46167.556641689815</v>
@@ -4141,7 +4144,7 @@
         <v>46199.56372103009</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>25</v>
@@ -4165,7 +4168,7 @@
         <v>26</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4180,7 +4183,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B38" s="5">
         <v>46167.55686952546</v>
@@ -4192,16 +4195,16 @@
         <v>46195.930020127314</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46160</v>
@@ -4219,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q38" s="5">
         <v>46160</v>
@@ -4234,7 +4237,7 @@
         <v>46183</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -4245,7 +4248,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B39" s="9">
         <v>46167.556874270835</v>
@@ -4257,16 +4260,16 @@
         <v>46195.92806517361</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I39" s="9">
         <v>46160</v>
@@ -4284,13 +4287,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4306,7 +4309,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B40" s="5">
         <v>46167.55687946759</v>
@@ -4318,16 +4321,16 @@
         <v>46195.92988494213</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I40" s="5">
         <v>46162</v>
@@ -4345,13 +4348,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4367,7 +4370,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B41" s="9">
         <v>46167.55696103009</v>
@@ -4377,16 +4380,16 @@
         <v>46220.1910684375</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I41" s="9">
         <v>46160</v>
@@ -4404,10 +4407,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4419,7 +4422,7 @@
         <v>46219</v>
       </c>
       <c r="S41" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
@@ -4430,7 +4433,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B42" s="5">
         <v>46167.556965254626</v>
@@ -4440,16 +4443,16 @@
         <v>46212.654553368055</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I42" s="5">
         <v>46161</v>
@@ -4467,13 +4470,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4483,7 +4486,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B43" s="9">
         <v>46167.55696965278</v>
@@ -4493,16 +4496,16 @@
         <v>46219.16843491898</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I43" s="9">
         <v>46171</v>
@@ -4520,13 +4523,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4536,7 +4539,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B44" s="5">
         <v>46167.556973784725</v>
@@ -4548,16 +4551,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46192</v>
@@ -4575,13 +4578,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q44" s="5">
         <v>46192</v>
@@ -4590,7 +4593,7 @@
         <v>46204</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4601,7 +4604,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B45" s="9">
         <v>46167.556978611115</v>
@@ -4613,16 +4616,16 @@
         <v>46199.56362072917</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I45" s="9">
         <v>46192</v>
@@ -4640,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4662,7 +4665,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B46" s="5">
         <v>46167.55698368055</v>
@@ -4674,16 +4677,16 @@
         <v>46199.563687118054</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46196</v>
@@ -4701,13 +4704,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4723,7 +4726,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B47" s="9">
         <v>46167.556988842596</v>
@@ -4735,16 +4738,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I47" s="9">
         <v>46192</v>
@@ -4762,10 +4765,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4777,7 +4780,7 @@
         <v>46204</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4788,7 +4791,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B48" s="5">
         <v>46167.556992708334</v>
@@ -4800,16 +4803,16 @@
         <v>46199.56375667824</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I48" s="5">
         <v>46192</v>
@@ -4827,13 +4830,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4843,7 +4846,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B49" s="9">
         <v>46167.5569971875</v>
@@ -4855,16 +4858,16 @@
         <v>46199.56447744213</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I49" s="9">
         <v>46196</v>
@@ -4882,13 +4885,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4898,7 +4901,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>46167.55700140046</v>
@@ -4910,16 +4913,16 @@
         <v>46204.59613972223</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4937,10 +4940,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4963,7 +4966,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" s="9">
         <v>46167.55700519676</v>
@@ -4975,16 +4978,16 @@
         <v>46204.5950621875</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -5002,13 +5005,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5018,7 +5021,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B52" s="5">
         <v>46167.557010034725</v>
@@ -5030,16 +5033,16 @@
         <v>46204.59515966436</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -5057,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5073,7 +5076,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B53" s="9">
         <v>46167.55701476852</v>
@@ -5083,16 +5086,16 @@
         <v>46204.59516696759</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5110,10 +5113,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" s="5">
         <v>46167.55701769676</v>
@@ -5138,16 +5141,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I54" s="5">
         <v>46192</v>
@@ -5165,10 +5168,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5180,7 +5183,7 @@
         <v>46204</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -5191,7 +5194,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" s="9">
         <v>46167.557021678236</v>
@@ -5203,16 +5206,16 @@
         <v>46199.564400601856</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I55" s="9">
         <v>46192</v>
@@ -5230,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B56" s="5">
         <v>46167.55702634259</v>
@@ -5258,16 +5261,16 @@
         <v>46199.56458967592</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I56" s="5">
         <v>46196</v>
@@ -5285,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5301,7 +5304,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B57" s="9">
         <v>46167.55703671296</v>
@@ -5311,7 +5314,7 @@
         <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5335,7 +5338,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5348,7 +5351,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46167.557040520835</v>
@@ -5360,16 +5363,16 @@
         <v>46197.715067453704</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5387,13 +5390,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5402,7 +5405,7 @@
         <v>46168</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5413,7 +5416,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46167.557045856476</v>
@@ -5425,16 +5428,16 @@
         <v>46197.71510291667</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5452,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5467,7 +5470,7 @@
         <v>46188</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5478,7 +5481,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46167.5570519676</v>
@@ -5490,16 +5493,16 @@
         <v>46190.1997147338</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5517,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5532,7 +5535,7 @@
         <v>46189</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
@@ -5553,16 +5556,16 @@
         <v>46167.740869988425</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5580,10 +5583,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5606,7 +5609,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5616,16 +5619,16 @@
         <v>46167.74085901621</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5643,13 +5646,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5669,16 +5672,16 @@
         <v>46167.74085574074</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5696,13 +5699,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5712,7 +5715,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5722,16 +5725,16 @@
         <v>46167.74085291667</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5749,13 +5752,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5765,7 +5768,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5775,16 +5778,16 @@
         <v>46167.74085050926</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5802,13 +5805,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5818,7 +5821,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5828,16 +5831,16 @@
         <v>46167.74084565972</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5855,13 +5858,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5871,7 +5874,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5881,16 +5884,16 @@
         <v>46167.74084013889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5908,13 +5911,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5924,7 +5927,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5934,16 +5937,16 @@
         <v>46167.740839074075</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5961,13 +5964,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5977,7 +5980,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5987,16 +5990,16 @@
         <v>46167.740838356476</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -6014,13 +6017,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -6030,7 +6033,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -6042,7 +6045,7 @@
         <v>46216.8019547338</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6066,7 +6069,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6083,7 +6086,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6095,16 +6098,16 @@
         <v>46216.686107546295</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6122,13 +6125,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6137,7 +6140,7 @@
         <v>46206</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -6148,7 +6151,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6160,16 +6163,16 @@
         <v>46216.802392673606</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6187,13 +6190,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6202,7 +6205,7 @@
         <v>46210</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6213,7 +6216,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6225,16 +6228,16 @@
         <v>46216.68612113426</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6252,13 +6255,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6267,7 +6270,7 @@
         <v>46206</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T73" s="10">
         <v>1</v>
@@ -6278,7 +6281,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6290,16 +6293,16 @@
         <v>46216.801934849536</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6317,13 +6320,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6332,7 +6335,7 @@
         <v>46210</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6343,7 +6346,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6355,16 +6358,16 @@
         <v>46216.68613528935</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6382,13 +6385,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6397,7 +6400,7 @@
         <v>46206</v>
       </c>
       <c r="S75" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6408,7 +6411,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6420,16 +6423,16 @@
         <v>46216.801944085644</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6447,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6462,7 +6465,7 @@
         <v>46210</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6473,7 +6476,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6483,7 +6486,7 @@
         <v>46203.50206653935</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6507,7 +6510,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6520,7 +6523,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6529,19 +6532,19 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46225.58945462963</v>
+        <v>46225.86189571759</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6559,13 +6562,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6574,7 +6577,7 @@
         <v>46213</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6585,7 +6588,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
         <v>46167.557178229166</v>
@@ -6597,16 +6600,16 @@
         <v>46216.80193877315</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6624,13 +6627,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6640,7 +6643,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46167.55718505787</v>
@@ -6652,16 +6655,16 @@
         <v>46216.80193822917</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6679,13 +6682,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6695,7 +6698,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46167.629964050924</v>
@@ -6707,16 +6710,16 @@
         <v>46216.801934814815</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6734,13 +6737,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6750,7 +6753,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46167.6299746875</v>
@@ -6762,16 +6765,16 @@
         <v>46216.80193553241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6789,13 +6792,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6805,7 +6808,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46167.63011578703</v>
@@ -6817,16 +6820,16 @@
         <v>46216.80193606482</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6844,13 +6847,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6860,7 +6863,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46167.630126516204</v>
@@ -6872,16 +6875,16 @@
         <v>46216.801936585645</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6899,13 +6902,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6915,7 +6918,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="9">
         <v>46167.63145555556</v>
@@ -6927,16 +6930,16 @@
         <v>46216.801937083335</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6954,13 +6957,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6970,7 +6973,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46167.631772685185</v>
@@ -6982,16 +6985,16 @@
         <v>46216.801937592594</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -7009,13 +7012,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7025,7 +7028,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B87" s="9">
         <v>46167.557190844906</v>
@@ -7035,16 +7038,16 @@
         <v>46221.17198219907</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -7062,13 +7065,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -7077,7 +7080,7 @@
         <v>46220</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -7088,7 +7091,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B88" s="5">
         <v>46167.557195092595</v>
@@ -7100,16 +7103,16 @@
         <v>46209.725033622686</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7127,13 +7130,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7143,7 +7146,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B89" s="9">
         <v>46167.557200995376</v>
@@ -7155,16 +7158,16 @@
         <v>46209.72516011574</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7182,13 +7185,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7198,7 +7201,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B90" s="5">
         <v>46167.63214916667</v>
@@ -7210,16 +7213,16 @@
         <v>46209.725171666665</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7237,13 +7240,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B91" s="9">
         <v>46167.63219107639</v>
@@ -7265,16 +7268,16 @@
         <v>46209.72518666666</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7292,13 +7295,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7308,7 +7311,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B92" s="5">
         <v>46167.63220099537</v>
@@ -7320,16 +7323,16 @@
         <v>46209.725205462964</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7347,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7363,7 +7366,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B93" s="9">
         <v>46167.63220839121</v>
@@ -7373,16 +7376,16 @@
         <v>46220.16910454861</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7400,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7416,7 +7419,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B94" s="5">
         <v>46167.63225591435</v>
@@ -7428,16 +7431,16 @@
         <v>46203.50339560185</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7455,13 +7458,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7471,7 +7474,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B95" s="9">
         <v>46167.63226373843</v>
@@ -7483,16 +7486,16 @@
         <v>46203.50367474537</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7510,13 +7513,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7526,7 +7529,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B96" s="5">
         <v>46167.5572065625</v>
@@ -7536,16 +7539,16 @@
         <v>46224.20563896991</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7563,13 +7566,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7578,7 +7581,7 @@
         <v>46223</v>
       </c>
       <c r="S96" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
@@ -7589,7 +7592,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B97" s="9">
         <v>46167.557210914354</v>
@@ -7601,16 +7604,16 @@
         <v>46209.725893599534</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7628,13 +7631,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7644,7 +7647,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B98" s="5">
         <v>46167.55721697917</v>
@@ -7656,16 +7659,16 @@
         <v>46209.725886851855</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7683,13 +7686,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7699,7 +7702,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B99" s="9">
         <v>46167.632342048615</v>
@@ -7711,16 +7714,16 @@
         <v>46209.72588194444</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7738,10 +7741,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7754,7 +7757,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B100" s="5">
         <v>46167.63235868055</v>
@@ -7766,16 +7769,16 @@
         <v>46209.72587559027</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7793,13 +7796,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7809,7 +7812,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B101" s="9">
         <v>46167.63236590278</v>
@@ -7821,16 +7824,16 @@
         <v>46209.725869594906</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7848,13 +7851,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7864,7 +7867,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B102" s="5">
         <v>46167.63237413194</v>
@@ -7874,16 +7877,16 @@
         <v>46223.16901707176</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7901,13 +7904,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7917,7 +7920,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B103" s="9">
         <v>46167.63244320602</v>
@@ -7929,16 +7932,16 @@
         <v>46209.7258571875</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7956,13 +7959,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7972,7 +7975,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B104" s="5">
         <v>46167.63245268518</v>
@@ -7984,16 +7987,16 @@
         <v>46209.725848692135</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -8011,13 +8014,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8027,7 +8030,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B105" s="9">
         <v>46167.55722248842</v>
@@ -8037,7 +8040,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -8061,7 +8064,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -8074,7 +8077,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B106" s="5">
         <v>46167.557225682875</v>
@@ -8084,16 +8087,16 @@
         <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -8111,13 +8114,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q106" s="5">
         <v>46184</v>
@@ -8126,7 +8129,7 @@
         <v>46184</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -8137,7 +8140,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B107" s="9">
         <v>46167.557231493054</v>
@@ -8147,16 +8150,16 @@
         <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8174,13 +8177,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8189,7 +8192,7 @@
         <v>46167</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
@@ -8200,7 +8203,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46167.55723746528</v>
@@ -8210,16 +8213,16 @@
         <v>46189.87818384259</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8237,13 +8240,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q108" s="5">
         <v>46168</v>
@@ -8263,7 +8266,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B109" s="9">
         <v>46167.55724847222</v>
@@ -8273,16 +8276,16 @@
         <v>46204.59517594907</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8300,13 +8303,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q109" s="9">
         <v>46265</v>
@@ -8326,7 +8329,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46167.55725353009</v>
@@ -8342,10 +8345,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8363,13 +8366,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q110" s="5">
         <v>46220</v>
@@ -8378,7 +8381,7 @@
         <v>46220</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
@@ -8389,7 +8392,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B111" s="9">
         <v>46167.5572591088</v>
@@ -8399,7 +8402,7 @@
         <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8423,7 +8426,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8436,7 +8439,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B112" s="5">
         <v>46167.557262685186</v>
@@ -8446,7 +8449,7 @@
         <v>46223.57427424769</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8455,7 +8458,7 @@
         <v>101</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I112" s="5">
         <v>46224</v>
@@ -8473,13 +8476,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q112" s="5">
         <v>46224</v>
@@ -8499,7 +8502,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B113" s="9">
         <v>46167.55727085649</v>
@@ -8509,7 +8512,7 @@
         <v>46223.57360364583</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8518,7 +8521,7 @@
         <v>101</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I113" s="9">
         <v>46224</v>
@@ -8536,10 +8539,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8552,7 +8555,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B114" s="5">
         <v>46167.55727532407</v>
@@ -8562,7 +8565,7 @@
         <v>46223.57360296296</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8571,7 +8574,7 @@
         <v>101</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I114" s="5">
         <v>46224</v>
@@ -8589,10 +8592,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8605,7 +8608,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B115" s="9">
         <v>46167.632606053245</v>
@@ -8617,7 +8620,7 @@
         <v>46223.573618090275</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8626,7 +8629,7 @@
         <v>101</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I115" s="9">
         <v>46224</v>
@@ -8644,13 +8647,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8660,7 +8663,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46167.63261443287</v>
@@ -8672,7 +8675,7 @@
         <v>46223.57361446759</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8681,7 +8684,7 @@
         <v>101</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I116" s="5">
         <v>46224</v>
@@ -8699,13 +8702,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8715,7 +8718,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B117" s="9">
         <v>46167.63262241898</v>
@@ -8727,7 +8730,7 @@
         <v>46223.57361017361</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8736,7 +8739,7 @@
         <v>101</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I117" s="9">
         <v>46224</v>
@@ -8754,13 +8757,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8770,7 +8773,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B118" s="5">
         <v>46167.63263039352</v>
@@ -8780,7 +8783,7 @@
         <v>46223.573600034724</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8789,7 +8792,7 @@
         <v>101</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I118" s="5">
         <v>46224</v>
@@ -8807,13 +8810,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8823,7 +8826,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B119" s="9">
         <v>46167.63269008102</v>
@@ -8835,7 +8838,7 @@
         <v>46223.57359932871</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8844,7 +8847,7 @@
         <v>101</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I119" s="9">
         <v>46224</v>
@@ -8862,13 +8865,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8878,7 +8881,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B120" s="5">
         <v>46167.632698738424</v>
@@ -8890,7 +8893,7 @@
         <v>46223.57359854167</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8899,7 +8902,7 @@
         <v>101</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I120" s="5">
         <v>46224</v>
@@ -8917,13 +8920,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8933,7 +8936,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B121" s="9">
         <v>46167.55727960648</v>
@@ -8943,7 +8946,7 @@
         <v>46224.18997180555</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8952,7 +8955,7 @@
         <v>101</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I121" s="9">
         <v>46231</v>
@@ -8970,13 +8973,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q121" s="9">
         <v>46231</v>
@@ -8996,7 +8999,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B122" s="5">
         <v>46167.557284375</v>
@@ -9006,7 +9009,7 @@
         <v>46223.5737202662</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9015,7 +9018,7 @@
         <v>101</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I122" s="5">
         <v>46231</v>
@@ -9033,13 +9036,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9049,7 +9052,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B123" s="9">
         <v>46167.55729009259</v>
@@ -9059,7 +9062,7 @@
         <v>46223.573719583335</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9068,7 +9071,7 @@
         <v>101</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I123" s="9">
         <v>46231</v>
@@ -9086,13 +9089,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9102,7 +9105,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B124" s="5">
         <v>46167.6328130787</v>
@@ -9112,7 +9115,7 @@
         <v>46223.57371890046</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9121,7 +9124,7 @@
         <v>101</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I124" s="5">
         <v>46231</v>
@@ -9139,13 +9142,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9155,7 +9158,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B125" s="9">
         <v>46167.63283585648</v>
@@ -9165,7 +9168,7 @@
         <v>46223.57371819444</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9174,7 +9177,7 @@
         <v>101</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I125" s="9">
         <v>46231</v>
@@ -9192,13 +9195,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9208,7 +9211,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B126" s="5">
         <v>46167.63284336806</v>
@@ -9218,7 +9221,7 @@
         <v>46223.5737175463</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9227,7 +9230,7 @@
         <v>101</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I126" s="5">
         <v>46231</v>
@@ -9245,13 +9248,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9261,7 +9264,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B127" s="9">
         <v>46167.63285163195</v>
@@ -9271,7 +9274,7 @@
         <v>46223.57371685185</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9280,7 +9283,7 @@
         <v>101</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I127" s="9">
         <v>46231</v>
@@ -9298,13 +9301,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9314,7 +9317,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B128" s="5">
         <v>46167.63289178241</v>
@@ -9324,7 +9327,7 @@
         <v>46223.57371615741</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9333,7 +9336,7 @@
         <v>101</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I128" s="5">
         <v>46231</v>
@@ -9351,13 +9354,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9367,7 +9370,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B129" s="9">
         <v>46167.632899212964</v>
@@ -9377,7 +9380,7 @@
         <v>46223.57371547454</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9386,7 +9389,7 @@
         <v>101</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I129" s="9">
         <v>46231</v>
@@ -9404,13 +9407,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9420,7 +9423,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B130" s="5">
         <v>46167.55733736111</v>
@@ -9430,7 +9433,7 @@
         <v>46225.195242835645</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9439,7 +9442,7 @@
         <v>101</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I130" s="5">
         <v>46232</v>
@@ -9457,13 +9460,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q130" s="5">
         <v>46232</v>
@@ -9483,7 +9486,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B131" s="9">
         <v>46167.557343645836</v>
@@ -9493,7 +9496,7 @@
         <v>46223.573848125</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9502,7 +9505,7 @@
         <v>101</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I131" s="10"/>
       <c r="J131" s="9">
@@ -9518,13 +9521,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9534,7 +9537,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B132" s="5">
         <v>46167.55735079861</v>
@@ -9544,7 +9547,7 @@
         <v>46223.57384737268</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9553,7 +9556,7 @@
         <v>101</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9569,13 +9572,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9585,7 +9588,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B133" s="9">
         <v>46167.63302359954</v>
@@ -9595,7 +9598,7 @@
         <v>46223.5738466551</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9604,7 +9607,7 @@
         <v>101</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I133" s="10"/>
       <c r="J133" s="9">
@@ -9620,13 +9623,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9636,7 +9639,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B134" s="5">
         <v>46167.63303486111</v>
@@ -9646,7 +9649,7 @@
         <v>46223.573846018524</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9655,7 +9658,7 @@
         <v>101</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9671,13 +9674,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9687,7 +9690,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B135" s="9">
         <v>46167.633050648146</v>
@@ -9697,7 +9700,7 @@
         <v>46223.5738453588</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9706,7 +9709,7 @@
         <v>101</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I135" s="10"/>
       <c r="J135" s="9">
@@ -9722,13 +9725,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9738,7 +9741,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B136" s="5">
         <v>46167.633060671295</v>
@@ -9748,7 +9751,7 @@
         <v>46223.573844687504</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9757,7 +9760,7 @@
         <v>101</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9773,13 +9776,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9789,7 +9792,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B137" s="9">
         <v>46167.633115185185</v>
@@ -9799,7 +9802,7 @@
         <v>46223.57384399306</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9808,7 +9811,7 @@
         <v>101</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I137" s="10"/>
       <c r="J137" s="9">
@@ -9824,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9840,7 +9843,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B138" s="5">
         <v>46167.6331228125</v>
@@ -9850,7 +9853,7 @@
         <v>46223.57384329861</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9859,7 +9862,7 @@
         <v>101</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9875,13 +9878,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9891,7 +9894,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B139" s="9">
         <v>46167.557357488426</v>
@@ -9901,7 +9904,7 @@
         <v>46223.5742721875</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9910,7 +9913,7 @@
         <v>101</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I139" s="9">
         <v>46233</v>
@@ -9928,13 +9931,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q139" s="9">
         <v>46233</v>
@@ -9954,7 +9957,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B140" s="5">
         <v>46167.55736211805</v>
@@ -9964,7 +9967,7 @@
         <v>46223.573953645835</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9973,7 +9976,7 @@
         <v>101</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I140" s="5">
         <v>46233</v>
@@ -9991,13 +9994,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10007,7 +10010,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B141" s="9">
         <v>46167.55737267361</v>
@@ -10017,7 +10020,7 @@
         <v>46223.573953009254</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10026,7 +10029,7 @@
         <v>101</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I141" s="9">
         <v>46233</v>
@@ -10044,13 +10047,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -10060,7 +10063,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B142" s="5">
         <v>46167.63325159722</v>
@@ -10070,7 +10073,7 @@
         <v>46223.57395239583</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10079,7 +10082,7 @@
         <v>101</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I142" s="5">
         <v>46233</v>
@@ -10097,13 +10100,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10113,7 +10116,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B143" s="9">
         <v>46167.63325929398</v>
@@ -10123,7 +10126,7 @@
         <v>46223.57395174769</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10132,7 +10135,7 @@
         <v>101</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I143" s="9">
         <v>46233</v>
@@ -10150,13 +10153,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10166,7 +10169,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B144" s="5">
         <v>46167.633274293985</v>
@@ -10176,7 +10179,7 @@
         <v>46223.57395109953</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10185,7 +10188,7 @@
         <v>101</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I144" s="5">
         <v>46233</v>
@@ -10203,13 +10206,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10219,7 +10222,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B145" s="9">
         <v>46167.633281875</v>
@@ -10229,7 +10232,7 @@
         <v>46223.57395048611</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10238,7 +10241,7 @@
         <v>101</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I145" s="9">
         <v>46233</v>
@@ -10256,13 +10259,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10272,7 +10275,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B146" s="5">
         <v>46167.63332260417</v>
@@ -10282,7 +10285,7 @@
         <v>46223.57394983796</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10291,7 +10294,7 @@
         <v>101</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I146" s="5">
         <v>46233</v>
@@ -10309,13 +10312,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10325,7 +10328,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B147" s="9">
         <v>46167.633331689816</v>
@@ -10335,7 +10338,7 @@
         <v>46223.57394920139</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10344,7 +10347,7 @@
         <v>101</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I147" s="9">
         <v>46233</v>
@@ -10362,13 +10365,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10378,7 +10381,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B148" s="5">
         <v>46167.557378287034</v>
@@ -10388,7 +10391,7 @@
         <v>46223.574271527774</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10397,7 +10400,7 @@
         <v>101</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I148" s="5">
         <v>46234</v>
@@ -10415,13 +10418,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q148" s="5">
         <v>46234</v>
@@ -10441,7 +10444,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B149" s="9">
         <v>46167.55738292824</v>
@@ -10451,7 +10454,7 @@
         <v>46223.57407541666</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10460,7 +10463,7 @@
         <v>101</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I149" s="9">
         <v>46234</v>
@@ -10478,13 +10481,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10494,7 +10497,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B150" s="5">
         <v>46167.5573883912</v>
@@ -10504,7 +10507,7 @@
         <v>46223.5740747338</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10513,7 +10516,7 @@
         <v>101</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I150" s="5">
         <v>46234</v>
@@ -10531,13 +10534,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10547,7 +10550,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B151" s="9">
         <v>46167.63341660879</v>
@@ -10557,7 +10560,7 @@
         <v>46223.57407407407</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10566,7 +10569,7 @@
         <v>101</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I151" s="9">
         <v>46234</v>
@@ -10584,13 +10587,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10600,7 +10603,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B152" s="5">
         <v>46167.63343371528</v>
@@ -10610,7 +10613,7 @@
         <v>46223.5740733912</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10619,7 +10622,7 @@
         <v>101</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I152" s="5">
         <v>46234</v>
@@ -10637,13 +10640,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10653,7 +10656,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B153" s="9">
         <v>46167.63344365741</v>
@@ -10663,7 +10666,7 @@
         <v>46223.57407268518</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10672,7 +10675,7 @@
         <v>101</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I153" s="9">
         <v>46234</v>
@@ -10690,13 +10693,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10706,7 +10709,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B154" s="5">
         <v>46167.63345188658</v>
@@ -10716,7 +10719,7 @@
         <v>46223.574072013886</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10725,7 +10728,7 @@
         <v>101</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I154" s="5">
         <v>46234</v>
@@ -10743,13 +10746,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10759,7 +10762,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B155" s="9">
         <v>46167.633506412036</v>
@@ -10769,7 +10772,7 @@
         <v>46223.57407130787</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10778,7 +10781,7 @@
         <v>101</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I155" s="9">
         <v>46234</v>
@@ -10796,13 +10799,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10812,7 +10815,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B156" s="5">
         <v>46167.63351399306</v>
@@ -10822,7 +10825,7 @@
         <v>46223.574070648145</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10831,7 +10834,7 @@
         <v>101</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I156" s="5">
         <v>46234</v>
@@ -10849,13 +10852,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10865,7 +10868,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B157" s="9">
         <v>46167.55739407407</v>
@@ -10875,7 +10878,7 @@
         <v>46223.57427081019</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10884,7 +10887,7 @@
         <v>101</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I157" s="9">
         <v>46238</v>
@@ -10902,13 +10905,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q157" s="9">
         <v>46238</v>
@@ -10928,7 +10931,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B158" s="5">
         <v>46167.55739920139</v>
@@ -10938,7 +10941,7 @@
         <v>46223.57418311342</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10947,7 +10950,7 @@
         <v>101</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I158" s="5">
         <v>46238</v>
@@ -10965,13 +10968,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10981,7 +10984,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B159" s="9">
         <v>46167.5574040162</v>
@@ -10991,7 +10994,7 @@
         <v>46223.574182488424</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11000,7 +11003,7 @@
         <v>101</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I159" s="9">
         <v>46238</v>
@@ -11018,13 +11021,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -11034,7 +11037,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B160" s="5">
         <v>46167.633843206015</v>
@@ -11044,7 +11047,7 @@
         <v>46223.57418185185</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11053,7 +11056,7 @@
         <v>101</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I160" s="5">
         <v>46238</v>
@@ -11071,13 +11074,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11087,7 +11090,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B161" s="9">
         <v>46167.633849895836</v>
@@ -11097,7 +11100,7 @@
         <v>46223.57418118056</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11106,7 +11109,7 @@
         <v>101</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I161" s="9">
         <v>46238</v>
@@ -11124,13 +11127,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11140,7 +11143,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B162" s="5">
         <v>46167.63385791666</v>
@@ -11150,7 +11153,7 @@
         <v>46223.57418053241</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11159,7 +11162,7 @@
         <v>101</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I162" s="5">
         <v>46238</v>
@@ -11177,13 +11180,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11193,7 +11196,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B163" s="9">
         <v>46167.633867083336</v>
@@ -11203,7 +11206,7 @@
         <v>46223.57417979167</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11212,7 +11215,7 @@
         <v>101</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I163" s="9">
         <v>46238</v>
@@ -11230,13 +11233,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11246,7 +11249,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B164" s="5">
         <v>46167.63391234954</v>
@@ -11256,7 +11259,7 @@
         <v>46223.57417917824</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11265,7 +11268,7 @@
         <v>101</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I164" s="5">
         <v>46238</v>
@@ -11283,13 +11286,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11299,7 +11302,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B165" s="9">
         <v>46167.63392017361</v>
@@ -11309,7 +11312,7 @@
         <v>46223.57417856481</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11318,7 +11321,7 @@
         <v>101</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I165" s="9">
         <v>46238</v>
@@ -11336,13 +11339,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11352,7 +11355,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B166" s="5">
         <v>46167.557409201385</v>
@@ -11362,7 +11365,7 @@
         <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -11386,7 +11389,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11399,7 +11402,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B167" s="9">
         <v>46167.5574132176</v>
@@ -11409,16 +11412,16 @@
         <v>46212.62539956019</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I167" s="9">
         <v>46230</v>
@@ -11436,13 +11439,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q167" s="9">
         <v>46230</v>
@@ -11462,7 +11465,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B168" s="5">
         <v>46167.55742054398</v>
@@ -11472,16 +11475,16 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I168" s="5">
         <v>46239</v>
@@ -11499,13 +11502,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11515,7 +11518,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B169" s="9">
         <v>46167.557425520834</v>
@@ -11525,16 +11528,16 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H169" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I169" s="9">
         <v>46239</v>
@@ -11552,13 +11555,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11568,7 +11571,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B170" s="5">
         <v>46167.55743020833</v>
@@ -11578,16 +11581,16 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I170" s="5">
         <v>46239</v>
@@ -11605,13 +11608,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11621,7 +11624,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B171" s="9">
         <v>46167.557434918985</v>
@@ -11631,16 +11634,16 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I171" s="9">
         <v>46239</v>
@@ -11658,13 +11661,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11674,7 +11677,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B172" s="5">
         <v>46167.636403032404</v>
@@ -11684,16 +11687,16 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I172" s="5">
         <v>46239</v>
@@ -11711,13 +11714,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11727,7 +11730,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B173" s="9">
         <v>46167.63641173611</v>
@@ -11737,16 +11740,16 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H173" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I173" s="9">
         <v>46239</v>
@@ -11764,13 +11767,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11780,7 +11783,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B174" s="5">
         <v>46167.636428645834</v>
@@ -11790,16 +11793,16 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I174" s="5">
         <v>46239</v>
@@ -11817,13 +11820,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11833,7 +11836,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B175" s="9">
         <v>46167.636439849535</v>
@@ -11843,16 +11846,16 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I175" s="9">
         <v>46239</v>
@@ -11870,13 +11873,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11886,7 +11889,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B176" s="5">
         <v>46167.636677511575</v>
@@ -11902,10 +11905,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I176" s="5">
         <v>46230</v>
@@ -11923,7 +11926,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>64</v>
@@ -11939,7 +11942,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B177" s="9">
         <v>46167.63669306713</v>
@@ -11955,10 +11958,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H177" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I177" s="9">
         <v>46230</v>
@@ -11976,7 +11979,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>64</v>
@@ -11992,7 +11995,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B178" s="5">
         <v>46167.6367015162</v>
@@ -12008,10 +12011,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I178" s="5">
         <v>46230</v>
@@ -12029,7 +12032,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>64</v>
@@ -12045,7 +12048,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B179" s="9">
         <v>46167.6367112963</v>
@@ -12061,10 +12064,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I179" s="9">
         <v>46230</v>
@@ -12082,7 +12085,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>64</v>
@@ -12098,7 +12101,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B180" s="5">
         <v>46167.63672008102</v>
@@ -12114,10 +12117,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I180" s="5">
         <v>46230</v>
@@ -12135,7 +12138,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>64</v>
@@ -12151,7 +12154,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B181" s="9">
         <v>46167.636729247686</v>
@@ -12167,10 +12170,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I181" s="9">
         <v>46230</v>
@@ -12188,7 +12191,7 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O181" s="10" t="s">
         <v>64</v>
@@ -12204,7 +12207,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B182" s="5">
         <v>46167.63683603009</v>
@@ -12220,10 +12223,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I182" s="5">
         <v>46230</v>
@@ -12241,7 +12244,7 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>72</v>
@@ -12257,7 +12260,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B183" s="9">
         <v>46167.636846319445</v>
@@ -12273,10 +12276,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I183" s="9">
         <v>46230</v>
@@ -12294,7 +12297,7 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>72</v>
@@ -12310,7 +12313,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B184" s="5">
         <v>46167.55743945602</v>
@@ -12320,7 +12323,7 @@
         <v>46223.57466138889</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12329,7 +12332,7 @@
         <v>101</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I184" s="5">
         <v>46170</v>
@@ -12347,13 +12350,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q184" s="5">
         <v>46231</v>
@@ -12373,7 +12376,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B185" s="9">
         <v>46167.55744423611</v>
@@ -12383,7 +12386,7 @@
         <v>46223.57463326389</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12392,7 +12395,7 @@
         <v>101</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I185" s="10"/>
       <c r="J185" s="9">
@@ -12408,13 +12411,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12424,7 +12427,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B186" s="5">
         <v>46167.55744884259</v>
@@ -12434,7 +12437,7 @@
         <v>46223.57463260417</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12443,7 +12446,7 @@
         <v>101</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I186" s="6"/>
       <c r="J186" s="5">
@@ -12459,13 +12462,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12475,7 +12478,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B187" s="9">
         <v>46167.55745349537</v>
@@ -12485,7 +12488,7 @@
         <v>46223.57463199074</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12494,7 +12497,7 @@
         <v>101</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I187" s="10"/>
       <c r="J187" s="9">
@@ -12510,13 +12513,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12526,7 +12529,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B188" s="5">
         <v>46167.55745777777</v>
@@ -12536,7 +12539,7 @@
         <v>46223.57463131944</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12545,7 +12548,7 @@
         <v>101</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I188" s="6"/>
       <c r="J188" s="5">
@@ -12561,13 +12564,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12577,7 +12580,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B189" s="9">
         <v>46167.637670833334</v>
@@ -12587,7 +12590,7 @@
         <v>46223.5746305787</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12596,7 +12599,7 @@
         <v>101</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I189" s="10"/>
       <c r="J189" s="9">
@@ -12612,13 +12615,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12628,7 +12631,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B190" s="5">
         <v>46167.63768076389</v>
@@ -12638,7 +12641,7 @@
         <v>46223.574629849536</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12647,7 +12650,7 @@
         <v>101</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I190" s="6"/>
       <c r="J190" s="5">
@@ -12663,13 +12666,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12679,7 +12682,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B191" s="9">
         <v>46167.637724016204</v>
@@ -12689,7 +12692,7 @@
         <v>46223.57462922454</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12698,7 +12701,7 @@
         <v>101</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I191" s="10"/>
       <c r="J191" s="9">
@@ -12714,13 +12717,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12730,7 +12733,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B192" s="5">
         <v>46167.63773231482</v>
@@ -12740,7 +12743,7 @@
         <v>46223.574628622686</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12749,7 +12752,7 @@
         <v>101</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -12765,13 +12768,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12781,7 +12784,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B193" s="9">
         <v>46167.63788011574</v>
@@ -12800,7 +12803,7 @@
         <v>101</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I193" s="9">
         <v>46231</v>
@@ -12818,7 +12821,7 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O193" s="10" t="s">
         <v>65</v>
@@ -12834,7 +12837,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B194" s="5">
         <v>46167.637888530095</v>
@@ -12853,7 +12856,7 @@
         <v>101</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I194" s="5">
         <v>46231</v>
@@ -12871,7 +12874,7 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O194" s="6" t="s">
         <v>64</v>
@@ -12887,7 +12890,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B195" s="9">
         <v>46167.63789722222</v>
@@ -12906,7 +12909,7 @@
         <v>101</v>
       </c>
       <c r="H195" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I195" s="9">
         <v>46231</v>
@@ -12924,7 +12927,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O195" s="10" t="s">
         <v>64</v>
@@ -12940,7 +12943,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B196" s="5">
         <v>46167.63790768519</v>
@@ -12959,7 +12962,7 @@
         <v>101</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I196" s="5">
         <v>46231</v>
@@ -12977,7 +12980,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>64</v>
@@ -12993,7 +12996,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B197" s="9">
         <v>46167.63791662037</v>
@@ -13012,7 +13015,7 @@
         <v>101</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I197" s="9">
         <v>46231</v>
@@ -13030,7 +13033,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O197" s="10" t="s">
         <v>64</v>
@@ -13046,7 +13049,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B198" s="5">
         <v>46167.637946689814</v>
@@ -13065,7 +13068,7 @@
         <v>101</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I198" s="5">
         <v>46231</v>
@@ -13083,7 +13086,7 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>64</v>
@@ -13099,7 +13102,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B199" s="9">
         <v>46167.637995729165</v>
@@ -13118,7 +13121,7 @@
         <v>101</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I199" s="9">
         <v>46231</v>
@@ -13136,7 +13139,7 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O199" s="10" t="s">
         <v>72</v>
@@ -13152,7 +13155,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B200" s="5">
         <v>46167.63800420139</v>
@@ -13171,7 +13174,7 @@
         <v>101</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I200" s="5">
         <v>46231</v>
@@ -13189,7 +13192,7 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>72</v>
@@ -13205,7 +13208,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B201" s="9">
         <v>46167.55746224537</v>
@@ -13215,16 +13218,16 @@
         <v>46212.62523481481</v>
       </c>
       <c r="E201" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H201" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13242,13 +13245,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O201" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P201" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q201" s="9">
         <v>46241</v>
@@ -13268,7 +13271,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B202" s="5">
         <v>46167.55746689815</v>
@@ -13278,16 +13281,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H202" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13305,13 +13308,13 @@
         <v>26</v>
       </c>
       <c r="N202" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
@@ -13321,7 +13324,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B203" s="9">
         <v>46167.55747543981</v>
@@ -13331,16 +13334,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H203" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13358,13 +13361,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P203" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q203" s="10"/>
       <c r="R203" s="10"/>
@@ -13374,7 +13377,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B204" s="5">
         <v>46167.557519270835</v>
@@ -13384,16 +13387,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13411,13 +13414,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q204" s="6"/>
       <c r="R204" s="6"/>
@@ -13427,7 +13430,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B205" s="9">
         <v>46167.5575253125</v>
@@ -13437,16 +13440,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H205" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13464,13 +13467,13 @@
         <v>26</v>
       </c>
       <c r="N205" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P205" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q205" s="10"/>
       <c r="R205" s="10"/>
@@ -13480,7 +13483,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B206" s="5">
         <v>46167.6385715162</v>
@@ -13490,16 +13493,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13517,13 +13520,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13533,7 +13536,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B207" s="9">
         <v>46167.63857899306</v>
@@ -13543,16 +13546,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H207" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13570,13 +13573,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13586,7 +13589,7 @@
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B208" s="5">
         <v>46167.638659930555</v>
@@ -13596,16 +13599,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H208" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13623,13 +13626,13 @@
         <v>26</v>
       </c>
       <c r="N208" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q208" s="6"/>
       <c r="R208" s="6"/>
@@ -13639,7 +13642,7 @@
     </row>
     <row r="209" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B209" s="9">
         <v>46167.638666956016</v>
@@ -13649,16 +13652,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H209" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13676,13 +13679,13 @@
         <v>26</v>
       </c>
       <c r="N209" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P209" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q209" s="10"/>
       <c r="R209" s="10"/>
@@ -13692,7 +13695,7 @@
     </row>
     <row r="210" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B210" s="5">
         <v>46167.6387090162</v>
@@ -13708,10 +13711,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H210" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13729,7 +13732,7 @@
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O210" s="6" t="s">
         <v>64</v>
@@ -13745,7 +13748,7 @@
     </row>
     <row r="211" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B211" s="9">
         <v>46167.63871641204</v>
@@ -13761,10 +13764,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H211" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13782,7 +13785,7 @@
         <v>26</v>
       </c>
       <c r="N211" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O211" s="10" t="s">
         <v>64</v>
@@ -13798,7 +13801,7 @@
     </row>
     <row r="212" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B212" s="5">
         <v>46167.638723599535</v>
@@ -13814,10 +13817,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13835,7 +13838,7 @@
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O212" s="6" t="s">
         <v>64</v>
@@ -13851,7 +13854,7 @@
     </row>
     <row r="213" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B213" s="9">
         <v>46167.63873144676</v>
@@ -13867,10 +13870,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13888,7 +13891,7 @@
         <v>26</v>
       </c>
       <c r="N213" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O213" s="10" t="s">
         <v>64</v>
@@ -13904,7 +13907,7 @@
     </row>
     <row r="214" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B214" s="5">
         <v>46167.6387405787</v>
@@ -13920,10 +13923,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13941,7 +13944,7 @@
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O214" s="6" t="s">
         <v>64</v>
@@ -13957,7 +13960,7 @@
     </row>
     <row r="215" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B215" s="9">
         <v>46167.63874844907</v>
@@ -13973,10 +13976,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H215" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -13994,7 +13997,7 @@
         <v>26</v>
       </c>
       <c r="N215" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O215" s="10" t="s">
         <v>64</v>
@@ -14010,7 +14013,7 @@
     </row>
     <row r="216" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B216" s="5">
         <v>46167.638756562505</v>
@@ -14026,10 +14029,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H216" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -14047,13 +14050,13 @@
         <v>26</v>
       </c>
       <c r="N216" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O216" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q216" s="6"/>
       <c r="R216" s="6"/>
@@ -14063,7 +14066,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B217" s="9">
         <v>46167.63883428241</v>
@@ -14079,10 +14082,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -14100,13 +14103,13 @@
         <v>26</v>
       </c>
       <c r="N217" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O217" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P217" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q217" s="10"/>
       <c r="R217" s="10"/>
@@ -14116,7 +14119,7 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B218" s="5">
         <v>46167.55752998842</v>
@@ -14126,16 +14129,16 @@
         <v>46212.62527664352</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H218" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -14153,13 +14156,13 @@
         <v>26</v>
       </c>
       <c r="N218" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O218" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q218" s="5">
         <v>46244</v>
@@ -14179,7 +14182,7 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B219" s="9">
         <v>46167.55753614583</v>
@@ -14189,16 +14192,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H219" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14216,13 +14219,13 @@
         <v>26</v>
       </c>
       <c r="N219" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P219" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q219" s="10"/>
       <c r="R219" s="10"/>
@@ -14232,7 +14235,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B220" s="5">
         <v>46167.557540381946</v>
@@ -14242,16 +14245,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H220" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14269,13 +14272,13 @@
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q220" s="6"/>
       <c r="R220" s="6"/>
@@ -14285,7 +14288,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B221" s="9">
         <v>46167.557545069445</v>
@@ -14295,16 +14298,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H221" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14322,13 +14325,13 @@
         <v>26</v>
       </c>
       <c r="N221" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P221" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q221" s="10"/>
       <c r="R221" s="10"/>
@@ -14338,7 +14341,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B222" s="5">
         <v>46167.55754895833</v>
@@ -14348,16 +14351,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H222" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14375,13 +14378,13 @@
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q222" s="6"/>
       <c r="R222" s="6"/>
@@ -14391,7 +14394,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B223" s="9">
         <v>46167.63903770833</v>
@@ -14401,16 +14404,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14428,10 +14431,10 @@
         <v>26</v>
       </c>
       <c r="N223" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14444,7 +14447,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B224" s="5">
         <v>46167.639049317135</v>
@@ -14454,16 +14457,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H224" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14481,10 +14484,10 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14497,7 +14500,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B225" s="9">
         <v>46167.639172118055</v>
@@ -14507,16 +14510,16 @@
         <v>46167.743832430555</v>
       </c>
       <c r="E225" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H225" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14534,10 +14537,10 @@
         <v>26</v>
       </c>
       <c r="N225" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14550,7 +14553,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B226" s="5">
         <v>46167.63918146991</v>
@@ -14560,16 +14563,16 @@
         <v>46167.74382957176</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H226" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14587,10 +14590,10 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14603,7 +14606,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B227" s="9">
         <v>46167.63922125</v>
@@ -14619,10 +14622,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14640,7 +14643,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O227" s="10" t="s">
         <v>64</v>
@@ -14656,7 +14659,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B228" s="5">
         <v>46167.63923230324</v>
@@ -14672,10 +14675,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H228" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14693,7 +14696,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O228" s="6" t="s">
         <v>64</v>
@@ -14709,7 +14712,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B229" s="9">
         <v>46167.63924049769</v>
@@ -14725,10 +14728,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H229" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14746,7 +14749,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O229" s="10" t="s">
         <v>64</v>
@@ -14762,7 +14765,7 @@
     </row>
     <row r="230" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B230" s="5">
         <v>46167.63924949074</v>
@@ -14778,10 +14781,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H230" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14799,7 +14802,7 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O230" s="6" t="s">
         <v>64</v>
@@ -14815,7 +14818,7 @@
     </row>
     <row r="231" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B231" s="9">
         <v>46167.639259375</v>
@@ -14831,10 +14834,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H231" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14852,7 +14855,7 @@
         <v>26</v>
       </c>
       <c r="N231" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O231" s="10" t="s">
         <v>64</v>
@@ -14868,7 +14871,7 @@
     </row>
     <row r="232" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B232" s="5">
         <v>46167.63926804398</v>
@@ -14884,10 +14887,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H232" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14905,7 +14908,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O232" s="6" t="s">
         <v>64</v>
@@ -14921,7 +14924,7 @@
     </row>
     <row r="233" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B233" s="9">
         <v>46167.63935532408</v>
@@ -14931,16 +14934,16 @@
         <v>46167.74380655093</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H233" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -14958,7 +14961,7 @@
         <v>26</v>
       </c>
       <c r="N233" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O233" s="10" t="s">
         <v>72</v>
@@ -14974,7 +14977,7 @@
     </row>
     <row r="234" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B234" s="5">
         <v>46167.63936689815</v>
@@ -14984,16 +14987,16 @@
         <v>46167.74380591435</v>
       </c>
       <c r="E234" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H234" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>
@@ -15011,7 +15014,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O234" s="6" t="s">
         <v>72</v>
@@ -15027,7 +15030,7 @@
     </row>
     <row r="235" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B235" s="9">
         <v>46167.55755266204</v>
@@ -15037,7 +15040,7 @@
         <v>46167.73498962963</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>25</v>
@@ -15061,7 +15064,7 @@
         <v>26</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>26</v>
@@ -15074,7 +15077,7 @@
     </row>
     <row r="236" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B236" s="5">
         <v>46167.55755585648</v>
@@ -15084,16 +15087,16 @@
         <v>46167.743865428245</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G236" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H236" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I236" s="5">
         <v>46245</v>
@@ -15111,13 +15114,13 @@
         <v>26</v>
       </c>
       <c r="N236" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P236" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q236" s="5">
         <v>46245</v>
@@ -15137,7 +15140,7 @@
     </row>
     <row r="237" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B237" s="9">
         <v>46167.55756052083</v>
@@ -15147,7 +15150,7 @@
         <v>46189.872060740745</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>26</v>
@@ -15174,13 +15177,13 @@
         <v>26</v>
       </c>
       <c r="N237" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P237" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q237" s="9">
         <v>46245</v>
@@ -15200,7 +15203,7 @@
     </row>
     <row r="238" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B238" s="5">
         <v>46167.557566296295</v>
@@ -15210,7 +15213,7 @@
         <v>46167.73546241898</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>25</v>
@@ -15234,7 +15237,7 @@
         <v>26</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>26</v>
@@ -15253,7 +15256,7 @@
     </row>
     <row r="239" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B239" s="9">
         <v>46167.55756988426</v>
@@ -15263,7 +15266,7 @@
         <v>46167.743959513886</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>26</v>
@@ -15290,13 +15293,13 @@
         <v>26</v>
       </c>
       <c r="N239" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O239" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P239" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q239" s="9">
         <v>46245</v>
@@ -15316,7 +15319,7 @@
     </row>
     <row r="240" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B240" s="5">
         <v>46167.557574895836</v>
@@ -15326,7 +15329,7 @@
         <v>46167.74395664352</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>26</v>
@@ -15353,13 +15356,13 @@
         <v>26</v>
       </c>
       <c r="N240" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O240" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P240" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q240" s="5">
         <v>46254</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46223.5742721875</v>
+        <v>46226.191206724536</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>347</v>
@@ -9945,8 +9945,8 @@
       <c r="R139" s="9">
         <v>46233</v>
       </c>
-      <c r="S139" s="7" t="s">
-        <v>33</v>
+      <c r="S139" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T139" s="10">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -253,7 +253,7 @@
     <t>Ingenieria Servicios ,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -400,9 +400,6 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser  ot 4328 - 4330</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>1215103776642061</t>
   </si>
   <si>
@@ -710,6 +707,9 @@
   </si>
   <si>
     <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215103926643820</t>
@@ -1612,12 +1612,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46220.20472001158</v>
+        <v>46228.20609821759</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2704,7 +2704,7 @@
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="12" t="s">
+      <c r="U12" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46167.73754430556</v>
+        <v>46227.1689678125</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>64</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46167.7375415162</v>
+        <v>46227.16896998843</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>64</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46167.737538692134</v>
+        <v>46227.16897136574</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46167.737535625</v>
+        <v>46227.16897266204</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>64</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46167.73753288195</v>
+        <v>46227.168973900465</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>64</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46167.73753034722</v>
+        <v>46227.16897515046</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>64</v>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46167.737524641205</v>
+        <v>46227.16897641204</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>72</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46171.51095925926</v>
+        <v>46227.16897766203</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>72</v>
@@ -3177,7 +3177,7 @@
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
-      <c r="U21" s="11" t="s">
+      <c r="U21" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -3679,8 +3679,8 @@
       <c r="R29" s="9">
         <v>46191</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>108</v>
+      <c r="S29" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5">
         <v>46167.55683648148</v>
@@ -3703,7 +3703,7 @@
         <v>46223.57337341435</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3736,7 +3736,7 @@
         <v>106</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="5">
         <v>46190</v>
@@ -3744,8 +3744,8 @@
       <c r="R30" s="5">
         <v>46191</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>108</v>
+      <c r="S30" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3756,7 +3756,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="9">
         <v>46167.55684075231</v>
@@ -3768,7 +3768,7 @@
         <v>46223.573370266204</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3801,7 +3801,7 @@
         <v>106</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q31" s="9">
         <v>46190</v>
@@ -3809,8 +3809,8 @@
       <c r="R31" s="9">
         <v>46191</v>
       </c>
-      <c r="S31" s="12" t="s">
-        <v>108</v>
+      <c r="S31" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T31" s="10">
         <v>1</v>
@@ -3821,7 +3821,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="5">
         <v>46167.55684506944</v>
@@ -3833,7 +3833,7 @@
         <v>46223.573365069446</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3866,7 +3866,7 @@
         <v>106</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q32" s="5">
         <v>46190</v>
@@ -3874,8 +3874,8 @@
       <c r="R32" s="5">
         <v>46191</v>
       </c>
-      <c r="S32" s="12" t="s">
-        <v>108</v>
+      <c r="S32" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B33" s="9">
         <v>46167.55684913194</v>
@@ -3898,7 +3898,7 @@
         <v>46209.564447372686</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3931,7 +3931,7 @@
         <v>51</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q33" s="9">
         <v>46157</v>
@@ -3951,7 +3951,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B34" s="5">
         <v>46189.87339945602</v>
@@ -3963,7 +3963,7 @@
         <v>46190.643601261574</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>25</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B35" s="9">
         <v>46189.874116527775</v>
@@ -4016,7 +4016,7 @@
         <v>46223.573449062504</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -4043,10 +4043,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -4057,8 +4057,8 @@
       <c r="R35" s="9">
         <v>46167</v>
       </c>
-      <c r="S35" s="12" t="s">
-        <v>108</v>
+      <c r="S35" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -4069,7 +4069,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B36" s="5">
         <v>46189.87428425926</v>
@@ -4081,7 +4081,7 @@
         <v>46223.57344547454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -4108,13 +4108,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q36" s="5">
         <v>46160</v>
@@ -4122,19 +4122,19 @@
       <c r="R36" s="5">
         <v>46167</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>108</v>
+      <c r="S36" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
       </c>
-      <c r="U36" s="11" t="s">
+      <c r="U36" s="12" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B37" s="9">
         <v>46167.556641689815</v>
@@ -4144,7 +4144,7 @@
         <v>46199.56372103009</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>25</v>
@@ -4168,7 +4168,7 @@
         <v>26</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -4177,13 +4177,13 @@
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
-      <c r="U37" s="11" t="s">
+      <c r="U37" s="12" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B38" s="5">
         <v>46167.55686952546</v>
@@ -4195,16 +4195,16 @@
         <v>46195.930020127314</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46160</v>
@@ -4222,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q38" s="5">
         <v>46160</v>
@@ -4236,8 +4236,8 @@
       <c r="R38" s="5">
         <v>46183</v>
       </c>
-      <c r="S38" s="12" t="s">
-        <v>108</v>
+      <c r="S38" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B39" s="9">
         <v>46167.556874270835</v>
@@ -4260,16 +4260,16 @@
         <v>46195.92806517361</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I39" s="9">
         <v>46160</v>
@@ -4287,13 +4287,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4303,13 +4303,13 @@
       <c r="T39" s="10">
         <v>0</v>
       </c>
-      <c r="U39" s="12" t="s">
+      <c r="U39" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B40" s="5">
         <v>46167.55687946759</v>
@@ -4321,16 +4321,16 @@
         <v>46195.92988494213</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I40" s="5">
         <v>46162</v>
@@ -4348,13 +4348,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4364,13 +4364,13 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
+      <c r="U40" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B41" s="9">
         <v>46167.55696103009</v>
@@ -4380,16 +4380,16 @@
         <v>46220.1910684375</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I41" s="9">
         <v>46160</v>
@@ -4407,10 +4407,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4421,19 +4421,19 @@
       <c r="R41" s="9">
         <v>46219</v>
       </c>
-      <c r="S41" s="12" t="s">
-        <v>108</v>
+      <c r="S41" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T41" s="10">
         <v>0</v>
       </c>
-      <c r="U41" s="12" t="s">
+      <c r="U41" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="5">
         <v>46167.556965254626</v>
@@ -4443,16 +4443,16 @@
         <v>46212.654553368055</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I42" s="5">
         <v>46161</v>
@@ -4470,13 +4470,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B43" s="9">
         <v>46167.55696965278</v>
@@ -4496,16 +4496,16 @@
         <v>46219.16843491898</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I43" s="9">
         <v>46171</v>
@@ -4523,13 +4523,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B44" s="5">
         <v>46167.556973784725</v>
@@ -4551,16 +4551,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46192</v>
@@ -4578,13 +4578,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q44" s="5">
         <v>46192</v>
@@ -4592,8 +4592,8 @@
       <c r="R44" s="5">
         <v>46204</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>108</v>
+      <c r="S44" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4604,7 +4604,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B45" s="9">
         <v>46167.556978611115</v>
@@ -4616,16 +4616,16 @@
         <v>46199.56362072917</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I45" s="9">
         <v>46192</v>
@@ -4643,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>105</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4659,13 +4659,13 @@
       <c r="T45" s="10">
         <v>0</v>
       </c>
-      <c r="U45" s="12" t="s">
+      <c r="U45" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B46" s="5">
         <v>46167.55698368055</v>
@@ -4677,16 +4677,16 @@
         <v>46199.563687118054</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46196</v>
@@ -4704,13 +4704,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4720,13 +4720,13 @@
       <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="U46" s="12" t="s">
+      <c r="U46" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B47" s="9">
         <v>46167.556988842596</v>
@@ -4738,16 +4738,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I47" s="9">
         <v>46192</v>
@@ -4765,10 +4765,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4779,8 +4779,8 @@
       <c r="R47" s="9">
         <v>46204</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>108</v>
+      <c r="S47" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
         <v>46167.556992708334</v>
@@ -4803,16 +4803,16 @@
         <v>46199.56375667824</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I48" s="5">
         <v>46192</v>
@@ -4830,13 +4830,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B49" s="9">
         <v>46167.5569971875</v>
@@ -4858,16 +4858,16 @@
         <v>46199.56447744213</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I49" s="9">
         <v>46196</v>
@@ -4885,13 +4885,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5">
         <v>46167.55700140046</v>
@@ -4913,16 +4913,16 @@
         <v>46204.59613972223</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I50" s="5">
         <v>46192</v>
@@ -4940,10 +4940,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B51" s="9">
         <v>46167.55700519676</v>
@@ -4978,16 +4978,16 @@
         <v>46204.5950621875</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="I51" s="9">
         <v>46192</v>
@@ -5005,13 +5005,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B52" s="5">
         <v>46167.557010034725</v>
@@ -5033,16 +5033,16 @@
         <v>46204.59515966436</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I52" s="5">
         <v>46233</v>
@@ -5060,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -5076,7 +5076,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
         <v>46167.55701476852</v>
@@ -5086,16 +5086,16 @@
         <v>46204.59516696759</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I53" s="9">
         <v>46262</v>
@@ -5113,10 +5113,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -5129,7 +5129,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B54" s="5">
         <v>46167.55701769676</v>
@@ -5141,16 +5141,16 @@
         <v>46205.169011087964</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I54" s="5">
         <v>46192</v>
@@ -5168,10 +5168,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -5182,8 +5182,8 @@
       <c r="R54" s="5">
         <v>46204</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>108</v>
+      <c r="S54" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46167.557021678236</v>
@@ -5206,16 +5206,16 @@
         <v>46199.564400601856</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I55" s="9">
         <v>46192</v>
@@ -5233,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B56" s="5">
         <v>46167.55702634259</v>
@@ -5261,16 +5261,16 @@
         <v>46199.56458967592</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I56" s="5">
         <v>46196</v>
@@ -5288,13 +5288,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B57" s="9">
         <v>46167.55703671296</v>
@@ -5314,7 +5314,7 @@
         <v>46189.891556296294</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -5338,7 +5338,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46167.557040520835</v>
@@ -5363,16 +5363,16 @@
         <v>46197.715067453704</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
+      <c r="H58" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46161</v>
@@ -5390,13 +5390,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="5">
         <v>46161</v>
@@ -5404,8 +5404,8 @@
       <c r="R58" s="5">
         <v>46168</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>108</v>
+      <c r="S58" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46167.557045856476</v>
@@ -5428,16 +5428,16 @@
         <v>46197.71510291667</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I59" s="9">
         <v>46182</v>
@@ -5455,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="9">
         <v>46182</v>
@@ -5469,8 +5469,8 @@
       <c r="R59" s="9">
         <v>46188</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>108</v>
+      <c r="S59" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5481,7 +5481,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46167.5570519676</v>
@@ -5499,10 +5499,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="I60" s="5">
         <v>46189</v>
@@ -5520,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q60" s="5">
         <v>46189</v>
@@ -5534,8 +5534,8 @@
       <c r="R60" s="5">
         <v>46189</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>108</v>
+      <c r="S60" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5546,26 +5546,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46167.55706452546</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46167.740869988425</v>
+        <v>46230.185757071755</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5583,10 +5583,10 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5597,13 +5597,13 @@
       <c r="R61" s="9">
         <v>46237</v>
       </c>
-      <c r="S61" s="7" t="s">
-        <v>33</v>
+      <c r="S61" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="12" t="s">
+      <c r="U61" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5625,10 +5625,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5646,7 +5646,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>213</v>
@@ -5678,10 +5678,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I63" s="9">
         <v>46237</v>
@@ -5699,7 +5699,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>213</v>
@@ -5731,10 +5731,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5752,7 +5752,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>213</v>
@@ -5784,10 +5784,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I65" s="9">
         <v>46237</v>
@@ -5805,7 +5805,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>213</v>
@@ -5837,10 +5837,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5858,7 +5858,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>213</v>
@@ -5890,10 +5890,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I67" s="9">
         <v>46237</v>
@@ -5911,7 +5911,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>213</v>
@@ -5943,10 +5943,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46237</v>
@@ -5964,7 +5964,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>222</v>
@@ -5996,10 +5996,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>210</v>
       </c>
       <c r="I69" s="9">
         <v>46237</v>
@@ -6017,7 +6017,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>222</v>
@@ -6128,7 +6128,7 @@
         <v>225</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>231</v>
@@ -6139,8 +6139,8 @@
       <c r="R71" s="9">
         <v>46206</v>
       </c>
-      <c r="S71" s="12" t="s">
-        <v>108</v>
+      <c r="S71" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T71" s="10">
         <v>1</v>
@@ -6169,10 +6169,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I72" s="5">
         <v>46209</v>
@@ -6204,8 +6204,8 @@
       <c r="R72" s="5">
         <v>46210</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>108</v>
+      <c r="S72" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6258,7 +6258,7 @@
         <v>225</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>238</v>
@@ -6269,8 +6269,8 @@
       <c r="R73" s="9">
         <v>46206</v>
       </c>
-      <c r="S73" s="12" t="s">
-        <v>108</v>
+      <c r="S73" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T73" s="10">
         <v>1</v>
@@ -6299,10 +6299,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I74" s="5">
         <v>46209</v>
@@ -6334,8 +6334,8 @@
       <c r="R74" s="5">
         <v>46210</v>
       </c>
-      <c r="S74" s="12" t="s">
-        <v>108</v>
+      <c r="S74" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6388,7 +6388,7 @@
         <v>225</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>244</v>
@@ -6399,8 +6399,8 @@
       <c r="R75" s="9">
         <v>46206</v>
       </c>
-      <c r="S75" s="12" t="s">
-        <v>108</v>
+      <c r="S75" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6429,10 +6429,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I76" s="5">
         <v>46209</v>
@@ -6464,8 +6464,8 @@
       <c r="R76" s="5">
         <v>46210</v>
       </c>
-      <c r="S76" s="12" t="s">
-        <v>108</v>
+      <c r="S76" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T76" s="6">
         <v>1</v>
@@ -6576,8 +6576,8 @@
       <c r="R78" s="5">
         <v>46213</v>
       </c>
-      <c r="S78" s="12" t="s">
-        <v>108</v>
+      <c r="S78" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -7068,7 +7068,7 @@
         <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>247</v>
@@ -7079,13 +7079,13 @@
       <c r="R87" s="9">
         <v>46220</v>
       </c>
-      <c r="S87" s="12" t="s">
-        <v>108</v>
+      <c r="S87" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="11" t="s">
+      <c r="U87" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
         <v>213</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7545,10 +7545,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I96" s="5">
         <v>46223</v>
@@ -7569,7 +7569,7 @@
         <v>247</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>247</v>
@@ -7580,13 +7580,13 @@
       <c r="R96" s="5">
         <v>46223</v>
       </c>
-      <c r="S96" s="12" t="s">
-        <v>108</v>
+      <c r="S96" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="11" t="s">
+      <c r="U96" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -7610,10 +7610,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I97" s="9">
         <v>46223</v>
@@ -7665,10 +7665,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I98" s="5">
         <v>46223</v>
@@ -7720,10 +7720,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I99" s="9">
         <v>46223</v>
@@ -7775,10 +7775,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I100" s="5">
         <v>46223</v>
@@ -7830,10 +7830,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I101" s="9">
         <v>46223</v>
@@ -7883,10 +7883,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I102" s="5">
         <v>46223</v>
@@ -7938,10 +7938,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I103" s="9">
         <v>46223</v>
@@ -7993,10 +7993,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I104" s="5">
         <v>46223</v>
@@ -8117,7 +8117,7 @@
         <v>225</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>293</v>
@@ -8128,13 +8128,13 @@
       <c r="R106" s="5">
         <v>46184</v>
       </c>
-      <c r="S106" s="12" t="s">
-        <v>108</v>
+      <c r="S106" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="11" t="s">
+      <c r="U106" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
         <v>46190.64346133102</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -8180,7 +8180,7 @@
         <v>225</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>235</v>
@@ -8191,13 +8191,13 @@
       <c r="R107" s="9">
         <v>46167</v>
       </c>
-      <c r="S107" s="12" t="s">
-        <v>108</v>
+      <c r="S107" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T107" s="10">
         <v>0</v>
       </c>
-      <c r="U107" s="11" t="s">
+      <c r="U107" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
         <v>46189.87818384259</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8260,7 +8260,7 @@
       <c r="T108" s="6">
         <v>0</v>
       </c>
-      <c r="U108" s="11" t="s">
+      <c r="U108" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8306,7 +8306,7 @@
         <v>225</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>299</v>
@@ -8323,7 +8323,7 @@
       <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="11" t="s">
+      <c r="U109" s="12" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
         <v>225</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>301</v>
@@ -8380,13 +8380,13 @@
       <c r="R110" s="5">
         <v>46220</v>
       </c>
-      <c r="S110" s="12" t="s">
-        <v>108</v>
+      <c r="S110" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
       </c>
-      <c r="U110" s="12" t="s">
+      <c r="U110" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46223.57427424769</v>
+        <v>46230.16889403935</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>306</v>
@@ -8490,13 +8490,13 @@
       <c r="R112" s="5">
         <v>46230</v>
       </c>
-      <c r="S112" s="11" t="s">
-        <v>61</v>
+      <c r="S112" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="12" t="s">
+      <c r="U112" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46223.57360364583</v>
+        <v>46230.16889255787</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>213</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46223.57360296296</v>
+        <v>46230.16889612269</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>213</v>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46223.573600034724</v>
+        <v>46230.16885648148</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>213</v>
@@ -8976,7 +8976,7 @@
         <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>303</v>
@@ -8987,13 +8987,13 @@
       <c r="R121" s="9">
         <v>46231</v>
       </c>
-      <c r="S121" s="11" t="s">
-        <v>61</v>
+      <c r="S121" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T121" s="10">
         <v>0</v>
       </c>
-      <c r="U121" s="12" t="s">
+      <c r="U121" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
         <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>303</v>
@@ -9474,13 +9474,13 @@
       <c r="R130" s="5">
         <v>46232</v>
       </c>
-      <c r="S130" s="11" t="s">
-        <v>61</v>
+      <c r="S130" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
       </c>
-      <c r="U130" s="12" t="s">
+      <c r="U130" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
         <v>303</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>303</v>
@@ -9945,13 +9945,13 @@
       <c r="R139" s="9">
         <v>46233</v>
       </c>
-      <c r="S139" s="11" t="s">
-        <v>61</v>
+      <c r="S139" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T139" s="10">
         <v>0</v>
       </c>
-      <c r="U139" s="12" t="s">
+      <c r="U139" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46223.574271527774</v>
+        <v>46227.17132248843</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>363</v>
@@ -10421,7 +10421,7 @@
         <v>303</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>303</v>
@@ -10432,13 +10432,13 @@
       <c r="R148" s="5">
         <v>46234</v>
       </c>
-      <c r="S148" s="7" t="s">
-        <v>33</v>
+      <c r="S148" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T148" s="6">
         <v>0</v>
       </c>
-      <c r="U148" s="12" t="s">
+      <c r="U148" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
         <v>303</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>375</v>
@@ -10925,7 +10925,7 @@
       <c r="T157" s="10">
         <v>0</v>
       </c>
-      <c r="U157" s="12" t="s">
+      <c r="U157" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       <c r="T167" s="10">
         <v>0</v>
       </c>
-      <c r="U167" s="12" t="s">
+      <c r="U167" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46167.742840844905</v>
+        <v>46230.16885827546</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>65</v>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="C177" s="10"/>
       <c r="D177" s="9">
-        <v>46167.742838136575</v>
+        <v>46230.168860046295</v>
       </c>
       <c r="E177" s="10" t="s">
         <v>64</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46167.742835763886</v>
+        <v>46230.16886130787</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>64</v>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="C179" s="10"/>
       <c r="D179" s="9">
-        <v>46167.74282516204</v>
+        <v>46230.16886262731</v>
       </c>
       <c r="E179" s="10" t="s">
         <v>64</v>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46167.742824456014</v>
+        <v>46230.16886431713</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>64</v>
@@ -12161,7 +12161,7 @@
       </c>
       <c r="C181" s="10"/>
       <c r="D181" s="9">
-        <v>46167.74282375</v>
+        <v>46230.16886560185</v>
       </c>
       <c r="E181" s="10" t="s">
         <v>64</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46167.74282306713</v>
+        <v>46230.16886701389</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>72</v>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="C183" s="10"/>
       <c r="D183" s="9">
-        <v>46167.74282237269</v>
+        <v>46230.16886826389</v>
       </c>
       <c r="E183" s="10" t="s">
         <v>72</v>
@@ -12370,7 +12370,7 @@
       <c r="T184" s="6">
         <v>0</v>
       </c>
-      <c r="U184" s="12" t="s">
+      <c r="U184" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -13265,7 +13265,7 @@
       <c r="T201" s="10">
         <v>0</v>
       </c>
-      <c r="U201" s="12" t="s">
+      <c r="U201" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       <c r="T218" s="6">
         <v>0</v>
       </c>
-      <c r="U218" s="12" t="s">
+      <c r="U218" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       <c r="T236" s="6">
         <v>0</v>
       </c>
-      <c r="U236" s="12" t="s">
+      <c r="U236" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -15197,7 +15197,7 @@
       <c r="T237" s="10">
         <v>0</v>
       </c>
-      <c r="U237" s="12" t="s">
+      <c r="U237" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       <c r="T238" s="6">
         <v>0</v>
       </c>
-      <c r="U238" s="12" t="s">
+      <c r="U238" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -15313,7 +15313,7 @@
       <c r="T239" s="10">
         <v>0</v>
       </c>
-      <c r="U239" s="12" t="s">
+      <c r="U239" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       <c r="T240" s="6">
         <v>0</v>
       </c>
-      <c r="U240" s="12" t="s">
+      <c r="U240" s="11" t="s">
         <v>62</v>
       </c>
     </row>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -835,7 +835,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46228.20609821759</v>
+        <v>46231.51884047454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -6532,7 +6532,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46225.86189571759</v>
+        <v>46231.56037715278</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46230.16889403935</v>
+        <v>46231.18536899306</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>306</v>
@@ -8490,8 +8490,8 @@
       <c r="R112" s="5">
         <v>46230</v>
       </c>
-      <c r="S112" s="12" t="s">
-        <v>211</v>
+      <c r="S112" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46224.18997180555</v>
+        <v>46231.16835796296</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>318</v>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46223.5737202662</v>
+        <v>46231.16835666666</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>213</v>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46223.573719583335</v>
+        <v>46231.16835527778</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>213</v>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46223.57371890046</v>
+        <v>46231.16833541667</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>213</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46223.57371819444</v>
+        <v>46231.16833734953</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>213</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46223.5737175463</v>
+        <v>46231.16833881944</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>213</v>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46223.57371685185</v>
+        <v>46231.16834034723</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>213</v>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46223.57371615741</v>
+        <v>46231.168341701385</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>222</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46223.57371547454</v>
+        <v>46231.16834335648</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>222</v>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46223.57427081019</v>
+        <v>46231.18471695602</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>374</v>
@@ -10919,8 +10919,8 @@
       <c r="R157" s="9">
         <v>46238</v>
       </c>
-      <c r="S157" s="7" t="s">
-        <v>33</v>
+      <c r="S157" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="T157" s="10">
         <v>0</v>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="C193" s="10"/>
       <c r="D193" s="9">
-        <v>46223.574627974536</v>
+        <v>46231.16834474537</v>
       </c>
       <c r="E193" s="10" t="s">
         <v>64</v>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46223.57462730324</v>
+        <v>46231.16834625</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>64</v>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="C195" s="10"/>
       <c r="D195" s="9">
-        <v>46223.57462666667</v>
+        <v>46231.168347557876</v>
       </c>
       <c r="E195" s="10" t="s">
         <v>64</v>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46223.574626030095</v>
+        <v>46231.168348935185</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>64</v>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="C197" s="10"/>
       <c r="D197" s="9">
-        <v>46223.574625416666</v>
+        <v>46231.168350196764</v>
       </c>
       <c r="E197" s="10" t="s">
         <v>64</v>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46223.57462474537</v>
+        <v>46231.16835141204</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>64</v>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="C199" s="10"/>
       <c r="D199" s="9">
-        <v>46223.57462407407</v>
+        <v>46231.168352569446</v>
       </c>
       <c r="E199" s="10" t="s">
         <v>72</v>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46223.574623402776</v>
+        <v>46231.16835383102</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>72</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6532,7 +6532,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46231.56037715278</v>
+        <v>46231.65309628472</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -844,7 +844,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -6541,7 +6541,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46231.65309628472</v>
+        <v>46232.83597806713</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>251</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -844,7 +844,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46232.16826707176</v>
+        <v>46233.20600145833</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>334</v>
@@ -9483,8 +9483,8 @@
       <c r="R130" s="5">
         <v>46232</v>
       </c>
-      <c r="S130" s="12" t="s">
-        <v>212</v>
+      <c r="S130" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="T130" s="6">
         <v>0</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46226.191206724536</v>
+        <v>46233.1682352662</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>348</v>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46223.573953645835</v>
+        <v>46233.16823734954</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>214</v>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46223.573953009254</v>
+        <v>46233.16821421296</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>214</v>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46223.57395239583</v>
+        <v>46233.16822767361</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>214</v>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46223.57395174769</v>
+        <v>46233.16822928241</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>214</v>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46223.57395109953</v>
+        <v>46233.16823053241</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>214</v>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46223.57395048611</v>
+        <v>46233.16823174768</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>214</v>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46223.57394983796</v>
+        <v>46233.168232870376</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>223</v>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46223.57394920139</v>
+        <v>46233.16823409722</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>223</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46223.57466138889</v>
+        <v>46233.1876546875</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>412</v>
@@ -12373,8 +12373,8 @@
       <c r="R184" s="5">
         <v>46240</v>
       </c>
-      <c r="S184" s="7" t="s">
-        <v>33</v>
+      <c r="S184" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="T184" s="6">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6541,7 +6541,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46232.83597806713</v>
+        <v>46233.64825909722</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>251</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -9910,7 +9910,7 @@
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46233.1682352662</v>
+        <v>46234.20725170139</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>348</v>
@@ -9954,8 +9954,8 @@
       <c r="R139" s="9">
         <v>46233</v>
       </c>
-      <c r="S139" s="12" t="s">
-        <v>212</v>
+      <c r="S139" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="T139" s="10">
         <v>0</v>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46227.17132248843</v>
+        <v>46234.16991210648</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>364</v>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46223.57407541666</v>
+        <v>46234.169914293976</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>214</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46223.5740747338</v>
+        <v>46234.16991547454</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>214</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46223.57407407407</v>
+        <v>46234.16990346065</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>214</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46223.5740733912</v>
+        <v>46234.1699049537</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>214</v>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46223.57407268518</v>
+        <v>46234.16990650463</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>214</v>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46223.574072013886</v>
+        <v>46234.16990775463</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>214</v>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46223.57407130787</v>
+        <v>46234.169909108794</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>223</v>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46223.574070648145</v>
+        <v>46234.16991053241</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>223</v>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="C201" s="10"/>
       <c r="D201" s="9">
-        <v>46212.62523481481</v>
+        <v>46234.203733518516</v>
       </c>
       <c r="E201" s="10" t="s">
         <v>433</v>
@@ -13268,8 +13268,8 @@
       <c r="R201" s="9">
         <v>46241</v>
       </c>
-      <c r="S201" s="7" t="s">
-        <v>33</v>
+      <c r="S201" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="T201" s="10">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -10397,7 +10397,7 @@
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46234.16991210648</v>
+        <v>46235.18785761574</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>364</v>
@@ -10441,8 +10441,8 @@
       <c r="R148" s="5">
         <v>46234</v>
       </c>
-      <c r="S148" s="12" t="s">
-        <v>212</v>
+      <c r="S148" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="T148" s="6">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -4087,7 +4087,7 @@
         <v>46190.643442395834</v>
       </c>
       <c r="D36" s="5">
-        <v>46223.57344547454</v>
+        <v>46237.542045069444</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>127</v>
@@ -4137,8 +4137,8 @@
       <c r="T36" s="6">
         <v>1</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>78</v>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46230.185757071755</v>
+        <v>46237.16928670139</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>208</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46167.74085901621</v>
+        <v>46237.16928884259</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>214</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46167.74085574074</v>
+        <v>46237.16928469908</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>214</v>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46167.74085291667</v>
+        <v>46237.169367615745</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>214</v>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46167.74085050926</v>
+        <v>46237.16936979166</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>214</v>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46167.74084565972</v>
+        <v>46237.169371909724</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>214</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46167.74084013889</v>
+        <v>46237.169373530094</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>214</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46167.740839074075</v>
+        <v>46237.16937496528</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>223</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46167.740838356476</v>
+        <v>46237.1693767824</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>223</v>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46221.17198219907</v>
+        <v>46237.54214103009</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>268</v>
@@ -7094,8 +7094,8 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
-        <v>78</v>
+      <c r="U87" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46231.18536899306</v>
+        <v>46237.54222934028</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>307</v>
@@ -8505,8 +8505,8 @@
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="11" t="s">
-        <v>63</v>
+      <c r="U112" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46232.18621211806</v>
+        <v>46237.54226962963</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>319</v>
@@ -9002,8 +9002,8 @@
       <c r="T121" s="10">
         <v>0</v>
       </c>
-      <c r="U121" s="11" t="s">
-        <v>63</v>
+      <c r="U121" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46233.20600145833</v>
+        <v>46237.54233449074</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>334</v>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46234.20725170139</v>
+        <v>46237.54241185186</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>348</v>
@@ -9960,8 +9960,8 @@
       <c r="T139" s="10">
         <v>0</v>
       </c>
-      <c r="U139" s="11" t="s">
-        <v>63</v>
+      <c r="U139" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="C218" s="6"/>
       <c r="D218" s="5">
-        <v>46212.62527664352</v>
+        <v>46237.17530560185</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>456</v>
@@ -14179,8 +14179,8 @@
       <c r="R218" s="5">
         <v>46244</v>
       </c>
-      <c r="S218" s="7" t="s">
-        <v>33</v>
+      <c r="S218" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="T218" s="6">
         <v>0</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -844,7 +844,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -6541,7 +6541,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46233.64825909722</v>
+        <v>46237.57050361111</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>251</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46203.50206653935</v>
+        <v>46237.7209872338</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>248</v>
@@ -6541,7 +6541,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46237.57050361111</v>
+        <v>46237.81015790509</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>251</v>
@@ -7543,9 +7543,11 @@
       <c r="B96" s="5">
         <v>46167.5572065625</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46237.7209808912</v>
+      </c>
       <c r="D96" s="5">
-        <v>46224.20563896991</v>
+        <v>46237.72100107639</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>280</v>
@@ -7593,10 +7595,10 @@
         <v>62</v>
       </c>
       <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="12" t="s">
-        <v>78</v>
+        <v>1</v>
+      </c>
+      <c r="U96" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -718,499 +718,499 @@
     <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
+    <t>1215103926643820</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103776749962</t>
+  </si>
+  <si>
+    <t>1215103495723837</t>
+  </si>
+  <si>
+    <t>1215103495723838</t>
+  </si>
+  <si>
+    <t>1215103495723839</t>
+  </si>
+  <si>
+    <t>1215103495723840</t>
+  </si>
+  <si>
+    <t>O 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103495723841</t>
+  </si>
+  <si>
+    <t>OT 4330 - ZVN 1-9-63/2</t>
+  </si>
+  <si>
+    <t>1215103495723842</t>
+  </si>
+  <si>
+    <t>1215103776749974</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215103975192169</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215103975192191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Bodega:</t>
+  </si>
+  <si>
+    <t>1215103975192341</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215103776754403</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103875866783</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215103875866800</t>
+  </si>
+  <si>
+    <t>1215103776789924</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>OT 4328  Control de calidad Armado,Preparación Materiales,OT 4328 Armado</t>
+  </si>
+  <si>
+    <t>1215103776789936</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215103926667039</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103875953926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215103495723625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215103495723626</t>
+  </si>
+  <si>
+    <t>1215103495723627</t>
+  </si>
+  <si>
+    <t>1215103495723628</t>
+  </si>
+  <si>
+    <t>1215103495723629</t>
+  </si>
+  <si>
+    <t>1215103495723630</t>
+  </si>
+  <si>
+    <t>1215103875953948</t>
+  </si>
+  <si>
+    <t>OT 4328 Armado</t>
+  </si>
+  <si>
+    <t>1215103926669155</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,check planos</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 Armado</t>
+  </si>
+  <si>
+    <t>1215103926669273</t>
+  </si>
+  <si>
+    <t>1215103495723631</t>
+  </si>
+  <si>
+    <t>1215103495723632</t>
+  </si>
+  <si>
+    <t>1215103495723633</t>
+  </si>
+  <si>
+    <t>1215103495723634</t>
+  </si>
+  <si>
+    <t>1215103495723635</t>
+  </si>
+  <si>
+    <t>1215103495723636</t>
+  </si>
+  <si>
+    <t>1215103926669295</t>
+  </si>
+  <si>
+    <t>OT 4328  Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215103776817021</t>
+  </si>
+  <si>
+    <t>OT 4328  Control de calidad Armado,ot 4328 - 4330 Revestimiento,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103875982913</t>
+  </si>
+  <si>
+    <t>1215103495723637</t>
+  </si>
+  <si>
+    <t>1215103495723638</t>
+  </si>
+  <si>
+    <t>1215103495723639</t>
+  </si>
+  <si>
+    <t>1215103495723640</t>
+  </si>
+  <si>
+    <t>1215103495723641</t>
+  </si>
+  <si>
+    <t>1215103495723642</t>
+  </si>
+  <si>
+    <t>1215103875982935</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe ot 4328 - 4330,Recepcion motor ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103776817429</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,Bodega:,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103776817451</t>
+  </si>
+  <si>
+    <t>1215103975280532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,Bodega:,OT 4328 - ZVN 1-9-86/2,Reserva Motor  4328 - 4330 </t>
+  </si>
+  <si>
+    <t>1215103975280650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Revestimiento,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103975280667</t>
+  </si>
+  <si>
+    <t>OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4331- TABLERO SS 63 KW,OT 4331- TABLERO SS 63 KW,Revision Tableros</t>
+  </si>
+  <si>
+    <t>1215103975290005</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Montaje motor,ot 4328 - 4330 Revestimiento,ot 4328 - 4330 Montaje Alabe,ot 4328 - 4330 Montaje Rodete,ot 4328 - 4330 Pruebas FAT,ot 4328 - 4330 RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215103975290017</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215103926689480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215103975291283</t>
+  </si>
+  <si>
+    <t>1215103495723643</t>
+  </si>
+  <si>
+    <t>1215103495723644</t>
+  </si>
+  <si>
+    <t>1215103495723645</t>
+  </si>
+  <si>
+    <t>1215103495723646</t>
+  </si>
+  <si>
+    <t>1215103495723647</t>
+  </si>
+  <si>
+    <t>1215103495723648</t>
+  </si>
+  <si>
+    <t>1215103975291300</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215103926689693</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe ot 4328 - 4330,check planos</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Montaje Alabe,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103875995330</t>
+  </si>
+  <si>
+    <t>1215103495723649</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,Recepcion Alabe ot 4328 - 4330,check planos</t>
+  </si>
+  <si>
+    <t>1215103495723650</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,check planos,Recepcion Alabe ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103495723651</t>
+  </si>
+  <si>
+    <t>1215103495723652</t>
+  </si>
+  <si>
+    <t>1215103495723653</t>
+  </si>
+  <si>
+    <t>OT 4330 - ZVN 1-9-63/2,check planos,Recepcion Alabe ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103495723654</t>
+  </si>
+  <si>
+    <t>1215103875882313</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215103926715037</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,ot 4328 - 4330 Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215103876023928</t>
+  </si>
+  <si>
+    <t>1215103495723655</t>
+  </si>
+  <si>
+    <t>1215103495723656</t>
+  </si>
+  <si>
+    <t>1215103495723657</t>
+  </si>
+  <si>
+    <t>1215103495723658</t>
+  </si>
+  <si>
+    <t>1215103495723659</t>
+  </si>
+  <si>
+    <t>OT 4330 - ZVN 1-9-63/2,check planos,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215103495723660</t>
+  </si>
+  <si>
+    <t>OT 4330 - ZVN 1-9-63/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1215103776870737</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Montaje motor</t>
+  </si>
+  <si>
+    <t>1215103776870754</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,Recepcion motor ot 4328 - 4330,check planos</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Montaje motor,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103975325192</t>
+  </si>
+  <si>
+    <t>1215103495723661</t>
+  </si>
+  <si>
+    <t>check planos,Recepcion motor ot 4328 - 4330,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103495723662</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,check planos,Recepcion motor ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103495723663</t>
+  </si>
+  <si>
+    <t>1215103495723664</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,Recepcion motor ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103495723665</t>
+  </si>
+  <si>
+    <t>OT 4330 - ZVN 1-9-63/2,Recepcion motor ot 4328 - 4330</t>
+  </si>
+  <si>
+    <t>1215103495723666</t>
+  </si>
+  <si>
+    <t>1215103975325214</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1215103975335574</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 Pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215104027758696</t>
+  </si>
+  <si>
+    <t>1215103495723667</t>
+  </si>
+  <si>
+    <t>1215103495723668</t>
+  </si>
+  <si>
+    <t>1215103495723669</t>
+  </si>
+  <si>
+    <t>1215103495723670</t>
+  </si>
+  <si>
+    <t>1215103495723673</t>
+  </si>
+  <si>
+    <t>1215103495723674</t>
+  </si>
+  <si>
+    <t>1215104027758718</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215103926643820</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103776749962</t>
-  </si>
-  <si>
-    <t>1215103495723837</t>
-  </si>
-  <si>
-    <t>1215103495723838</t>
-  </si>
-  <si>
-    <t>1215103495723839</t>
-  </si>
-  <si>
-    <t>1215103495723840</t>
-  </si>
-  <si>
-    <t>O 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103495723841</t>
-  </si>
-  <si>
-    <t>OT 4330 - ZVN 1-9-63/2</t>
-  </si>
-  <si>
-    <t>1215103495723842</t>
-  </si>
-  <si>
-    <t>1215103776749974</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215103975192169</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215103975192191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Bodega:</t>
-  </si>
-  <si>
-    <t>1215103975192341</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215103776754403</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103875866783</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215103875866800</t>
-  </si>
-  <si>
-    <t>1215103776789924</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>OT 4328  Control de calidad Armado,Preparación Materiales,OT 4328 Armado</t>
-  </si>
-  <si>
-    <t>1215103776789936</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215103926667039</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103875953926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215103495723625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215103495723626</t>
-  </si>
-  <si>
-    <t>1215103495723627</t>
-  </si>
-  <si>
-    <t>1215103495723628</t>
-  </si>
-  <si>
-    <t>1215103495723629</t>
-  </si>
-  <si>
-    <t>1215103495723630</t>
-  </si>
-  <si>
-    <t>1215103875953948</t>
-  </si>
-  <si>
-    <t>OT 4328 Armado</t>
-  </si>
-  <si>
-    <t>1215103926669155</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,check planos</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 Armado</t>
-  </si>
-  <si>
-    <t>1215103926669273</t>
-  </si>
-  <si>
-    <t>1215103495723631</t>
-  </si>
-  <si>
-    <t>1215103495723632</t>
-  </si>
-  <si>
-    <t>1215103495723633</t>
-  </si>
-  <si>
-    <t>1215103495723634</t>
-  </si>
-  <si>
-    <t>1215103495723635</t>
-  </si>
-  <si>
-    <t>1215103495723636</t>
-  </si>
-  <si>
-    <t>1215103926669295</t>
-  </si>
-  <si>
-    <t>OT 4328  Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215103776817021</t>
-  </si>
-  <si>
-    <t>OT 4328  Control de calidad Armado,ot 4328 - 4330 Revestimiento,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103875982913</t>
-  </si>
-  <si>
-    <t>1215103495723637</t>
-  </si>
-  <si>
-    <t>1215103495723638</t>
-  </si>
-  <si>
-    <t>1215103495723639</t>
-  </si>
-  <si>
-    <t>1215103495723640</t>
-  </si>
-  <si>
-    <t>1215103495723641</t>
-  </si>
-  <si>
-    <t>1215103495723642</t>
-  </si>
-  <si>
-    <t>1215103875982935</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe ot 4328 - 4330,Recepcion motor ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103776817429</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,Bodega:,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103776817451</t>
-  </si>
-  <si>
-    <t>1215103975280532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4330 - ZVN 1-9-63/2,OT 4330 - ZVN 1-9-63/2,OT 4328 - ZVN 1-9-86/2,Bodega:,OT 4328 - ZVN 1-9-86/2,Reserva Motor  4328 - 4330 </t>
-  </si>
-  <si>
-    <t>1215103975280650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Revestimiento,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103975280667</t>
-  </si>
-  <si>
-    <t>OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4329 - TABLERO SS 86 KW,OT 4331- TABLERO SS 63 KW,OT 4331- TABLERO SS 63 KW,Revision Tableros</t>
-  </si>
-  <si>
-    <t>1215103975290005</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Montaje motor,ot 4328 - 4330 Revestimiento,ot 4328 - 4330 Montaje Alabe,ot 4328 - 4330 Montaje Rodete,ot 4328 - 4330 Pruebas FAT,ot 4328 - 4330 RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215103975290017</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215103926689480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4328 - ZVN 1-9-86/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215103975291283</t>
-  </si>
-  <si>
-    <t>1215103495723643</t>
-  </si>
-  <si>
-    <t>1215103495723644</t>
-  </si>
-  <si>
-    <t>1215103495723645</t>
-  </si>
-  <si>
-    <t>1215103495723646</t>
-  </si>
-  <si>
-    <t>1215103495723647</t>
-  </si>
-  <si>
-    <t>1215103495723648</t>
-  </si>
-  <si>
-    <t>1215103975291300</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215103926689693</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe ot 4328 - 4330,check planos</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Montaje Alabe,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103875995330</t>
-  </si>
-  <si>
-    <t>1215103495723649</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Recepcion Alabe ot 4328 - 4330,check planos</t>
-  </si>
-  <si>
-    <t>1215103495723650</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,check planos,Recepcion Alabe ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103495723651</t>
-  </si>
-  <si>
-    <t>1215103495723652</t>
-  </si>
-  <si>
-    <t>1215103495723653</t>
-  </si>
-  <si>
-    <t>OT 4330 - ZVN 1-9-63/2,check planos,Recepcion Alabe ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103495723654</t>
-  </si>
-  <si>
-    <t>1215103875882313</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215103926715037</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,ot 4328 - 4330 Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215103876023928</t>
-  </si>
-  <si>
-    <t>1215103495723655</t>
-  </si>
-  <si>
-    <t>1215103495723656</t>
-  </si>
-  <si>
-    <t>1215103495723657</t>
-  </si>
-  <si>
-    <t>1215103495723658</t>
-  </si>
-  <si>
-    <t>1215103495723659</t>
-  </si>
-  <si>
-    <t>OT 4330 - ZVN 1-9-63/2,check planos,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215103495723660</t>
-  </si>
-  <si>
-    <t>OT 4330 - ZVN 1-9-63/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1215103776870737</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Montaje motor</t>
-  </si>
-  <si>
-    <t>1215103776870754</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Recepcion motor ot 4328 - 4330,check planos</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Montaje motor,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103975325192</t>
-  </si>
-  <si>
-    <t>1215103495723661</t>
-  </si>
-  <si>
-    <t>check planos,Recepcion motor ot 4328 - 4330,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103495723662</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,check planos,Recepcion motor ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103495723663</t>
-  </si>
-  <si>
-    <t>1215103495723664</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,Recepcion motor ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103495723665</t>
-  </si>
-  <si>
-    <t>OT 4330 - ZVN 1-9-63/2,Recepcion motor ot 4328 - 4330</t>
-  </si>
-  <si>
-    <t>1215103495723666</t>
-  </si>
-  <si>
-    <t>1215103975325214</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1215103975335574</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 Pruebas FAT,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215104027758696</t>
-  </si>
-  <si>
-    <t>1215103495723667</t>
-  </si>
-  <si>
-    <t>1215103495723668</t>
-  </si>
-  <si>
-    <t>1215103495723669</t>
-  </si>
-  <si>
-    <t>1215103495723670</t>
-  </si>
-  <si>
-    <t>1215103495723673</t>
-  </si>
-  <si>
-    <t>1215103495723674</t>
-  </si>
-  <si>
-    <t>1215104027758718</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1215103975335766</t>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46237.16928670139</v>
+        <v>46238.19311207176</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>208</v>
@@ -5606,8 +5606,8 @@
       <c r="R61" s="9">
         <v>46237</v>
       </c>
-      <c r="S61" s="12" t="s">
-        <v>212</v>
+      <c r="S61" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="T61" s="10">
         <v>0</v>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B62" s="5">
         <v>46167.5570684375</v>
@@ -5628,7 +5628,7 @@
         <v>46237.16928884259</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5658,10 +5658,10 @@
         <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5671,7 +5671,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B63" s="9">
         <v>46167.55707274306</v>
@@ -5681,7 +5681,7 @@
         <v>46237.16928469908</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5711,10 +5711,10 @@
         <v>208</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>214</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46167.65975748842</v>
@@ -5734,7 +5734,7 @@
         <v>46237.169367615745</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5764,10 +5764,10 @@
         <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46167.65976925926</v>
@@ -5787,7 +5787,7 @@
         <v>46237.16936979166</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5817,10 +5817,10 @@
         <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5830,7 +5830,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46167.65978199074</v>
@@ -5840,7 +5840,7 @@
         <v>46237.169371909724</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5870,10 +5870,10 @@
         <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
         <v>46167.659797824075</v>
@@ -5893,7 +5893,7 @@
         <v>46237.169373530094</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5923,10 +5923,10 @@
         <v>208</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
         <v>46167.65987638889</v>
@@ -5946,7 +5946,7 @@
         <v>46237.16937496528</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5976,10 +5976,10 @@
         <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5989,7 +5989,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
         <v>46167.65988679398</v>
@@ -5999,7 +5999,7 @@
         <v>46237.1693767824</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -6029,10 +6029,10 @@
         <v>208</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -6042,7 +6042,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B70" s="5">
         <v>46167.5570771412</v>
@@ -6054,7 +6054,7 @@
         <v>46216.8019547338</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -6078,7 +6078,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -6095,7 +6095,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
         <v>46167.55708079861</v>
@@ -6107,16 +6107,16 @@
         <v>46216.686107546295</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="H71" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="I71" s="9">
         <v>46205</v>
@@ -6134,13 +6134,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>160</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="9">
         <v>46205</v>
@@ -6160,7 +6160,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46167.5570859838</v>
@@ -6172,7 +6172,7 @@
         <v>46216.802392673606</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -6199,13 +6199,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="Q72" s="5">
         <v>46209</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B73" s="9">
         <v>46167.55709181713</v>
@@ -6237,16 +6237,16 @@
         <v>46216.68612113426</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="I73" s="9">
         <v>46205</v>
@@ -6264,13 +6264,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>168</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q73" s="9">
         <v>46205</v>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B74" s="5">
         <v>46167.55709682871</v>
@@ -6302,7 +6302,7 @@
         <v>46216.801934849536</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6329,13 +6329,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="5">
         <v>46209</v>
@@ -6355,7 +6355,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46167.55715278935</v>
@@ -6367,16 +6367,16 @@
         <v>46216.68613528935</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="I75" s="9">
         <v>46205</v>
@@ -6394,13 +6394,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="9">
         <v>46205</v>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46167.55716416667</v>
@@ -6432,7 +6432,7 @@
         <v>46216.801944085644</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6459,13 +6459,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q76" s="5">
         <v>46209</v>
@@ -6485,7 +6485,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46167.557168680556</v>
@@ -6495,7 +6495,7 @@
         <v>46237.7209872338</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6519,7 +6519,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6532,7 +6532,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46167.55717219907</v>
@@ -6544,16 +6544,16 @@
         <v>46237.81015790509</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I78" s="5">
         <v>46211</v>
@@ -6571,13 +6571,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="5">
         <v>46211</v>
@@ -6597,7 +6597,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
         <v>46167.557178229166</v>
@@ -6609,16 +6609,16 @@
         <v>46216.80193877315</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I79" s="9">
         <v>46211</v>
@@ -6636,13 +6636,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6652,7 +6652,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46167.55718505787</v>
@@ -6664,16 +6664,16 @@
         <v>46216.80193822917</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I80" s="5">
         <v>46211</v>
@@ -6691,13 +6691,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46167.629964050924</v>
@@ -6719,16 +6719,16 @@
         <v>46216.801934814815</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I81" s="9">
         <v>46211</v>
@@ -6746,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46167.6299746875</v>
@@ -6774,16 +6774,16 @@
         <v>46216.80193553241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I82" s="5">
         <v>46211</v>
@@ -6801,13 +6801,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6817,7 +6817,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46167.63011578703</v>
@@ -6829,16 +6829,16 @@
         <v>46216.80193606482</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I83" s="9">
         <v>46211</v>
@@ -6856,13 +6856,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6872,7 +6872,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46167.630126516204</v>
@@ -6884,16 +6884,16 @@
         <v>46216.801936585645</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I84" s="5">
         <v>46211</v>
@@ -6911,13 +6911,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B85" s="9">
         <v>46167.63145555556</v>
@@ -6939,16 +6939,16 @@
         <v>46216.801937083335</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I85" s="9">
         <v>46211</v>
@@ -6966,13 +6966,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46167.631772685185</v>
@@ -6994,16 +6994,16 @@
         <v>46216.801937592594</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I86" s="5">
         <v>46211</v>
@@ -7021,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7037,7 +7037,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B87" s="9">
         <v>46167.557190844906</v>
@@ -7047,16 +7047,16 @@
         <v>46237.54214103009</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I87" s="9">
         <v>46216</v>
@@ -7074,13 +7074,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>211</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q87" s="9">
         <v>46216</v>
@@ -7100,7 +7100,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B88" s="5">
         <v>46167.557195092595</v>
@@ -7112,16 +7112,16 @@
         <v>46209.725033622686</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I88" s="5">
         <v>46216</v>
@@ -7139,13 +7139,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>270</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -7155,7 +7155,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B89" s="9">
         <v>46167.557200995376</v>
@@ -7167,16 +7167,16 @@
         <v>46209.72516011574</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I89" s="9">
         <v>46216</v>
@@ -7194,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B90" s="5">
         <v>46167.63214916667</v>
@@ -7222,16 +7222,16 @@
         <v>46209.725171666665</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I90" s="5">
         <v>46216</v>
@@ -7249,10 +7249,10 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>211</v>
@@ -7265,7 +7265,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B91" s="9">
         <v>46167.63219107639</v>
@@ -7277,16 +7277,16 @@
         <v>46209.72518666666</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I91" s="9">
         <v>46216</v>
@@ -7304,13 +7304,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7320,7 +7320,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B92" s="5">
         <v>46167.63220099537</v>
@@ -7332,16 +7332,16 @@
         <v>46209.725205462964</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I92" s="5">
         <v>46216</v>
@@ -7359,13 +7359,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7375,7 +7375,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B93" s="9">
         <v>46167.63220839121</v>
@@ -7385,16 +7385,16 @@
         <v>46220.16910454861</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I93" s="9">
         <v>46216</v>
@@ -7412,13 +7412,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7428,7 +7428,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B94" s="5">
         <v>46167.63225591435</v>
@@ -7440,16 +7440,16 @@
         <v>46203.50339560185</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I94" s="5">
         <v>46216</v>
@@ -7467,13 +7467,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B95" s="9">
         <v>46167.63226373843</v>
@@ -7495,16 +7495,16 @@
         <v>46203.50367474537</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I95" s="9">
         <v>46216</v>
@@ -7522,13 +7522,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B96" s="5">
         <v>46167.5572065625</v>
@@ -7550,7 +7550,7 @@
         <v>46237.72100107639</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7577,13 +7577,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>211</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q96" s="5">
         <v>46223</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B97" s="9">
         <v>46167.557210914354</v>
@@ -7615,7 +7615,7 @@
         <v>46209.725893599534</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7642,13 +7642,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7658,7 +7658,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B98" s="5">
         <v>46167.55721697917</v>
@@ -7670,7 +7670,7 @@
         <v>46209.725886851855</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7697,13 +7697,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B99" s="9">
         <v>46167.632342048615</v>
@@ -7725,7 +7725,7 @@
         <v>46209.72588194444</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7752,10 +7752,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>26</v>
@@ -7768,7 +7768,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B100" s="5">
         <v>46167.63235868055</v>
@@ -7780,7 +7780,7 @@
         <v>46209.72587559027</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7807,13 +7807,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7823,7 +7823,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B101" s="9">
         <v>46167.63236590278</v>
@@ -7835,7 +7835,7 @@
         <v>46209.725869594906</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7862,13 +7862,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B102" s="5">
         <v>46167.63237413194</v>
@@ -7888,7 +7888,7 @@
         <v>46223.16901707176</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7915,13 +7915,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B103" s="9">
         <v>46167.63244320602</v>
@@ -7943,7 +7943,7 @@
         <v>46209.7258571875</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7970,13 +7970,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B104" s="5">
         <v>46167.63245268518</v>
@@ -7998,7 +7998,7 @@
         <v>46209.725848692135</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8025,13 +8025,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B105" s="9">
         <v>46167.55722248842</v>
@@ -8051,7 +8051,7 @@
         <v>46189.87746019676</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>25</v>
@@ -8075,7 +8075,7 @@
         <v>26</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>26</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B106" s="5">
         <v>46167.557225682875</v>
@@ -8098,16 +8098,16 @@
         <v>46195.92990200232</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I106" s="5">
         <v>46184</v>
@@ -8125,13 +8125,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q106" s="5">
         <v>46184</v>
@@ -8151,7 +8151,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B107" s="9">
         <v>46167.557231493054</v>
@@ -8167,10 +8167,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="I107" s="9">
         <v>46167</v>
@@ -8188,13 +8188,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>127</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q107" s="9">
         <v>46167</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B108" s="5">
         <v>46167.55723746528</v>
@@ -8230,10 +8230,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I108" s="5">
         <v>46168</v>
@@ -8251,13 +8251,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q108" s="5">
         <v>46168</v>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B109" s="9">
         <v>46167.55724847222</v>
@@ -8287,16 +8287,16 @@
         <v>46204.59517594907</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="I109" s="9">
         <v>46265</v>
@@ -8314,13 +8314,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>178</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q109" s="9">
         <v>46265</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46167.55725353009</v>
@@ -8356,10 +8356,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="I110" s="5">
         <v>46220</v>
@@ -8377,13 +8377,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>149</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q110" s="5">
         <v>46220</v>
@@ -8403,7 +8403,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B111" s="9">
         <v>46167.5572591088</v>
@@ -8413,7 +8413,7 @@
         <v>46167.73130032407</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -8437,7 +8437,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B112" s="5">
         <v>46167.557262685186</v>
@@ -8460,7 +8460,7 @@
         <v>46237.54222934028</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8487,13 +8487,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q112" s="5">
         <v>46224</v>
@@ -8513,7 +8513,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B113" s="9">
         <v>46167.55727085649</v>
@@ -8523,7 +8523,7 @@
         <v>46230.16889255787</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8550,10 +8550,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8566,7 +8566,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B114" s="5">
         <v>46167.55727532407</v>
@@ -8576,7 +8576,7 @@
         <v>46230.16889612269</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8603,10 +8603,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8619,7 +8619,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B115" s="9">
         <v>46167.632606053245</v>
@@ -8631,7 +8631,7 @@
         <v>46223.573618090275</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8658,13 +8658,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8674,7 +8674,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46167.63261443287</v>
@@ -8686,7 +8686,7 @@
         <v>46223.57361446759</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8713,13 +8713,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B117" s="9">
         <v>46167.63262241898</v>
@@ -8741,7 +8741,7 @@
         <v>46223.57361017361</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8768,13 +8768,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8784,7 +8784,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B118" s="5">
         <v>46167.63263039352</v>
@@ -8794,7 +8794,7 @@
         <v>46230.16885648148</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8821,13 +8821,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8837,7 +8837,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B119" s="9">
         <v>46167.63269008102</v>
@@ -8849,7 +8849,7 @@
         <v>46223.57359932871</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8876,13 +8876,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8892,7 +8892,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B120" s="5">
         <v>46167.632698738424</v>
@@ -8904,7 +8904,7 @@
         <v>46223.57359854167</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8931,13 +8931,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8947,7 +8947,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B121" s="9">
         <v>46167.55727960648</v>
@@ -8957,7 +8957,7 @@
         <v>46237.54226962963</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8984,13 +8984,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>211</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q121" s="9">
         <v>46231</v>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B122" s="5">
         <v>46167.557284375</v>
@@ -9020,7 +9020,7 @@
         <v>46231.16835666666</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9047,13 +9047,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O122" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="P122" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>322</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9063,7 +9063,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B123" s="9">
         <v>46167.55729009259</v>
@@ -9073,7 +9073,7 @@
         <v>46231.16835527778</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -9100,13 +9100,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O123" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="P123" s="10" t="s">
         <v>321</v>
-      </c>
-      <c r="P123" s="10" t="s">
-        <v>322</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -9116,7 +9116,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B124" s="5">
         <v>46167.6328130787</v>
@@ -9126,7 +9126,7 @@
         <v>46231.16833541667</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9153,13 +9153,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B125" s="9">
         <v>46167.63283585648</v>
@@ -9179,7 +9179,7 @@
         <v>46231.16833734953</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -9206,13 +9206,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B126" s="5">
         <v>46167.63284336806</v>
@@ -9232,7 +9232,7 @@
         <v>46231.16833881944</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9259,13 +9259,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B127" s="9">
         <v>46167.63285163195</v>
@@ -9285,7 +9285,7 @@
         <v>46231.16834034723</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -9312,13 +9312,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9328,7 +9328,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B128" s="5">
         <v>46167.63289178241</v>
@@ -9338,7 +9338,7 @@
         <v>46231.168341701385</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9365,13 +9365,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9381,7 +9381,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B129" s="9">
         <v>46167.632899212964</v>
@@ -9391,7 +9391,7 @@
         <v>46231.16834335648</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9418,13 +9418,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9434,7 +9434,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B130" s="5">
         <v>46167.55733736111</v>
@@ -9444,7 +9444,7 @@
         <v>46237.54233449074</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9471,13 +9471,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>211</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q130" s="5">
         <v>46232</v>
@@ -9497,7 +9497,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B131" s="9">
         <v>46167.557343645836</v>
@@ -9507,7 +9507,7 @@
         <v>46232.168270462964</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9532,13 +9532,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O131" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="P131" s="10" t="s">
         <v>336</v>
-      </c>
-      <c r="P131" s="10" t="s">
-        <v>337</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9548,7 +9548,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B132" s="5">
         <v>46167.55735079861</v>
@@ -9558,7 +9558,7 @@
         <v>46232.16826924769</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9583,13 +9583,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B133" s="9">
         <v>46167.63302359954</v>
@@ -9609,7 +9609,7 @@
         <v>46232.1682587963</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9634,13 +9634,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B134" s="5">
         <v>46167.63303486111</v>
@@ -9660,7 +9660,7 @@
         <v>46232.16826065972</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9685,13 +9685,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9701,7 +9701,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B135" s="9">
         <v>46167.633050648146</v>
@@ -9711,7 +9711,7 @@
         <v>46232.16826200232</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9736,13 +9736,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9752,7 +9752,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B136" s="5">
         <v>46167.633060671295</v>
@@ -9762,7 +9762,7 @@
         <v>46232.16826334491</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9787,13 +9787,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9803,7 +9803,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B137" s="9">
         <v>46167.633115185185</v>
@@ -9813,7 +9813,7 @@
         <v>46232.168264629625</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9838,13 +9838,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9854,7 +9854,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B138" s="5">
         <v>46167.6331228125</v>
@@ -9864,7 +9864,7 @@
         <v>46232.1682658912</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9889,13 +9889,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9905,7 +9905,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B139" s="9">
         <v>46167.557357488426</v>
@@ -9915,7 +9915,7 @@
         <v>46237.54241185186</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9942,13 +9942,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>211</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q139" s="9">
         <v>46233</v>
@@ -9968,7 +9968,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B140" s="5">
         <v>46167.55736211805</v>
@@ -9978,7 +9978,7 @@
         <v>46233.16823734954</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10005,13 +10005,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O140" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="P140" s="6" t="s">
         <v>350</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>351</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10021,7 +10021,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B141" s="9">
         <v>46167.55737267361</v>
@@ -10031,7 +10031,7 @@
         <v>46233.16821421296</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -10058,13 +10058,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O141" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="P141" s="10" t="s">
         <v>350</v>
-      </c>
-      <c r="P141" s="10" t="s">
-        <v>351</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -10074,7 +10074,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B142" s="5">
         <v>46167.63325159722</v>
@@ -10084,7 +10084,7 @@
         <v>46233.16822767361</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10111,13 +10111,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10127,7 +10127,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B143" s="9">
         <v>46167.63325929398</v>
@@ -10137,7 +10137,7 @@
         <v>46233.16822928241</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -10164,13 +10164,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -10180,7 +10180,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B144" s="5">
         <v>46167.633274293985</v>
@@ -10190,7 +10190,7 @@
         <v>46233.16823053241</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10217,13 +10217,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10233,7 +10233,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B145" s="9">
         <v>46167.633281875</v>
@@ -10243,7 +10243,7 @@
         <v>46233.16823174768</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -10270,13 +10270,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B146" s="5">
         <v>46167.63332260417</v>
@@ -10296,7 +10296,7 @@
         <v>46233.168232870376</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10323,13 +10323,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10339,7 +10339,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B147" s="9">
         <v>46167.633331689816</v>
@@ -10349,7 +10349,7 @@
         <v>46233.16823409722</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -10376,13 +10376,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -10392,7 +10392,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B148" s="5">
         <v>46167.557378287034</v>
@@ -10402,7 +10402,7 @@
         <v>46235.18785761574</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10429,13 +10429,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>211</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q148" s="5">
         <v>46234</v>
@@ -10455,7 +10455,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B149" s="9">
         <v>46167.55738292824</v>
@@ -10465,7 +10465,7 @@
         <v>46234.169914293976</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10492,13 +10492,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10508,7 +10508,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B150" s="5">
         <v>46167.5573883912</v>
@@ -10518,7 +10518,7 @@
         <v>46234.16991547454</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10545,13 +10545,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10561,7 +10561,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B151" s="9">
         <v>46167.63341660879</v>
@@ -10571,7 +10571,7 @@
         <v>46234.16990346065</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10598,13 +10598,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B152" s="5">
         <v>46167.63343371528</v>
@@ -10624,7 +10624,7 @@
         <v>46234.1699049537</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10651,13 +10651,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10667,7 +10667,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B153" s="9">
         <v>46167.63344365741</v>
@@ -10677,7 +10677,7 @@
         <v>46234.16990650463</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10704,13 +10704,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B154" s="5">
         <v>46167.63345188658</v>
@@ -10730,7 +10730,7 @@
         <v>46234.16990775463</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10757,13 +10757,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B155" s="9">
         <v>46167.633506412036</v>
@@ -10783,7 +10783,7 @@
         <v>46234.169909108794</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10810,13 +10810,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10826,7 +10826,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B156" s="5">
         <v>46167.63351399306</v>
@@ -10836,7 +10836,7 @@
         <v>46234.16991053241</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10863,13 +10863,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10879,17 +10879,17 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B157" s="9">
         <v>46167.55739407407</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46231.18471695602</v>
+        <v>46238.168338703705</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
@@ -10916,13 +10916,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O157" s="10" t="s">
         <v>211</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q157" s="9">
         <v>46238</v>
@@ -10931,7 +10931,7 @@
         <v>46238</v>
       </c>
       <c r="S157" s="12" t="s">
-        <v>212</v>
+        <v>376</v>
       </c>
       <c r="T157" s="10">
         <v>0</v>
@@ -10949,10 +10949,10 @@
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46223.57418311342</v>
+        <v>46238.168336041665</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10979,10 +10979,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>378</v>
@@ -11002,10 +11002,10 @@
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46223.574182488424</v>
+        <v>46238.16833738426</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
@@ -11032,10 +11032,10 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P159" s="10" t="s">
         <v>378</v>
@@ -11055,10 +11055,10 @@
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46223.57418185185</v>
+        <v>46238.168326597224</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11085,13 +11085,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11108,10 +11108,10 @@
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46223.57418118056</v>
+        <v>46238.16832803241</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
@@ -11138,13 +11138,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -11161,10 +11161,10 @@
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46223.57418053241</v>
+        <v>46238.168329259264</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11191,13 +11191,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11214,10 +11214,10 @@
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46223.57417979167</v>
+        <v>46238.16833069445</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11244,13 +11244,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -11267,10 +11267,10 @@
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46223.57417917824</v>
+        <v>46238.168331875</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11297,13 +11297,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11320,10 +11320,10 @@
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46223.57417856481</v>
+        <v>46238.168333194444</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
@@ -11350,13 +11350,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11465,7 +11465,7 @@
         <v>46239</v>
       </c>
       <c r="S167" s="12" t="s">
-        <v>212</v>
+        <v>376</v>
       </c>
       <c r="T167" s="10">
         <v>0</v>
@@ -11486,7 +11486,7 @@
         <v>46167.74286244213</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11516,7 +11516,7 @@
         <v>390</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>395</v>
@@ -11539,7 +11539,7 @@
         <v>46167.742859606486</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11569,7 +11569,7 @@
         <v>390</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>395</v>
@@ -11592,7 +11592,7 @@
         <v>46167.74285702546</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11622,7 +11622,7 @@
         <v>390</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>395</v>
@@ -11645,7 +11645,7 @@
         <v>46167.742854375</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11675,7 +11675,7 @@
         <v>390</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P171" s="10" t="s">
         <v>395</v>
@@ -11698,7 +11698,7 @@
         <v>46167.74285166667</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11728,10 +11728,10 @@
         <v>390</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11751,7 +11751,7 @@
         <v>46167.74284892361</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11781,10 +11781,10 @@
         <v>390</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11804,7 +11804,7 @@
         <v>46167.742846469904</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11834,10 +11834,10 @@
         <v>390</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11857,7 +11857,7 @@
         <v>46167.74284369213</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11887,10 +11887,10 @@
         <v>390</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -12376,7 +12376,7 @@
         <v>46240</v>
       </c>
       <c r="S184" s="12" t="s">
-        <v>212</v>
+        <v>376</v>
       </c>
       <c r="T184" s="6">
         <v>0</v>
@@ -12397,7 +12397,7 @@
         <v>46223.57463326389</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
@@ -12425,7 +12425,7 @@
         <v>412</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P185" s="10" t="s">
         <v>415</v>
@@ -12448,7 +12448,7 @@
         <v>46223.57463260417</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12476,7 +12476,7 @@
         <v>412</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>417</v>
@@ -12499,7 +12499,7 @@
         <v>46223.57463199074</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
@@ -12527,7 +12527,7 @@
         <v>412</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P187" s="10" t="s">
         <v>417</v>
@@ -12550,7 +12550,7 @@
         <v>46223.57463131944</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12578,7 +12578,7 @@
         <v>412</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>417</v>
@@ -12601,7 +12601,7 @@
         <v>46223.5746305787</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
@@ -12629,10 +12629,10 @@
         <v>412</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12652,7 +12652,7 @@
         <v>46223.574629849536</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12680,10 +12680,10 @@
         <v>412</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12703,7 +12703,7 @@
         <v>46223.57462922454</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
@@ -12731,10 +12731,10 @@
         <v>412</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12754,7 +12754,7 @@
         <v>46223.574628622686</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -12782,10 +12782,10 @@
         <v>412</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13235,10 +13235,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H201" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I201" s="9">
         <v>46241</v>
@@ -13271,7 +13271,7 @@
         <v>46241</v>
       </c>
       <c r="S201" s="12" t="s">
-        <v>212</v>
+        <v>376</v>
       </c>
       <c r="T201" s="10">
         <v>0</v>
@@ -13292,16 +13292,16 @@
         <v>46167.74367725695</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G202" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H202" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H202" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I202" s="5">
         <v>46241</v>
@@ -13322,7 +13322,7 @@
         <v>433</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>435</v>
@@ -13345,16 +13345,16 @@
         <v>46167.743674363424</v>
       </c>
       <c r="E203" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F203" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H203" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I203" s="9">
         <v>46241</v>
@@ -13375,7 +13375,7 @@
         <v>433</v>
       </c>
       <c r="O203" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P203" s="10" t="s">
         <v>437</v>
@@ -13398,16 +13398,16 @@
         <v>46167.743671840275</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I204" s="5">
         <v>46241</v>
@@ -13428,7 +13428,7 @@
         <v>433</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>439</v>
@@ -13451,16 +13451,16 @@
         <v>46167.74366940973</v>
       </c>
       <c r="E205" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F205" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G205" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H205" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I205" s="9">
         <v>46241</v>
@@ -13481,7 +13481,7 @@
         <v>433</v>
       </c>
       <c r="O205" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P205" s="10" t="s">
         <v>439</v>
@@ -13504,16 +13504,16 @@
         <v>46167.74366684028</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H206" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I206" s="5">
         <v>46241</v>
@@ -13534,10 +13534,10 @@
         <v>433</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q206" s="6"/>
       <c r="R206" s="6"/>
@@ -13557,16 +13557,16 @@
         <v>46167.74366416667</v>
       </c>
       <c r="E207" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F207" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H207" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I207" s="9">
         <v>46241</v>
@@ -13587,10 +13587,10 @@
         <v>433</v>
       </c>
       <c r="O207" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P207" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q207" s="10"/>
       <c r="R207" s="10"/>
@@ -13610,16 +13610,16 @@
         <v>46167.74366101852</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G208" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H208" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H208" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I208" s="5">
         <v>46241</v>
@@ -13640,7 +13640,7 @@
         <v>433</v>
       </c>
       <c r="O208" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P208" s="6" t="s">
         <v>444</v>
@@ -13663,16 +13663,16 @@
         <v>46167.743658402775</v>
       </c>
       <c r="E209" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G209" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H209" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I209" s="9">
         <v>46241</v>
@@ -13693,7 +13693,7 @@
         <v>433</v>
       </c>
       <c r="O209" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P209" s="10" t="s">
         <v>444</v>
@@ -13722,10 +13722,10 @@
         <v>26</v>
       </c>
       <c r="G210" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H210" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H210" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I210" s="5">
         <v>46241</v>
@@ -13775,10 +13775,10 @@
         <v>26</v>
       </c>
       <c r="G211" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H211" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I211" s="9">
         <v>46241</v>
@@ -13828,10 +13828,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H212" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I212" s="5">
         <v>46241</v>
@@ -13881,10 +13881,10 @@
         <v>26</v>
       </c>
       <c r="G213" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H213" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I213" s="9">
         <v>46241</v>
@@ -13934,10 +13934,10 @@
         <v>26</v>
       </c>
       <c r="G214" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H214" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I214" s="5">
         <v>46241</v>
@@ -13987,10 +13987,10 @@
         <v>26</v>
       </c>
       <c r="G215" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H215" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I215" s="9">
         <v>46241</v>
@@ -14040,10 +14040,10 @@
         <v>26</v>
       </c>
       <c r="G216" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H216" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H216" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I216" s="5">
         <v>46241</v>
@@ -14093,10 +14093,10 @@
         <v>26</v>
       </c>
       <c r="G217" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H217" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I217" s="9">
         <v>46241</v>
@@ -14146,10 +14146,10 @@
         <v>26</v>
       </c>
       <c r="G218" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H218" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H218" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I218" s="5">
         <v>46244</v>
@@ -14182,7 +14182,7 @@
         <v>46244</v>
       </c>
       <c r="S218" s="12" t="s">
-        <v>212</v>
+        <v>376</v>
       </c>
       <c r="T218" s="6">
         <v>0</v>
@@ -14203,16 +14203,16 @@
         <v>46167.74384899306</v>
       </c>
       <c r="E219" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G219" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H219" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H219" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I219" s="9">
         <v>46244</v>
@@ -14233,7 +14233,7 @@
         <v>456</v>
       </c>
       <c r="O219" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P219" s="10" t="s">
         <v>456</v>
@@ -14256,16 +14256,16 @@
         <v>46167.74384597222</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G220" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H220" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H220" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I220" s="5">
         <v>46244</v>
@@ -14286,7 +14286,7 @@
         <v>456</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>456</v>
@@ -14309,16 +14309,16 @@
         <v>46167.743843414355</v>
       </c>
       <c r="E221" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G221" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H221" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H221" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I221" s="9">
         <v>46244</v>
@@ -14339,7 +14339,7 @@
         <v>456</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>456</v>
@@ -14362,16 +14362,16 @@
         <v>46167.7438406713</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G222" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H222" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H222" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I222" s="5">
         <v>46244</v>
@@ -14392,7 +14392,7 @@
         <v>456</v>
       </c>
       <c r="O222" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P222" s="6" t="s">
         <v>456</v>
@@ -14415,16 +14415,16 @@
         <v>46167.743837939815</v>
       </c>
       <c r="E223" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G223" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H223" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H223" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I223" s="9">
         <v>46244</v>
@@ -14445,7 +14445,7 @@
         <v>456</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>26</v>
@@ -14468,16 +14468,16 @@
         <v>46167.74383519676</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G224" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H224" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H224" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I224" s="5">
         <v>46244</v>
@@ -14498,7 +14498,7 @@
         <v>456</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>26</v>
@@ -14527,10 +14527,10 @@
         <v>26</v>
       </c>
       <c r="G225" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H225" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H225" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I225" s="9">
         <v>46244</v>
@@ -14551,7 +14551,7 @@
         <v>456</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>26</v>
@@ -14580,10 +14580,10 @@
         <v>26</v>
       </c>
       <c r="G226" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H226" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I226" s="5">
         <v>46244</v>
@@ -14604,7 +14604,7 @@
         <v>456</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>26</v>
@@ -14633,10 +14633,10 @@
         <v>26</v>
       </c>
       <c r="G227" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H227" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H227" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I227" s="9">
         <v>46244</v>
@@ -14686,10 +14686,10 @@
         <v>26</v>
       </c>
       <c r="G228" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H228" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H228" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I228" s="5">
         <v>46244</v>
@@ -14739,10 +14739,10 @@
         <v>26</v>
       </c>
       <c r="G229" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H229" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H229" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I229" s="9">
         <v>46244</v>
@@ -14792,10 +14792,10 @@
         <v>26</v>
       </c>
       <c r="G230" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H230" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H230" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I230" s="5">
         <v>46244</v>
@@ -14845,10 +14845,10 @@
         <v>26</v>
       </c>
       <c r="G231" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H231" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H231" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I231" s="9">
         <v>46244</v>
@@ -14898,10 +14898,10 @@
         <v>26</v>
       </c>
       <c r="G232" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H232" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H232" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I232" s="5">
         <v>46244</v>
@@ -14951,10 +14951,10 @@
         <v>26</v>
       </c>
       <c r="G233" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H233" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="H233" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="I233" s="9">
         <v>46244</v>
@@ -15004,10 +15004,10 @@
         <v>26</v>
       </c>
       <c r="G234" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H234" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="H234" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="I234" s="5">
         <v>46244</v>

--- a/data/50001554 - MAPIMI.xlsx
+++ b/data/50001554 - MAPIMI.xlsx
@@ -841,7 +841,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4328 - ZVN 1-9-86/2,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215103926667039</t>
@@ -1210,58 +1210,58 @@
     <t>Montaje:,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1215103975335766</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330 RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1215103975335783</t>
+  </si>
+  <si>
+    <t>1215103495723675</t>
+  </si>
+  <si>
+    <t>1215103495723676</t>
+  </si>
+  <si>
+    <t>1215103495723677</t>
+  </si>
+  <si>
+    <t>1215103495723678</t>
+  </si>
+  <si>
+    <t>1215103495723679</t>
+  </si>
+  <si>
+    <t>1215103495723680</t>
+  </si>
+  <si>
+    <t>1215103876049064</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330- 4329  Embalaje,ot 4328 - 4330- 4329   Despacho,ot 4328 - 4330- 4329 PACKING LIST,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1215103876049076</t>
+  </si>
+  <si>
+    <t>ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Revision Tableros,ot 4328 - 4330 RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215103975335766</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330 RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1215103975335783</t>
-  </si>
-  <si>
-    <t>1215103495723675</t>
-  </si>
-  <si>
-    <t>1215103495723676</t>
-  </si>
-  <si>
-    <t>1215103495723677</t>
-  </si>
-  <si>
-    <t>1215103495723678</t>
-  </si>
-  <si>
-    <t>1215103495723679</t>
-  </si>
-  <si>
-    <t>1215103495723680</t>
-  </si>
-  <si>
-    <t>1215103876049064</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330- 4329  Embalaje,ot 4328 - 4330- 4329   Despacho,ot 4328 - 4330- 4329 PACKING LIST,ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1215103876049076</t>
-  </si>
-  <si>
-    <t>ot 4328 - 4330- 4329  Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,Revision Tableros,ot 4328 - 4330 RE-PINTADO,OT 4328 - ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1215104027762191</t>
@@ -6541,7 +6541,7 @@
         <v>46203.50206046297</v>
       </c>
       <c r="D78" s="5">
-        <v>46237.81015790509</v>
+        <v>46239.574233692125</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46238.168338703705</v>
+        <v>46239.1994606713</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>374</v>
@@ -10930,8 +10930,8 @@
       <c r="R157" s="9">
         <v>46238</v>
       </c>
-      <c r="S157" s="12" t="s">
-        <v>376</v>
+      <c r="S157" s="11" t="s">
+        <v>62</v>
       </c>
       <c r="T157" s="10">
         <v>0</v>
@@ -10942,7 +10942,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B158" s="5">
         <v>46167.55739920139</v>
@@ -10985,7 +10985,7 @@
         <v>213</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10995,7 +10995,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B159" s="9">
         <v>46167.5574040162</v>
@@ -11038,7 +11038,7 @@
         <v>213</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -11048,7 +11048,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B160" s="5">
         <v>46167.633843206015</v>
@@ -11101,7 +11101,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B161" s="9">
         <v>46167.633849895836</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B162" s="5">
         <v>46167.63385791666</v>
@@ -11207,7 +11207,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B163" s="9">
         <v>46167.633867083336</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B164" s="5">
         <v>46167.63391234954</v>
@@ -11313,7 +11313,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B165" s="9">
         <v>46167.63392017361</v>
@@ -11366,7 +11366,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B166" s="5">
         <v>46167.557409201385</v>
@@ -11376,7 +11376,7 @@
         <v>46167.734742650464</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -11400,7 +11400,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11413,26 +11413,26 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B167" s="9">
         <v>46167.5574132176</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46232.170859826394</v>
+        <v>46239.16830528935</v>
       </c>
       <c r="E167" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G167" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="F167" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G167" s="10" t="s">
+      <c r="H167" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I167" s="9">
         <v>46230</v>
@@ -11450,13 +11450,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q167" s="9">
         <v>46230</v>
@@ -11465,7 +11465,7 @@
         <v>46239</v>
       </c>
       <c r="S167" s="12" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="T167" s="10">
         <v>0</v>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46167.74286244213</v>
+        <v>46239.168311331014</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>213</v>
@@ -11492,10 +11492,10 @@
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H168" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="I168" s="5">
         <v>46239</v>
@@ -11513,7 +11513,7 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O168" s="6" t="s">
         <v>213</v>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46167.742859606486</v>
+        <v>46239.16830773148</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>213</v>
@@ -11545,10 +11545,10 @@
         <v>26</v>
       </c>
       <c r="G169" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H169" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H169" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I169" s="9">
         <v>46239</v>
@@ -11566,7 +11566,7 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O169" s="10" t="s">
         <v>213</v>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46167.74285702546</v>
+        <v>46239.16830892361</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>213</v>
@@ -11598,10 +11598,10 @@
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H170" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="I170" s="5">
         <v>46239</v>
@@ -11619,7 +11619,7 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O170" s="6" t="s">
         <v>213</v>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46167.742854375</v>
+        <v>46239.16831011574</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>213</v>
@@ -11651,10 +11651,10 @@
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H171" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I171" s="9">
         <v>46239</v>
@@ -11672,7 +11672,7 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O171" s="10" t="s">
         <v>213</v>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46167.74285166667</v>
+        <v>46239.16829961806</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>213</v>
@@ -11704,10 +11704,10 @@
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H172" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H172" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="I172" s="5">
         <v>46239</v>
@@ -11725,7 +11725,7 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>213</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="C173" s="10"/>
       <c r="D173" s="9">
-        <v>46167.74284892361</v>
+        <v>46239.168301377314</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>213</v>
@@ -11757,10 +11757,10 @@
         <v>26</v>
       </c>
       <c r="G173" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H173" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H173" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I173" s="9">
         <v>46239</v>
@@ -11778,7 +11778,7 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O173" s="10" t="s">
         <v>220</v>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46167.742846469904</v>
+        <v>46239.16830259259</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>222</v>
@@ -11810,10 +11810,10 @@
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H174" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H174" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="I174" s="5">
         <v>46239</v>
@@ -11831,7 +11831,7 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>222</v>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="C175" s="10"/>
       <c r="D175" s="9">
-        <v>46167.74284369213</v>
+        <v>46239.16830391204</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>222</v>
@@ -11863,10 +11863,10 @@
         <v>26</v>
       </c>
       <c r="G175" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H175" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I175" s="9">
         <v>46239</v>
@@ -11884,7 +11884,7 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O175" s="10" t="s">
         <v>222</v>
@@ -11916,10 +11916,10 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H176" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H176" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="I176" s="5">
         <v>46230</v>
@@ -11937,7 +11937,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>65</v>
@@ -11969,10 +11969,10 @@
         <v>26</v>
       </c>
       <c r="G177" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H177" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H177" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I177" s="9">
         <v>46230</v>
@@ -11990,7 +11990,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>65</v>
@@ -12022,10 +12022,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="I178" s="5">
         <v>46230</v>
@@ -12043,7 +12043,7 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>65</v>
@@ -12075,10 +12075,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="H179" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="H179" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="I179" s="9">
         <v>46230</v>
@@ -12096,7 +12096,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>65</v>
@@ -12128,10 +12128,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>391</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>392</v>
       </c>
       <c r="I180" s="5">
         <v>46230</v>
@@ -12149,7 +12149,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>65</v>
@@ -12181,10 +12181,10 @@
         <v>26</v>
       </c>
       <c r=